--- a/reports/AEGIS_LATEST.xlsx
+++ b/reports/AEGIS_LATEST.xlsx
@@ -444,7 +444,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-11  /  2026-09-11</t>
+          <t>2026-09-14  /  2026-09-11</t>
         </is>
       </c>
     </row>

--- a/reports/AEGIS_LATEST.xlsx
+++ b/reports/AEGIS_LATEST.xlsx
@@ -444,7 +444,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-14  /  2026-09-11</t>
+          <t>2026-09-15  /  2026-09-11</t>
         </is>
       </c>
     </row>

--- a/reports/AEGIS_LATEST.xlsx
+++ b/reports/AEGIS_LATEST.xlsx
@@ -444,7 +444,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-15  /  2026-09-11</t>
+          <t>2026-09-16  /  2026-09-11</t>
         </is>
       </c>
     </row>

--- a/reports/AEGIS_LATEST.xlsx
+++ b/reports/AEGIS_LATEST.xlsx
@@ -479,7 +479,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6">
@@ -489,7 +489,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7">
@@ -512,7 +512,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -524,7 +524,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ICICIBANK (78)</t>
+          <t>ICICIBANK (70)</t>
         </is>
       </c>
     </row>
@@ -536,7 +536,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>DABUR (46)</t>
+          <t>DABUR (49)</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>WIPRO</t>
         </is>
       </c>
     </row>
@@ -571,7 +571,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -664,7 +664,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Hold a 11-stock risk-managed portfolio</t>
+          <t>Hold a 10-stock risk-managed portfolio</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-16  /  2026-09-11</t>
+          <t>2026-09-16  /  2026-09-15</t>
         </is>
       </c>
     </row>
@@ -760,7 +760,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -908,7 +908,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>15.4%</t>
+          <t>15.2%</t>
         </is>
       </c>
     </row>
@@ -920,7 +920,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>1.91</t>
         </is>
       </c>
     </row>
@@ -1322,7 +1322,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>-5.8%</t>
+          <t>-6.2%</t>
         </is>
       </c>
     </row>
@@ -1361,7 +1361,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB12"/>
+  <dimension ref="A1:AB11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1513,11 +1513,11 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Risk/Vol +24 · Historical +20 · Trend/Tech +16 · Regime +9 · Sector +9 = 78</t>
+          <t>Risk/Vol +23 · Historical +20 · Sector +10 · Regime +9 · Trend/Tech +8 = 70</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -1527,20 +1527,20 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Sector</t>
+          <t>Trend/Tech</t>
         </is>
       </c>
       <c r="F2" t="n">
         <v>66</v>
       </c>
       <c r="G2" t="n">
-        <v>79</v>
+        <v>40</v>
       </c>
       <c r="H2" t="n">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I2" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="J2" t="n">
         <v>60</v>
@@ -1556,11 +1556,11 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>1371.8</v>
+        <v>1350.4</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>1337 - 1407</t>
+          <t>1316 - 1384</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -1574,15 +1574,15 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>Above 200-DMA (+1.1%)</t>
+          <t>Below 200-DMA (-0.5%)</t>
         </is>
       </c>
       <c r="S2" t="n">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -1591,17 +1591,17 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="V2" t="n">
-        <v>24692</v>
+        <v>33760</v>
       </c>
       <c r="W2" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="X2" t="n">
-        <v>8.300000000000001</v>
+        <v>11.6</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
@@ -1615,70 +1615,70 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ICICIBANK: 78; IDFCFIRSTB: 66, PNB: 66, SBIN: 63</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ICICIBANK: 70; PNB: 66, IDFCFIRSTB: 65, SBIN: 63</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>Low-risk Financials holding (low vol) • above 200-dma (+1.1%) • outperforming Nifty • sector strength 90/100 • regime cautious (partial deploy) • 8 similar past recs: 75% positive, median +5.3%</t>
+          <t>Low-risk Financials holding (low vol) • below 200-dma (-0.5%) • outperforming Nifty • sector strength 100/100 • regime cautious (partial deploy) • 8 similar past recs: 75% positive, median +5.3%</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>STRONG BUY</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Risk/Vol +22 · Historical +15 · Trend/Tech +14 · Regime +9 · Sector +8 = 68</t>
+          <t>Historical +20 · Risk/Vol +18 · Sector +10 · Regime +9 · Trend/Tech +6 = 63</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Risk/Vol</t>
+          <t>Historical</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sector</t>
+          <t>Trend/Tech</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="G3" t="n">
+        <v>31</v>
+      </c>
+      <c r="H3" t="n">
         <v>70</v>
       </c>
-      <c r="H3" t="n">
-        <v>89</v>
-      </c>
       <c r="I3" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="J3" t="n">
         <v>60</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>COALINDIA</t>
+          <t>SBIN</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Metal</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="M3" t="n">
-        <v>432.9</v>
+        <v>968</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>421 - 445</t>
+          <t>938 - 998</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -1692,15 +1692,15 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>Above 200-DMA (+0.7%)</t>
+          <t>Below 200-DMA (-6.9%)</t>
         </is>
       </c>
       <c r="S3" t="n">
-        <v>73</v>
+        <v>13</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -1709,21 +1709,21 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="V3" t="n">
-        <v>32467</v>
+        <v>20328</v>
       </c>
       <c r="W3" t="n">
-        <v>75</v>
+        <v>21</v>
       </c>
       <c r="X3" t="n">
-        <v>10.9</v>
+        <v>6.9</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Metal name under the sector cap</t>
+          <t>Historical + Risk/Vol strongest; chosen as a lowest-volatility Financials name under the sector cap</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -1733,12 +1733,12 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — COALINDIA: 68; TATASTEEL: 59, SAIL: 50, HINDZINC: 48</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — SBIN: 63; ICICIBANK: 70, PNB: 66, IDFCFIRSTB: 65. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>Low-risk Metal holding (low vol) • above 200-dma (+0.7%) • sector strength 80/100 • regime cautious (partial deploy) • 3 similar past recs: 67% positive, median +0.8%</t>
+          <t>Low-risk Financials holding (low vol) • below 200-dma (-6.9%) • sector strength 100/100 • regime cautious (partial deploy) • 2 similar past recs: 100% positive, median +8.9%</t>
         </is>
       </c>
     </row>
@@ -1749,16 +1749,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Historical +20 · Risk/Vol +19 · Regime +9 · Sector +9 · Trend/Tech +6 = 63</t>
+          <t>Risk/Vol +22 · Historical +15 · Regime +9 · Sector +9 · Trend/Tech +7 = 62</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Historical</t>
+          <t>Risk/Vol</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1767,36 +1767,36 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>65</v>
+        <v>51</v>
       </c>
       <c r="G4" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="H4" t="n">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="I4" t="n">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="J4" t="n">
         <v>60</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>SBIN</t>
+          <t>COALINDIA</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Metal</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>998</v>
+        <v>419.2</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>968 - 1028</t>
+          <t>408 - 431</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -1814,11 +1814,11 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-4.0%)</t>
+          <t>Below 200-DMA (-2.6%)</t>
         </is>
       </c>
       <c r="S4" t="n">
-        <v>26</v>
+        <v>61</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1827,21 +1827,21 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="V4" t="n">
-        <v>17964</v>
+        <v>33540</v>
       </c>
       <c r="W4" t="n">
-        <v>18</v>
+        <v>80</v>
       </c>
       <c r="X4" t="n">
-        <v>6.3</v>
+        <v>11.3</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>Historical + Risk/Vol strongest; chosen as a lowest-volatility Financials name under the sector cap</t>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Metal name under the sector cap</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1851,12 +1851,12 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — SBIN: 63; ICICIBANK: 78, IDFCFIRSTB: 66, PNB: 66. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — COALINDIA: 62; TATASTEEL: 61, SAIL: 50, HINDZINC: 47</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>Low-risk Financials holding (low vol) • below 200-dma (-4.0%) • sector strength 90/100 • regime cautious (partial deploy) • 2 similar past recs: 100% positive, median +8.9%</t>
+          <t>Low-risk Metal holding (low vol) • below 200-dma (-2.6%) • sector strength 89/100 • regime cautious (partial deploy) • 3 similar past recs: 67% positive, median +0.8%</t>
         </is>
       </c>
     </row>
@@ -1867,11 +1867,11 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Risk/Vol +20 · Historical +16 · Regime +9 · Trend/Tech +8 · Sector +7 = 60</t>
+          <t>Risk/Vol +21 · Historical +15 · Regime +9 · Sector +9 · Trend/Tech +7 = 61</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1881,40 +1881,40 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Sector</t>
+          <t>Trend/Tech</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="G5" t="n">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="H5" t="n">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="I5" t="n">
-        <v>70</v>
+        <v>89</v>
       </c>
       <c r="J5" t="n">
         <v>60</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>ONGC</t>
+          <t>TATASTEEL</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Metal</t>
         </is>
       </c>
       <c r="M5" t="n">
-        <v>239.6</v>
+        <v>183.6</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>233 - 247</t>
+          <t>179 - 189</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -1928,15 +1928,15 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-6.8%)</t>
+          <t>Below 200-DMA (-4.8%)</t>
         </is>
       </c>
       <c r="S5" t="n">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1945,21 +1945,21 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="V5" t="n">
-        <v>29710</v>
+        <v>29751</v>
       </c>
       <c r="W5" t="n">
-        <v>124</v>
+        <v>162</v>
       </c>
       <c r="X5" t="n">
-        <v>10</v>
+        <v>9.9</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Energy name under the sector cap</t>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Metal name under the sector cap</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1969,12 +1969,12 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ONGC: 60; IOC: 55</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — TATASTEEL: 61; COALINDIA: 62, SAIL: 50, HINDZINC: 47. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>Low-risk Energy holding (low vol) • below 200-dma (-6.8%) • sector strength 70/100 • regime cautious (partial deploy) • 2 similar past recs: 50% positive, median +9.0%</t>
+          <t>Low-risk Metal holding (low vol) • below 200-dma (-4.8%) • sector strength 89/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
         </is>
       </c>
     </row>
@@ -1985,11 +1985,11 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Risk/Vol +21 · Historical +15 · Regime +9 · Sector +8 · Trend/Tech +6 = 59</t>
+          <t>Risk/Vol +19 · Historical +16 · Trend/Tech +9 · Regime +9 · Sector +8 = 61</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1999,40 +1999,40 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Trend/Tech</t>
+          <t>Sector</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="G6" t="n">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="H6" t="n">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="I6" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="J6" t="n">
         <v>60</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>TATASTEEL</t>
+          <t>ONGC</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Metal</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="M6" t="n">
-        <v>182.1</v>
+        <v>235.9</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>177 - 187</t>
+          <t>229 - 243</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -2046,15 +2046,15 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-5.5%)</t>
+          <t>Below 200-DMA (-8.2%)</t>
         </is>
       </c>
       <c r="S6" t="n">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -2063,21 +2063,21 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="V6" t="n">
-        <v>21487</v>
+        <v>29494</v>
       </c>
       <c r="W6" t="n">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="X6" t="n">
-        <v>7.2</v>
+        <v>9.9</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Metal name under the sector cap</t>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Energy name under the sector cap</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -2087,12 +2087,12 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — TATASTEEL: 59; COALINDIA: 68, SAIL: 50, HINDZINC: 48. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ONGC: 61; IOC: 52</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>Low-risk Metal holding (low vol) • below 200-dma (-5.5%) • sector strength 80/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
+          <t>Low-risk Energy holding (low vol) • below 200-dma (-8.2%) • sector strength 78/100 • regime cautious (partial deploy) • 2 similar past recs: 50% positive, median +9.0%</t>
         </is>
       </c>
     </row>
@@ -2103,16 +2103,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Risk/Vol +18 · Historical +17 · Trend/Tech +9 · Regime +9 · Sector +5 = 58</t>
+          <t>Historical +17 · Risk/Vol +17 · Trend/Tech +10 · Regime +9 · Sector +7 = 60</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Risk/Vol</t>
+          <t>Historical</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -2124,13 +2124,13 @@
         <v>57</v>
       </c>
       <c r="G7" t="n">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="H7" t="n">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="I7" t="n">
-        <v>50</v>
+        <v>67</v>
       </c>
       <c r="J7" t="n">
         <v>60</v>
@@ -2146,11 +2146,11 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>76.2</v>
+        <v>76</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>74 - 79</t>
+          <t>74 - 78</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -2164,15 +2164,15 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-2.0%)</t>
+          <t>Below 200-DMA (-2.2%)</t>
         </is>
       </c>
       <c r="S7" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -2181,21 +2181,21 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="V7" t="n">
-        <v>30500</v>
+        <v>24257</v>
       </c>
       <c r="W7" t="n">
-        <v>400</v>
+        <v>319</v>
       </c>
       <c r="X7" t="n">
-        <v>10.2</v>
+        <v>8.1</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Power name under the sector cap</t>
+          <t>Historical + Risk/Vol strongest; chosen as a lowest-volatility Power name under the sector cap</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -2205,12 +2205,12 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — NHPC: 58; TATAPOWER: 58, ADANIPOWER: 51, JSWENERGY: 51</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — NHPC: 60; TATAPOWER: 59, ADANIPOWER: 51, NLCINDIA: 35</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>Low-risk Power holding (low vol) • below 200-dma (-2.0%) • outperforming Nifty • sector strength 50/100 • regime cautious (partial deploy) • 1 similar past recs: 100% positive, median +7.2%</t>
+          <t>Low-risk Power holding (medium vol) • below 200-dma (-2.2%) • outperforming Nifty • sector strength 67/100 • regime cautious (partial deploy) • 1 similar past recs: 100% positive, median +7.2%</t>
         </is>
       </c>
     </row>
@@ -2221,11 +2221,11 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Risk/Vol +23 · Historical +15 · Regime +9 · Trend/Tech +6 · Sector +5 = 58</t>
+          <t>Risk/Vol +22 · Historical +15 · Regime +9 · Sector +7 · Trend/Tech +6 = 59</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -2235,20 +2235,20 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Sector</t>
+          <t>Trend/Tech</t>
         </is>
       </c>
       <c r="F8" t="n">
         <v>50</v>
       </c>
       <c r="G8" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="H8" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I8" t="n">
-        <v>50</v>
+        <v>67</v>
       </c>
       <c r="J8" t="n">
         <v>60</v>
@@ -2264,11 +2264,11 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>363.5</v>
+        <v>363</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>354 - 373</t>
+          <t>353 - 373</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -2282,7 +2282,7 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>
@@ -2290,7 +2290,7 @@
         </is>
       </c>
       <c r="S8" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -2299,17 +2299,17 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="V8" t="n">
-        <v>23991</v>
+        <v>25410</v>
       </c>
       <c r="W8" t="n">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="X8" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -2323,12 +2323,12 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — TATAPOWER: 58; NHPC: 58, ADANIPOWER: 51, JSWENERGY: 51</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — TATAPOWER: 59; NHPC: 60, ADANIPOWER: 51, NLCINDIA: 35. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>Low-risk Power holding (low vol) • below 200-dma (-6.2%) • sector strength 50/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
+          <t>Low-risk Power holding (low vol) • below 200-dma (-6.2%) • sector strength 67/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
         </is>
       </c>
     </row>
@@ -2343,7 +2343,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Risk/Vol +22 · Historical +15 · Regime +9 · Trend/Tech +6 · Sector +3 = 55</t>
+          <t>Risk/Vol +20 · Historical +15 · Regime +9 · Sector +6 · Trend/Tech +5 = 55</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2353,20 +2353,20 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Sector</t>
+          <t>Trend/Tech</t>
         </is>
       </c>
       <c r="F9" t="n">
         <v>50</v>
       </c>
       <c r="G9" t="n">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="H9" t="n">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="I9" t="n">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="J9" t="n">
         <v>60</v>
@@ -2382,11 +2382,11 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>401.2</v>
+        <v>382.9</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>390 - 412</t>
+          <t>372 - 394</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -2404,11 +2404,11 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-4.2%)</t>
+          <t>Below 200-DMA (-8.5%)</t>
         </is>
       </c>
       <c r="S9" t="n">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -2417,17 +2417,17 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="V9" t="n">
-        <v>29692</v>
+        <v>35993</v>
       </c>
       <c r="W9" t="n">
-        <v>74</v>
+        <v>94</v>
       </c>
       <c r="X9" t="n">
-        <v>10</v>
+        <v>12.1</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -2441,92 +2441,92 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — BEL: 55; KEI: 32</t>
+          <t>No same-sector peer in the universe.</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>Low-risk Industrials holding (low vol) • below 200-dma (-4.2%) • sector strength 30/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
+          <t>Low-risk Industrials holding (low vol) • below 200-dma (-8.5%) • sector strength 56/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>ACCUMULATE</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Historical +19 · Risk/Vol +17 · Regime +9 · Sector +6 · Trend/Tech +4 = 55</t>
+          <t>Risk/Vol +24 · Historical +13 · Regime +9 · Trend/Tech +4 · Sector +1 = 51</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Historical</t>
+          <t>Risk/Vol</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Trend/Tech</t>
+          <t>Sector</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>62</v>
+        <v>44</v>
       </c>
       <c r="G10" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="H10" t="n">
-        <v>69</v>
+        <v>97</v>
       </c>
       <c r="I10" t="n">
-        <v>60</v>
+        <v>11</v>
       </c>
       <c r="J10" t="n">
         <v>60</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>WIPRO</t>
+          <t>ITC</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>166.6</v>
+        <v>258</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>161 - 172</t>
+          <t>252 - 264</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-4% to +3%</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>56%</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-19.7%)</t>
+          <t>Below 200-DMA (-17.1%)</t>
         </is>
       </c>
       <c r="S10" t="n">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -2535,21 +2535,21 @@
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="V10" t="n">
-        <v>22823</v>
+        <v>38700</v>
       </c>
       <c r="W10" t="n">
-        <v>137</v>
+        <v>150</v>
       </c>
       <c r="X10" t="n">
-        <v>7.7</v>
+        <v>13</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>Historical + Risk/Vol strongest; chosen as a lowest-volatility IT name under the sector cap</t>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility FMCG name under the sector cap</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
@@ -2559,12 +2559,12 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — WIPRO: 55; TECHM: 56, TCS: 41, INFY: 37. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ITC: 51; DABUR: 49</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>Low-risk IT holding (low vol) • below 200-dma (-19.7%) • sector strength 60/100 • regime cautious (partial deploy) • 2 similar past recs: 100% positive, median +5.1%</t>
+          <t>Low-risk FMCG holding (low vol) • below 200-dma (-17.1%) • sector strength 11/100 • regime cautious (partial deploy) • 9 similar past recs: 56% positive, median +0.3%</t>
         </is>
       </c>
     </row>
@@ -2575,11 +2575,11 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Risk/Vol +24 · Historical +13 · Regime +9 · Trend/Tech +4 · Sector +1 = 51</t>
+          <t>Risk/Vol +18 · Historical +15 · Regime +9 · Trend/Tech +6 · Sector +1 = 49</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2593,23 +2593,23 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="G11" t="n">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="H11" t="n">
-        <v>97</v>
+        <v>73</v>
       </c>
       <c r="I11" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J11" t="n">
         <v>60</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>ITC</t>
+          <t>DABUR</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -2618,33 +2618,33 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>260.1</v>
+        <v>384.9</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>254 - 266</t>
+          <t>373 - 396</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>-4% to +3%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>56%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-16.9%)</t>
+          <t>Below 200-DMA (-15.6%)</t>
         </is>
       </c>
       <c r="S11" t="n">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -2653,17 +2653,17 @@
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="V11" t="n">
-        <v>39015</v>
+        <v>26173</v>
       </c>
       <c r="W11" t="n">
-        <v>150</v>
+        <v>68</v>
       </c>
       <c r="X11" t="n">
-        <v>13</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -2677,130 +2677,12 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ITC: 51; DABUR: 46</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — DABUR: 49; ITC: 51. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>Low-risk FMCG holding (low vol) • below 200-dma (-16.9%) • sector strength 10/100 • regime cautious (partial deploy) • 9 similar past recs: 56% positive, median +0.3%</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>ACCUMULATE</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>46</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Risk/Vol +18 · Historical +15 · Regime +9 · Trend/Tech +3 · Sector +1 = 46</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Risk/Vol</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Sector</t>
-        </is>
-      </c>
-      <c r="F12" t="n">
-        <v>50</v>
-      </c>
-      <c r="G12" t="n">
-        <v>15</v>
-      </c>
-      <c r="H12" t="n">
-        <v>74</v>
-      </c>
-      <c r="I12" t="n">
-        <v>10</v>
-      </c>
-      <c r="J12" t="n">
-        <v>60</v>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>DABUR</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>FMCG</t>
-        </is>
-      </c>
-      <c r="M12" t="n">
-        <v>373.2</v>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>362 - 385</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Q12" t="n">
-        <v>61</v>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>Below 200-DMA (-18.4%)</t>
-        </is>
-      </c>
-      <c r="S12" t="n">
-        <v>21</v>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>3 months (3M)</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>2026-10-11</t>
-        </is>
-      </c>
-      <c r="V12" t="n">
-        <v>25381</v>
-      </c>
-      <c r="W12" t="n">
-        <v>68</v>
-      </c>
-      <c r="X12" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility FMCG name under the sector cap</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>Fundamentals · Earnings · News · Flows</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — DABUR: 46; ITC: 51. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>Low-risk FMCG holding (low vol) • below 200-dma (-18.4%) • sector strength 10/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
+          <t>Low-risk FMCG holding (low vol) • below 200-dma (-15.6%) • sector strength 11/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
         </is>
       </c>
     </row>
@@ -3355,15 +3237,9 @@
       <c r="L2" t="n">
         <v>4.34</v>
       </c>
-      <c r="M2" t="n">
-        <v>31.6</v>
-      </c>
-      <c r="N2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O2" t="n">
-        <v>100</v>
-      </c>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
       <c r="P2" t="n">
         <v>200.3</v>
       </c>
@@ -3598,15 +3474,9 @@
       <c r="L5" t="n">
         <v>1.6</v>
       </c>
-      <c r="M5" t="n">
-        <v>24.3</v>
-      </c>
-      <c r="N5" t="n">
-        <v>-0.8</v>
-      </c>
-      <c r="O5" t="n">
-        <v>98</v>
-      </c>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
       <c r="P5" t="n">
         <v>135.9</v>
       </c>
@@ -3922,15 +3792,9 @@
       <c r="L9" t="n">
         <v>0.77</v>
       </c>
-      <c r="M9" t="n">
-        <v>14.7</v>
-      </c>
-      <c r="N9" t="n">
-        <v>-5.3</v>
-      </c>
-      <c r="O9" t="n">
-        <v>62</v>
-      </c>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
       <c r="P9" t="n">
         <v>41.4</v>
       </c>
@@ -4003,15 +3867,9 @@
       <c r="L10" t="n">
         <v>0.7</v>
       </c>
-      <c r="M10" t="n">
-        <v>10</v>
-      </c>
-      <c r="N10" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O10" t="n">
-        <v>88</v>
-      </c>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
       <c r="P10" t="n">
         <v>40.2</v>
       </c>
@@ -4408,15 +4266,9 @@
       <c r="L15" t="n">
         <v>-0.07000000000000001</v>
       </c>
-      <c r="M15" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="N15" t="n">
-        <v>-13.5</v>
-      </c>
-      <c r="O15" t="n">
-        <v>-39</v>
-      </c>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
       <c r="P15" t="n">
         <v>-6.6</v>
       </c>
@@ -4489,15 +4341,9 @@
       <c r="L16" t="n">
         <v>-0.53</v>
       </c>
-      <c r="M16" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="N16" t="n">
-        <v>-9.1</v>
-      </c>
-      <c r="O16" t="n">
-        <v>-331</v>
-      </c>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
       <c r="P16" t="n">
         <v>-30.7</v>
       </c>
@@ -4651,15 +4497,9 @@
       <c r="L18" t="n">
         <v>0.41</v>
       </c>
-      <c r="M18" t="n">
-        <v>14.6</v>
-      </c>
-      <c r="N18" t="n">
-        <v>-3.2</v>
-      </c>
-      <c r="O18" t="n">
-        <v>61</v>
-      </c>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
       <c r="P18" t="n">
         <v>41.1</v>
       </c>
@@ -5218,15 +5058,9 @@
       <c r="L25" t="n">
         <v>-0.35</v>
       </c>
-      <c r="M25" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="N25" t="n">
-        <v>-14.8</v>
-      </c>
-      <c r="O25" t="n">
-        <v>-64</v>
-      </c>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr"/>
       <c r="P25" t="n">
         <v>-25.7</v>
       </c>
@@ -5299,15 +5133,9 @@
       <c r="L26" t="n">
         <v>-0.73</v>
       </c>
-      <c r="M26" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="N26" t="n">
-        <v>-11.5</v>
-      </c>
-      <c r="O26" t="n">
-        <v>-1734</v>
-      </c>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr"/>
       <c r="P26" t="n">
         <v>-27.5</v>
       </c>
@@ -6346,15 +6174,9 @@
       <c r="L39" t="n">
         <v>-0.23</v>
       </c>
-      <c r="M39" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="N39" t="n">
-        <v>-22.2</v>
-      </c>
-      <c r="O39" t="n">
-        <v>-322</v>
-      </c>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
+      <c r="O39" t="inlineStr"/>
       <c r="P39" t="n">
         <v>-19.9</v>
       </c>
@@ -6508,15 +6330,9 @@
       <c r="L41" t="n">
         <v>-0.27</v>
       </c>
-      <c r="M41" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="N41" t="n">
-        <v>-19.4</v>
-      </c>
-      <c r="O41" t="n">
-        <v>-702</v>
-      </c>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
+      <c r="O41" t="inlineStr"/>
       <c r="P41" t="n">
         <v>-27.3</v>
       </c>
@@ -6589,15 +6405,9 @@
       <c r="L42" t="n">
         <v>-0.63</v>
       </c>
-      <c r="M42" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="N42" t="n">
-        <v>-16.5</v>
-      </c>
-      <c r="O42" t="n">
-        <v>-157</v>
-      </c>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
+      <c r="O42" t="inlineStr"/>
       <c r="P42" t="n">
         <v>-29.3</v>
       </c>
@@ -6751,15 +6561,9 @@
       <c r="L44" t="n">
         <v>-0.64</v>
       </c>
-      <c r="M44" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="N44" t="n">
-        <v>-12.7</v>
-      </c>
-      <c r="O44" t="n">
-        <v>-260</v>
-      </c>
+      <c r="M44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
+      <c r="O44" t="inlineStr"/>
       <c r="P44" t="n">
         <v>-30.8</v>
       </c>
@@ -6994,15 +6798,9 @@
       <c r="L47" t="n">
         <v>3.05</v>
       </c>
-      <c r="M47" t="n">
-        <v>39.2</v>
-      </c>
-      <c r="N47" t="n">
-        <v>0</v>
-      </c>
-      <c r="O47" t="n">
-        <v>97</v>
-      </c>
+      <c r="M47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
+      <c r="O47" t="inlineStr"/>
       <c r="P47" t="n">
         <v>263.7</v>
       </c>
@@ -7075,15 +6873,9 @@
       <c r="L48" t="n">
         <v>1.05</v>
       </c>
-      <c r="M48" t="n">
-        <v>19.2</v>
-      </c>
-      <c r="N48" t="n">
-        <v>-0.7</v>
-      </c>
-      <c r="O48" t="n">
-        <v>98</v>
-      </c>
+      <c r="M48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
+      <c r="O48" t="inlineStr"/>
       <c r="P48" t="n">
         <v>99.5</v>
       </c>
@@ -7156,15 +6948,9 @@
       <c r="L49" t="n">
         <v>0.57</v>
       </c>
-      <c r="M49" t="n">
-        <v>14.8</v>
-      </c>
-      <c r="N49" t="n">
-        <v>-1.3</v>
-      </c>
-      <c r="O49" t="n">
-        <v>72</v>
-      </c>
+      <c r="M49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
+      <c r="O49" t="inlineStr"/>
       <c r="P49" t="n">
         <v>50.2</v>
       </c>
@@ -7237,15 +7023,9 @@
       <c r="L50" t="n">
         <v>0.5600000000000001</v>
       </c>
-      <c r="M50" t="n">
-        <v>14.6</v>
-      </c>
-      <c r="N50" t="n">
-        <v>-2.1</v>
-      </c>
-      <c r="O50" t="n">
-        <v>55</v>
-      </c>
+      <c r="M50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
+      <c r="O50" t="inlineStr"/>
       <c r="P50" t="n">
         <v>36.5</v>
       </c>
@@ -8205,15 +7985,9 @@
       <c r="L62" t="n">
         <v>0.92</v>
       </c>
-      <c r="M62" t="n">
-        <v>22.1</v>
-      </c>
-      <c r="N62" t="n">
-        <v>0</v>
-      </c>
-      <c r="O62" t="n">
-        <v>93</v>
-      </c>
+      <c r="M62" t="inlineStr"/>
+      <c r="N62" t="inlineStr"/>
+      <c r="O62" t="inlineStr"/>
       <c r="P62" t="n">
         <v>112</v>
       </c>
@@ -8529,15 +8303,9 @@
       <c r="L66" t="n">
         <v>0.77</v>
       </c>
-      <c r="M66" t="n">
-        <v>26.8</v>
-      </c>
-      <c r="N66" t="n">
-        <v>0</v>
-      </c>
-      <c r="O66" t="n">
-        <v>49</v>
-      </c>
+      <c r="M66" t="inlineStr"/>
+      <c r="N66" t="inlineStr"/>
+      <c r="O66" t="inlineStr"/>
       <c r="P66" t="n">
         <v>63.2</v>
       </c>
@@ -8610,15 +8378,9 @@
       <c r="L67" t="n">
         <v>0.74</v>
       </c>
-      <c r="M67" t="n">
-        <v>14.3</v>
-      </c>
-      <c r="N67" t="n">
-        <v>-1.5</v>
-      </c>
-      <c r="O67" t="n">
-        <v>85</v>
-      </c>
+      <c r="M67" t="inlineStr"/>
+      <c r="N67" t="inlineStr"/>
+      <c r="O67" t="inlineStr"/>
       <c r="P67" t="n">
         <v>58.6</v>
       </c>
@@ -8691,15 +8453,9 @@
       <c r="L68" t="n">
         <v>0.35</v>
       </c>
-      <c r="M68" t="n">
-        <v>23.7</v>
-      </c>
-      <c r="N68" t="n">
-        <v>0</v>
-      </c>
-      <c r="O68" t="n">
-        <v>46</v>
-      </c>
+      <c r="M68" t="inlineStr"/>
+      <c r="N68" t="inlineStr"/>
+      <c r="O68" t="inlineStr"/>
       <c r="P68" t="n">
         <v>51</v>
       </c>
@@ -8934,15 +8690,9 @@
       <c r="L71" t="n">
         <v>0.48</v>
       </c>
-      <c r="M71" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="N71" t="n">
-        <v>-5.5</v>
-      </c>
-      <c r="O71" t="n">
-        <v>51</v>
-      </c>
+      <c r="M71" t="inlineStr"/>
+      <c r="N71" t="inlineStr"/>
+      <c r="O71" t="inlineStr"/>
       <c r="P71" t="n">
         <v>16.9</v>
       </c>
@@ -9015,15 +8765,9 @@
       <c r="L72" t="n">
         <v>0.17</v>
       </c>
-      <c r="M72" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="N72" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="O72" t="n">
-        <v>29</v>
-      </c>
+      <c r="M72" t="inlineStr"/>
+      <c r="N72" t="inlineStr"/>
+      <c r="O72" t="inlineStr"/>
       <c r="P72" t="n">
         <v>13.3</v>
       </c>
@@ -9825,15 +9569,9 @@
       <c r="L82" t="n">
         <v>0.4</v>
       </c>
-      <c r="M82" t="n">
-        <v>25.7</v>
-      </c>
-      <c r="N82" t="n">
-        <v>-5.4</v>
-      </c>
-      <c r="O82" t="n">
-        <v>21</v>
-      </c>
+      <c r="M82" t="inlineStr"/>
+      <c r="N82" t="inlineStr"/>
+      <c r="O82" t="inlineStr"/>
       <c r="P82" t="n">
         <v>23.2</v>
       </c>
@@ -10392,15 +10130,9 @@
       <c r="L89" t="n">
         <v>-0.48</v>
       </c>
-      <c r="M89" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="N89" t="n">
-        <v>-6.3</v>
-      </c>
-      <c r="O89" t="n">
-        <v>-153</v>
-      </c>
+      <c r="M89" t="inlineStr"/>
+      <c r="N89" t="inlineStr"/>
+      <c r="O89" t="inlineStr"/>
       <c r="P89" t="n">
         <v>-19.5</v>
       </c>
@@ -10473,12 +10205,8 @@
       <c r="L90" t="n">
         <v>-0.6899999999999999</v>
       </c>
-      <c r="M90" t="n">
-        <v>0</v>
-      </c>
-      <c r="N90" t="n">
-        <v>-12.5</v>
-      </c>
+      <c r="M90" t="inlineStr"/>
+      <c r="N90" t="inlineStr"/>
       <c r="O90" t="inlineStr"/>
       <c r="P90" t="n">
         <v>-38.1</v>
@@ -10552,12 +10280,8 @@
       <c r="L91" t="n">
         <v>-0.59</v>
       </c>
-      <c r="M91" t="n">
-        <v>0</v>
-      </c>
-      <c r="N91" t="n">
-        <v>-12</v>
-      </c>
+      <c r="M91" t="inlineStr"/>
+      <c r="N91" t="inlineStr"/>
       <c r="O91" t="inlineStr"/>
       <c r="P91" t="n">
         <v>-40.1</v>
@@ -10793,15 +10517,9 @@
       <c r="L94" t="n">
         <v>0.7</v>
       </c>
-      <c r="M94" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="N94" t="n">
-        <v>0</v>
-      </c>
-      <c r="O94" t="n">
-        <v>100</v>
-      </c>
+      <c r="M94" t="inlineStr"/>
+      <c r="N94" t="inlineStr"/>
+      <c r="O94" t="inlineStr"/>
       <c r="P94" t="n">
         <v>49.4</v>
       </c>
@@ -10874,15 +10592,9 @@
       <c r="L95" t="n">
         <v>1</v>
       </c>
-      <c r="M95" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="N95" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O95" t="n">
-        <v>82</v>
-      </c>
+      <c r="M95" t="inlineStr"/>
+      <c r="N95" t="inlineStr"/>
+      <c r="O95" t="inlineStr"/>
       <c r="P95" t="n">
         <v>47.5</v>
       </c>
@@ -11036,15 +10748,9 @@
       <c r="L97" t="n">
         <v>0.44</v>
       </c>
-      <c r="M97" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="N97" t="n">
-        <v>-4.1</v>
-      </c>
-      <c r="O97" t="n">
-        <v>68</v>
-      </c>
+      <c r="M97" t="inlineStr"/>
+      <c r="N97" t="inlineStr"/>
+      <c r="O97" t="inlineStr"/>
       <c r="P97" t="n">
         <v>27.3</v>
       </c>
@@ -11684,15 +11390,9 @@
       <c r="L105" t="n">
         <v>-0.75</v>
       </c>
-      <c r="M105" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="N105" t="n">
-        <v>-16</v>
-      </c>
-      <c r="O105" t="n">
-        <v>-4582</v>
-      </c>
+      <c r="M105" t="inlineStr"/>
+      <c r="N105" t="inlineStr"/>
+      <c r="O105" t="inlineStr"/>
       <c r="P105" t="n">
         <v>-32</v>
       </c>
@@ -11765,15 +11465,9 @@
       <c r="L106" t="n">
         <v>-1.05</v>
       </c>
-      <c r="M106" t="n">
-        <v>1</v>
-      </c>
-      <c r="N106" t="n">
-        <v>-17.4</v>
-      </c>
-      <c r="O106" t="n">
-        <v>-1645</v>
-      </c>
+      <c r="M106" t="inlineStr"/>
+      <c r="N106" t="inlineStr"/>
+      <c r="O106" t="inlineStr"/>
       <c r="P106" t="n">
         <v>-51.4</v>
       </c>
@@ -12332,15 +12026,9 @@
       <c r="L113" t="n">
         <v>1.1</v>
       </c>
-      <c r="M113" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="N113" t="n">
-        <v>-1.2</v>
-      </c>
-      <c r="O113" t="n">
-        <v>87</v>
-      </c>
+      <c r="M113" t="inlineStr"/>
+      <c r="N113" t="inlineStr"/>
+      <c r="O113" t="inlineStr"/>
       <c r="P113" t="n">
         <v>81.09999999999999</v>
       </c>
@@ -13142,15 +12830,9 @@
       <c r="L123" t="n">
         <v>2.63</v>
       </c>
-      <c r="M123" t="n">
-        <v>28.8</v>
-      </c>
-      <c r="N123" t="n">
-        <v>-0.8</v>
-      </c>
-      <c r="O123" t="n">
-        <v>86</v>
-      </c>
+      <c r="M123" t="inlineStr"/>
+      <c r="N123" t="inlineStr"/>
+      <c r="O123" t="inlineStr"/>
       <c r="P123" t="n">
         <v>143.4</v>
       </c>
@@ -13547,15 +13229,9 @@
       <c r="L128" t="n">
         <v>0.37</v>
       </c>
-      <c r="M128" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="N128" t="n">
-        <v>0</v>
-      </c>
-      <c r="O128" t="n">
-        <v>83</v>
-      </c>
+      <c r="M128" t="inlineStr"/>
+      <c r="N128" t="inlineStr"/>
+      <c r="O128" t="inlineStr"/>
       <c r="P128" t="n">
         <v>35</v>
       </c>
@@ -14357,15 +14033,9 @@
       <c r="L138" t="n">
         <v>1.71</v>
       </c>
-      <c r="M138" t="n">
-        <v>24.5</v>
-      </c>
-      <c r="N138" t="n">
-        <v>-1.8</v>
-      </c>
-      <c r="O138" t="n">
-        <v>100</v>
-      </c>
+      <c r="M138" t="inlineStr"/>
+      <c r="N138" t="inlineStr"/>
+      <c r="O138" t="inlineStr"/>
       <c r="P138" t="n">
         <v>140.6</v>
       </c>
@@ -14600,15 +14270,9 @@
       <c r="L141" t="n">
         <v>1.18</v>
       </c>
-      <c r="M141" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="N141" t="n">
-        <v>-0.8</v>
-      </c>
-      <c r="O141" t="n">
-        <v>100</v>
-      </c>
+      <c r="M141" t="inlineStr"/>
+      <c r="N141" t="inlineStr"/>
+      <c r="O141" t="inlineStr"/>
       <c r="P141" t="n">
         <v>90.59999999999999</v>
       </c>
@@ -16214,15 +15878,9 @@
       <c r="L161" t="n">
         <v>-0.38</v>
       </c>
-      <c r="M161" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="N161" t="n">
-        <v>-5</v>
-      </c>
-      <c r="O161" t="n">
-        <v>-46</v>
-      </c>
+      <c r="M161" t="inlineStr"/>
+      <c r="N161" t="inlineStr"/>
+      <c r="O161" t="inlineStr"/>
       <c r="P161" t="n">
         <v>-18.5</v>
       </c>
@@ -16376,15 +16034,9 @@
       <c r="L163" t="n">
         <v>-0.62</v>
       </c>
-      <c r="M163" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="N163" t="n">
-        <v>-9.300000000000001</v>
-      </c>
-      <c r="O163" t="n">
-        <v>-2292</v>
-      </c>
+      <c r="M163" t="inlineStr"/>
+      <c r="N163" t="inlineStr"/>
+      <c r="O163" t="inlineStr"/>
       <c r="P163" t="n">
         <v>-32.4</v>
       </c>
@@ -18717,15 +18369,9 @@
       <c r="L192" t="n">
         <v>0.05</v>
       </c>
-      <c r="M192" t="n">
-        <v>11</v>
-      </c>
-      <c r="N192" t="n">
-        <v>0</v>
-      </c>
-      <c r="O192" t="n">
-        <v>9</v>
-      </c>
+      <c r="M192" t="inlineStr"/>
+      <c r="N192" t="inlineStr"/>
+      <c r="O192" t="inlineStr"/>
       <c r="P192" t="n">
         <v>4.2</v>
       </c>
@@ -18879,15 +18525,9 @@
       <c r="L194" t="n">
         <v>-0.09</v>
       </c>
-      <c r="M194" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="N194" t="n">
-        <v>-5.6</v>
-      </c>
-      <c r="O194" t="n">
-        <v>-40</v>
-      </c>
+      <c r="M194" t="inlineStr"/>
+      <c r="N194" t="inlineStr"/>
+      <c r="O194" t="inlineStr"/>
       <c r="P194" t="n">
         <v>-6.8</v>
       </c>
@@ -19122,15 +18762,9 @@
       <c r="L197" t="n">
         <v>0.27</v>
       </c>
-      <c r="M197" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="N197" t="n">
-        <v>-3.7</v>
-      </c>
-      <c r="O197" t="n">
-        <v>46</v>
-      </c>
+      <c r="M197" t="inlineStr"/>
+      <c r="N197" t="inlineStr"/>
+      <c r="O197" t="inlineStr"/>
       <c r="P197" t="n">
         <v>22.8</v>
       </c>
@@ -19203,15 +18837,9 @@
       <c r="L198" t="n">
         <v>0.27</v>
       </c>
-      <c r="M198" t="n">
-        <v>16.6</v>
-      </c>
-      <c r="N198" t="n">
-        <v>-1.6</v>
-      </c>
-      <c r="O198" t="n">
-        <v>20</v>
-      </c>
+      <c r="M198" t="inlineStr"/>
+      <c r="N198" t="inlineStr"/>
+      <c r="O198" t="inlineStr"/>
       <c r="P198" t="n">
         <v>14.2</v>
       </c>
@@ -20011,15 +19639,9 @@
       <c r="L208" t="n">
         <v>-0.64</v>
       </c>
-      <c r="M208" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="N208" t="n">
-        <v>-12.7</v>
-      </c>
-      <c r="O208" t="n">
-        <v>-413</v>
-      </c>
+      <c r="M208" t="inlineStr"/>
+      <c r="N208" t="inlineStr"/>
+      <c r="O208" t="inlineStr"/>
       <c r="P208" t="n">
         <v>-40.3</v>
       </c>
@@ -20254,12 +19876,8 @@
       <c r="L211" t="n">
         <v>-2.56</v>
       </c>
-      <c r="M211" t="n">
-        <v>0</v>
-      </c>
-      <c r="N211" t="n">
-        <v>-26.2</v>
-      </c>
+      <c r="M211" t="inlineStr"/>
+      <c r="N211" t="inlineStr"/>
       <c r="O211" t="inlineStr"/>
       <c r="P211" t="n">
         <v>-70.09999999999999</v>
@@ -20495,15 +20113,9 @@
       <c r="L214" t="n">
         <v>1.4</v>
       </c>
-      <c r="M214" t="n">
-        <v>14.2</v>
-      </c>
-      <c r="N214" t="n">
-        <v>-9.800000000000001</v>
-      </c>
-      <c r="O214" t="n">
-        <v>100</v>
-      </c>
+      <c r="M214" t="inlineStr"/>
+      <c r="N214" t="inlineStr"/>
+      <c r="O214" t="inlineStr"/>
       <c r="P214" t="n">
         <v>70</v>
       </c>
@@ -21538,15 +21150,9 @@
       <c r="L227" t="n">
         <v>0.86</v>
       </c>
-      <c r="M227" t="n">
-        <v>17.4</v>
-      </c>
-      <c r="N227" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O227" t="n">
-        <v>89</v>
-      </c>
+      <c r="M227" t="inlineStr"/>
+      <c r="N227" t="inlineStr"/>
+      <c r="O227" t="inlineStr"/>
       <c r="P227" t="n">
         <v>77.3</v>
       </c>
@@ -21943,15 +21549,9 @@
       <c r="L232" t="n">
         <v>0.38</v>
       </c>
-      <c r="M232" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="N232" t="n">
-        <v>-2.1</v>
-      </c>
-      <c r="O232" t="n">
-        <v>51</v>
-      </c>
+      <c r="M232" t="inlineStr"/>
+      <c r="N232" t="inlineStr"/>
+      <c r="O232" t="inlineStr"/>
       <c r="P232" t="n">
         <v>25.2</v>
       </c>
@@ -22105,15 +21705,9 @@
       <c r="L234" t="n">
         <v>0.32</v>
       </c>
-      <c r="M234" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="N234" t="n">
-        <v>-7.2</v>
-      </c>
-      <c r="O234" t="n">
-        <v>86</v>
-      </c>
+      <c r="M234" t="inlineStr"/>
+      <c r="N234" t="inlineStr"/>
+      <c r="O234" t="inlineStr"/>
       <c r="P234" t="n">
         <v>19.7</v>
       </c>
@@ -22915,15 +22509,9 @@
       <c r="L244" t="n">
         <v>0.5600000000000001</v>
       </c>
-      <c r="M244" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="N244" t="n">
-        <v>-7.6</v>
-      </c>
-      <c r="O244" t="n">
-        <v>83</v>
-      </c>
+      <c r="M244" t="inlineStr"/>
+      <c r="N244" t="inlineStr"/>
+      <c r="O244" t="inlineStr"/>
       <c r="P244" t="n">
         <v>30.3</v>
       </c>
@@ -23881,12 +23469,8 @@
       <c r="L256" t="n">
         <v>-0.57</v>
       </c>
-      <c r="M256" t="n">
-        <v>0</v>
-      </c>
-      <c r="N256" t="n">
-        <v>-10.6</v>
-      </c>
+      <c r="M256" t="inlineStr"/>
+      <c r="N256" t="inlineStr"/>
       <c r="O256" t="inlineStr"/>
       <c r="P256" t="n">
         <v>-36.1</v>
@@ -24203,15 +23787,9 @@
       <c r="L260" t="n">
         <v>0.29</v>
       </c>
-      <c r="M260" t="n">
-        <v>10.9</v>
-      </c>
-      <c r="N260" t="n">
-        <v>-2.1</v>
-      </c>
-      <c r="O260" t="n">
-        <v>44</v>
-      </c>
+      <c r="M260" t="inlineStr"/>
+      <c r="N260" t="inlineStr"/>
+      <c r="O260" t="inlineStr"/>
       <c r="P260" t="n">
         <v>20.4</v>
       </c>
@@ -24284,15 +23862,9 @@
       <c r="L261" t="n">
         <v>0.24</v>
       </c>
-      <c r="M261" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="N261" t="n">
-        <v>-2.1</v>
-      </c>
-      <c r="O261" t="n">
-        <v>38</v>
-      </c>
+      <c r="M261" t="inlineStr"/>
+      <c r="N261" t="inlineStr"/>
+      <c r="O261" t="inlineStr"/>
       <c r="P261" t="n">
         <v>11.5</v>
       </c>
@@ -25580,15 +25152,9 @@
       <c r="L277" t="n">
         <v>0.29</v>
       </c>
-      <c r="M277" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="N277" t="n">
-        <v>-3.4</v>
-      </c>
-      <c r="O277" t="n">
-        <v>45</v>
-      </c>
+      <c r="M277" t="inlineStr"/>
+      <c r="N277" t="inlineStr"/>
+      <c r="O277" t="inlineStr"/>
       <c r="P277" t="n">
         <v>16.6</v>
       </c>
@@ -25742,15 +25308,9 @@
       <c r="L279" t="n">
         <v>0.27</v>
       </c>
-      <c r="M279" t="n">
-        <v>23.5</v>
-      </c>
-      <c r="N279" t="n">
-        <v>0</v>
-      </c>
-      <c r="O279" t="n">
-        <v>10</v>
-      </c>
+      <c r="M279" t="inlineStr"/>
+      <c r="N279" t="inlineStr"/>
+      <c r="O279" t="inlineStr"/>
       <c r="P279" t="n">
         <v>10.2</v>
       </c>
@@ -26147,15 +25707,9 @@
       <c r="L284" t="n">
         <v>-0.53</v>
       </c>
-      <c r="M284" t="n">
-        <v>1</v>
-      </c>
-      <c r="N284" t="n">
-        <v>-16.5</v>
-      </c>
-      <c r="O284" t="n">
-        <v>-1163</v>
-      </c>
+      <c r="M284" t="inlineStr"/>
+      <c r="N284" t="inlineStr"/>
+      <c r="O284" t="inlineStr"/>
       <c r="P284" t="n">
         <v>-37.6</v>
       </c>
@@ -26769,7 +26323,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>-2.9</v>
+        <v>-1.6</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -26811,7 +26365,7 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>-10.7</v>
+        <v>-9.800000000000001</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -26853,7 +26407,7 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>-13.9</v>
+        <v>-14.1</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -26895,7 +26449,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>-8.1</v>
+        <v>-13</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -26937,7 +26491,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>-4.5</v>
+        <v>-4.9</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -26979,7 +26533,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>-9.300000000000001</v>
+        <v>-9.6</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -27021,7 +26575,7 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>-3</v>
+        <v>-3.7</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -27105,7 +26659,7 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>-2.4</v>
+        <v>-2.9</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -27147,7 +26701,7 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>-3.8</v>
+        <v>-4.3</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -27273,7 +26827,7 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>-4.7</v>
+        <v>-4.5</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -27315,7 +26869,7 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>-7.3</v>
+        <v>-7.4</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -27357,7 +26911,7 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>-9.1</v>
+        <v>-8.9</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -27399,7 +26953,7 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>-3.3</v>
+        <v>-3.2</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -27441,7 +26995,7 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>-3.8</v>
+        <v>-4</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -27483,7 +27037,7 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>-4.2</v>
+        <v>-4.5</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -27525,7 +27079,7 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>-11.8</v>
+        <v>-13</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -27577,7 +27131,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27605,7 +27159,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>12.9%</t>
+          <t>13.0%</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -27615,12 +27169,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Power</t>
+          <t>Metal</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>10.9%</t>
+          <t>12.7%</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -27630,12 +27184,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Metal</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>10.9%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -27645,12 +27199,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Power</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>8.8%</t>
+          <t>10.0%</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -27660,12 +27214,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>6.0%</t>
+          <t>7.2%</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -27675,12 +27229,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>6.0%</t>
+          <t>5.9%</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -27690,47 +27244,32 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>CASH (intentional)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>4.6%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CASH (intentional)</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>40.0%</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
           <t>100.0%</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>11 stocks / 7 sectors</t>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>10 stocks / 6 sectors</t>
         </is>
       </c>
     </row>

--- a/reports/AEGIS_LATEST.xlsx
+++ b/reports/AEGIS_LATEST.xlsx
@@ -489,7 +489,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7">
@@ -512,7 +512,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
     </row>
@@ -536,7 +536,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>DABUR (49)</t>
+          <t>DABUR (53)</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-16  /  2026-09-15</t>
+          <t>2026-09-16  /  2026-09-16</t>
         </is>
       </c>
     </row>
@@ -760,7 +760,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
     </row>
@@ -1322,7 +1322,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>-6.2%</t>
+          <t>-5.8%</t>
         </is>
       </c>
     </row>
@@ -1534,7 +1534,7 @@
         <v>66</v>
       </c>
       <c r="G2" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="H2" t="n">
         <v>93</v>
@@ -1556,7 +1556,7 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>1350.4</v>
+        <v>1350</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -1582,7 +1582,7 @@
         </is>
       </c>
       <c r="S2" t="n">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -1591,17 +1591,17 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="V2" t="n">
-        <v>33760</v>
+        <v>32400</v>
       </c>
       <c r="W2" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="X2" t="n">
-        <v>11.6</v>
+        <v>11</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
@@ -1652,7 +1652,7 @@
         <v>65</v>
       </c>
       <c r="G3" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="H3" t="n">
         <v>70</v>
@@ -1674,11 +1674,11 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>968</v>
+        <v>981.8</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>938 - 998</t>
+          <t>952 - 1012</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -1696,11 +1696,11 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-6.9%)</t>
+          <t>Below 200-DMA (-5.6%)</t>
         </is>
       </c>
       <c r="S3" t="n">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -1709,17 +1709,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="V3" t="n">
-        <v>20328</v>
+        <v>18654</v>
       </c>
       <c r="W3" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="X3" t="n">
-        <v>6.9</v>
+        <v>6.2</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>Low-risk Financials holding (low vol) • below 200-dma (-6.9%) • sector strength 100/100 • regime cautious (partial deploy) • 2 similar past recs: 100% positive, median +8.9%</t>
+          <t>Low-risk Financials holding (low vol) • below 200-dma (-5.6%) • sector strength 100/100 • regime cautious (partial deploy) • 2 similar past recs: 100% positive, median +8.9%</t>
         </is>
       </c>
     </row>
@@ -1767,10 +1767,10 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G4" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H4" t="n">
         <v>87</v>
@@ -1783,7 +1783,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>COALINDIA</t>
+          <t>TATASTEEL</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -1792,11 +1792,11 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>419.2</v>
+        <v>184.4</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>408 - 431</t>
+          <t>180 - 189</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -1810,15 +1810,15 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-2.6%)</t>
+          <t>Below 200-DMA (-4.5%)</t>
         </is>
       </c>
       <c r="S4" t="n">
-        <v>61</v>
+        <v>45</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1827,17 +1827,17 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="V4" t="n">
-        <v>33540</v>
+        <v>33552</v>
       </c>
       <c r="W4" t="n">
-        <v>80</v>
+        <v>182</v>
       </c>
       <c r="X4" t="n">
-        <v>11.3</v>
+        <v>11.2</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -1851,12 +1851,12 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — COALINDIA: 62; TATASTEEL: 61, SAIL: 50, HINDZINC: 47</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — TATASTEEL: 62; COALINDIA: 61, SAIL: 49, HINDZINC: 48</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>Low-risk Metal holding (low vol) • below 200-dma (-2.6%) • sector strength 89/100 • regime cautious (partial deploy) • 3 similar past recs: 67% positive, median +0.8%</t>
+          <t>Low-risk Metal holding (low vol) • below 200-dma (-4.5%) • sector strength 89/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
         </is>
       </c>
     </row>
@@ -1885,7 +1885,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G5" t="n">
         <v>37</v>
@@ -1901,7 +1901,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>TATASTEEL</t>
+          <t>COALINDIA</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1910,11 +1910,11 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>183.6</v>
+        <v>420.8</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>179 - 189</t>
+          <t>409 - 432</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -1928,15 +1928,15 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-4.8%)</t>
+          <t>Below 200-DMA (-2.3%)</t>
         </is>
       </c>
       <c r="S5" t="n">
-        <v>44</v>
+        <v>65</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1945,17 +1945,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="V5" t="n">
-        <v>29751</v>
+        <v>32818</v>
       </c>
       <c r="W5" t="n">
-        <v>162</v>
+        <v>78</v>
       </c>
       <c r="X5" t="n">
-        <v>9.9</v>
+        <v>11</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -1969,12 +1969,12 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — TATASTEEL: 61; COALINDIA: 62, SAIL: 50, HINDZINC: 47. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — COALINDIA: 61; TATASTEEL: 62, SAIL: 49, HINDZINC: 48. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>Low-risk Metal holding (low vol) • below 200-dma (-4.8%) • sector strength 89/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
+          <t>Low-risk Metal holding (low vol) • below 200-dma (-2.3%) • sector strength 89/100 • regime cautious (partial deploy) • 3 similar past recs: 67% positive, median +0.8%</t>
         </is>
       </c>
     </row>
@@ -1985,11 +1985,11 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Risk/Vol +19 · Historical +16 · Trend/Tech +9 · Regime +9 · Sector +8 = 61</t>
+          <t>Risk/Vol +18 · Historical +16 · Regime +9 · Trend/Tech +8 · Sector +8 = 59</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -2006,10 +2006,10 @@
         <v>53</v>
       </c>
       <c r="G6" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="H6" t="n">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="I6" t="n">
         <v>78</v>
@@ -2028,11 +2028,11 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>235.9</v>
+        <v>235</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>229 - 243</t>
+          <t>228 - 242</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -2050,11 +2050,11 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-8.2%)</t>
+          <t>Below 200-DMA (-8.6%)</t>
         </is>
       </c>
       <c r="S6" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -2063,17 +2063,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="V6" t="n">
-        <v>29494</v>
+        <v>28204</v>
       </c>
       <c r="W6" t="n">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="X6" t="n">
-        <v>9.9</v>
+        <v>9.4</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -2087,12 +2087,12 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ONGC: 61; IOC: 52</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ONGC: 59; IOC: 53</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>Low-risk Energy holding (low vol) • below 200-dma (-8.2%) • sector strength 78/100 • regime cautious (partial deploy) • 2 similar past recs: 50% positive, median +9.0%</t>
+          <t>Low-risk Energy holding (low vol) • below 200-dma (-8.6%) • sector strength 78/100 • regime cautious (partial deploy) • 2 similar past recs: 50% positive, median +9.0%</t>
         </is>
       </c>
     </row>
@@ -2103,31 +2103,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Historical +17 · Risk/Vol +17 · Trend/Tech +10 · Regime +9 · Sector +7 = 60</t>
+          <t>Risk/Vol +20 · Historical +15 · Regime +9 · Sector +7 · Trend/Tech +4 = 55</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Historical</t>
+          <t>Risk/Vol</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Sector</t>
+          <t>Trend/Tech</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="G7" t="n">
-        <v>51</v>
+        <v>22</v>
       </c>
       <c r="H7" t="n">
-        <v>67</v>
+        <v>80</v>
       </c>
       <c r="I7" t="n">
         <v>67</v>
@@ -2137,20 +2137,20 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>NHPC</t>
+          <t>BEL</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Power</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>76</v>
+        <v>389.4</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>74 - 78</t>
+          <t>379 - 400</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -2164,15 +2164,15 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-2.2%)</t>
+          <t>Below 200-DMA (-7.0%)</t>
         </is>
       </c>
       <c r="S7" t="n">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -2181,21 +2181,21 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="V7" t="n">
-        <v>24257</v>
+        <v>21414</v>
       </c>
       <c r="W7" t="n">
-        <v>319</v>
+        <v>55</v>
       </c>
       <c r="X7" t="n">
-        <v>8.1</v>
+        <v>7.2</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>Historical + Risk/Vol strongest; chosen as a lowest-volatility Power name under the sector cap</t>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Industrials name under the sector cap</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -2205,27 +2205,27 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — NHPC: 60; TATAPOWER: 59, ADANIPOWER: 51, NLCINDIA: 35</t>
+          <t>No same-sector peer in the universe.</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>Low-risk Power holding (medium vol) • below 200-dma (-2.2%) • outperforming Nifty • sector strength 67/100 • regime cautious (partial deploy) • 1 similar past recs: 100% positive, median +7.2%</t>
+          <t>Low-risk Industrials holding (low vol) • below 200-dma (-7.0%) • sector strength 67/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>ACCUMULATE</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Risk/Vol +22 · Historical +15 · Regime +9 · Sector +7 · Trend/Tech +6 = 59</t>
+          <t>Risk/Vol +24 · Historical +13 · Regime +9 · Trend/Tech +4 · Sector +4 = 54</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -2235,62 +2235,62 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Trend/Tech</t>
+          <t>Sector</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="G8" t="n">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="H8" t="n">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="I8" t="n">
-        <v>67</v>
+        <v>44</v>
       </c>
       <c r="J8" t="n">
         <v>60</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>TATAPOWER</t>
+          <t>ITC</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Power</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="M8" t="n">
-        <v>363</v>
+        <v>262.7</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>353 - 373</t>
+          <t>257 - 269</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-4% to +3%</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>56%</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-6.2%)</t>
+          <t>Below 200-DMA (-15.5%)</t>
         </is>
       </c>
       <c r="S8" t="n">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -2299,21 +2299,21 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="V8" t="n">
-        <v>25410</v>
+        <v>39668</v>
       </c>
       <c r="W8" t="n">
-        <v>70</v>
+        <v>151</v>
       </c>
       <c r="X8" t="n">
-        <v>8.6</v>
+        <v>13.3</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Power name under the sector cap</t>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility FMCG name under the sector cap</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
@@ -2323,27 +2323,27 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — TATAPOWER: 59; NHPC: 60, ADANIPOWER: 51, NLCINDIA: 35. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ITC: 54; DABUR: 53</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>Low-risk Power holding (low vol) • below 200-dma (-6.2%) • sector strength 67/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
+          <t>Low-risk FMCG holding (low vol) • below 200-dma (-15.5%) • sector strength 44/100 • regime cautious (partial deploy) • 9 similar past recs: 56% positive, median +0.3%</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>ACCUMULATE</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Risk/Vol +20 · Historical +15 · Regime +9 · Sector +6 · Trend/Tech +5 = 55</t>
+          <t>Risk/Vol +22 · Historical +15 · Regime +9 · Trend/Tech +6 · Sector +2 = 54</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2353,40 +2353,40 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Trend/Tech</t>
+          <t>Sector</t>
         </is>
       </c>
       <c r="F9" t="n">
         <v>50</v>
       </c>
       <c r="G9" t="n">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="H9" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="I9" t="n">
-        <v>56</v>
+        <v>22</v>
       </c>
       <c r="J9" t="n">
         <v>60</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>BEL</t>
+          <t>TATAPOWER</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Power</t>
         </is>
       </c>
       <c r="M9" t="n">
-        <v>382.9</v>
+        <v>363.6</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>372 - 394</t>
+          <t>354 - 373</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -2400,15 +2400,15 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-8.5%)</t>
+          <t>Below 200-DMA (-6.1%)</t>
         </is>
       </c>
       <c r="S9" t="n">
-        <v>26</v>
+        <v>64</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -2417,21 +2417,21 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="V9" t="n">
-        <v>35993</v>
+        <v>34178</v>
       </c>
       <c r="W9" t="n">
         <v>94</v>
       </c>
       <c r="X9" t="n">
-        <v>12.1</v>
+        <v>11.5</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Industrials name under the sector cap</t>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Power name under the sector cap</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
@@ -2441,12 +2441,12 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>No same-sector peer in the universe.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — TATAPOWER: 54; NHPC: 53, ADANIPOWER: 42, NLCINDIA: 29</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>Low-risk Industrials holding (low vol) • below 200-dma (-8.5%) • sector strength 56/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
+          <t>Low-risk Power holding (low vol) • below 200-dma (-6.1%) • sector strength 22/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
         </is>
       </c>
     </row>
@@ -2457,16 +2457,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Risk/Vol +24 · Historical +13 · Regime +9 · Trend/Tech +4 · Sector +1 = 51</t>
+          <t>Historical +17 · Risk/Vol +16 · Trend/Tech +9 · Regime +9 · Sector +2 = 53</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Risk/Vol</t>
+          <t>Historical</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -2475,58 +2475,58 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="G10" t="n">
-        <v>19</v>
+        <v>47</v>
       </c>
       <c r="H10" t="n">
-        <v>97</v>
+        <v>63</v>
       </c>
       <c r="I10" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="J10" t="n">
         <v>60</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>ITC</t>
+          <t>NHPC</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>Power</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>258</v>
+        <v>75.7</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>252 - 264</t>
+          <t>73 - 78</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>-4% to +3%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>56%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-17.1%)</t>
+          <t>Below 200-DMA (-2.7%)</t>
         </is>
       </c>
       <c r="S10" t="n">
-        <v>17</v>
+        <v>46</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -2535,21 +2535,21 @@
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="V10" t="n">
-        <v>38700</v>
+        <v>30583</v>
       </c>
       <c r="W10" t="n">
-        <v>150</v>
+        <v>404</v>
       </c>
       <c r="X10" t="n">
-        <v>13</v>
+        <v>10.2</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility FMCG name under the sector cap</t>
+          <t>Historical + Risk/Vol strongest; chosen as a lowest-volatility Power name under the sector cap</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
@@ -2559,12 +2559,12 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ITC: 51; DABUR: 49</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — NHPC: 53; TATAPOWER: 54, ADANIPOWER: 42, NLCINDIA: 29. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>Low-risk FMCG holding (low vol) • below 200-dma (-17.1%) • sector strength 11/100 • regime cautious (partial deploy) • 9 similar past recs: 56% positive, median +0.3%</t>
+          <t>Low-risk Power holding (medium vol) • below 200-dma (-2.7%) • outperforming Nifty • sector strength 22/100 • regime cautious (partial deploy) • 1 similar past recs: 100% positive, median +7.2%</t>
         </is>
       </c>
     </row>
@@ -2575,11 +2575,11 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Risk/Vol +18 · Historical +15 · Regime +9 · Trend/Tech +6 · Sector +1 = 49</t>
+          <t>Risk/Vol +19 · Historical +15 · Regime +9 · Trend/Tech +6 · Sector +4 = 53</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2596,13 +2596,13 @@
         <v>50</v>
       </c>
       <c r="G11" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H11" t="n">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="I11" t="n">
-        <v>11</v>
+        <v>44</v>
       </c>
       <c r="J11" t="n">
         <v>60</v>
@@ -2618,11 +2618,11 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>384.9</v>
+        <v>386.1</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>373 - 396</t>
+          <t>375 - 397</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -2636,15 +2636,15 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-15.6%)</t>
+          <t>Below 200-DMA (-15.3%)</t>
         </is>
       </c>
       <c r="S11" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -2653,17 +2653,17 @@
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="V11" t="n">
-        <v>26173</v>
+        <v>27027</v>
       </c>
       <c r="W11" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="X11" t="n">
-        <v>8.699999999999999</v>
+        <v>9</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -2677,12 +2677,12 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — DABUR: 49; ITC: 51. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — DABUR: 53; ITC: 54. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>Low-risk FMCG holding (low vol) • below 200-dma (-15.6%) • sector strength 11/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
+          <t>Low-risk FMCG holding (low vol) • below 200-dma (-15.3%) • sector strength 44/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
         </is>
       </c>
     </row>
@@ -3237,9 +3237,15 @@
       <c r="L2" t="n">
         <v>4.34</v>
       </c>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
+      <c r="M2" t="n">
+        <v>31.6</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" t="n">
+        <v>100</v>
+      </c>
       <c r="P2" t="n">
         <v>200.3</v>
       </c>
@@ -3474,9 +3480,15 @@
       <c r="L5" t="n">
         <v>1.6</v>
       </c>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
+      <c r="M5" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="N5" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="O5" t="n">
+        <v>98</v>
+      </c>
       <c r="P5" t="n">
         <v>135.9</v>
       </c>
@@ -3792,9 +3804,15 @@
       <c r="L9" t="n">
         <v>0.77</v>
       </c>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
+      <c r="M9" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="N9" t="n">
+        <v>-5.3</v>
+      </c>
+      <c r="O9" t="n">
+        <v>62</v>
+      </c>
       <c r="P9" t="n">
         <v>41.4</v>
       </c>
@@ -3867,9 +3885,15 @@
       <c r="L10" t="n">
         <v>0.7</v>
       </c>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
+      <c r="M10" t="n">
+        <v>10</v>
+      </c>
+      <c r="N10" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O10" t="n">
+        <v>88</v>
+      </c>
       <c r="P10" t="n">
         <v>40.2</v>
       </c>
@@ -4266,9 +4290,15 @@
       <c r="L15" t="n">
         <v>-0.07000000000000001</v>
       </c>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
-      <c r="O15" t="inlineStr"/>
+      <c r="M15" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="N15" t="n">
+        <v>-13.5</v>
+      </c>
+      <c r="O15" t="n">
+        <v>-39</v>
+      </c>
       <c r="P15" t="n">
         <v>-6.6</v>
       </c>
@@ -4341,9 +4371,15 @@
       <c r="L16" t="n">
         <v>-0.53</v>
       </c>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
-      <c r="O16" t="inlineStr"/>
+      <c r="M16" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="N16" t="n">
+        <v>-9.1</v>
+      </c>
+      <c r="O16" t="n">
+        <v>-331</v>
+      </c>
       <c r="P16" t="n">
         <v>-30.7</v>
       </c>
@@ -4497,9 +4533,15 @@
       <c r="L18" t="n">
         <v>0.41</v>
       </c>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
-      <c r="O18" t="inlineStr"/>
+      <c r="M18" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="N18" t="n">
+        <v>-3.2</v>
+      </c>
+      <c r="O18" t="n">
+        <v>61</v>
+      </c>
       <c r="P18" t="n">
         <v>41.1</v>
       </c>
@@ -5058,9 +5100,15 @@
       <c r="L25" t="n">
         <v>-0.35</v>
       </c>
-      <c r="M25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
-      <c r="O25" t="inlineStr"/>
+      <c r="M25" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="N25" t="n">
+        <v>-14.8</v>
+      </c>
+      <c r="O25" t="n">
+        <v>-64</v>
+      </c>
       <c r="P25" t="n">
         <v>-25.7</v>
       </c>
@@ -5133,9 +5181,15 @@
       <c r="L26" t="n">
         <v>-0.73</v>
       </c>
-      <c r="M26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
-      <c r="O26" t="inlineStr"/>
+      <c r="M26" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="N26" t="n">
+        <v>-11.5</v>
+      </c>
+      <c r="O26" t="n">
+        <v>-1734</v>
+      </c>
       <c r="P26" t="n">
         <v>-27.5</v>
       </c>
@@ -6174,9 +6228,15 @@
       <c r="L39" t="n">
         <v>-0.23</v>
       </c>
-      <c r="M39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
-      <c r="O39" t="inlineStr"/>
+      <c r="M39" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="N39" t="n">
+        <v>-22.2</v>
+      </c>
+      <c r="O39" t="n">
+        <v>-322</v>
+      </c>
       <c r="P39" t="n">
         <v>-19.9</v>
       </c>
@@ -6330,9 +6390,15 @@
       <c r="L41" t="n">
         <v>-0.27</v>
       </c>
-      <c r="M41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
-      <c r="O41" t="inlineStr"/>
+      <c r="M41" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N41" t="n">
+        <v>-19.4</v>
+      </c>
+      <c r="O41" t="n">
+        <v>-702</v>
+      </c>
       <c r="P41" t="n">
         <v>-27.3</v>
       </c>
@@ -6405,9 +6471,15 @@
       <c r="L42" t="n">
         <v>-0.63</v>
       </c>
-      <c r="M42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
-      <c r="O42" t="inlineStr"/>
+      <c r="M42" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="N42" t="n">
+        <v>-16.5</v>
+      </c>
+      <c r="O42" t="n">
+        <v>-157</v>
+      </c>
       <c r="P42" t="n">
         <v>-29.3</v>
       </c>
@@ -6561,9 +6633,15 @@
       <c r="L44" t="n">
         <v>-0.64</v>
       </c>
-      <c r="M44" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
-      <c r="O44" t="inlineStr"/>
+      <c r="M44" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N44" t="n">
+        <v>-12.7</v>
+      </c>
+      <c r="O44" t="n">
+        <v>-260</v>
+      </c>
       <c r="P44" t="n">
         <v>-30.8</v>
       </c>
@@ -6798,9 +6876,15 @@
       <c r="L47" t="n">
         <v>3.05</v>
       </c>
-      <c r="M47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
-      <c r="O47" t="inlineStr"/>
+      <c r="M47" t="n">
+        <v>39.2</v>
+      </c>
+      <c r="N47" t="n">
+        <v>0</v>
+      </c>
+      <c r="O47" t="n">
+        <v>97</v>
+      </c>
       <c r="P47" t="n">
         <v>263.7</v>
       </c>
@@ -6873,9 +6957,15 @@
       <c r="L48" t="n">
         <v>1.05</v>
       </c>
-      <c r="M48" t="inlineStr"/>
-      <c r="N48" t="inlineStr"/>
-      <c r="O48" t="inlineStr"/>
+      <c r="M48" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="N48" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="O48" t="n">
+        <v>98</v>
+      </c>
       <c r="P48" t="n">
         <v>99.5</v>
       </c>
@@ -6948,9 +7038,15 @@
       <c r="L49" t="n">
         <v>0.57</v>
       </c>
-      <c r="M49" t="inlineStr"/>
-      <c r="N49" t="inlineStr"/>
-      <c r="O49" t="inlineStr"/>
+      <c r="M49" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="N49" t="n">
+        <v>-1.3</v>
+      </c>
+      <c r="O49" t="n">
+        <v>72</v>
+      </c>
       <c r="P49" t="n">
         <v>50.2</v>
       </c>
@@ -7023,9 +7119,15 @@
       <c r="L50" t="n">
         <v>0.5600000000000001</v>
       </c>
-      <c r="M50" t="inlineStr"/>
-      <c r="N50" t="inlineStr"/>
-      <c r="O50" t="inlineStr"/>
+      <c r="M50" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="N50" t="n">
+        <v>-2.1</v>
+      </c>
+      <c r="O50" t="n">
+        <v>55</v>
+      </c>
       <c r="P50" t="n">
         <v>36.5</v>
       </c>
@@ -7985,9 +8087,15 @@
       <c r="L62" t="n">
         <v>0.92</v>
       </c>
-      <c r="M62" t="inlineStr"/>
-      <c r="N62" t="inlineStr"/>
-      <c r="O62" t="inlineStr"/>
+      <c r="M62" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="N62" t="n">
+        <v>0</v>
+      </c>
+      <c r="O62" t="n">
+        <v>93</v>
+      </c>
       <c r="P62" t="n">
         <v>112</v>
       </c>
@@ -8303,9 +8411,15 @@
       <c r="L66" t="n">
         <v>0.77</v>
       </c>
-      <c r="M66" t="inlineStr"/>
-      <c r="N66" t="inlineStr"/>
-      <c r="O66" t="inlineStr"/>
+      <c r="M66" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="N66" t="n">
+        <v>0</v>
+      </c>
+      <c r="O66" t="n">
+        <v>49</v>
+      </c>
       <c r="P66" t="n">
         <v>63.2</v>
       </c>
@@ -8378,9 +8492,15 @@
       <c r="L67" t="n">
         <v>0.74</v>
       </c>
-      <c r="M67" t="inlineStr"/>
-      <c r="N67" t="inlineStr"/>
-      <c r="O67" t="inlineStr"/>
+      <c r="M67" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="N67" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="O67" t="n">
+        <v>85</v>
+      </c>
       <c r="P67" t="n">
         <v>58.6</v>
       </c>
@@ -8453,9 +8573,15 @@
       <c r="L68" t="n">
         <v>0.35</v>
       </c>
-      <c r="M68" t="inlineStr"/>
-      <c r="N68" t="inlineStr"/>
-      <c r="O68" t="inlineStr"/>
+      <c r="M68" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="N68" t="n">
+        <v>0</v>
+      </c>
+      <c r="O68" t="n">
+        <v>46</v>
+      </c>
       <c r="P68" t="n">
         <v>51</v>
       </c>
@@ -8690,9 +8816,15 @@
       <c r="L71" t="n">
         <v>0.48</v>
       </c>
-      <c r="M71" t="inlineStr"/>
-      <c r="N71" t="inlineStr"/>
-      <c r="O71" t="inlineStr"/>
+      <c r="M71" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="N71" t="n">
+        <v>-5.5</v>
+      </c>
+      <c r="O71" t="n">
+        <v>51</v>
+      </c>
       <c r="P71" t="n">
         <v>16.9</v>
       </c>
@@ -8765,9 +8897,15 @@
       <c r="L72" t="n">
         <v>0.17</v>
       </c>
-      <c r="M72" t="inlineStr"/>
-      <c r="N72" t="inlineStr"/>
-      <c r="O72" t="inlineStr"/>
+      <c r="M72" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="N72" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="O72" t="n">
+        <v>29</v>
+      </c>
       <c r="P72" t="n">
         <v>13.3</v>
       </c>
@@ -9569,9 +9707,15 @@
       <c r="L82" t="n">
         <v>0.4</v>
       </c>
-      <c r="M82" t="inlineStr"/>
-      <c r="N82" t="inlineStr"/>
-      <c r="O82" t="inlineStr"/>
+      <c r="M82" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="N82" t="n">
+        <v>-5.4</v>
+      </c>
+      <c r="O82" t="n">
+        <v>21</v>
+      </c>
       <c r="P82" t="n">
         <v>23.2</v>
       </c>
@@ -10130,9 +10274,15 @@
       <c r="L89" t="n">
         <v>-0.48</v>
       </c>
-      <c r="M89" t="inlineStr"/>
-      <c r="N89" t="inlineStr"/>
-      <c r="O89" t="inlineStr"/>
+      <c r="M89" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="N89" t="n">
+        <v>-6.3</v>
+      </c>
+      <c r="O89" t="n">
+        <v>-153</v>
+      </c>
       <c r="P89" t="n">
         <v>-19.5</v>
       </c>
@@ -10205,8 +10355,12 @@
       <c r="L90" t="n">
         <v>-0.6899999999999999</v>
       </c>
-      <c r="M90" t="inlineStr"/>
-      <c r="N90" t="inlineStr"/>
+      <c r="M90" t="n">
+        <v>0</v>
+      </c>
+      <c r="N90" t="n">
+        <v>-12.5</v>
+      </c>
       <c r="O90" t="inlineStr"/>
       <c r="P90" t="n">
         <v>-38.1</v>
@@ -10280,8 +10434,12 @@
       <c r="L91" t="n">
         <v>-0.59</v>
       </c>
-      <c r="M91" t="inlineStr"/>
-      <c r="N91" t="inlineStr"/>
+      <c r="M91" t="n">
+        <v>0</v>
+      </c>
+      <c r="N91" t="n">
+        <v>-12</v>
+      </c>
       <c r="O91" t="inlineStr"/>
       <c r="P91" t="n">
         <v>-40.1</v>
@@ -10517,9 +10675,15 @@
       <c r="L94" t="n">
         <v>0.7</v>
       </c>
-      <c r="M94" t="inlineStr"/>
-      <c r="N94" t="inlineStr"/>
-      <c r="O94" t="inlineStr"/>
+      <c r="M94" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="N94" t="n">
+        <v>0</v>
+      </c>
+      <c r="O94" t="n">
+        <v>100</v>
+      </c>
       <c r="P94" t="n">
         <v>49.4</v>
       </c>
@@ -10592,9 +10756,15 @@
       <c r="L95" t="n">
         <v>1</v>
       </c>
-      <c r="M95" t="inlineStr"/>
-      <c r="N95" t="inlineStr"/>
-      <c r="O95" t="inlineStr"/>
+      <c r="M95" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="N95" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O95" t="n">
+        <v>82</v>
+      </c>
       <c r="P95" t="n">
         <v>47.5</v>
       </c>
@@ -10748,9 +10918,15 @@
       <c r="L97" t="n">
         <v>0.44</v>
       </c>
-      <c r="M97" t="inlineStr"/>
-      <c r="N97" t="inlineStr"/>
-      <c r="O97" t="inlineStr"/>
+      <c r="M97" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="N97" t="n">
+        <v>-4.1</v>
+      </c>
+      <c r="O97" t="n">
+        <v>68</v>
+      </c>
       <c r="P97" t="n">
         <v>27.3</v>
       </c>
@@ -11390,9 +11566,15 @@
       <c r="L105" t="n">
         <v>-0.75</v>
       </c>
-      <c r="M105" t="inlineStr"/>
-      <c r="N105" t="inlineStr"/>
-      <c r="O105" t="inlineStr"/>
+      <c r="M105" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="N105" t="n">
+        <v>-16</v>
+      </c>
+      <c r="O105" t="n">
+        <v>-4582</v>
+      </c>
       <c r="P105" t="n">
         <v>-32</v>
       </c>
@@ -11465,9 +11647,15 @@
       <c r="L106" t="n">
         <v>-1.05</v>
       </c>
-      <c r="M106" t="inlineStr"/>
-      <c r="N106" t="inlineStr"/>
-      <c r="O106" t="inlineStr"/>
+      <c r="M106" t="n">
+        <v>1</v>
+      </c>
+      <c r="N106" t="n">
+        <v>-17.4</v>
+      </c>
+      <c r="O106" t="n">
+        <v>-1645</v>
+      </c>
       <c r="P106" t="n">
         <v>-51.4</v>
       </c>
@@ -12026,9 +12214,15 @@
       <c r="L113" t="n">
         <v>1.1</v>
       </c>
-      <c r="M113" t="inlineStr"/>
-      <c r="N113" t="inlineStr"/>
-      <c r="O113" t="inlineStr"/>
+      <c r="M113" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="N113" t="n">
+        <v>-1.2</v>
+      </c>
+      <c r="O113" t="n">
+        <v>87</v>
+      </c>
       <c r="P113" t="n">
         <v>81.09999999999999</v>
       </c>
@@ -12830,9 +13024,15 @@
       <c r="L123" t="n">
         <v>2.63</v>
       </c>
-      <c r="M123" t="inlineStr"/>
-      <c r="N123" t="inlineStr"/>
-      <c r="O123" t="inlineStr"/>
+      <c r="M123" t="n">
+        <v>28.8</v>
+      </c>
+      <c r="N123" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="O123" t="n">
+        <v>86</v>
+      </c>
       <c r="P123" t="n">
         <v>143.4</v>
       </c>
@@ -13229,9 +13429,15 @@
       <c r="L128" t="n">
         <v>0.37</v>
       </c>
-      <c r="M128" t="inlineStr"/>
-      <c r="N128" t="inlineStr"/>
-      <c r="O128" t="inlineStr"/>
+      <c r="M128" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0</v>
+      </c>
+      <c r="O128" t="n">
+        <v>83</v>
+      </c>
       <c r="P128" t="n">
         <v>35</v>
       </c>
@@ -14033,9 +14239,15 @@
       <c r="L138" t="n">
         <v>1.71</v>
       </c>
-      <c r="M138" t="inlineStr"/>
-      <c r="N138" t="inlineStr"/>
-      <c r="O138" t="inlineStr"/>
+      <c r="M138" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="N138" t="n">
+        <v>-1.8</v>
+      </c>
+      <c r="O138" t="n">
+        <v>100</v>
+      </c>
       <c r="P138" t="n">
         <v>140.6</v>
       </c>
@@ -14270,9 +14482,15 @@
       <c r="L141" t="n">
         <v>1.18</v>
       </c>
-      <c r="M141" t="inlineStr"/>
-      <c r="N141" t="inlineStr"/>
-      <c r="O141" t="inlineStr"/>
+      <c r="M141" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="N141" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="O141" t="n">
+        <v>100</v>
+      </c>
       <c r="P141" t="n">
         <v>90.59999999999999</v>
       </c>
@@ -15878,9 +16096,15 @@
       <c r="L161" t="n">
         <v>-0.38</v>
       </c>
-      <c r="M161" t="inlineStr"/>
-      <c r="N161" t="inlineStr"/>
-      <c r="O161" t="inlineStr"/>
+      <c r="M161" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="N161" t="n">
+        <v>-5</v>
+      </c>
+      <c r="O161" t="n">
+        <v>-46</v>
+      </c>
       <c r="P161" t="n">
         <v>-18.5</v>
       </c>
@@ -16034,9 +16258,15 @@
       <c r="L163" t="n">
         <v>-0.62</v>
       </c>
-      <c r="M163" t="inlineStr"/>
-      <c r="N163" t="inlineStr"/>
-      <c r="O163" t="inlineStr"/>
+      <c r="M163" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="N163" t="n">
+        <v>-9.300000000000001</v>
+      </c>
+      <c r="O163" t="n">
+        <v>-2292</v>
+      </c>
       <c r="P163" t="n">
         <v>-32.4</v>
       </c>
@@ -18369,9 +18599,15 @@
       <c r="L192" t="n">
         <v>0.05</v>
       </c>
-      <c r="M192" t="inlineStr"/>
-      <c r="N192" t="inlineStr"/>
-      <c r="O192" t="inlineStr"/>
+      <c r="M192" t="n">
+        <v>11</v>
+      </c>
+      <c r="N192" t="n">
+        <v>0</v>
+      </c>
+      <c r="O192" t="n">
+        <v>9</v>
+      </c>
       <c r="P192" t="n">
         <v>4.2</v>
       </c>
@@ -18525,9 +18761,15 @@
       <c r="L194" t="n">
         <v>-0.09</v>
       </c>
-      <c r="M194" t="inlineStr"/>
-      <c r="N194" t="inlineStr"/>
-      <c r="O194" t="inlineStr"/>
+      <c r="M194" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="N194" t="n">
+        <v>-5.6</v>
+      </c>
+      <c r="O194" t="n">
+        <v>-40</v>
+      </c>
       <c r="P194" t="n">
         <v>-6.8</v>
       </c>
@@ -18762,9 +19004,15 @@
       <c r="L197" t="n">
         <v>0.27</v>
       </c>
-      <c r="M197" t="inlineStr"/>
-      <c r="N197" t="inlineStr"/>
-      <c r="O197" t="inlineStr"/>
+      <c r="M197" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="N197" t="n">
+        <v>-3.7</v>
+      </c>
+      <c r="O197" t="n">
+        <v>46</v>
+      </c>
       <c r="P197" t="n">
         <v>22.8</v>
       </c>
@@ -18837,9 +19085,15 @@
       <c r="L198" t="n">
         <v>0.27</v>
       </c>
-      <c r="M198" t="inlineStr"/>
-      <c r="N198" t="inlineStr"/>
-      <c r="O198" t="inlineStr"/>
+      <c r="M198" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="N198" t="n">
+        <v>-1.6</v>
+      </c>
+      <c r="O198" t="n">
+        <v>20</v>
+      </c>
       <c r="P198" t="n">
         <v>14.2</v>
       </c>
@@ -19639,9 +19893,15 @@
       <c r="L208" t="n">
         <v>-0.64</v>
       </c>
-      <c r="M208" t="inlineStr"/>
-      <c r="N208" t="inlineStr"/>
-      <c r="O208" t="inlineStr"/>
+      <c r="M208" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="N208" t="n">
+        <v>-12.7</v>
+      </c>
+      <c r="O208" t="n">
+        <v>-413</v>
+      </c>
       <c r="P208" t="n">
         <v>-40.3</v>
       </c>
@@ -19876,8 +20136,12 @@
       <c r="L211" t="n">
         <v>-2.56</v>
       </c>
-      <c r="M211" t="inlineStr"/>
-      <c r="N211" t="inlineStr"/>
+      <c r="M211" t="n">
+        <v>0</v>
+      </c>
+      <c r="N211" t="n">
+        <v>-26.2</v>
+      </c>
       <c r="O211" t="inlineStr"/>
       <c r="P211" t="n">
         <v>-70.09999999999999</v>
@@ -20113,9 +20377,15 @@
       <c r="L214" t="n">
         <v>1.4</v>
       </c>
-      <c r="M214" t="inlineStr"/>
-      <c r="N214" t="inlineStr"/>
-      <c r="O214" t="inlineStr"/>
+      <c r="M214" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="N214" t="n">
+        <v>-9.800000000000001</v>
+      </c>
+      <c r="O214" t="n">
+        <v>100</v>
+      </c>
       <c r="P214" t="n">
         <v>70</v>
       </c>
@@ -21150,9 +21420,15 @@
       <c r="L227" t="n">
         <v>0.86</v>
       </c>
-      <c r="M227" t="inlineStr"/>
-      <c r="N227" t="inlineStr"/>
-      <c r="O227" t="inlineStr"/>
+      <c r="M227" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="N227" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O227" t="n">
+        <v>89</v>
+      </c>
       <c r="P227" t="n">
         <v>77.3</v>
       </c>
@@ -21549,9 +21825,15 @@
       <c r="L232" t="n">
         <v>0.38</v>
       </c>
-      <c r="M232" t="inlineStr"/>
-      <c r="N232" t="inlineStr"/>
-      <c r="O232" t="inlineStr"/>
+      <c r="M232" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="N232" t="n">
+        <v>-2.1</v>
+      </c>
+      <c r="O232" t="n">
+        <v>51</v>
+      </c>
       <c r="P232" t="n">
         <v>25.2</v>
       </c>
@@ -21705,9 +21987,15 @@
       <c r="L234" t="n">
         <v>0.32</v>
       </c>
-      <c r="M234" t="inlineStr"/>
-      <c r="N234" t="inlineStr"/>
-      <c r="O234" t="inlineStr"/>
+      <c r="M234" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="N234" t="n">
+        <v>-7.2</v>
+      </c>
+      <c r="O234" t="n">
+        <v>86</v>
+      </c>
       <c r="P234" t="n">
         <v>19.7</v>
       </c>
@@ -22509,9 +22797,15 @@
       <c r="L244" t="n">
         <v>0.5600000000000001</v>
       </c>
-      <c r="M244" t="inlineStr"/>
-      <c r="N244" t="inlineStr"/>
-      <c r="O244" t="inlineStr"/>
+      <c r="M244" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="N244" t="n">
+        <v>-7.6</v>
+      </c>
+      <c r="O244" t="n">
+        <v>83</v>
+      </c>
       <c r="P244" t="n">
         <v>30.3</v>
       </c>
@@ -23469,8 +23763,12 @@
       <c r="L256" t="n">
         <v>-0.57</v>
       </c>
-      <c r="M256" t="inlineStr"/>
-      <c r="N256" t="inlineStr"/>
+      <c r="M256" t="n">
+        <v>0</v>
+      </c>
+      <c r="N256" t="n">
+        <v>-10.6</v>
+      </c>
       <c r="O256" t="inlineStr"/>
       <c r="P256" t="n">
         <v>-36.1</v>
@@ -23787,9 +24085,15 @@
       <c r="L260" t="n">
         <v>0.29</v>
       </c>
-      <c r="M260" t="inlineStr"/>
-      <c r="N260" t="inlineStr"/>
-      <c r="O260" t="inlineStr"/>
+      <c r="M260" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="N260" t="n">
+        <v>-2.1</v>
+      </c>
+      <c r="O260" t="n">
+        <v>44</v>
+      </c>
       <c r="P260" t="n">
         <v>20.4</v>
       </c>
@@ -23862,9 +24166,15 @@
       <c r="L261" t="n">
         <v>0.24</v>
       </c>
-      <c r="M261" t="inlineStr"/>
-      <c r="N261" t="inlineStr"/>
-      <c r="O261" t="inlineStr"/>
+      <c r="M261" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="N261" t="n">
+        <v>-2.1</v>
+      </c>
+      <c r="O261" t="n">
+        <v>38</v>
+      </c>
       <c r="P261" t="n">
         <v>11.5</v>
       </c>
@@ -25152,9 +25462,15 @@
       <c r="L277" t="n">
         <v>0.29</v>
       </c>
-      <c r="M277" t="inlineStr"/>
-      <c r="N277" t="inlineStr"/>
-      <c r="O277" t="inlineStr"/>
+      <c r="M277" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="N277" t="n">
+        <v>-3.4</v>
+      </c>
+      <c r="O277" t="n">
+        <v>45</v>
+      </c>
       <c r="P277" t="n">
         <v>16.6</v>
       </c>
@@ -25308,9 +25624,15 @@
       <c r="L279" t="n">
         <v>0.27</v>
       </c>
-      <c r="M279" t="inlineStr"/>
-      <c r="N279" t="inlineStr"/>
-      <c r="O279" t="inlineStr"/>
+      <c r="M279" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="N279" t="n">
+        <v>0</v>
+      </c>
+      <c r="O279" t="n">
+        <v>10</v>
+      </c>
       <c r="P279" t="n">
         <v>10.2</v>
       </c>
@@ -25707,9 +26029,15 @@
       <c r="L284" t="n">
         <v>-0.53</v>
       </c>
-      <c r="M284" t="inlineStr"/>
-      <c r="N284" t="inlineStr"/>
-      <c r="O284" t="inlineStr"/>
+      <c r="M284" t="n">
+        <v>1</v>
+      </c>
+      <c r="N284" t="n">
+        <v>-16.5</v>
+      </c>
+      <c r="O284" t="n">
+        <v>-1163</v>
+      </c>
       <c r="P284" t="n">
         <v>-37.6</v>
       </c>
@@ -26323,7 +26651,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>-1.6</v>
+        <v>-2.9</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -26365,7 +26693,7 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>-9.800000000000001</v>
+        <v>-10.7</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -26407,7 +26735,7 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>-14.1</v>
+        <v>-13.9</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -26449,7 +26777,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>-13</v>
+        <v>-8.1</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -26491,7 +26819,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>-4.9</v>
+        <v>-4.5</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -26533,7 +26861,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>-9.6</v>
+        <v>-9.300000000000001</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -26575,7 +26903,7 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>-3.7</v>
+        <v>-3</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -26659,7 +26987,7 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>-2.9</v>
+        <v>-2.4</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -26701,7 +27029,7 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>-4.3</v>
+        <v>-3.8</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -26827,7 +27155,7 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>-4.5</v>
+        <v>-4.7</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -26869,7 +27197,7 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>-7.4</v>
+        <v>-7.3</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -26911,7 +27239,7 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>-8.9</v>
+        <v>-9.1</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -26953,7 +27281,7 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>-3.2</v>
+        <v>-3.3</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -26995,7 +27323,7 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>-4</v>
+        <v>-3.8</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -27037,7 +27365,7 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>-4.5</v>
+        <v>-4.2</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -27079,7 +27407,7 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>-13</v>
+        <v>-11.8</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -27159,7 +27487,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>13.0%</t>
+          <t>13.4%</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -27174,7 +27502,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>12.7%</t>
+          <t>13.3%</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -27184,12 +27512,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Power</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>13.0%</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -27199,12 +27527,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Power</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>10.3%</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -27214,12 +27542,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>7.2%</t>
+          <t>5.7%</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -27229,12 +27557,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>5.9%</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="C7" t="n">

--- a/reports/AEGIS_LATEST.xlsx
+++ b/reports/AEGIS_LATEST.xlsx
@@ -444,7 +444,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-16  /  2026-09-16</t>
+          <t>2026-09-17  /  2026-09-16</t>
         </is>
       </c>
     </row>

--- a/reports/AEGIS_LATEST.xlsx
+++ b/reports/AEGIS_LATEST.xlsx
@@ -444,7 +444,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
     </row>
@@ -479,7 +479,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6">
@@ -489,7 +489,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7">
@@ -512,7 +512,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
     </row>
@@ -524,7 +524,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ICICIBANK (70)</t>
+          <t>ICICIBANK (69)</t>
         </is>
       </c>
     </row>
@@ -536,7 +536,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>DABUR (53)</t>
+          <t>DABUR (52)</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>WIPRO</t>
+          <t>NHPC</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Hold a 10-stock risk-managed portfolio</t>
+          <t>Hold a 9-stock risk-managed portfolio</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-17  /  2026-09-16</t>
+          <t>2026-09-18  /  2026-09-17</t>
         </is>
       </c>
     </row>
@@ -760,7 +760,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
     </row>
@@ -908,7 +908,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>15.2%</t>
+          <t>15.3%</t>
         </is>
       </c>
     </row>
@@ -920,7 +920,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>1.92</t>
         </is>
       </c>
     </row>
@@ -1322,7 +1322,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>-5.8%</t>
+          <t>-6.3%</t>
         </is>
       </c>
     </row>
@@ -1361,7 +1361,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB11"/>
+  <dimension ref="A1:AB10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1513,11 +1513,11 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Risk/Vol +23 · Historical +20 · Sector +10 · Regime +9 · Trend/Tech +8 = 70</t>
+          <t>Risk/Vol +23 · Historical +20 · Sector +10 · Regime +9 · Trend/Tech +7 = 69</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -1534,10 +1534,10 @@
         <v>66</v>
       </c>
       <c r="G2" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="H2" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I2" t="n">
         <v>100</v>
@@ -1556,11 +1556,11 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>1350</v>
+        <v>1347.6</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>1316 - 1384</t>
+          <t>1314 - 1381</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -1574,15 +1574,15 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-0.5%)</t>
+          <t>Below 200-DMA (-0.7%)</t>
         </is>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -1591,17 +1591,17 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="V2" t="n">
-        <v>32400</v>
+        <v>37733</v>
       </c>
       <c r="W2" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="X2" t="n">
-        <v>11</v>
+        <v>12.6</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
@@ -1615,12 +1615,12 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ICICIBANK: 70; PNB: 66, IDFCFIRSTB: 65, SBIN: 63</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ICICIBANK: 69; PNB: 65, IDFCFIRSTB: 63, SBIN: 61</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>Low-risk Financials holding (low vol) • below 200-dma (-0.5%) • outperforming Nifty • sector strength 100/100 • regime cautious (partial deploy) • 8 similar past recs: 75% positive, median +5.3%</t>
+          <t>Low-risk Financials holding (low vol) • below 200-dma (-0.7%) • outperforming Nifty • sector strength 100/100 • regime cautious (partial deploy) • 8 similar past recs: 75% positive, median +5.3%</t>
         </is>
       </c>
     </row>
@@ -1631,16 +1631,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Historical +20 · Risk/Vol +18 · Sector +10 · Regime +9 · Trend/Tech +6 = 63</t>
+          <t>Risk/Vol +21 · Historical +15 · Regime +9 · Sector +9 · Trend/Tech +8 = 62</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Historical</t>
+          <t>Risk/Vol</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1649,36 +1649,36 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="G3" t="n">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="H3" t="n">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="I3" t="n">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="J3" t="n">
         <v>60</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>SBIN</t>
+          <t>TATASTEEL</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Metal</t>
         </is>
       </c>
       <c r="M3" t="n">
-        <v>981.8</v>
+        <v>187.3</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>952 - 1012</t>
+          <t>182 - 192</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -1692,15 +1692,15 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-5.6%)</t>
+          <t>Below 200-DMA (-3.0%)</t>
         </is>
       </c>
       <c r="S3" t="n">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -1709,21 +1709,21 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="V3" t="n">
-        <v>18654</v>
+        <v>29405</v>
       </c>
       <c r="W3" t="n">
-        <v>19</v>
+        <v>157</v>
       </c>
       <c r="X3" t="n">
-        <v>6.2</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>Historical + Risk/Vol strongest; chosen as a lowest-volatility Financials name under the sector cap</t>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Metal name under the sector cap</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -1733,12 +1733,12 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — SBIN: 63; ICICIBANK: 70, PNB: 66, IDFCFIRSTB: 65. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — TATASTEEL: 62; COALINDIA: 60, HINDZINC: 50, SAIL: 49</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>Low-risk Financials holding (low vol) • below 200-dma (-5.6%) • sector strength 100/100 • regime cautious (partial deploy) • 2 similar past recs: 100% positive, median +8.9%</t>
+          <t>Low-risk Metal holding (low vol) • below 200-dma (-3.0%) • sector strength 88/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
         </is>
       </c>
     </row>
@@ -1749,16 +1749,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Risk/Vol +22 · Historical +15 · Regime +9 · Sector +9 · Trend/Tech +7 = 62</t>
+          <t>Historical +20 · Risk/Vol +16 · Sector +10 · Regime +9 · Trend/Tech +6 = 61</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Risk/Vol</t>
+          <t>Historical</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1767,36 +1767,36 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="G4" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="H4" t="n">
-        <v>87</v>
+        <v>65</v>
       </c>
       <c r="I4" t="n">
-        <v>89</v>
+        <v>100</v>
       </c>
       <c r="J4" t="n">
         <v>60</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>TATASTEEL</t>
+          <t>SBIN</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Metal</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>184.4</v>
+        <v>988.7</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>180 - 189</t>
+          <t>959 - 1019</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -1810,15 +1810,15 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-4.5%)</t>
+          <t>Below 200-DMA (-4.9%)</t>
         </is>
       </c>
       <c r="S4" t="n">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1827,21 +1827,21 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="V4" t="n">
-        <v>33552</v>
+        <v>37571</v>
       </c>
       <c r="W4" t="n">
-        <v>182</v>
+        <v>38</v>
       </c>
       <c r="X4" t="n">
-        <v>11.2</v>
+        <v>12.7</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Metal name under the sector cap</t>
+          <t>Historical + Risk/Vol strongest; chosen as a lowest-volatility Financials name under the sector cap</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1851,12 +1851,12 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — TATASTEEL: 62; COALINDIA: 61, SAIL: 49, HINDZINC: 48</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — SBIN: 61; ICICIBANK: 69, PNB: 65, IDFCFIRSTB: 63. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>Low-risk Metal holding (low vol) • below 200-dma (-4.5%) • sector strength 89/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
+          <t>Low-risk Financials holding (medium vol) • below 200-dma (-4.9%) • sector strength 100/100 • regime cautious (partial deploy) • 2 similar past recs: 100% positive, median +8.9%</t>
         </is>
       </c>
     </row>
@@ -1867,11 +1867,11 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Risk/Vol +21 · Historical +15 · Regime +9 · Sector +9 · Trend/Tech +7 = 61</t>
+          <t>Risk/Vol +20 · Historical +15 · Regime +9 · Sector +9 · Trend/Tech +7 = 60</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1888,13 +1888,13 @@
         <v>51</v>
       </c>
       <c r="G5" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H5" t="n">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="I5" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="J5" t="n">
         <v>60</v>
@@ -1910,11 +1910,11 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>420.8</v>
+        <v>418</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>409 - 432</t>
+          <t>407 - 429</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -1932,11 +1932,11 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-2.3%)</t>
+          <t>Below 200-DMA (-3.0%)</t>
         </is>
       </c>
       <c r="S5" t="n">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1945,17 +1945,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="V5" t="n">
-        <v>32818</v>
+        <v>39710</v>
       </c>
       <c r="W5" t="n">
-        <v>78</v>
+        <v>95</v>
       </c>
       <c r="X5" t="n">
-        <v>11</v>
+        <v>13.3</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -1969,12 +1969,12 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — COALINDIA: 61; TATASTEEL: 62, SAIL: 49, HINDZINC: 48. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — COALINDIA: 60; TATASTEEL: 62, HINDZINC: 50, SAIL: 49. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>Low-risk Metal holding (low vol) • below 200-dma (-2.3%) • sector strength 89/100 • regime cautious (partial deploy) • 3 similar past recs: 67% positive, median +0.8%</t>
+          <t>Low-risk Metal holding (low vol) • below 200-dma (-3.0%) • sector strength 88/100 • regime cautious (partial deploy) • 3 similar past recs: 67% positive, median +0.8%</t>
         </is>
       </c>
     </row>
@@ -1985,11 +1985,11 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Risk/Vol +18 · Historical +16 · Regime +9 · Trend/Tech +8 · Sector +8 = 59</t>
+          <t>Risk/Vol +17 · Historical +16 · Regime +9 · Trend/Tech +8 · Sector +8 = 58</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -2006,13 +2006,13 @@
         <v>53</v>
       </c>
       <c r="G6" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="H6" t="n">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="I6" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="J6" t="n">
         <v>60</v>
@@ -2028,11 +2028,11 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>235</v>
+        <v>232.4</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>228 - 242</t>
+          <t>226 - 239</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -2046,15 +2046,15 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-8.6%)</t>
+          <t>Below 200-DMA (-9.5%)</t>
         </is>
       </c>
       <c r="S6" t="n">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -2063,17 +2063,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="V6" t="n">
-        <v>28204</v>
+        <v>33470</v>
       </c>
       <c r="W6" t="n">
-        <v>120</v>
+        <v>144</v>
       </c>
       <c r="X6" t="n">
-        <v>9.4</v>
+        <v>11.2</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -2087,12 +2087,12 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ONGC: 59; IOC: 53</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ONGC: 58; IOC: 54</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>Low-risk Energy holding (low vol) • below 200-dma (-8.6%) • sector strength 78/100 • regime cautious (partial deploy) • 2 similar past recs: 50% positive, median +9.0%</t>
+          <t>Low-risk Energy holding (low vol) • below 200-dma (-9.5%) • sector strength 75/100 • regime cautious (partial deploy) • 2 similar past recs: 50% positive, median +9.0%</t>
         </is>
       </c>
     </row>
@@ -2103,11 +2103,11 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Risk/Vol +20 · Historical +15 · Regime +9 · Sector +7 · Trend/Tech +4 = 55</t>
+          <t>Risk/Vol +24 · Historical +13 · Regime +9 · Trend/Tech +6 · Sector +4 = 56</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -2117,62 +2117,62 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Trend/Tech</t>
+          <t>Sector</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="G7" t="n">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="H7" t="n">
-        <v>80</v>
+        <v>96</v>
       </c>
       <c r="I7" t="n">
-        <v>67</v>
+        <v>38</v>
       </c>
       <c r="J7" t="n">
         <v>60</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>BEL</t>
+          <t>ITC</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>389.4</v>
+        <v>266.2</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>379 - 400</t>
+          <t>260 - 272</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-4% to +3%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>56%</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-7.0%)</t>
+          <t>Below 200-DMA (-14.1%)</t>
         </is>
       </c>
       <c r="S7" t="n">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -2181,21 +2181,21 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="V7" t="n">
-        <v>21414</v>
+        <v>35138</v>
       </c>
       <c r="W7" t="n">
-        <v>55</v>
+        <v>132</v>
       </c>
       <c r="X7" t="n">
-        <v>7.2</v>
+        <v>11.7</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Industrials name under the sector cap</t>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility FMCG name under the sector cap</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -2205,27 +2205,27 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>No same-sector peer in the universe.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ITC: 56; DABUR: 52</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>Low-risk Industrials holding (low vol) • below 200-dma (-7.0%) • sector strength 67/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
+          <t>Low-risk FMCG holding (low vol) • below 200-dma (-14.1%) • sector strength 38/100 • regime cautious (partial deploy) • 9 similar past recs: 56% positive, median +0.3%</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ACCUMULATE</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Risk/Vol +24 · Historical +13 · Regime +9 · Trend/Tech +4 · Sector +4 = 54</t>
+          <t>Risk/Vol +19 · Historical +15 · Regime +9 · Trend/Tech +7 · Sector +6 = 56</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -2239,58 +2239,58 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="G8" t="n">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="H8" t="n">
-        <v>97</v>
+        <v>77</v>
       </c>
       <c r="I8" t="n">
-        <v>44</v>
+        <v>62</v>
       </c>
       <c r="J8" t="n">
         <v>60</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>ITC</t>
+          <t>BEL</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="M8" t="n">
-        <v>262.7</v>
+        <v>395.5</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>257 - 269</t>
+          <t>385 - 406</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>-4% to +3%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>56%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-15.5%)</t>
+          <t>Below 200-DMA (-5.5%)</t>
         </is>
       </c>
       <c r="S8" t="n">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -2299,21 +2299,21 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="V8" t="n">
-        <v>39668</v>
+        <v>31636</v>
       </c>
       <c r="W8" t="n">
-        <v>151</v>
+        <v>80</v>
       </c>
       <c r="X8" t="n">
-        <v>13.3</v>
+        <v>10.6</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility FMCG name under the sector cap</t>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Industrials name under the sector cap</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
@@ -2323,12 +2323,12 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ITC: 54; DABUR: 53</t>
+          <t>No same-sector peer in the universe.</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>Low-risk FMCG holding (low vol) • below 200-dma (-15.5%) • sector strength 44/100 • regime cautious (partial deploy) • 9 similar past recs: 56% positive, median +0.3%</t>
+          <t>Low-risk Industrials holding (low vol) • below 200-dma (-5.5%) • sector strength 62/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
         </is>
       </c>
     </row>
@@ -2343,7 +2343,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Risk/Vol +22 · Historical +15 · Regime +9 · Trend/Tech +6 · Sector +2 = 54</t>
+          <t>Risk/Vol +22 · Historical +15 · Regime +9 · Trend/Tech +7 · Sector +1 = 54</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2360,13 +2360,13 @@
         <v>50</v>
       </c>
       <c r="G9" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="H9" t="n">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="I9" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="J9" t="n">
         <v>60</v>
@@ -2382,11 +2382,11 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>363.6</v>
+        <v>369</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>354 - 373</t>
+          <t>359 - 379</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -2404,11 +2404,11 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-6.1%)</t>
+          <t>Below 200-DMA (-4.6%)</t>
         </is>
       </c>
       <c r="S9" t="n">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -2417,17 +2417,17 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="V9" t="n">
-        <v>34178</v>
+        <v>29520</v>
       </c>
       <c r="W9" t="n">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="X9" t="n">
-        <v>11.5</v>
+        <v>9.9</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -2441,12 +2441,12 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — TATAPOWER: 54; NHPC: 53, ADANIPOWER: 42, NLCINDIA: 29</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — TATAPOWER: 54; NHPC: 50, ADANIPOWER: 44, NLCINDIA: 30</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>Low-risk Power holding (low vol) • below 200-dma (-6.1%) • sector strength 22/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
+          <t>Low-risk Power holding (low vol) • below 200-dma (-4.6%) • sector strength 12/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
         </is>
       </c>
     </row>
@@ -2457,16 +2457,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Historical +17 · Risk/Vol +16 · Trend/Tech +9 · Regime +9 · Sector +2 = 53</t>
+          <t>Risk/Vol +18 · Historical +15 · Regime +9 · Trend/Tech +6 · Sector +4 = 52</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Historical</t>
+          <t>Risk/Vol</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -2475,36 +2475,36 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="G10" t="n">
-        <v>47</v>
+        <v>31</v>
       </c>
       <c r="H10" t="n">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="I10" t="n">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="J10" t="n">
         <v>60</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>NHPC</t>
+          <t>DABUR</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Power</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>75.7</v>
+        <v>384.5</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>73 - 78</t>
+          <t>373 - 396</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -2518,15 +2518,15 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-2.7%)</t>
+          <t>Below 200-DMA (-15.5%)</t>
         </is>
       </c>
       <c r="S10" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -2535,21 +2535,21 @@
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="V10" t="n">
-        <v>30583</v>
+        <v>24227</v>
       </c>
       <c r="W10" t="n">
-        <v>404</v>
+        <v>63</v>
       </c>
       <c r="X10" t="n">
-        <v>10.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>Historical + Risk/Vol strongest; chosen as a lowest-volatility Power name under the sector cap</t>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility FMCG name under the sector cap</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
@@ -2559,130 +2559,12 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — NHPC: 53; TATAPOWER: 54, ADANIPOWER: 42, NLCINDIA: 29. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — DABUR: 52; ITC: 56. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>Low-risk Power holding (medium vol) • below 200-dma (-2.7%) • outperforming Nifty • sector strength 22/100 • regime cautious (partial deploy) • 1 similar past recs: 100% positive, median +7.2%</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>ACCUMULATE</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>53</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Risk/Vol +19 · Historical +15 · Regime +9 · Trend/Tech +6 · Sector +4 = 53</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Risk/Vol</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Sector</t>
-        </is>
-      </c>
-      <c r="F11" t="n">
-        <v>50</v>
-      </c>
-      <c r="G11" t="n">
-        <v>31</v>
-      </c>
-      <c r="H11" t="n">
-        <v>77</v>
-      </c>
-      <c r="I11" t="n">
-        <v>44</v>
-      </c>
-      <c r="J11" t="n">
-        <v>60</v>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>DABUR</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>FMCG</t>
-        </is>
-      </c>
-      <c r="M11" t="n">
-        <v>386.1</v>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>375 - 397</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Q11" t="n">
-        <v>64</v>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>Below 200-DMA (-15.3%)</t>
-        </is>
-      </c>
-      <c r="S11" t="n">
-        <v>50</v>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>3 months (3M)</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
-      <c r="V11" t="n">
-        <v>27027</v>
-      </c>
-      <c r="W11" t="n">
-        <v>70</v>
-      </c>
-      <c r="X11" t="n">
-        <v>9</v>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility FMCG name under the sector cap</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>Fundamentals · Earnings · News · Flows</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — DABUR: 53; ITC: 54. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>Low-risk FMCG holding (low vol) • below 200-dma (-15.3%) • sector strength 44/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
+          <t>Low-risk FMCG holding (low vol) • below 200-dma (-15.5%) • sector strength 38/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
         </is>
       </c>
     </row>
@@ -3237,15 +3119,9 @@
       <c r="L2" t="n">
         <v>4.34</v>
       </c>
-      <c r="M2" t="n">
-        <v>31.6</v>
-      </c>
-      <c r="N2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O2" t="n">
-        <v>100</v>
-      </c>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
       <c r="P2" t="n">
         <v>200.3</v>
       </c>
@@ -3318,15 +3194,9 @@
       <c r="L3" t="n">
         <v>2.12</v>
       </c>
-      <c r="M3" t="n">
-        <v>38</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O3" t="n">
-        <v>81</v>
-      </c>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
       <c r="P3" t="n">
         <v>194.1</v>
       </c>
@@ -3885,15 +3755,9 @@
       <c r="L10" t="n">
         <v>0.7</v>
       </c>
-      <c r="M10" t="n">
-        <v>10</v>
-      </c>
-      <c r="N10" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O10" t="n">
-        <v>88</v>
-      </c>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
       <c r="P10" t="n">
         <v>40.2</v>
       </c>
@@ -3966,15 +3830,9 @@
       <c r="L11" t="n">
         <v>0.49</v>
       </c>
-      <c r="M11" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="N11" t="n">
-        <v>-9.9</v>
-      </c>
-      <c r="O11" t="n">
-        <v>92</v>
-      </c>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
       <c r="P11" t="n">
         <v>29.9</v>
       </c>
@@ -4209,15 +4067,9 @@
       <c r="L14" t="n">
         <v>-0.14</v>
       </c>
-      <c r="M14" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="N14" t="n">
-        <v>-3.9</v>
-      </c>
-      <c r="O14" t="n">
-        <v>-21</v>
-      </c>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
       <c r="P14" t="n">
         <v>-4.7</v>
       </c>
@@ -4371,15 +4223,9 @@
       <c r="L16" t="n">
         <v>-0.53</v>
       </c>
-      <c r="M16" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="N16" t="n">
-        <v>-9.1</v>
-      </c>
-      <c r="O16" t="n">
-        <v>-331</v>
-      </c>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
       <c r="P16" t="n">
         <v>-30.7</v>
       </c>
@@ -4695,15 +4541,9 @@
       <c r="L20" t="n">
         <v>0.48</v>
       </c>
-      <c r="M20" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="N20" t="n">
-        <v>-10.6</v>
-      </c>
-      <c r="O20" t="n">
-        <v>87</v>
-      </c>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
       <c r="P20" t="n">
         <v>24.2</v>
       </c>
@@ -5100,15 +4940,9 @@
       <c r="L25" t="n">
         <v>-0.35</v>
       </c>
-      <c r="M25" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="N25" t="n">
-        <v>-14.8</v>
-      </c>
-      <c r="O25" t="n">
-        <v>-64</v>
-      </c>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr"/>
       <c r="P25" t="n">
         <v>-25.7</v>
       </c>
@@ -5499,15 +5333,9 @@
       <c r="L30" t="n">
         <v>-1.18</v>
       </c>
-      <c r="M30" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="N30" t="n">
-        <v>-16.1</v>
-      </c>
-      <c r="O30" t="n">
-        <v>-1221</v>
-      </c>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="O30" t="inlineStr"/>
       <c r="P30" t="n">
         <v>-43.4</v>
       </c>
@@ -5580,15 +5408,9 @@
       <c r="L31" t="n">
         <v>-0.92</v>
       </c>
-      <c r="M31" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="N31" t="n">
-        <v>-19.4</v>
-      </c>
-      <c r="O31" t="n">
-        <v>-456</v>
-      </c>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="O31" t="inlineStr"/>
       <c r="P31" t="n">
         <v>-47.7</v>
       </c>
@@ -5661,15 +5483,9 @@
       <c r="L32" t="n">
         <v>0.71</v>
       </c>
-      <c r="M32" t="n">
-        <v>16.3</v>
-      </c>
-      <c r="N32" t="n">
-        <v>-1.3</v>
-      </c>
-      <c r="O32" t="n">
-        <v>100</v>
-      </c>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="O32" t="inlineStr"/>
       <c r="P32" t="n">
         <v>82.59999999999999</v>
       </c>
@@ -5742,15 +5558,9 @@
       <c r="L33" t="n">
         <v>1.08</v>
       </c>
-      <c r="M33" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="N33" t="n">
-        <v>-4.8</v>
-      </c>
-      <c r="O33" t="n">
-        <v>100</v>
-      </c>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="O33" t="inlineStr"/>
       <c r="P33" t="n">
         <v>38.1</v>
       </c>
@@ -6471,15 +6281,9 @@
       <c r="L42" t="n">
         <v>-0.63</v>
       </c>
-      <c r="M42" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="N42" t="n">
-        <v>-16.5</v>
-      </c>
-      <c r="O42" t="n">
-        <v>-157</v>
-      </c>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
+      <c r="O42" t="inlineStr"/>
       <c r="P42" t="n">
         <v>-29.3</v>
       </c>
@@ -6552,15 +6356,9 @@
       <c r="L43" t="n">
         <v>-0.76</v>
       </c>
-      <c r="M43" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="N43" t="n">
-        <v>-14.3</v>
-      </c>
-      <c r="O43" t="n">
-        <v>-642</v>
-      </c>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
+      <c r="O43" t="inlineStr"/>
       <c r="P43" t="n">
         <v>-29.6</v>
       </c>
@@ -6876,15 +6674,9 @@
       <c r="L47" t="n">
         <v>3.05</v>
       </c>
-      <c r="M47" t="n">
-        <v>39.2</v>
-      </c>
-      <c r="N47" t="n">
-        <v>0</v>
-      </c>
-      <c r="O47" t="n">
-        <v>97</v>
-      </c>
+      <c r="M47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
+      <c r="O47" t="inlineStr"/>
       <c r="P47" t="n">
         <v>263.7</v>
       </c>
@@ -7119,15 +6911,9 @@
       <c r="L50" t="n">
         <v>0.5600000000000001</v>
       </c>
-      <c r="M50" t="n">
-        <v>14.6</v>
-      </c>
-      <c r="N50" t="n">
-        <v>-2.1</v>
-      </c>
-      <c r="O50" t="n">
-        <v>55</v>
-      </c>
+      <c r="M50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
+      <c r="O50" t="inlineStr"/>
       <c r="P50" t="n">
         <v>36.5</v>
       </c>
@@ -7200,15 +6986,9 @@
       <c r="L51" t="n">
         <v>0.2</v>
       </c>
-      <c r="M51" t="n">
-        <v>3</v>
-      </c>
-      <c r="N51" t="n">
-        <v>-10.7</v>
-      </c>
-      <c r="O51" t="n">
-        <v>68</v>
-      </c>
+      <c r="M51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
+      <c r="O51" t="inlineStr"/>
       <c r="P51" t="n">
         <v>8.4</v>
       </c>
@@ -7281,15 +7061,9 @@
       <c r="L52" t="n">
         <v>0.08</v>
       </c>
-      <c r="M52" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="N52" t="n">
-        <v>-10.4</v>
-      </c>
-      <c r="O52" t="n">
-        <v>60</v>
-      </c>
+      <c r="M52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
+      <c r="O52" t="inlineStr"/>
       <c r="P52" t="n">
         <v>5.7</v>
       </c>
@@ -7362,15 +7136,9 @@
       <c r="L53" t="n">
         <v>-0.05</v>
       </c>
-      <c r="M53" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N53" t="n">
-        <v>-8.199999999999999</v>
-      </c>
-      <c r="O53" t="n">
-        <v>-38</v>
-      </c>
+      <c r="M53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
+      <c r="O53" t="inlineStr"/>
       <c r="P53" t="n">
         <v>-3.8</v>
       </c>
@@ -7443,15 +7211,9 @@
       <c r="L54" t="n">
         <v>-0.09</v>
       </c>
-      <c r="M54" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="N54" t="n">
-        <v>-6.8</v>
-      </c>
-      <c r="O54" t="n">
-        <v>-26</v>
-      </c>
+      <c r="M54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
+      <c r="O54" t="inlineStr"/>
       <c r="P54" t="n">
         <v>-4.4</v>
       </c>
@@ -7524,15 +7286,9 @@
       <c r="L55" t="n">
         <v>-0.43</v>
       </c>
-      <c r="M55" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="N55" t="n">
-        <v>-18.1</v>
-      </c>
-      <c r="O55" t="n">
-        <v>-243</v>
-      </c>
+      <c r="M55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
+      <c r="O55" t="inlineStr"/>
       <c r="P55" t="n">
         <v>-31</v>
       </c>
@@ -8330,15 +8086,9 @@
       <c r="L65" t="n">
         <v>1.25</v>
       </c>
-      <c r="M65" t="n">
-        <v>20.6</v>
-      </c>
-      <c r="N65" t="n">
-        <v>0</v>
-      </c>
-      <c r="O65" t="n">
-        <v>66</v>
-      </c>
+      <c r="M65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
+      <c r="O65" t="inlineStr"/>
       <c r="P65" t="n">
         <v>67.2</v>
       </c>
@@ -8411,15 +8161,9 @@
       <c r="L66" t="n">
         <v>0.77</v>
       </c>
-      <c r="M66" t="n">
-        <v>26.8</v>
-      </c>
-      <c r="N66" t="n">
-        <v>0</v>
-      </c>
-      <c r="O66" t="n">
-        <v>49</v>
-      </c>
+      <c r="M66" t="inlineStr"/>
+      <c r="N66" t="inlineStr"/>
+      <c r="O66" t="inlineStr"/>
       <c r="P66" t="n">
         <v>63.2</v>
       </c>
@@ -8735,15 +8479,9 @@
       <c r="L70" t="n">
         <v>0.43</v>
       </c>
-      <c r="M70" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="N70" t="n">
-        <v>-1.4</v>
-      </c>
-      <c r="O70" t="n">
-        <v>61</v>
-      </c>
+      <c r="M70" t="inlineStr"/>
+      <c r="N70" t="inlineStr"/>
+      <c r="O70" t="inlineStr"/>
       <c r="P70" t="n">
         <v>21.9</v>
       </c>
@@ -8978,15 +8716,9 @@
       <c r="L73" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="M73" t="n">
-        <v>7</v>
-      </c>
-      <c r="N73" t="n">
-        <v>-2.3</v>
-      </c>
-      <c r="O73" t="n">
-        <v>11</v>
-      </c>
+      <c r="M73" t="inlineStr"/>
+      <c r="N73" t="inlineStr"/>
+      <c r="O73" t="inlineStr"/>
       <c r="P73" t="n">
         <v>3.1</v>
       </c>
@@ -9059,15 +8791,9 @@
       <c r="L74" t="n">
         <v>-0.04</v>
       </c>
-      <c r="M74" t="n">
-        <v>12.9</v>
-      </c>
-      <c r="N74" t="n">
-        <v>-4.6</v>
-      </c>
-      <c r="O74" t="n">
-        <v>-4</v>
-      </c>
+      <c r="M74" t="inlineStr"/>
+      <c r="N74" t="inlineStr"/>
+      <c r="O74" t="inlineStr"/>
       <c r="P74" t="n">
         <v>-2</v>
       </c>
@@ -9140,15 +8866,9 @@
       <c r="L75" t="n">
         <v>-0.06</v>
       </c>
-      <c r="M75" t="n">
-        <v>13.3</v>
-      </c>
-      <c r="N75" t="n">
-        <v>-2.6</v>
-      </c>
-      <c r="O75" t="n">
-        <v>-12</v>
-      </c>
+      <c r="M75" t="inlineStr"/>
+      <c r="N75" t="inlineStr"/>
+      <c r="O75" t="inlineStr"/>
       <c r="P75" t="n">
         <v>-6.1</v>
       </c>
@@ -9464,15 +9184,9 @@
       <c r="L79" t="n">
         <v>3.16</v>
       </c>
-      <c r="M79" t="n">
-        <v>49.7</v>
-      </c>
-      <c r="N79" t="n">
-        <v>-3</v>
-      </c>
-      <c r="O79" t="n">
-        <v>100</v>
-      </c>
+      <c r="M79" t="inlineStr"/>
+      <c r="N79" t="inlineStr"/>
+      <c r="O79" t="inlineStr"/>
       <c r="P79" t="n">
         <v>402.7</v>
       </c>
@@ -9788,15 +9502,9 @@
       <c r="L83" t="n">
         <v>0.21</v>
       </c>
-      <c r="M83" t="n">
-        <v>8</v>
-      </c>
-      <c r="N83" t="n">
-        <v>-4.5</v>
-      </c>
-      <c r="O83" t="n">
-        <v>36</v>
-      </c>
+      <c r="M83" t="inlineStr"/>
+      <c r="N83" t="inlineStr"/>
+      <c r="O83" t="inlineStr"/>
       <c r="P83" t="n">
         <v>12.2</v>
       </c>
@@ -9869,15 +9577,9 @@
       <c r="L84" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="M84" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="N84" t="n">
-        <v>-2.1</v>
-      </c>
-      <c r="O84" t="n">
-        <v>23</v>
-      </c>
+      <c r="M84" t="inlineStr"/>
+      <c r="N84" t="inlineStr"/>
+      <c r="O84" t="inlineStr"/>
       <c r="P84" t="n">
         <v>4.3</v>
       </c>
@@ -10112,15 +9814,9 @@
       <c r="L87" t="n">
         <v>-0.14</v>
       </c>
-      <c r="M87" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="N87" t="n">
-        <v>-3.2</v>
-      </c>
-      <c r="O87" t="n">
-        <v>-49</v>
-      </c>
+      <c r="M87" t="inlineStr"/>
+      <c r="N87" t="inlineStr"/>
+      <c r="O87" t="inlineStr"/>
       <c r="P87" t="n">
         <v>-9.300000000000001</v>
       </c>
@@ -10434,12 +10130,8 @@
       <c r="L91" t="n">
         <v>-0.59</v>
       </c>
-      <c r="M91" t="n">
-        <v>0</v>
-      </c>
-      <c r="N91" t="n">
-        <v>-12</v>
-      </c>
+      <c r="M91" t="inlineStr"/>
+      <c r="N91" t="inlineStr"/>
       <c r="O91" t="inlineStr"/>
       <c r="P91" t="n">
         <v>-40.1</v>
@@ -10594,15 +10286,9 @@
       <c r="L93" t="n">
         <v>1.23</v>
       </c>
-      <c r="M93" t="n">
-        <v>17.7</v>
-      </c>
-      <c r="N93" t="n">
-        <v>-2.9</v>
-      </c>
-      <c r="O93" t="n">
-        <v>100</v>
-      </c>
+      <c r="M93" t="inlineStr"/>
+      <c r="N93" t="inlineStr"/>
+      <c r="O93" t="inlineStr"/>
       <c r="P93" t="n">
         <v>91.7</v>
       </c>
@@ -11080,15 +10766,9 @@
       <c r="L99" t="n">
         <v>0.28</v>
       </c>
-      <c r="M99" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="N99" t="n">
-        <v>-5.6</v>
-      </c>
-      <c r="O99" t="n">
-        <v>58</v>
-      </c>
+      <c r="M99" t="inlineStr"/>
+      <c r="N99" t="inlineStr"/>
+      <c r="O99" t="inlineStr"/>
       <c r="P99" t="n">
         <v>11.1</v>
       </c>
@@ -11647,15 +11327,9 @@
       <c r="L106" t="n">
         <v>-1.05</v>
       </c>
-      <c r="M106" t="n">
-        <v>1</v>
-      </c>
-      <c r="N106" t="n">
-        <v>-17.4</v>
-      </c>
-      <c r="O106" t="n">
-        <v>-1645</v>
-      </c>
+      <c r="M106" t="inlineStr"/>
+      <c r="N106" t="inlineStr"/>
+      <c r="O106" t="inlineStr"/>
       <c r="P106" t="n">
         <v>-51.4</v>
       </c>
@@ -11728,15 +11402,9 @@
       <c r="L107" t="n">
         <v>1.65</v>
       </c>
-      <c r="M107" t="n">
-        <v>24.5</v>
-      </c>
-      <c r="N107" t="n">
-        <v>-2.9</v>
-      </c>
-      <c r="O107" t="n">
-        <v>99</v>
-      </c>
+      <c r="M107" t="inlineStr"/>
+      <c r="N107" t="inlineStr"/>
+      <c r="O107" t="inlineStr"/>
       <c r="P107" t="n">
         <v>138.8</v>
       </c>
@@ -11890,15 +11558,9 @@
       <c r="L109" t="n">
         <v>1.48</v>
       </c>
-      <c r="M109" t="n">
-        <v>22</v>
-      </c>
-      <c r="N109" t="n">
-        <v>-0.6</v>
-      </c>
-      <c r="O109" t="n">
-        <v>99</v>
-      </c>
+      <c r="M109" t="inlineStr"/>
+      <c r="N109" t="inlineStr"/>
+      <c r="O109" t="inlineStr"/>
       <c r="P109" t="n">
         <v>120.4</v>
       </c>
@@ -12133,15 +11795,9 @@
       <c r="L112" t="n">
         <v>1.4</v>
       </c>
-      <c r="M112" t="n">
-        <v>16.3</v>
-      </c>
-      <c r="N112" t="n">
-        <v>-1.8</v>
-      </c>
-      <c r="O112" t="n">
-        <v>100</v>
-      </c>
+      <c r="M112" t="inlineStr"/>
+      <c r="N112" t="inlineStr"/>
+      <c r="O112" t="inlineStr"/>
       <c r="P112" t="n">
         <v>82.7</v>
       </c>
@@ -12781,15 +12437,9 @@
       <c r="L120" t="n">
         <v>0.15</v>
       </c>
-      <c r="M120" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="N120" t="n">
-        <v>-3.2</v>
-      </c>
-      <c r="O120" t="n">
-        <v>56</v>
-      </c>
+      <c r="M120" t="inlineStr"/>
+      <c r="N120" t="inlineStr"/>
+      <c r="O120" t="inlineStr"/>
       <c r="P120" t="n">
         <v>10.3</v>
       </c>
@@ -13024,15 +12674,9 @@
       <c r="L123" t="n">
         <v>2.63</v>
       </c>
-      <c r="M123" t="n">
-        <v>28.8</v>
-      </c>
-      <c r="N123" t="n">
-        <v>-0.8</v>
-      </c>
-      <c r="O123" t="n">
-        <v>86</v>
-      </c>
+      <c r="M123" t="inlineStr"/>
+      <c r="N123" t="inlineStr"/>
+      <c r="O123" t="inlineStr"/>
       <c r="P123" t="n">
         <v>143.4</v>
       </c>
@@ -13105,15 +12749,9 @@
       <c r="L124" t="n">
         <v>0.86</v>
       </c>
-      <c r="M124" t="n">
-        <v>14.3</v>
-      </c>
-      <c r="N124" t="n">
-        <v>0</v>
-      </c>
-      <c r="O124" t="n">
-        <v>90</v>
-      </c>
+      <c r="M124" t="inlineStr"/>
+      <c r="N124" t="inlineStr"/>
+      <c r="O124" t="inlineStr"/>
       <c r="P124" t="n">
         <v>62</v>
       </c>
@@ -13186,15 +12824,9 @@
       <c r="L125" t="n">
         <v>0.89</v>
       </c>
-      <c r="M125" t="n">
-        <v>13.8</v>
-      </c>
-      <c r="N125" t="n">
-        <v>-0.4</v>
-      </c>
-      <c r="O125" t="n">
-        <v>92</v>
-      </c>
+      <c r="M125" t="inlineStr"/>
+      <c r="N125" t="inlineStr"/>
+      <c r="O125" t="inlineStr"/>
       <c r="P125" t="n">
         <v>61.1</v>
       </c>
@@ -13429,15 +13061,9 @@
       <c r="L128" t="n">
         <v>0.37</v>
       </c>
-      <c r="M128" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="N128" t="n">
-        <v>0</v>
-      </c>
-      <c r="O128" t="n">
-        <v>83</v>
-      </c>
+      <c r="M128" t="inlineStr"/>
+      <c r="N128" t="inlineStr"/>
+      <c r="O128" t="inlineStr"/>
       <c r="P128" t="n">
         <v>35</v>
       </c>
@@ -13753,15 +13379,9 @@
       <c r="L132" t="n">
         <v>0.16</v>
       </c>
-      <c r="M132" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="N132" t="n">
-        <v>-5.2</v>
-      </c>
-      <c r="O132" t="n">
-        <v>100</v>
-      </c>
+      <c r="M132" t="inlineStr"/>
+      <c r="N132" t="inlineStr"/>
+      <c r="O132" t="inlineStr"/>
       <c r="P132" t="n">
         <v>13.5</v>
       </c>
@@ -14239,15 +13859,9 @@
       <c r="L138" t="n">
         <v>1.71</v>
       </c>
-      <c r="M138" t="n">
-        <v>24.5</v>
-      </c>
-      <c r="N138" t="n">
-        <v>-1.8</v>
-      </c>
-      <c r="O138" t="n">
-        <v>100</v>
-      </c>
+      <c r="M138" t="inlineStr"/>
+      <c r="N138" t="inlineStr"/>
+      <c r="O138" t="inlineStr"/>
       <c r="P138" t="n">
         <v>140.6</v>
       </c>
@@ -14482,15 +14096,9 @@
       <c r="L141" t="n">
         <v>1.18</v>
       </c>
-      <c r="M141" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="N141" t="n">
-        <v>-0.8</v>
-      </c>
-      <c r="O141" t="n">
-        <v>100</v>
-      </c>
+      <c r="M141" t="inlineStr"/>
+      <c r="N141" t="inlineStr"/>
+      <c r="O141" t="inlineStr"/>
       <c r="P141" t="n">
         <v>90.59999999999999</v>
       </c>
@@ -14968,15 +14576,9 @@
       <c r="L147" t="n">
         <v>0.49</v>
       </c>
-      <c r="M147" t="n">
-        <v>16.2</v>
-      </c>
-      <c r="N147" t="n">
-        <v>-1.9</v>
-      </c>
-      <c r="O147" t="n">
-        <v>50</v>
-      </c>
+      <c r="M147" t="inlineStr"/>
+      <c r="N147" t="inlineStr"/>
+      <c r="O147" t="inlineStr"/>
       <c r="P147" t="n">
         <v>36.9</v>
       </c>
@@ -15697,15 +15299,9 @@
       <c r="L156" t="n">
         <v>0.29</v>
       </c>
-      <c r="M156" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="N156" t="n">
-        <v>-2.3</v>
-      </c>
-      <c r="O156" t="n">
-        <v>61</v>
-      </c>
+      <c r="M156" t="inlineStr"/>
+      <c r="N156" t="inlineStr"/>
+      <c r="O156" t="inlineStr"/>
       <c r="P156" t="n">
         <v>26</v>
       </c>
@@ -16021,9 +15617,15 @@
       <c r="L160" t="n">
         <v>-0.46</v>
       </c>
-      <c r="M160" t="inlineStr"/>
-      <c r="N160" t="inlineStr"/>
-      <c r="O160" t="inlineStr"/>
+      <c r="M160" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="N160" t="n">
+        <v>-14.7</v>
+      </c>
+      <c r="O160" t="n">
+        <v>-593</v>
+      </c>
       <c r="P160" t="n">
         <v>-18.1</v>
       </c>
@@ -16096,15 +15698,9 @@
       <c r="L161" t="n">
         <v>-0.38</v>
       </c>
-      <c r="M161" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="N161" t="n">
-        <v>-5</v>
-      </c>
-      <c r="O161" t="n">
-        <v>-46</v>
-      </c>
+      <c r="M161" t="inlineStr"/>
+      <c r="N161" t="inlineStr"/>
+      <c r="O161" t="inlineStr"/>
       <c r="P161" t="n">
         <v>-18.5</v>
       </c>
@@ -16580,15 +16176,9 @@
       <c r="L167" t="n">
         <v>1.03</v>
       </c>
-      <c r="M167" t="n">
-        <v>27.7</v>
-      </c>
-      <c r="N167" t="n">
-        <v>0</v>
-      </c>
-      <c r="O167" t="n">
-        <v>84</v>
-      </c>
+      <c r="M167" t="inlineStr"/>
+      <c r="N167" t="inlineStr"/>
+      <c r="O167" t="inlineStr"/>
       <c r="P167" t="n">
         <v>130.5</v>
       </c>
@@ -16904,9 +16494,15 @@
       <c r="L171" t="n">
         <v>1.61</v>
       </c>
-      <c r="M171" t="inlineStr"/>
-      <c r="N171" t="inlineStr"/>
-      <c r="O171" t="inlineStr"/>
+      <c r="M171" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="N171" t="n">
+        <v>-4.1</v>
+      </c>
+      <c r="O171" t="n">
+        <v>87</v>
+      </c>
       <c r="P171" t="n">
         <v>91.40000000000001</v>
       </c>
@@ -17222,15 +16818,9 @@
       <c r="L175" t="n">
         <v>0.88</v>
       </c>
-      <c r="M175" t="n">
-        <v>14.1</v>
-      </c>
-      <c r="N175" t="n">
-        <v>-3.8</v>
-      </c>
-      <c r="O175" t="n">
-        <v>81</v>
-      </c>
+      <c r="M175" t="inlineStr"/>
+      <c r="N175" t="inlineStr"/>
+      <c r="O175" t="inlineStr"/>
       <c r="P175" t="n">
         <v>54</v>
       </c>
@@ -18356,15 +17946,9 @@
       <c r="L189" t="n">
         <v>0.09</v>
       </c>
-      <c r="M189" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="N189" t="n">
-        <v>-2</v>
-      </c>
-      <c r="O189" t="n">
-        <v>25</v>
-      </c>
+      <c r="M189" t="inlineStr"/>
+      <c r="N189" t="inlineStr"/>
+      <c r="O189" t="inlineStr"/>
       <c r="P189" t="n">
         <v>6.5</v>
       </c>
@@ -18599,15 +18183,9 @@
       <c r="L192" t="n">
         <v>0.05</v>
       </c>
-      <c r="M192" t="n">
-        <v>11</v>
-      </c>
-      <c r="N192" t="n">
-        <v>0</v>
-      </c>
-      <c r="O192" t="n">
-        <v>9</v>
-      </c>
+      <c r="M192" t="inlineStr"/>
+      <c r="N192" t="inlineStr"/>
+      <c r="O192" t="inlineStr"/>
       <c r="P192" t="n">
         <v>4.2</v>
       </c>
@@ -19490,15 +19068,9 @@
       <c r="L203" t="n">
         <v>-0.31</v>
       </c>
-      <c r="M203" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="N203" t="n">
-        <v>-11.6</v>
-      </c>
-      <c r="O203" t="n">
-        <v>-111</v>
-      </c>
+      <c r="M203" t="inlineStr"/>
+      <c r="N203" t="inlineStr"/>
+      <c r="O203" t="inlineStr"/>
       <c r="P203" t="n">
         <v>-12.9</v>
       </c>
@@ -19733,15 +19305,9 @@
       <c r="L206" t="n">
         <v>-0.36</v>
       </c>
-      <c r="M206" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="N206" t="n">
-        <v>-8.5</v>
-      </c>
-      <c r="O206" t="n">
-        <v>-3098</v>
-      </c>
+      <c r="M206" t="inlineStr"/>
+      <c r="N206" t="inlineStr"/>
+      <c r="O206" t="inlineStr"/>
       <c r="P206" t="n">
         <v>-21.3</v>
       </c>
@@ -19893,15 +19459,9 @@
       <c r="L208" t="n">
         <v>-0.64</v>
       </c>
-      <c r="M208" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="N208" t="n">
-        <v>-12.7</v>
-      </c>
-      <c r="O208" t="n">
-        <v>-413</v>
-      </c>
+      <c r="M208" t="inlineStr"/>
+      <c r="N208" t="inlineStr"/>
+      <c r="O208" t="inlineStr"/>
       <c r="P208" t="n">
         <v>-40.3</v>
       </c>
@@ -20377,15 +19937,9 @@
       <c r="L214" t="n">
         <v>1.4</v>
       </c>
-      <c r="M214" t="n">
-        <v>14.2</v>
-      </c>
-      <c r="N214" t="n">
-        <v>-9.800000000000001</v>
-      </c>
-      <c r="O214" t="n">
-        <v>100</v>
-      </c>
+      <c r="M214" t="inlineStr"/>
+      <c r="N214" t="inlineStr"/>
+      <c r="O214" t="inlineStr"/>
       <c r="P214" t="n">
         <v>70</v>
       </c>
@@ -20701,15 +20255,9 @@
       <c r="L218" t="n">
         <v>0.63</v>
       </c>
-      <c r="M218" t="n">
-        <v>9.9</v>
-      </c>
-      <c r="N218" t="n">
-        <v>-3</v>
-      </c>
-      <c r="O218" t="n">
-        <v>100</v>
-      </c>
+      <c r="M218" t="inlineStr"/>
+      <c r="N218" t="inlineStr"/>
+      <c r="O218" t="inlineStr"/>
       <c r="P218" t="n">
         <v>45.9</v>
       </c>
@@ -21185,12 +20733,8 @@
       <c r="L224" t="n">
         <v>-0.61</v>
       </c>
-      <c r="M224" t="n">
-        <v>0</v>
-      </c>
-      <c r="N224" t="n">
-        <v>-16.5</v>
-      </c>
+      <c r="M224" t="inlineStr"/>
+      <c r="N224" t="inlineStr"/>
       <c r="O224" t="inlineStr"/>
       <c r="P224" t="n">
         <v>-27.8</v>
@@ -21420,15 +20964,9 @@
       <c r="L227" t="n">
         <v>0.86</v>
       </c>
-      <c r="M227" t="n">
-        <v>17.4</v>
-      </c>
-      <c r="N227" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O227" t="n">
-        <v>89</v>
-      </c>
+      <c r="M227" t="inlineStr"/>
+      <c r="N227" t="inlineStr"/>
+      <c r="O227" t="inlineStr"/>
       <c r="P227" t="n">
         <v>77.3</v>
       </c>
@@ -21582,15 +21120,9 @@
       <c r="L229" t="n">
         <v>0.53</v>
       </c>
-      <c r="M229" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="N229" t="n">
-        <v>-5.9</v>
-      </c>
-      <c r="O229" t="n">
-        <v>100</v>
-      </c>
+      <c r="M229" t="inlineStr"/>
+      <c r="N229" t="inlineStr"/>
+      <c r="O229" t="inlineStr"/>
       <c r="P229" t="n">
         <v>30.4</v>
       </c>
@@ -21825,15 +21357,9 @@
       <c r="L232" t="n">
         <v>0.38</v>
       </c>
-      <c r="M232" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="N232" t="n">
-        <v>-2.1</v>
-      </c>
-      <c r="O232" t="n">
-        <v>51</v>
-      </c>
+      <c r="M232" t="inlineStr"/>
+      <c r="N232" t="inlineStr"/>
+      <c r="O232" t="inlineStr"/>
       <c r="P232" t="n">
         <v>25.2</v>
       </c>
@@ -22068,15 +21594,9 @@
       <c r="L235" t="n">
         <v>0.06</v>
       </c>
-      <c r="M235" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="N235" t="n">
-        <v>-4.7</v>
-      </c>
-      <c r="O235" t="n">
-        <v>49</v>
-      </c>
+      <c r="M235" t="inlineStr"/>
+      <c r="N235" t="inlineStr"/>
+      <c r="O235" t="inlineStr"/>
       <c r="P235" t="n">
         <v>3.2</v>
       </c>
@@ -22716,15 +22236,9 @@
       <c r="L243" t="n">
         <v>0.42</v>
       </c>
-      <c r="M243" t="n">
-        <v>12.9</v>
-      </c>
-      <c r="N243" t="n">
-        <v>0</v>
-      </c>
-      <c r="O243" t="n">
-        <v>58</v>
-      </c>
+      <c r="M243" t="inlineStr"/>
+      <c r="N243" t="inlineStr"/>
+      <c r="O243" t="inlineStr"/>
       <c r="P243" t="n">
         <v>33.7</v>
       </c>
@@ -22797,15 +22311,9 @@
       <c r="L244" t="n">
         <v>0.5600000000000001</v>
       </c>
-      <c r="M244" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="N244" t="n">
-        <v>-7.6</v>
-      </c>
-      <c r="O244" t="n">
-        <v>83</v>
-      </c>
+      <c r="M244" t="inlineStr"/>
+      <c r="N244" t="inlineStr"/>
+      <c r="O244" t="inlineStr"/>
       <c r="P244" t="n">
         <v>30.3</v>
       </c>
@@ -23040,15 +22548,9 @@
       <c r="L247" t="n">
         <v>0.28</v>
       </c>
-      <c r="M247" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="N247" t="n">
-        <v>-11.2</v>
-      </c>
-      <c r="O247" t="n">
-        <v>88</v>
-      </c>
+      <c r="M247" t="inlineStr"/>
+      <c r="N247" t="inlineStr"/>
+      <c r="O247" t="inlineStr"/>
       <c r="P247" t="n">
         <v>19.5</v>
       </c>
@@ -23202,15 +22704,9 @@
       <c r="L249" t="n">
         <v>0.16</v>
       </c>
-      <c r="M249" t="n">
-        <v>6</v>
-      </c>
-      <c r="N249" t="n">
-        <v>-4.1</v>
-      </c>
-      <c r="O249" t="n">
-        <v>48</v>
-      </c>
+      <c r="M249" t="inlineStr"/>
+      <c r="N249" t="inlineStr"/>
+      <c r="O249" t="inlineStr"/>
       <c r="P249" t="n">
         <v>12.1</v>
       </c>
@@ -24166,15 +23662,9 @@
       <c r="L261" t="n">
         <v>0.24</v>
       </c>
-      <c r="M261" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="N261" t="n">
-        <v>-2.1</v>
-      </c>
-      <c r="O261" t="n">
-        <v>38</v>
-      </c>
+      <c r="M261" t="inlineStr"/>
+      <c r="N261" t="inlineStr"/>
+      <c r="O261" t="inlineStr"/>
       <c r="P261" t="n">
         <v>11.5</v>
       </c>
@@ -25057,15 +24547,9 @@
       <c r="L272" t="n">
         <v>0.93</v>
       </c>
-      <c r="M272" t="n">
-        <v>26.2</v>
-      </c>
-      <c r="N272" t="n">
-        <v>-1.2</v>
-      </c>
-      <c r="O272" t="n">
-        <v>96</v>
-      </c>
+      <c r="M272" t="inlineStr"/>
+      <c r="N272" t="inlineStr"/>
+      <c r="O272" t="inlineStr"/>
       <c r="P272" t="n">
         <v>145.4</v>
       </c>
@@ -25462,15 +24946,9 @@
       <c r="L277" t="n">
         <v>0.29</v>
       </c>
-      <c r="M277" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="N277" t="n">
-        <v>-3.4</v>
-      </c>
-      <c r="O277" t="n">
-        <v>45</v>
-      </c>
+      <c r="M277" t="inlineStr"/>
+      <c r="N277" t="inlineStr"/>
+      <c r="O277" t="inlineStr"/>
       <c r="P277" t="n">
         <v>16.6</v>
       </c>
@@ -25624,15 +25102,9 @@
       <c r="L279" t="n">
         <v>0.27</v>
       </c>
-      <c r="M279" t="n">
-        <v>23.5</v>
-      </c>
-      <c r="N279" t="n">
-        <v>0</v>
-      </c>
-      <c r="O279" t="n">
-        <v>10</v>
-      </c>
+      <c r="M279" t="inlineStr"/>
+      <c r="N279" t="inlineStr"/>
+      <c r="O279" t="inlineStr"/>
       <c r="P279" t="n">
         <v>10.2</v>
       </c>
@@ -26651,7 +26123,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>-2.9</v>
+        <v>-2.2</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -26693,7 +26165,7 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>-10.7</v>
+        <v>-9.6</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -26735,7 +26207,7 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>-13.9</v>
+        <v>-16.1</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -26777,7 +26249,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>-8.1</v>
+        <v>-12.6</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -26819,7 +26291,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>-4.5</v>
+        <v>-3.4</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -26861,7 +26333,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>-9.300000000000001</v>
+        <v>-11.9</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -26903,7 +26375,7 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>-3</v>
+        <v>-2.8</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -26945,7 +26417,7 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>-1.7</v>
+        <v>-1.5</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -26987,7 +26459,7 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>-2.4</v>
+        <v>-3.2</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -27029,7 +26501,7 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>-3.8</v>
+        <v>-4.6</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -27071,7 +26543,7 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>-2.9</v>
+        <v>-2.8</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -27155,7 +26627,7 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>-4.7</v>
+        <v>-4.8</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -27197,7 +26669,7 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>-7.3</v>
+        <v>-7.2</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -27239,7 +26711,7 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>-9.1</v>
+        <v>-9.300000000000001</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -27281,7 +26753,7 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>-3.3</v>
+        <v>-3.6</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -27323,7 +26795,7 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>-3.8</v>
+        <v>-3.5</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -27407,7 +26879,7 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>-11.8</v>
+        <v>-13.6</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -27482,12 +26954,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>13.4%</t>
+          <t>15.2%</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -27502,7 +26974,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>13.3%</t>
+          <t>13.9%</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -27512,12 +26984,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Power</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>13.0%</t>
+          <t>11.9%</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -27527,27 +26999,27 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>10.3%</t>
+          <t>6.7%</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>5.7%</t>
+          <t>6.3%</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -27557,12 +27029,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Power</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>6.0%</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -27597,7 +27069,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>10 stocks / 6 sectors</t>
+          <t>9 stocks / 6 sectors</t>
         </is>
       </c>
     </row>

--- a/reports/AEGIS_LATEST.xlsx
+++ b/reports/AEGIS_LATEST.xlsx
@@ -444,7 +444,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
     </row>
@@ -479,7 +479,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6">
@@ -489,7 +489,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7">
@@ -500,7 +500,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>3M (3 months)</t>
+          <t>2M (2 months)</t>
         </is>
       </c>
     </row>
@@ -512,7 +512,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-21</t>
         </is>
       </c>
     </row>
@@ -524,7 +524,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ICICIBANK (69)</t>
+          <t>ICICIBANK (68)</t>
         </is>
       </c>
     </row>
@@ -536,7 +536,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>DABUR (52)</t>
+          <t>NHPC (49)</t>
         </is>
       </c>
     </row>
@@ -548,7 +548,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>IOC, NHPC</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>NHPC</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -571,7 +571,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -664,7 +664,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Hold a 9-stock risk-managed portfolio</t>
+          <t>Hold a 11-stock risk-managed portfolio</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-18  /  2026-09-17</t>
+          <t>2026-09-21  /  2026-09-21</t>
         </is>
       </c>
     </row>
@@ -712,7 +712,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>3M (3 months)</t>
+          <t>2M (2 months)</t>
         </is>
       </c>
     </row>
@@ -760,7 +760,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-21</t>
         </is>
       </c>
     </row>
@@ -780,7 +780,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>66%</t>
+          <t>65%</t>
         </is>
       </c>
     </row>
@@ -792,7 +792,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>+2.6%</t>
+          <t>+2.3%</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Rs513,000</t>
+          <t>Rs511,500</t>
         </is>
       </c>
     </row>
@@ -816,7 +816,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Rs596,500</t>
+          <t>Rs602,000</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Rs460,500</t>
+          <t>Rs458,000</t>
         </is>
       </c>
     </row>
@@ -1310,7 +1310,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>3 months (63 trading days)</t>
+          <t>2 months (63 trading days)</t>
         </is>
       </c>
     </row>
@@ -1322,7 +1322,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>-6.3%</t>
+          <t>-5.8%</t>
         </is>
       </c>
     </row>
@@ -1361,7 +1361,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB10"/>
+  <dimension ref="A1:AB12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1513,11 +1513,11 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Risk/Vol +23 · Historical +20 · Sector +10 · Regime +9 · Trend/Tech +7 = 69</t>
+          <t>Risk/Vol +23 · Historical +20 · Regime +9 · Sector +9 · Trend/Tech +7 = 68</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -1534,13 +1534,13 @@
         <v>66</v>
       </c>
       <c r="G2" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="H2" t="n">
         <v>92</v>
       </c>
       <c r="I2" t="n">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="J2" t="n">
         <v>60</v>
@@ -1556,11 +1556,11 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>1347.6</v>
+        <v>1342.7</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>1314 - 1381</t>
+          <t>1310 - 1375</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -1578,30 +1578,30 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-0.7%)</t>
+          <t>Below 200-DMA (-1.0%)</t>
         </is>
       </c>
       <c r="S2" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>3 months (3M)</t>
+          <t>2 months (2M)</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="V2" t="n">
-        <v>37733</v>
+        <v>24169</v>
       </c>
       <c r="W2" t="n">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="X2" t="n">
-        <v>12.6</v>
+        <v>8.4</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
@@ -1615,12 +1615,12 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ICICIBANK: 69; PNB: 65, IDFCFIRSTB: 63, SBIN: 61</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ICICIBANK: 68; PNB: 66, IDFCFIRSTB: 62, SBIN: 60</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>Low-risk Financials holding (low vol) • below 200-dma (-0.7%) • outperforming Nifty • sector strength 100/100 • regime cautious (partial deploy) • 8 similar past recs: 75% positive, median +5.3%</t>
+          <t>Low-risk Financials holding (low vol) • below 200-dma (-1.0%) • sector strength 88/100 • regime cautious (partial deploy) • 8 similar past recs: 75% positive, median +5.3%</t>
         </is>
       </c>
     </row>
@@ -1631,11 +1631,11 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Risk/Vol +21 · Historical +15 · Regime +9 · Sector +9 · Trend/Tech +8 = 62</t>
+          <t>Risk/Vol +22 · Historical +15 · Sector +10 · Regime +9 · Trend/Tech +7 = 63</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -1652,13 +1652,13 @@
         <v>50</v>
       </c>
       <c r="G3" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="H3" t="n">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="I3" t="n">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="J3" t="n">
         <v>60</v>
@@ -1674,11 +1674,11 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>187.3</v>
+        <v>184.6</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>182 - 192</t>
+          <t>180 - 189</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -1696,30 +1696,30 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-3.0%)</t>
+          <t>Below 200-DMA (-4.4%)</t>
         </is>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>3 months (3M)</t>
+          <t>2 months (2M)</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="V3" t="n">
-        <v>29405</v>
+        <v>23819</v>
       </c>
       <c r="W3" t="n">
-        <v>157</v>
+        <v>129</v>
       </c>
       <c r="X3" t="n">
-        <v>9.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
@@ -1733,12 +1733,12 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — TATASTEEL: 62; COALINDIA: 60, HINDZINC: 50, SAIL: 49</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — TATASTEEL: 63; COALINDIA: 61, HINDZINC: 61, SAIL: 52</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>Low-risk Metal holding (low vol) • below 200-dma (-3.0%) • sector strength 88/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
+          <t>Low-risk Metal holding (low vol) • below 200-dma (-4.4%) • sector strength 100/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Historical +20 · Risk/Vol +16 · Sector +10 · Regime +9 · Trend/Tech +6 = 61</t>
+          <t>Risk/Vol +20 · Historical +15 · Sector +10 · Regime +9 · Trend/Tech +7 = 61</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Historical</t>
+          <t>Risk/Vol</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1767,13 +1767,13 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>65</v>
+        <v>51</v>
       </c>
       <c r="G4" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="H4" t="n">
-        <v>65</v>
+        <v>81</v>
       </c>
       <c r="I4" t="n">
         <v>100</v>
@@ -1783,20 +1783,20 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>SBIN</t>
+          <t>COALINDIA</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Metal</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>988.7</v>
+        <v>412</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>959 - 1019</t>
+          <t>401 - 423</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -1814,34 +1814,34 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-4.9%)</t>
+          <t>Below 200-DMA (-4.4%)</t>
         </is>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>57</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>3 months (3M)</t>
+          <t>2 months (2M)</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="V4" t="n">
-        <v>37571</v>
+        <v>36260</v>
       </c>
       <c r="W4" t="n">
-        <v>38</v>
+        <v>88</v>
       </c>
       <c r="X4" t="n">
-        <v>12.7</v>
+        <v>12.1</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>Historical + Risk/Vol strongest; chosen as a lowest-volatility Financials name under the sector cap</t>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Metal name under the sector cap</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1851,12 +1851,12 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — SBIN: 61; ICICIBANK: 69, PNB: 65, IDFCFIRSTB: 63. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — COALINDIA: 61; TATASTEEL: 63, HINDZINC: 61, SAIL: 52. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>Low-risk Financials holding (medium vol) • below 200-dma (-4.9%) • sector strength 100/100 • regime cautious (partial deploy) • 2 similar past recs: 100% positive, median +8.9%</t>
+          <t>Low-risk Metal holding (low vol) • below 200-dma (-4.4%) • sector strength 100/100 • regime cautious (partial deploy) • 3 similar past recs: 67% positive, median +0.8%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Risk/Vol +20 · Historical +15 · Regime +9 · Sector +9 · Trend/Tech +7 = 60</t>
+          <t>Historical +20 · Risk/Vol +16 · Regime +9 · Sector +9 · Trend/Tech +6 = 60</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Risk/Vol</t>
+          <t>Historical</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1885,13 +1885,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="G5" t="n">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="H5" t="n">
-        <v>81</v>
+        <v>65</v>
       </c>
       <c r="I5" t="n">
         <v>88</v>
@@ -1901,20 +1901,20 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>COALINDIA</t>
+          <t>SBIN</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Metal</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="M5" t="n">
-        <v>418</v>
+        <v>991.5</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>407 - 429</t>
+          <t>962 - 1021</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -1932,34 +1932,34 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-3.0%)</t>
+          <t>Below 200-DMA (-4.7%)</t>
         </is>
       </c>
       <c r="S5" t="n">
-        <v>61</v>
+        <v>31</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>3 months (3M)</t>
+          <t>2 months (2M)</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="V5" t="n">
-        <v>39710</v>
+        <v>17847</v>
       </c>
       <c r="W5" t="n">
-        <v>95</v>
+        <v>18</v>
       </c>
       <c r="X5" t="n">
-        <v>13.3</v>
+        <v>6.2</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Metal name under the sector cap</t>
+          <t>Historical + Risk/Vol strongest; chosen as a lowest-volatility Financials name under the sector cap</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1969,12 +1969,12 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — COALINDIA: 60; TATASTEEL: 62, HINDZINC: 50, SAIL: 49. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — SBIN: 60; ICICIBANK: 68, PNB: 66, IDFCFIRSTB: 62. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>Low-risk Metal holding (low vol) • below 200-dma (-3.0%) • sector strength 88/100 • regime cautious (partial deploy) • 3 similar past recs: 67% positive, median +0.8%</t>
+          <t>Low-risk Financials holding (medium vol) • below 200-dma (-4.7%) • sector strength 88/100 • regime cautious (partial deploy) • 2 similar past recs: 100% positive, median +8.9%</t>
         </is>
       </c>
     </row>
@@ -1985,11 +1985,11 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Risk/Vol +17 · Historical +16 · Regime +9 · Trend/Tech +8 · Sector +8 = 58</t>
+          <t>Risk/Vol +18 · Historical +16 · Regime +9 · Trend/Tech +8 · Sector +8 = 59</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -2009,7 +2009,7 @@
         <v>38</v>
       </c>
       <c r="H6" t="n">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="I6" t="n">
         <v>75</v>
@@ -2028,11 +2028,11 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>232.4</v>
+        <v>233.4</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>226 - 239</t>
+          <t>227 - 240</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -2046,34 +2046,34 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-9.5%)</t>
+          <t>Below 200-DMA (-9.1%)</t>
         </is>
       </c>
       <c r="S6" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>3 months (3M)</t>
+          <t>2 months (2M)</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="V6" t="n">
-        <v>33470</v>
+        <v>32675</v>
       </c>
       <c r="W6" t="n">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="X6" t="n">
-        <v>11.2</v>
+        <v>10.9</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -2087,27 +2087,27 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ONGC: 58; IOC: 54</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ONGC: 59; IOC: 53</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>Low-risk Energy holding (low vol) • below 200-dma (-9.5%) • sector strength 75/100 • regime cautious (partial deploy) • 2 similar past recs: 50% positive, median +9.0%</t>
+          <t>Low-risk Energy holding (low vol) • below 200-dma (-9.1%) • sector strength 75/100 • regime cautious (partial deploy) • 2 similar past recs: 50% positive, median +9.0%</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>ACCUMULATE</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Risk/Vol +24 · Historical +13 · Regime +9 · Trend/Tech +6 · Sector +4 = 56</t>
+          <t>Risk/Vol +24 · Historical +13 · Regime +9 · Trend/Tech +6 · Sector +2 = 54</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -2130,7 +2130,7 @@
         <v>96</v>
       </c>
       <c r="I7" t="n">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="J7" t="n">
         <v>60</v>
@@ -2146,7 +2146,7 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>266.2</v>
+        <v>266.3</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -2164,34 +2164,34 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-14.1%)</t>
+          <t>Below 200-DMA (-13.7%)</t>
         </is>
       </c>
       <c r="S7" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>3 months (3M)</t>
+          <t>2 months (2M)</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="V7" t="n">
-        <v>35138</v>
+        <v>35152</v>
       </c>
       <c r="W7" t="n">
         <v>132</v>
       </c>
       <c r="X7" t="n">
-        <v>11.7</v>
+        <v>11.8</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -2205,32 +2205,32 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ITC: 56; DABUR: 52</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ITC: 54; DABUR: 50</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>Low-risk FMCG holding (low vol) • below 200-dma (-14.1%) • sector strength 38/100 • regime cautious (partial deploy) • 9 similar past recs: 56% positive, median +0.3%</t>
+          <t>Low-risk FMCG holding (low vol) • below 200-dma (-13.7%) • sector strength 25/100 • regime cautious (partial deploy) • 9 similar past recs: 56% positive, median +0.3%</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>ACCUMULATE</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Risk/Vol +19 · Historical +15 · Regime +9 · Trend/Tech +7 · Sector +6 = 56</t>
+          <t>Historical +16 · Risk/Vol +12 · Regime +9 · Trend/Tech +8 · Sector +8 = 53</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Risk/Vol</t>
+          <t>Historical</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -2239,36 +2239,36 @@
         </is>
       </c>
       <c r="F8" t="n">
+        <v>52</v>
+      </c>
+      <c r="G8" t="n">
+        <v>38</v>
+      </c>
+      <c r="H8" t="n">
         <v>50</v>
       </c>
-      <c r="G8" t="n">
-        <v>36</v>
-      </c>
-      <c r="H8" t="n">
-        <v>77</v>
-      </c>
       <c r="I8" t="n">
-        <v>62</v>
+        <v>75</v>
       </c>
       <c r="J8" t="n">
         <v>60</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>BEL</t>
+          <t>IOC</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="M8" t="n">
-        <v>395.5</v>
+        <v>136.7</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>385 - 406</t>
+          <t>132 - 141</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -2282,38 +2282,38 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-5.5%)</t>
+          <t>Below 200-DMA (-8.6%)</t>
         </is>
       </c>
       <c r="S8" t="n">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>3 months (3M)</t>
+          <t>2 months (2M)</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="V8" t="n">
-        <v>31636</v>
+        <v>31856</v>
       </c>
       <c r="W8" t="n">
-        <v>80</v>
+        <v>233</v>
       </c>
       <c r="X8" t="n">
         <v>10.6</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Industrials name under the sector cap</t>
+          <t>Historical + Risk/Vol strongest; chosen as a lowest-volatility Energy name under the sector cap</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
@@ -2323,12 +2323,12 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>No same-sector peer in the universe.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — IOC: 53; ONGC: 59. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>Low-risk Industrials holding (low vol) • below 200-dma (-5.5%) • sector strength 62/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
+          <t>Low-risk Energy holding (medium vol) • below 200-dma (-8.6%) • sector strength 75/100 • regime cautious (partial deploy) • 2 similar past recs: 50% positive, median +8.1%</t>
         </is>
       </c>
     </row>
@@ -2339,11 +2339,11 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Risk/Vol +22 · Historical +15 · Regime +9 · Trend/Tech +7 · Sector +1 = 54</t>
+          <t>Risk/Vol +19 · Historical +15 · Regime +9 · Trend/Tech +5 · Sector +5 = 53</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2360,33 +2360,33 @@
         <v>50</v>
       </c>
       <c r="G9" t="n">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="H9" t="n">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="I9" t="n">
-        <v>12</v>
+        <v>50</v>
       </c>
       <c r="J9" t="n">
         <v>60</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>TATAPOWER</t>
+          <t>BEL</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Power</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="M9" t="n">
-        <v>369</v>
+        <v>394</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>359 - 379</t>
+          <t>383 - 405</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -2404,34 +2404,34 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-4.6%)</t>
+          <t>Below 200-DMA (-5.8%)</t>
         </is>
       </c>
       <c r="S9" t="n">
-        <v>69</v>
+        <v>37</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>3 months (3M)</t>
+          <t>2 months (2M)</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="V9" t="n">
-        <v>29520</v>
+        <v>26395</v>
       </c>
       <c r="W9" t="n">
-        <v>80</v>
+        <v>67</v>
       </c>
       <c r="X9" t="n">
-        <v>9.9</v>
+        <v>8.9</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Power name under the sector cap</t>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Industrials name under the sector cap</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
@@ -2441,12 +2441,12 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — TATAPOWER: 54; NHPC: 50, ADANIPOWER: 44, NLCINDIA: 30</t>
+          <t>No same-sector peer in the universe.</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>Low-risk Power holding (low vol) • below 200-dma (-4.6%) • sector strength 12/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
+          <t>Low-risk Industrials holding (low vol) • below 200-dma (-5.8%) • sector strength 50/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
         </is>
       </c>
     </row>
@@ -2461,7 +2461,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Risk/Vol +18 · Historical +15 · Regime +9 · Trend/Tech +6 · Sector +4 = 52</t>
+          <t>Risk/Vol +21 · Historical +15 · Regime +9 · Trend/Tech +6 · Sector +1 = 52</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2481,90 +2481,326 @@
         <v>31</v>
       </c>
       <c r="H10" t="n">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="I10" t="n">
-        <v>38</v>
+        <v>12</v>
       </c>
       <c r="J10" t="n">
         <v>60</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
+          <t>TATAPOWER</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>Power</t>
+        </is>
+      </c>
+      <c r="M10" t="n">
+        <v>366.1</v>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>356 - 376</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>63</v>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>Below 200-DMA (-5.3%)</t>
+        </is>
+      </c>
+      <c r="S10" t="n">
+        <v>64</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>2 months (2M)</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="V10" t="n">
+        <v>22698</v>
+      </c>
+      <c r="W10" t="n">
+        <v>62</v>
+      </c>
+      <c r="X10" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Power name under the sector cap</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>Fundamentals · Earnings · News · Flows</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — TATAPOWER: 52; NHPC: 49, ADANIPOWER: 44, NLCINDIA: 28</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>Low-risk Power holding (low vol) • below 200-dma (-5.3%) • sector strength 12/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>ACCUMULATE</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>50</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Risk/Vol +17 · Historical +15 · Regime +9 · Trend/Tech +7 · Sector +2 = 50</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Risk/Vol</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Sector</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>50</v>
+      </c>
+      <c r="G11" t="n">
+        <v>33</v>
+      </c>
+      <c r="H11" t="n">
+        <v>69</v>
+      </c>
+      <c r="I11" t="n">
+        <v>25</v>
+      </c>
+      <c r="J11" t="n">
+        <v>60</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
           <t>DABUR</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>FMCG</t>
         </is>
       </c>
-      <c r="M10" t="n">
-        <v>384.5</v>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>373 - 396</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
+      <c r="M11" t="n">
+        <v>389.5</v>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>378 - 401</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="P11" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="Q10" t="n">
-        <v>63</v>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>Below 200-DMA (-15.5%)</t>
-        </is>
-      </c>
-      <c r="S10" t="n">
+      <c r="Q11" t="n">
+        <v>62</v>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>Below 200-DMA (-14.1%)</t>
+        </is>
+      </c>
+      <c r="S11" t="n">
+        <v>55</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>2 months (2M)</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="V11" t="n">
+        <v>24152</v>
+      </c>
+      <c r="W11" t="n">
+        <v>62</v>
+      </c>
+      <c r="X11" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility FMCG name under the sector cap</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>Fundamentals · Earnings · News · Flows</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — DABUR: 50; ITC: 54. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>Low-risk FMCG holding (low vol) • below 200-dma (-14.1%) • sector strength 25/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>ACCUMULATE</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
         <v>49</v>
       </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>3 months (3M)</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>2026-10-17</t>
-        </is>
-      </c>
-      <c r="V10" t="n">
-        <v>24227</v>
-      </c>
-      <c r="W10" t="n">
-        <v>63</v>
-      </c>
-      <c r="X10" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility FMCG name under the sector cap</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Historical +17 · Risk/Vol +14 · Regime +9 · Trend/Tech +8 · Sector +1 = 49</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Historical</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Sector</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>57</v>
+      </c>
+      <c r="G12" t="n">
+        <v>40</v>
+      </c>
+      <c r="H12" t="n">
+        <v>58</v>
+      </c>
+      <c r="I12" t="n">
+        <v>12</v>
+      </c>
+      <c r="J12" t="n">
+        <v>60</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>NHPC</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>Power</t>
+        </is>
+      </c>
+      <c r="M12" t="n">
+        <v>75.90000000000001</v>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>74 - 78</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>65</v>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>Below 200-DMA (-2.4%)</t>
+        </is>
+      </c>
+      <c r="S12" t="n">
+        <v>48</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>2 months (2M)</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="V12" t="n">
+        <v>22247</v>
+      </c>
+      <c r="W12" t="n">
+        <v>293</v>
+      </c>
+      <c r="X12" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>Historical + Risk/Vol strongest; chosen as a lowest-volatility Power name under the sector cap</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
         <is>
           <t>Fundamentals · Earnings · News · Flows</t>
         </is>
       </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — DABUR: 52; ITC: 56. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>Low-risk FMCG holding (low vol) • below 200-dma (-15.5%) • sector strength 38/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — NHPC: 49; TATAPOWER: 52, ADANIPOWER: 44, NLCINDIA: 28. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>Low-risk Power holding (medium vol) • below 200-dma (-2.4%) • sector strength 12/100 • regime cautious (partial deploy) • 1 similar past recs: 100% positive, median +7.2%</t>
         </is>
       </c>
     </row>
@@ -3119,9 +3355,15 @@
       <c r="L2" t="n">
         <v>4.34</v>
       </c>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
+      <c r="M2" t="n">
+        <v>31.6</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" t="n">
+        <v>100</v>
+      </c>
       <c r="P2" t="n">
         <v>200.3</v>
       </c>
@@ -3194,9 +3436,15 @@
       <c r="L3" t="n">
         <v>2.12</v>
       </c>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
+      <c r="M3" t="n">
+        <v>38</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="n">
+        <v>81</v>
+      </c>
       <c r="P3" t="n">
         <v>194.1</v>
       </c>
@@ -3755,9 +4003,15 @@
       <c r="L10" t="n">
         <v>0.7</v>
       </c>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
+      <c r="M10" t="n">
+        <v>10</v>
+      </c>
+      <c r="N10" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O10" t="n">
+        <v>88</v>
+      </c>
       <c r="P10" t="n">
         <v>40.2</v>
       </c>
@@ -3830,9 +4084,15 @@
       <c r="L11" t="n">
         <v>0.49</v>
       </c>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr"/>
+      <c r="M11" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="N11" t="n">
+        <v>-9.9</v>
+      </c>
+      <c r="O11" t="n">
+        <v>92</v>
+      </c>
       <c r="P11" t="n">
         <v>29.9</v>
       </c>
@@ -4067,9 +4327,15 @@
       <c r="L14" t="n">
         <v>-0.14</v>
       </c>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr"/>
+      <c r="M14" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="N14" t="n">
+        <v>-3.9</v>
+      </c>
+      <c r="O14" t="n">
+        <v>-21</v>
+      </c>
       <c r="P14" t="n">
         <v>-4.7</v>
       </c>
@@ -4223,9 +4489,15 @@
       <c r="L16" t="n">
         <v>-0.53</v>
       </c>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
-      <c r="O16" t="inlineStr"/>
+      <c r="M16" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="N16" t="n">
+        <v>-9.1</v>
+      </c>
+      <c r="O16" t="n">
+        <v>-331</v>
+      </c>
       <c r="P16" t="n">
         <v>-30.7</v>
       </c>
@@ -4541,9 +4813,15 @@
       <c r="L20" t="n">
         <v>0.48</v>
       </c>
-      <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
-      <c r="O20" t="inlineStr"/>
+      <c r="M20" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="N20" t="n">
+        <v>-10.6</v>
+      </c>
+      <c r="O20" t="n">
+        <v>87</v>
+      </c>
       <c r="P20" t="n">
         <v>24.2</v>
       </c>
@@ -4940,9 +5218,15 @@
       <c r="L25" t="n">
         <v>-0.35</v>
       </c>
-      <c r="M25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
-      <c r="O25" t="inlineStr"/>
+      <c r="M25" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="N25" t="n">
+        <v>-14.8</v>
+      </c>
+      <c r="O25" t="n">
+        <v>-64</v>
+      </c>
       <c r="P25" t="n">
         <v>-25.7</v>
       </c>
@@ -5333,9 +5617,15 @@
       <c r="L30" t="n">
         <v>-1.18</v>
       </c>
-      <c r="M30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
-      <c r="O30" t="inlineStr"/>
+      <c r="M30" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N30" t="n">
+        <v>-16.1</v>
+      </c>
+      <c r="O30" t="n">
+        <v>-1221</v>
+      </c>
       <c r="P30" t="n">
         <v>-43.4</v>
       </c>
@@ -5408,9 +5698,15 @@
       <c r="L31" t="n">
         <v>-0.92</v>
       </c>
-      <c r="M31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
-      <c r="O31" t="inlineStr"/>
+      <c r="M31" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="N31" t="n">
+        <v>-19.4</v>
+      </c>
+      <c r="O31" t="n">
+        <v>-456</v>
+      </c>
       <c r="P31" t="n">
         <v>-47.7</v>
       </c>
@@ -5483,9 +5779,15 @@
       <c r="L32" t="n">
         <v>0.71</v>
       </c>
-      <c r="M32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
-      <c r="O32" t="inlineStr"/>
+      <c r="M32" t="n">
+        <v>16.3</v>
+      </c>
+      <c r="N32" t="n">
+        <v>-1.3</v>
+      </c>
+      <c r="O32" t="n">
+        <v>100</v>
+      </c>
       <c r="P32" t="n">
         <v>82.59999999999999</v>
       </c>
@@ -5558,9 +5860,15 @@
       <c r="L33" t="n">
         <v>1.08</v>
       </c>
-      <c r="M33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
-      <c r="O33" t="inlineStr"/>
+      <c r="M33" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="N33" t="n">
+        <v>-4.8</v>
+      </c>
+      <c r="O33" t="n">
+        <v>100</v>
+      </c>
       <c r="P33" t="n">
         <v>38.1</v>
       </c>
@@ -6281,9 +6589,15 @@
       <c r="L42" t="n">
         <v>-0.63</v>
       </c>
-      <c r="M42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
-      <c r="O42" t="inlineStr"/>
+      <c r="M42" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="N42" t="n">
+        <v>-16.5</v>
+      </c>
+      <c r="O42" t="n">
+        <v>-157</v>
+      </c>
       <c r="P42" t="n">
         <v>-29.3</v>
       </c>
@@ -6356,9 +6670,15 @@
       <c r="L43" t="n">
         <v>-0.76</v>
       </c>
-      <c r="M43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
-      <c r="O43" t="inlineStr"/>
+      <c r="M43" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="N43" t="n">
+        <v>-14.3</v>
+      </c>
+      <c r="O43" t="n">
+        <v>-642</v>
+      </c>
       <c r="P43" t="n">
         <v>-29.6</v>
       </c>
@@ -6674,9 +6994,15 @@
       <c r="L47" t="n">
         <v>3.05</v>
       </c>
-      <c r="M47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
-      <c r="O47" t="inlineStr"/>
+      <c r="M47" t="n">
+        <v>39.2</v>
+      </c>
+      <c r="N47" t="n">
+        <v>0</v>
+      </c>
+      <c r="O47" t="n">
+        <v>97</v>
+      </c>
       <c r="P47" t="n">
         <v>263.7</v>
       </c>
@@ -6911,9 +7237,15 @@
       <c r="L50" t="n">
         <v>0.5600000000000001</v>
       </c>
-      <c r="M50" t="inlineStr"/>
-      <c r="N50" t="inlineStr"/>
-      <c r="O50" t="inlineStr"/>
+      <c r="M50" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="N50" t="n">
+        <v>-2.1</v>
+      </c>
+      <c r="O50" t="n">
+        <v>55</v>
+      </c>
       <c r="P50" t="n">
         <v>36.5</v>
       </c>
@@ -6986,9 +7318,15 @@
       <c r="L51" t="n">
         <v>0.2</v>
       </c>
-      <c r="M51" t="inlineStr"/>
-      <c r="N51" t="inlineStr"/>
-      <c r="O51" t="inlineStr"/>
+      <c r="M51" t="n">
+        <v>3</v>
+      </c>
+      <c r="N51" t="n">
+        <v>-10.7</v>
+      </c>
+      <c r="O51" t="n">
+        <v>68</v>
+      </c>
       <c r="P51" t="n">
         <v>8.4</v>
       </c>
@@ -7061,9 +7399,15 @@
       <c r="L52" t="n">
         <v>0.08</v>
       </c>
-      <c r="M52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
-      <c r="O52" t="inlineStr"/>
+      <c r="M52" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="N52" t="n">
+        <v>-10.4</v>
+      </c>
+      <c r="O52" t="n">
+        <v>60</v>
+      </c>
       <c r="P52" t="n">
         <v>5.7</v>
       </c>
@@ -7136,9 +7480,15 @@
       <c r="L53" t="n">
         <v>-0.05</v>
       </c>
-      <c r="M53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
-      <c r="O53" t="inlineStr"/>
+      <c r="M53" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="N53" t="n">
+        <v>-8.199999999999999</v>
+      </c>
+      <c r="O53" t="n">
+        <v>-38</v>
+      </c>
       <c r="P53" t="n">
         <v>-3.8</v>
       </c>
@@ -7211,9 +7561,15 @@
       <c r="L54" t="n">
         <v>-0.09</v>
       </c>
-      <c r="M54" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
-      <c r="O54" t="inlineStr"/>
+      <c r="M54" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="N54" t="n">
+        <v>-6.8</v>
+      </c>
+      <c r="O54" t="n">
+        <v>-26</v>
+      </c>
       <c r="P54" t="n">
         <v>-4.4</v>
       </c>
@@ -7286,9 +7642,15 @@
       <c r="L55" t="n">
         <v>-0.43</v>
       </c>
-      <c r="M55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
-      <c r="O55" t="inlineStr"/>
+      <c r="M55" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="N55" t="n">
+        <v>-18.1</v>
+      </c>
+      <c r="O55" t="n">
+        <v>-243</v>
+      </c>
       <c r="P55" t="n">
         <v>-31</v>
       </c>
@@ -8086,9 +8448,15 @@
       <c r="L65" t="n">
         <v>1.25</v>
       </c>
-      <c r="M65" t="inlineStr"/>
-      <c r="N65" t="inlineStr"/>
-      <c r="O65" t="inlineStr"/>
+      <c r="M65" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="N65" t="n">
+        <v>0</v>
+      </c>
+      <c r="O65" t="n">
+        <v>66</v>
+      </c>
       <c r="P65" t="n">
         <v>67.2</v>
       </c>
@@ -8161,9 +8529,15 @@
       <c r="L66" t="n">
         <v>0.77</v>
       </c>
-      <c r="M66" t="inlineStr"/>
-      <c r="N66" t="inlineStr"/>
-      <c r="O66" t="inlineStr"/>
+      <c r="M66" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="N66" t="n">
+        <v>0</v>
+      </c>
+      <c r="O66" t="n">
+        <v>49</v>
+      </c>
       <c r="P66" t="n">
         <v>63.2</v>
       </c>
@@ -8479,9 +8853,15 @@
       <c r="L70" t="n">
         <v>0.43</v>
       </c>
-      <c r="M70" t="inlineStr"/>
-      <c r="N70" t="inlineStr"/>
-      <c r="O70" t="inlineStr"/>
+      <c r="M70" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="N70" t="n">
+        <v>-1.4</v>
+      </c>
+      <c r="O70" t="n">
+        <v>61</v>
+      </c>
       <c r="P70" t="n">
         <v>21.9</v>
       </c>
@@ -8716,9 +9096,15 @@
       <c r="L73" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="M73" t="inlineStr"/>
-      <c r="N73" t="inlineStr"/>
-      <c r="O73" t="inlineStr"/>
+      <c r="M73" t="n">
+        <v>7</v>
+      </c>
+      <c r="N73" t="n">
+        <v>-2.3</v>
+      </c>
+      <c r="O73" t="n">
+        <v>11</v>
+      </c>
       <c r="P73" t="n">
         <v>3.1</v>
       </c>
@@ -8791,9 +9177,15 @@
       <c r="L74" t="n">
         <v>-0.04</v>
       </c>
-      <c r="M74" t="inlineStr"/>
-      <c r="N74" t="inlineStr"/>
-      <c r="O74" t="inlineStr"/>
+      <c r="M74" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="N74" t="n">
+        <v>-4.6</v>
+      </c>
+      <c r="O74" t="n">
+        <v>-4</v>
+      </c>
       <c r="P74" t="n">
         <v>-2</v>
       </c>
@@ -8866,9 +9258,15 @@
       <c r="L75" t="n">
         <v>-0.06</v>
       </c>
-      <c r="M75" t="inlineStr"/>
-      <c r="N75" t="inlineStr"/>
-      <c r="O75" t="inlineStr"/>
+      <c r="M75" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="N75" t="n">
+        <v>-2.6</v>
+      </c>
+      <c r="O75" t="n">
+        <v>-12</v>
+      </c>
       <c r="P75" t="n">
         <v>-6.1</v>
       </c>
@@ -9184,9 +9582,15 @@
       <c r="L79" t="n">
         <v>3.16</v>
       </c>
-      <c r="M79" t="inlineStr"/>
-      <c r="N79" t="inlineStr"/>
-      <c r="O79" t="inlineStr"/>
+      <c r="M79" t="n">
+        <v>49.7</v>
+      </c>
+      <c r="N79" t="n">
+        <v>-3</v>
+      </c>
+      <c r="O79" t="n">
+        <v>100</v>
+      </c>
       <c r="P79" t="n">
         <v>402.7</v>
       </c>
@@ -9502,9 +9906,15 @@
       <c r="L83" t="n">
         <v>0.21</v>
       </c>
-      <c r="M83" t="inlineStr"/>
-      <c r="N83" t="inlineStr"/>
-      <c r="O83" t="inlineStr"/>
+      <c r="M83" t="n">
+        <v>8</v>
+      </c>
+      <c r="N83" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="O83" t="n">
+        <v>36</v>
+      </c>
       <c r="P83" t="n">
         <v>12.2</v>
       </c>
@@ -9577,9 +9987,15 @@
       <c r="L84" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="M84" t="inlineStr"/>
-      <c r="N84" t="inlineStr"/>
-      <c r="O84" t="inlineStr"/>
+      <c r="M84" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="N84" t="n">
+        <v>-2.1</v>
+      </c>
+      <c r="O84" t="n">
+        <v>23</v>
+      </c>
       <c r="P84" t="n">
         <v>4.3</v>
       </c>
@@ -9814,9 +10230,15 @@
       <c r="L87" t="n">
         <v>-0.14</v>
       </c>
-      <c r="M87" t="inlineStr"/>
-      <c r="N87" t="inlineStr"/>
-      <c r="O87" t="inlineStr"/>
+      <c r="M87" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="N87" t="n">
+        <v>-3.2</v>
+      </c>
+      <c r="O87" t="n">
+        <v>-49</v>
+      </c>
       <c r="P87" t="n">
         <v>-9.300000000000001</v>
       </c>
@@ -10130,8 +10552,12 @@
       <c r="L91" t="n">
         <v>-0.59</v>
       </c>
-      <c r="M91" t="inlineStr"/>
-      <c r="N91" t="inlineStr"/>
+      <c r="M91" t="n">
+        <v>0</v>
+      </c>
+      <c r="N91" t="n">
+        <v>-12</v>
+      </c>
       <c r="O91" t="inlineStr"/>
       <c r="P91" t="n">
         <v>-40.1</v>
@@ -10286,9 +10712,15 @@
       <c r="L93" t="n">
         <v>1.23</v>
       </c>
-      <c r="M93" t="inlineStr"/>
-      <c r="N93" t="inlineStr"/>
-      <c r="O93" t="inlineStr"/>
+      <c r="M93" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="N93" t="n">
+        <v>-2.9</v>
+      </c>
+      <c r="O93" t="n">
+        <v>100</v>
+      </c>
       <c r="P93" t="n">
         <v>91.7</v>
       </c>
@@ -10766,9 +11198,15 @@
       <c r="L99" t="n">
         <v>0.28</v>
       </c>
-      <c r="M99" t="inlineStr"/>
-      <c r="N99" t="inlineStr"/>
-      <c r="O99" t="inlineStr"/>
+      <c r="M99" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="N99" t="n">
+        <v>-5.6</v>
+      </c>
+      <c r="O99" t="n">
+        <v>58</v>
+      </c>
       <c r="P99" t="n">
         <v>11.1</v>
       </c>
@@ -11327,9 +11765,15 @@
       <c r="L106" t="n">
         <v>-1.05</v>
       </c>
-      <c r="M106" t="inlineStr"/>
-      <c r="N106" t="inlineStr"/>
-      <c r="O106" t="inlineStr"/>
+      <c r="M106" t="n">
+        <v>1</v>
+      </c>
+      <c r="N106" t="n">
+        <v>-17.4</v>
+      </c>
+      <c r="O106" t="n">
+        <v>-1645</v>
+      </c>
       <c r="P106" t="n">
         <v>-51.4</v>
       </c>
@@ -11402,9 +11846,15 @@
       <c r="L107" t="n">
         <v>1.65</v>
       </c>
-      <c r="M107" t="inlineStr"/>
-      <c r="N107" t="inlineStr"/>
-      <c r="O107" t="inlineStr"/>
+      <c r="M107" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="N107" t="n">
+        <v>-2.9</v>
+      </c>
+      <c r="O107" t="n">
+        <v>99</v>
+      </c>
       <c r="P107" t="n">
         <v>138.8</v>
       </c>
@@ -11558,9 +12008,15 @@
       <c r="L109" t="n">
         <v>1.48</v>
       </c>
-      <c r="M109" t="inlineStr"/>
-      <c r="N109" t="inlineStr"/>
-      <c r="O109" t="inlineStr"/>
+      <c r="M109" t="n">
+        <v>22</v>
+      </c>
+      <c r="N109" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="O109" t="n">
+        <v>99</v>
+      </c>
       <c r="P109" t="n">
         <v>120.4</v>
       </c>
@@ -11795,9 +12251,15 @@
       <c r="L112" t="n">
         <v>1.4</v>
       </c>
-      <c r="M112" t="inlineStr"/>
-      <c r="N112" t="inlineStr"/>
-      <c r="O112" t="inlineStr"/>
+      <c r="M112" t="n">
+        <v>16.3</v>
+      </c>
+      <c r="N112" t="n">
+        <v>-1.8</v>
+      </c>
+      <c r="O112" t="n">
+        <v>100</v>
+      </c>
       <c r="P112" t="n">
         <v>82.7</v>
       </c>
@@ -12437,9 +12899,15 @@
       <c r="L120" t="n">
         <v>0.15</v>
       </c>
-      <c r="M120" t="inlineStr"/>
-      <c r="N120" t="inlineStr"/>
-      <c r="O120" t="inlineStr"/>
+      <c r="M120" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="N120" t="n">
+        <v>-3.2</v>
+      </c>
+      <c r="O120" t="n">
+        <v>56</v>
+      </c>
       <c r="P120" t="n">
         <v>10.3</v>
       </c>
@@ -12674,9 +13142,15 @@
       <c r="L123" t="n">
         <v>2.63</v>
       </c>
-      <c r="M123" t="inlineStr"/>
-      <c r="N123" t="inlineStr"/>
-      <c r="O123" t="inlineStr"/>
+      <c r="M123" t="n">
+        <v>28.8</v>
+      </c>
+      <c r="N123" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="O123" t="n">
+        <v>86</v>
+      </c>
       <c r="P123" t="n">
         <v>143.4</v>
       </c>
@@ -12749,9 +13223,15 @@
       <c r="L124" t="n">
         <v>0.86</v>
       </c>
-      <c r="M124" t="inlineStr"/>
-      <c r="N124" t="inlineStr"/>
-      <c r="O124" t="inlineStr"/>
+      <c r="M124" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0</v>
+      </c>
+      <c r="O124" t="n">
+        <v>90</v>
+      </c>
       <c r="P124" t="n">
         <v>62</v>
       </c>
@@ -12824,9 +13304,15 @@
       <c r="L125" t="n">
         <v>0.89</v>
       </c>
-      <c r="M125" t="inlineStr"/>
-      <c r="N125" t="inlineStr"/>
-      <c r="O125" t="inlineStr"/>
+      <c r="M125" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="N125" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="O125" t="n">
+        <v>92</v>
+      </c>
       <c r="P125" t="n">
         <v>61.1</v>
       </c>
@@ -13061,9 +13547,15 @@
       <c r="L128" t="n">
         <v>0.37</v>
       </c>
-      <c r="M128" t="inlineStr"/>
-      <c r="N128" t="inlineStr"/>
-      <c r="O128" t="inlineStr"/>
+      <c r="M128" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0</v>
+      </c>
+      <c r="O128" t="n">
+        <v>83</v>
+      </c>
       <c r="P128" t="n">
         <v>35</v>
       </c>
@@ -13379,9 +13871,15 @@
       <c r="L132" t="n">
         <v>0.16</v>
       </c>
-      <c r="M132" t="inlineStr"/>
-      <c r="N132" t="inlineStr"/>
-      <c r="O132" t="inlineStr"/>
+      <c r="M132" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="N132" t="n">
+        <v>-5.2</v>
+      </c>
+      <c r="O132" t="n">
+        <v>100</v>
+      </c>
       <c r="P132" t="n">
         <v>13.5</v>
       </c>
@@ -13859,9 +14357,15 @@
       <c r="L138" t="n">
         <v>1.71</v>
       </c>
-      <c r="M138" t="inlineStr"/>
-      <c r="N138" t="inlineStr"/>
-      <c r="O138" t="inlineStr"/>
+      <c r="M138" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="N138" t="n">
+        <v>-1.8</v>
+      </c>
+      <c r="O138" t="n">
+        <v>100</v>
+      </c>
       <c r="P138" t="n">
         <v>140.6</v>
       </c>
@@ -14096,9 +14600,15 @@
       <c r="L141" t="n">
         <v>1.18</v>
       </c>
-      <c r="M141" t="inlineStr"/>
-      <c r="N141" t="inlineStr"/>
-      <c r="O141" t="inlineStr"/>
+      <c r="M141" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="N141" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="O141" t="n">
+        <v>100</v>
+      </c>
       <c r="P141" t="n">
         <v>90.59999999999999</v>
       </c>
@@ -14576,9 +15086,15 @@
       <c r="L147" t="n">
         <v>0.49</v>
       </c>
-      <c r="M147" t="inlineStr"/>
-      <c r="N147" t="inlineStr"/>
-      <c r="O147" t="inlineStr"/>
+      <c r="M147" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="N147" t="n">
+        <v>-1.9</v>
+      </c>
+      <c r="O147" t="n">
+        <v>50</v>
+      </c>
       <c r="P147" t="n">
         <v>36.9</v>
       </c>
@@ -15299,9 +15815,15 @@
       <c r="L156" t="n">
         <v>0.29</v>
       </c>
-      <c r="M156" t="inlineStr"/>
-      <c r="N156" t="inlineStr"/>
-      <c r="O156" t="inlineStr"/>
+      <c r="M156" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="N156" t="n">
+        <v>-2.3</v>
+      </c>
+      <c r="O156" t="n">
+        <v>61</v>
+      </c>
       <c r="P156" t="n">
         <v>26</v>
       </c>
@@ -15617,15 +16139,9 @@
       <c r="L160" t="n">
         <v>-0.46</v>
       </c>
-      <c r="M160" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="N160" t="n">
-        <v>-14.7</v>
-      </c>
-      <c r="O160" t="n">
-        <v>-593</v>
-      </c>
+      <c r="M160" t="inlineStr"/>
+      <c r="N160" t="inlineStr"/>
+      <c r="O160" t="inlineStr"/>
       <c r="P160" t="n">
         <v>-18.1</v>
       </c>
@@ -15698,9 +16214,15 @@
       <c r="L161" t="n">
         <v>-0.38</v>
       </c>
-      <c r="M161" t="inlineStr"/>
-      <c r="N161" t="inlineStr"/>
-      <c r="O161" t="inlineStr"/>
+      <c r="M161" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="N161" t="n">
+        <v>-5</v>
+      </c>
+      <c r="O161" t="n">
+        <v>-46</v>
+      </c>
       <c r="P161" t="n">
         <v>-18.5</v>
       </c>
@@ -16176,9 +16698,15 @@
       <c r="L167" t="n">
         <v>1.03</v>
       </c>
-      <c r="M167" t="inlineStr"/>
-      <c r="N167" t="inlineStr"/>
-      <c r="O167" t="inlineStr"/>
+      <c r="M167" t="n">
+        <v>27.7</v>
+      </c>
+      <c r="N167" t="n">
+        <v>0</v>
+      </c>
+      <c r="O167" t="n">
+        <v>84</v>
+      </c>
       <c r="P167" t="n">
         <v>130.5</v>
       </c>
@@ -16494,15 +17022,9 @@
       <c r="L171" t="n">
         <v>1.61</v>
       </c>
-      <c r="M171" t="n">
-        <v>20.3</v>
-      </c>
-      <c r="N171" t="n">
-        <v>-4.1</v>
-      </c>
-      <c r="O171" t="n">
-        <v>87</v>
-      </c>
+      <c r="M171" t="inlineStr"/>
+      <c r="N171" t="inlineStr"/>
+      <c r="O171" t="inlineStr"/>
       <c r="P171" t="n">
         <v>91.40000000000001</v>
       </c>
@@ -16818,9 +17340,15 @@
       <c r="L175" t="n">
         <v>0.88</v>
       </c>
-      <c r="M175" t="inlineStr"/>
-      <c r="N175" t="inlineStr"/>
-      <c r="O175" t="inlineStr"/>
+      <c r="M175" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="N175" t="n">
+        <v>-3.8</v>
+      </c>
+      <c r="O175" t="n">
+        <v>81</v>
+      </c>
       <c r="P175" t="n">
         <v>54</v>
       </c>
@@ -17946,9 +18474,15 @@
       <c r="L189" t="n">
         <v>0.09</v>
       </c>
-      <c r="M189" t="inlineStr"/>
-      <c r="N189" t="inlineStr"/>
-      <c r="O189" t="inlineStr"/>
+      <c r="M189" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="N189" t="n">
+        <v>-2</v>
+      </c>
+      <c r="O189" t="n">
+        <v>25</v>
+      </c>
       <c r="P189" t="n">
         <v>6.5</v>
       </c>
@@ -18183,9 +18717,15 @@
       <c r="L192" t="n">
         <v>0.05</v>
       </c>
-      <c r="M192" t="inlineStr"/>
-      <c r="N192" t="inlineStr"/>
-      <c r="O192" t="inlineStr"/>
+      <c r="M192" t="n">
+        <v>11</v>
+      </c>
+      <c r="N192" t="n">
+        <v>0</v>
+      </c>
+      <c r="O192" t="n">
+        <v>9</v>
+      </c>
       <c r="P192" t="n">
         <v>4.2</v>
       </c>
@@ -19068,9 +19608,15 @@
       <c r="L203" t="n">
         <v>-0.31</v>
       </c>
-      <c r="M203" t="inlineStr"/>
-      <c r="N203" t="inlineStr"/>
-      <c r="O203" t="inlineStr"/>
+      <c r="M203" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="N203" t="n">
+        <v>-11.6</v>
+      </c>
+      <c r="O203" t="n">
+        <v>-111</v>
+      </c>
       <c r="P203" t="n">
         <v>-12.9</v>
       </c>
@@ -19305,9 +19851,15 @@
       <c r="L206" t="n">
         <v>-0.36</v>
       </c>
-      <c r="M206" t="inlineStr"/>
-      <c r="N206" t="inlineStr"/>
-      <c r="O206" t="inlineStr"/>
+      <c r="M206" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="N206" t="n">
+        <v>-8.5</v>
+      </c>
+      <c r="O206" t="n">
+        <v>-3098</v>
+      </c>
       <c r="P206" t="n">
         <v>-21.3</v>
       </c>
@@ -19459,9 +20011,15 @@
       <c r="L208" t="n">
         <v>-0.64</v>
       </c>
-      <c r="M208" t="inlineStr"/>
-      <c r="N208" t="inlineStr"/>
-      <c r="O208" t="inlineStr"/>
+      <c r="M208" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="N208" t="n">
+        <v>-12.7</v>
+      </c>
+      <c r="O208" t="n">
+        <v>-413</v>
+      </c>
       <c r="P208" t="n">
         <v>-40.3</v>
       </c>
@@ -19937,9 +20495,15 @@
       <c r="L214" t="n">
         <v>1.4</v>
       </c>
-      <c r="M214" t="inlineStr"/>
-      <c r="N214" t="inlineStr"/>
-      <c r="O214" t="inlineStr"/>
+      <c r="M214" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="N214" t="n">
+        <v>-9.800000000000001</v>
+      </c>
+      <c r="O214" t="n">
+        <v>100</v>
+      </c>
       <c r="P214" t="n">
         <v>70</v>
       </c>
@@ -20255,9 +20819,15 @@
       <c r="L218" t="n">
         <v>0.63</v>
       </c>
-      <c r="M218" t="inlineStr"/>
-      <c r="N218" t="inlineStr"/>
-      <c r="O218" t="inlineStr"/>
+      <c r="M218" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="N218" t="n">
+        <v>-3</v>
+      </c>
+      <c r="O218" t="n">
+        <v>100</v>
+      </c>
       <c r="P218" t="n">
         <v>45.9</v>
       </c>
@@ -20733,8 +21303,12 @@
       <c r="L224" t="n">
         <v>-0.61</v>
       </c>
-      <c r="M224" t="inlineStr"/>
-      <c r="N224" t="inlineStr"/>
+      <c r="M224" t="n">
+        <v>0</v>
+      </c>
+      <c r="N224" t="n">
+        <v>-16.5</v>
+      </c>
       <c r="O224" t="inlineStr"/>
       <c r="P224" t="n">
         <v>-27.8</v>
@@ -20964,9 +21538,15 @@
       <c r="L227" t="n">
         <v>0.86</v>
       </c>
-      <c r="M227" t="inlineStr"/>
-      <c r="N227" t="inlineStr"/>
-      <c r="O227" t="inlineStr"/>
+      <c r="M227" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="N227" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O227" t="n">
+        <v>89</v>
+      </c>
       <c r="P227" t="n">
         <v>77.3</v>
       </c>
@@ -21120,9 +21700,15 @@
       <c r="L229" t="n">
         <v>0.53</v>
       </c>
-      <c r="M229" t="inlineStr"/>
-      <c r="N229" t="inlineStr"/>
-      <c r="O229" t="inlineStr"/>
+      <c r="M229" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="N229" t="n">
+        <v>-5.9</v>
+      </c>
+      <c r="O229" t="n">
+        <v>100</v>
+      </c>
       <c r="P229" t="n">
         <v>30.4</v>
       </c>
@@ -21357,9 +21943,15 @@
       <c r="L232" t="n">
         <v>0.38</v>
       </c>
-      <c r="M232" t="inlineStr"/>
-      <c r="N232" t="inlineStr"/>
-      <c r="O232" t="inlineStr"/>
+      <c r="M232" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="N232" t="n">
+        <v>-2.1</v>
+      </c>
+      <c r="O232" t="n">
+        <v>51</v>
+      </c>
       <c r="P232" t="n">
         <v>25.2</v>
       </c>
@@ -21594,9 +22186,15 @@
       <c r="L235" t="n">
         <v>0.06</v>
       </c>
-      <c r="M235" t="inlineStr"/>
-      <c r="N235" t="inlineStr"/>
-      <c r="O235" t="inlineStr"/>
+      <c r="M235" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="N235" t="n">
+        <v>-4.7</v>
+      </c>
+      <c r="O235" t="n">
+        <v>49</v>
+      </c>
       <c r="P235" t="n">
         <v>3.2</v>
       </c>
@@ -22236,9 +22834,15 @@
       <c r="L243" t="n">
         <v>0.42</v>
       </c>
-      <c r="M243" t="inlineStr"/>
-      <c r="N243" t="inlineStr"/>
-      <c r="O243" t="inlineStr"/>
+      <c r="M243" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="N243" t="n">
+        <v>0</v>
+      </c>
+      <c r="O243" t="n">
+        <v>58</v>
+      </c>
       <c r="P243" t="n">
         <v>33.7</v>
       </c>
@@ -22311,9 +22915,15 @@
       <c r="L244" t="n">
         <v>0.5600000000000001</v>
       </c>
-      <c r="M244" t="inlineStr"/>
-      <c r="N244" t="inlineStr"/>
-      <c r="O244" t="inlineStr"/>
+      <c r="M244" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="N244" t="n">
+        <v>-7.6</v>
+      </c>
+      <c r="O244" t="n">
+        <v>83</v>
+      </c>
       <c r="P244" t="n">
         <v>30.3</v>
       </c>
@@ -22548,9 +23158,15 @@
       <c r="L247" t="n">
         <v>0.28</v>
       </c>
-      <c r="M247" t="inlineStr"/>
-      <c r="N247" t="inlineStr"/>
-      <c r="O247" t="inlineStr"/>
+      <c r="M247" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="N247" t="n">
+        <v>-11.2</v>
+      </c>
+      <c r="O247" t="n">
+        <v>88</v>
+      </c>
       <c r="P247" t="n">
         <v>19.5</v>
       </c>
@@ -22704,9 +23320,15 @@
       <c r="L249" t="n">
         <v>0.16</v>
       </c>
-      <c r="M249" t="inlineStr"/>
-      <c r="N249" t="inlineStr"/>
-      <c r="O249" t="inlineStr"/>
+      <c r="M249" t="n">
+        <v>6</v>
+      </c>
+      <c r="N249" t="n">
+        <v>-4.1</v>
+      </c>
+      <c r="O249" t="n">
+        <v>48</v>
+      </c>
       <c r="P249" t="n">
         <v>12.1</v>
       </c>
@@ -23662,9 +24284,15 @@
       <c r="L261" t="n">
         <v>0.24</v>
       </c>
-      <c r="M261" t="inlineStr"/>
-      <c r="N261" t="inlineStr"/>
-      <c r="O261" t="inlineStr"/>
+      <c r="M261" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="N261" t="n">
+        <v>-2.1</v>
+      </c>
+      <c r="O261" t="n">
+        <v>38</v>
+      </c>
       <c r="P261" t="n">
         <v>11.5</v>
       </c>
@@ -24547,9 +25175,15 @@
       <c r="L272" t="n">
         <v>0.93</v>
       </c>
-      <c r="M272" t="inlineStr"/>
-      <c r="N272" t="inlineStr"/>
-      <c r="O272" t="inlineStr"/>
+      <c r="M272" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="N272" t="n">
+        <v>-1.2</v>
+      </c>
+      <c r="O272" t="n">
+        <v>96</v>
+      </c>
       <c r="P272" t="n">
         <v>145.4</v>
       </c>
@@ -24946,9 +25580,15 @@
       <c r="L277" t="n">
         <v>0.29</v>
       </c>
-      <c r="M277" t="inlineStr"/>
-      <c r="N277" t="inlineStr"/>
-      <c r="O277" t="inlineStr"/>
+      <c r="M277" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="N277" t="n">
+        <v>-3.4</v>
+      </c>
+      <c r="O277" t="n">
+        <v>45</v>
+      </c>
       <c r="P277" t="n">
         <v>16.6</v>
       </c>
@@ -25102,9 +25742,15 @@
       <c r="L279" t="n">
         <v>0.27</v>
       </c>
-      <c r="M279" t="inlineStr"/>
-      <c r="N279" t="inlineStr"/>
-      <c r="O279" t="inlineStr"/>
+      <c r="M279" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="N279" t="n">
+        <v>0</v>
+      </c>
+      <c r="O279" t="n">
+        <v>10</v>
+      </c>
       <c r="P279" t="n">
         <v>10.2</v>
       </c>
@@ -25838,13 +26484,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D4" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="E4" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F4" t="n">
         <v>-6.7</v>
@@ -25854,7 +26500,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -25871,13 +26517,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D5" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="E5" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F5" t="n">
         <v>-8.4</v>
@@ -25890,7 +26536,11 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>&lt;-- engine pick (regime)</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -25904,30 +26554,26 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D6" t="n">
         <v>2.6</v>
       </c>
       <c r="E6" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F6" t="n">
         <v>-7.9</v>
       </c>
       <c r="G6" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>&lt;-- engine pick (regime)</t>
-        </is>
-      </c>
+      <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -25941,13 +26587,13 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D7" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="E7" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F7" t="n">
         <v>-13.3</v>
@@ -25974,19 +26620,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D8" t="n">
-        <v>7.7</v>
+        <v>7.5</v>
       </c>
       <c r="E8" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F8" t="n">
-        <v>-8.699999999999999</v>
+        <v>-11.8</v>
       </c>
       <c r="G8" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -26007,13 +26653,13 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D9" t="n">
-        <v>6.7</v>
+        <v>6.6</v>
       </c>
       <c r="E9" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F9" t="n">
         <v>-7.6</v>
@@ -26123,7 +26769,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>-2.2</v>
+        <v>-2.9</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -26165,7 +26811,7 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>-9.6</v>
+        <v>-10.7</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -26207,7 +26853,7 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>-16.1</v>
+        <v>-13.9</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -26249,7 +26895,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>-12.6</v>
+        <v>-8.1</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -26291,7 +26937,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>-3.4</v>
+        <v>-4.5</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -26333,7 +26979,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>-11.9</v>
+        <v>-9.300000000000001</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -26375,7 +27021,7 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>-2.8</v>
+        <v>-3</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -26417,7 +27063,7 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>-1.5</v>
+        <v>-1.7</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -26459,7 +27105,7 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>-3.2</v>
+        <v>-2.4</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -26501,7 +27147,7 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>-4.6</v>
+        <v>-3.8</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -26543,7 +27189,7 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>-2.8</v>
+        <v>-2.9</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -26627,7 +27273,7 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>-4.8</v>
+        <v>-4.7</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -26669,7 +27315,7 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>-7.2</v>
+        <v>-7.3</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -26711,7 +27357,7 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>-9.300000000000001</v>
+        <v>-9.1</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -26753,7 +27399,7 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>-3.6</v>
+        <v>-3.3</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -26795,7 +27441,7 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>-3.5</v>
+        <v>-3.8</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -26879,7 +27525,7 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>-13.6</v>
+        <v>-11.8</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -26954,12 +27600,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>15.2%</t>
+          <t>12.9%</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -26974,7 +27620,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>13.9%</t>
+          <t>12.1%</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -26999,42 +27645,42 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Power</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>6.7%</t>
+          <t>9.0%</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>6.3%</t>
+          <t>8.7%</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Power</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>6.0%</t>
+          <t>5.3%</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -27069,7 +27715,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>9 stocks / 6 sectors</t>
+          <t>11 stocks / 6 sectors</t>
         </is>
       </c>
     </row>
@@ -27259,7 +27905,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Chosen by choose_horizon() from the backtested Horizon Matrix, REGIME-CONDITIONAL: risk-off favours a strong SHORT horizon (de-risk fast), risk-on lets it run longer. Today: 3M. The full menu of horizons (1W-1Y) with win rates is on this sheet so you can pick a shorter commitment. Per-STOCK horizons are NOT offered (small-sample skill ~random).</t>
+          <t>Chosen by choose_horizon() from the backtested Horizon Matrix, REGIME-CONDITIONAL: risk-off favours a strong SHORT horizon (de-risk fast), risk-on lets it run longer. Today: 2M. The full menu of horizons (1W-1Y) with win rates is on this sheet so you can pick a shorter commitment. Per-STOCK horizons are NOT offered (small-sample skill ~random).</t>
         </is>
       </c>
     </row>
@@ -27435,7 +28081,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>HISTORICALLY TESTED — all horizons backtested · best = 3M</t>
+          <t>HISTORICALLY TESTED — all horizons backtested · best = 2M</t>
         </is>
       </c>
     </row>

--- a/reports/AEGIS_LATEST.xlsx
+++ b/reports/AEGIS_LATEST.xlsx
@@ -444,7 +444,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
     </row>
@@ -489,7 +489,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7">
@@ -512,7 +512,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
     </row>
@@ -524,7 +524,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ICICIBANK (68)</t>
+          <t>ICICIBANK (67)</t>
         </is>
       </c>
     </row>
@@ -548,7 +548,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>IOC, NHPC</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -571,7 +571,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -688,7 +688,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-21  /  2026-09-21</t>
+          <t>2026-09-22  /  2026-09-22</t>
         </is>
       </c>
     </row>
@@ -760,7 +760,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
     </row>
@@ -1513,11 +1513,11 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Risk/Vol +23 · Historical +20 · Regime +9 · Sector +9 · Trend/Tech +7 = 68</t>
+          <t>Risk/Vol +23 · Historical +20 · Regime +9 · Sector +9 · Trend/Tech +6 = 67</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -1534,7 +1534,7 @@
         <v>66</v>
       </c>
       <c r="G2" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="H2" t="n">
         <v>92</v>
@@ -1556,11 +1556,11 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>1342.7</v>
+        <v>1339.4</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>1310 - 1375</t>
+          <t>1307 - 1371</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -1574,15 +1574,15 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-1.0%)</t>
+          <t>Below 200-DMA (-1.2%)</t>
         </is>
       </c>
       <c r="S2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -1591,17 +1591,17 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="V2" t="n">
-        <v>24169</v>
+        <v>32146</v>
       </c>
       <c r="W2" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="X2" t="n">
-        <v>8.4</v>
+        <v>10.9</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
@@ -1615,12 +1615,12 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ICICIBANK: 68; PNB: 66, IDFCFIRSTB: 62, SBIN: 60</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ICICIBANK: 67; PNB: 66, IDFCFIRSTB: 64, SBIN: 61</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>Low-risk Financials holding (low vol) • below 200-dma (-1.0%) • sector strength 88/100 • regime cautious (partial deploy) • 8 similar past recs: 75% positive, median +5.3%</t>
+          <t>Low-risk Financials holding (low vol) • below 200-dma (-1.2%) • sector strength 88/100 • regime cautious (partial deploy) • 8 similar past recs: 75% positive, median +5.3%</t>
         </is>
       </c>
     </row>
@@ -1631,11 +1631,11 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Risk/Vol +22 · Historical +15 · Sector +10 · Regime +9 · Trend/Tech +7 = 63</t>
+          <t>Risk/Vol +22 · Historical +15 · Sector +10 · Regime +9 · Trend/Tech +8 = 64</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -1652,7 +1652,7 @@
         <v>50</v>
       </c>
       <c r="G3" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="H3" t="n">
         <v>88</v>
@@ -1674,11 +1674,11 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>184.6</v>
+        <v>183.9</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>180 - 189</t>
+          <t>179 - 189</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -1692,15 +1692,15 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-4.4%)</t>
+          <t>Below 200-DMA (-4.9%)</t>
         </is>
       </c>
       <c r="S3" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -1709,17 +1709,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="V3" t="n">
-        <v>23819</v>
+        <v>22436</v>
       </c>
       <c r="W3" t="n">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="X3" t="n">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
@@ -1733,12 +1733,12 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — TATASTEEL: 63; COALINDIA: 61, HINDZINC: 61, SAIL: 52</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — TATASTEEL: 64; COALINDIA: 62, HINDZINC: 62, SAIL: 52</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>Low-risk Metal holding (low vol) • below 200-dma (-4.4%) • sector strength 100/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
+          <t>Low-risk Metal holding (low vol) • below 200-dma (-4.9%) • sector strength 100/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
         </is>
       </c>
     </row>
@@ -1749,11 +1749,11 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Risk/Vol +20 · Historical +15 · Sector +10 · Regime +9 · Trend/Tech +7 = 61</t>
+          <t>Risk/Vol +20 · Historical +15 · Sector +10 · Regime +9 · Trend/Tech +8 = 62</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1770,7 +1770,7 @@
         <v>51</v>
       </c>
       <c r="G4" t="n">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="H4" t="n">
         <v>81</v>
@@ -1792,11 +1792,11 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>412</v>
+        <v>426.1</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>401 - 423</t>
+          <t>415 - 438</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -1810,15 +1810,15 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-4.4%)</t>
+          <t>Below 200-DMA (-1.2%)</t>
         </is>
       </c>
       <c r="S4" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1827,17 +1827,17 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="V4" t="n">
-        <v>36260</v>
+        <v>30257</v>
       </c>
       <c r="W4" t="n">
-        <v>88</v>
+        <v>71</v>
       </c>
       <c r="X4" t="n">
-        <v>12.1</v>
+        <v>10.2</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -1851,12 +1851,12 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — COALINDIA: 61; TATASTEEL: 63, HINDZINC: 61, SAIL: 52. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — COALINDIA: 62; TATASTEEL: 64, HINDZINC: 62, SAIL: 52. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>Low-risk Metal holding (low vol) • below 200-dma (-4.4%) • sector strength 100/100 • regime cautious (partial deploy) • 3 similar past recs: 67% positive, median +0.8%</t>
+          <t>Low-risk Metal holding (low vol) • below 200-dma (-1.2%) • sector strength 100/100 • regime cautious (partial deploy) • 3 similar past recs: 67% positive, median +0.8%</t>
         </is>
       </c>
     </row>
@@ -1867,11 +1867,11 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Historical +20 · Risk/Vol +16 · Regime +9 · Sector +9 · Trend/Tech +6 = 60</t>
+          <t>Historical +20 · Risk/Vol +17 · Regime +9 · Sector +9 · Trend/Tech +6 = 61</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1888,10 +1888,10 @@
         <v>65</v>
       </c>
       <c r="G5" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H5" t="n">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="I5" t="n">
         <v>88</v>
@@ -1910,11 +1910,11 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>991.5</v>
+        <v>988.5</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>962 - 1021</t>
+          <t>960 - 1017</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -1932,11 +1932,11 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-4.7%)</t>
+          <t>Below 200-DMA (-5.0%)</t>
         </is>
       </c>
       <c r="S5" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1945,17 +1945,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="V5" t="n">
-        <v>17847</v>
+        <v>18782</v>
       </c>
       <c r="W5" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="X5" t="n">
-        <v>6.2</v>
+        <v>6.3</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -1969,12 +1969,12 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — SBIN: 60; ICICIBANK: 68, PNB: 66, IDFCFIRSTB: 62. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — SBIN: 61; ICICIBANK: 67, PNB: 66, IDFCFIRSTB: 64. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>Low-risk Financials holding (medium vol) • below 200-dma (-4.7%) • sector strength 88/100 • regime cautious (partial deploy) • 2 similar past recs: 100% positive, median +8.9%</t>
+          <t>Low-risk Financials holding (low vol) • below 200-dma (-5.0%) • sector strength 88/100 • regime cautious (partial deploy) • 2 similar past recs: 100% positive, median +8.9%</t>
         </is>
       </c>
     </row>
@@ -1989,7 +1989,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Risk/Vol +18 · Historical +16 · Regime +9 · Trend/Tech +8 · Sector +8 = 59</t>
+          <t>Risk/Vol +19 · Historical +15 · Regime +9 · Trend/Tech +8 · Sector +8 = 59</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -2003,13 +2003,13 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="G6" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H6" t="n">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="I6" t="n">
         <v>75</v>
@@ -2019,20 +2019,20 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>ONGC</t>
+          <t>BEL</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="M6" t="n">
-        <v>233.4</v>
+        <v>397.5</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>227 - 240</t>
+          <t>387 - 408</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -2046,11 +2046,11 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-9.1%)</t>
+          <t>Below 200-DMA (-4.9%)</t>
         </is>
       </c>
       <c r="S6" t="n">
@@ -2063,21 +2063,21 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="V6" t="n">
-        <v>32675</v>
+        <v>27828</v>
       </c>
       <c r="W6" t="n">
-        <v>140</v>
+        <v>70</v>
       </c>
       <c r="X6" t="n">
-        <v>10.9</v>
+        <v>9.4</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Energy name under the sector cap</t>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Industrials name under the sector cap</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -2087,27 +2087,27 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ONGC: 59; IOC: 53</t>
+          <t>No same-sector peer in the universe.</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>Low-risk Energy holding (low vol) • below 200-dma (-9.1%) • sector strength 75/100 • regime cautious (partial deploy) • 2 similar past recs: 50% positive, median +9.0%</t>
+          <t>Low-risk Industrials holding (low vol) • below 200-dma (-4.9%) • sector strength 75/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ACCUMULATE</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Risk/Vol +24 · Historical +13 · Regime +9 · Trend/Tech +6 · Sector +2 = 54</t>
+          <t>Risk/Vol +24 · Historical +13 · Regime +9 · Trend/Tech +6 · Sector +5 = 57</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -2124,13 +2124,13 @@
         <v>44</v>
       </c>
       <c r="G7" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H7" t="n">
         <v>96</v>
       </c>
       <c r="I7" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="J7" t="n">
         <v>60</v>
@@ -2164,15 +2164,15 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-13.7%)</t>
+          <t>Below 200-DMA (-13.5%)</t>
         </is>
       </c>
       <c r="S7" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -2181,17 +2181,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="V7" t="n">
-        <v>35152</v>
+        <v>36749</v>
       </c>
       <c r="W7" t="n">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="X7" t="n">
-        <v>11.8</v>
+        <v>12.3</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -2205,57 +2205,57 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ITC: 54; DABUR: 50</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ITC: 57; DABUR: 51</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>Low-risk FMCG holding (low vol) • below 200-dma (-13.7%) • sector strength 25/100 • regime cautious (partial deploy) • 9 similar past recs: 56% positive, median +0.3%</t>
+          <t>Low-risk FMCG holding (low vol) • below 200-dma (-13.5%) • sector strength 50/100 • regime cautious (partial deploy) • 9 similar past recs: 56% positive, median +0.3%</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ACCUMULATE</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="B8" t="n">
+        <v>57</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Risk/Vol +18 · Historical +16 · Regime +9 · Trend/Tech +8 · Sector +6 = 57</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Risk/Vol</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Sector</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
         <v>53</v>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Historical +16 · Risk/Vol +12 · Regime +9 · Trend/Tech +8 · Sector +8 = 53</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Historical</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Sector</t>
-        </is>
-      </c>
-      <c r="F8" t="n">
-        <v>52</v>
-      </c>
       <c r="G8" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="H8" t="n">
-        <v>50</v>
+        <v>73</v>
       </c>
       <c r="I8" t="n">
-        <v>75</v>
+        <v>62</v>
       </c>
       <c r="J8" t="n">
         <v>60</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>IOC</t>
+          <t>ONGC</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -2264,11 +2264,11 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>136.7</v>
+        <v>234.1</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>132 - 141</t>
+          <t>227 - 241</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -2282,15 +2282,15 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-8.6%)</t>
+          <t>Below 200-DMA (-8.9%)</t>
         </is>
       </c>
       <c r="S8" t="n">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -2299,21 +2299,21 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="V8" t="n">
-        <v>31856</v>
+        <v>28554</v>
       </c>
       <c r="W8" t="n">
-        <v>233</v>
+        <v>122</v>
       </c>
       <c r="X8" t="n">
-        <v>10.6</v>
+        <v>9.5</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>Historical + Risk/Vol strongest; chosen as a lowest-volatility Energy name under the sector cap</t>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Energy name under the sector cap</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
@@ -2323,12 +2323,12 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — IOC: 53; ONGC: 59. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ONGC: 57; IOC: 50</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>Low-risk Energy holding (medium vol) • below 200-dma (-8.6%) • sector strength 75/100 • regime cautious (partial deploy) • 2 similar past recs: 50% positive, median +8.1%</t>
+          <t>Low-risk Energy holding (low vol) • below 200-dma (-8.9%) • sector strength 62/100 • regime cautious (partial deploy) • 2 similar past recs: 50% positive, median +9.0%</t>
         </is>
       </c>
     </row>
@@ -2343,7 +2343,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Risk/Vol +19 · Historical +15 · Regime +9 · Trend/Tech +5 · Sector +5 = 53</t>
+          <t>Risk/Vol +21 · Historical +15 · Regime +9 · Trend/Tech +7 · Sector +1 = 53</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2360,33 +2360,33 @@
         <v>50</v>
       </c>
       <c r="G9" t="n">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="H9" t="n">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="I9" t="n">
-        <v>50</v>
+        <v>12</v>
       </c>
       <c r="J9" t="n">
         <v>60</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>BEL</t>
+          <t>TATAPOWER</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Power</t>
         </is>
       </c>
       <c r="M9" t="n">
-        <v>394</v>
+        <v>366.2</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>383 - 405</t>
+          <t>357 - 376</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -2404,11 +2404,11 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-5.8%)</t>
+          <t>Below 200-DMA (-5.3%)</t>
         </is>
       </c>
       <c r="S9" t="n">
-        <v>37</v>
+        <v>53</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -2417,21 +2417,21 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="V9" t="n">
-        <v>26395</v>
+        <v>28568</v>
       </c>
       <c r="W9" t="n">
-        <v>67</v>
+        <v>78</v>
       </c>
       <c r="X9" t="n">
-        <v>8.9</v>
+        <v>9.6</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Industrials name under the sector cap</t>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Power name under the sector cap</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
@@ -2441,12 +2441,12 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>No same-sector peer in the universe.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — TATAPOWER: 53; NHPC: 49, ADANIPOWER: 44, NLCINDIA: 28</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>Low-risk Industrials holding (low vol) • below 200-dma (-5.8%) • sector strength 50/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
+          <t>Low-risk Power holding (low vol) • below 200-dma (-5.3%) • sector strength 12/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
         </is>
       </c>
     </row>
@@ -2457,11 +2457,11 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Risk/Vol +21 · Historical +15 · Regime +9 · Trend/Tech +6 · Sector +1 = 52</t>
+          <t>Risk/Vol +16 · Historical +15 · Regime +9 · Trend/Tech +6 · Sector +5 = 51</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2478,33 +2478,33 @@
         <v>50</v>
       </c>
       <c r="G10" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H10" t="n">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="I10" t="n">
-        <v>12</v>
+        <v>50</v>
       </c>
       <c r="J10" t="n">
         <v>60</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>TATAPOWER</t>
+          <t>DABUR</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Power</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>366.1</v>
+        <v>386.2</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>356 - 376</t>
+          <t>375 - 397</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -2522,11 +2522,11 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-5.3%)</t>
+          <t>Below 200-DMA (-14.8%)</t>
         </is>
       </c>
       <c r="S10" t="n">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -2535,21 +2535,21 @@
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="V10" t="n">
-        <v>22698</v>
+        <v>25103</v>
       </c>
       <c r="W10" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="X10" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Power name under the sector cap</t>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility FMCG name under the sector cap</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
@@ -2559,12 +2559,12 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — TATAPOWER: 52; NHPC: 49, ADANIPOWER: 44, NLCINDIA: 28</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — DABUR: 51; ITC: 57. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>Low-risk Power holding (low vol) • below 200-dma (-5.3%) • sector strength 12/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
+          <t>Low-risk FMCG holding (medium vol) • below 200-dma (-14.8%) • sector strength 50/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
         </is>
       </c>
     </row>
@@ -2579,12 +2579,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Risk/Vol +17 · Historical +15 · Regime +9 · Trend/Tech +7 · Sector +2 = 50</t>
+          <t>Historical +16 · Risk/Vol +12 · Regime +9 · Trend/Tech +7 · Sector +6 = 50</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Risk/Vol</t>
+          <t>Historical</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -2593,36 +2593,36 @@
         </is>
       </c>
       <c r="F11" t="n">
+        <v>52</v>
+      </c>
+      <c r="G11" t="n">
+        <v>36</v>
+      </c>
+      <c r="H11" t="n">
         <v>50</v>
       </c>
-      <c r="G11" t="n">
-        <v>33</v>
-      </c>
-      <c r="H11" t="n">
-        <v>69</v>
-      </c>
       <c r="I11" t="n">
-        <v>25</v>
+        <v>62</v>
       </c>
       <c r="J11" t="n">
         <v>60</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>DABUR</t>
+          <t>IOC</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="M11" t="n">
-        <v>389.5</v>
+        <v>138.4</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>378 - 401</t>
+          <t>134 - 143</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -2636,15 +2636,15 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-14.1%)</t>
+          <t>Below 200-DMA (-7.4%)</t>
         </is>
       </c>
       <c r="S11" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -2653,21 +2653,21 @@
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="V11" t="n">
-        <v>24152</v>
+        <v>27680</v>
       </c>
       <c r="W11" t="n">
-        <v>62</v>
+        <v>200</v>
       </c>
       <c r="X11" t="n">
-        <v>8.1</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility FMCG name under the sector cap</t>
+          <t>Historical + Risk/Vol strongest; chosen as a lowest-volatility Energy name under the sector cap</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
@@ -2677,12 +2677,12 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — DABUR: 50; ITC: 54. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — IOC: 50; ONGC: 57. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>Low-risk FMCG holding (low vol) • below 200-dma (-14.1%) • sector strength 25/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
+          <t>Low-risk Energy holding (medium vol) • below 200-dma (-7.4%) • sector strength 62/100 • regime cautious (partial deploy) • 2 similar past recs: 50% positive, median +8.1%</t>
         </is>
       </c>
     </row>
@@ -2714,10 +2714,10 @@
         <v>57</v>
       </c>
       <c r="G12" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="H12" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="I12" t="n">
         <v>12</v>
@@ -2736,7 +2736,7 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>75.90000000000001</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
@@ -2758,11 +2758,11 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-2.4%)</t>
+          <t>Below 200-DMA (-2.1%)</t>
         </is>
       </c>
       <c r="S12" t="n">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2771,17 +2771,17 @@
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="V12" t="n">
-        <v>22247</v>
+        <v>20014</v>
       </c>
       <c r="W12" t="n">
-        <v>293</v>
+        <v>263</v>
       </c>
       <c r="X12" t="n">
-        <v>7.4</v>
+        <v>6.7</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -2795,12 +2795,12 @@
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — NHPC: 49; TATAPOWER: 52, ADANIPOWER: 44, NLCINDIA: 28. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — NHPC: 49; TATAPOWER: 53, ADANIPOWER: 44, NLCINDIA: 28. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>Low-risk Power holding (medium vol) • below 200-dma (-2.4%) • sector strength 12/100 • regime cautious (partial deploy) • 1 similar past recs: 100% positive, median +7.2%</t>
+          <t>Low-risk Power holding (medium vol) • below 200-dma (-2.1%) • sector strength 12/100 • regime cautious (partial deploy) • 1 similar past recs: 100% positive, median +7.2%</t>
         </is>
       </c>
     </row>
@@ -27600,12 +27600,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>12.9%</t>
+          <t>12.4%</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -27615,12 +27615,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Metal</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>12.1%</t>
+          <t>11.3%</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -27630,12 +27630,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>Metal</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>11.9%</t>
+          <t>10.6%</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -27645,12 +27645,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Power</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>9.0%</t>
+          <t>10.3%</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -27660,12 +27660,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Power</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>8.7%</t>
+          <t>9.7%</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -27680,7 +27680,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>5.3%</t>
+          <t>5.6%</t>
         </is>
       </c>
       <c r="C7" t="n">

--- a/reports/AEGIS_LATEST.xlsx
+++ b/reports/AEGIS_LATEST.xlsx
@@ -444,7 +444,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -512,7 +512,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
     </row>
@@ -536,7 +536,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>NHPC (49)</t>
+          <t>NHPC (50)</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-22  /  2026-09-22</t>
+          <t>2026-09-23  /  2026-09-23</t>
         </is>
       </c>
     </row>
@@ -760,7 +760,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
     </row>
@@ -1534,7 +1534,7 @@
         <v>66</v>
       </c>
       <c r="G2" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="H2" t="n">
         <v>92</v>
@@ -1556,11 +1556,11 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>1339.4</v>
+        <v>1338</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>1307 - 1371</t>
+          <t>1306 - 1370</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -1578,11 +1578,11 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-1.2%)</t>
+          <t>Below 200-DMA (-1.3%)</t>
         </is>
       </c>
       <c r="S2" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -1591,17 +1591,17 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="V2" t="n">
-        <v>32146</v>
+        <v>26760</v>
       </c>
       <c r="W2" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="X2" t="n">
-        <v>10.9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
@@ -1615,27 +1615,27 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ICICIBANK: 67; PNB: 66, IDFCFIRSTB: 64, SBIN: 61</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ICICIBANK: 67; PNB: 66, IDFCFIRSTB: 62, SBIN: 61</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>Low-risk Financials holding (low vol) • below 200-dma (-1.2%) • sector strength 88/100 • regime cautious (partial deploy) • 8 similar past recs: 75% positive, median +5.3%</t>
+          <t>Low-risk Financials holding (low vol) • below 200-dma (-1.3%) • sector strength 88/100 • regime cautious (partial deploy) • 8 similar past recs: 75% positive, median +5.3%</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>STRONG BUY</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Risk/Vol +22 · Historical +15 · Sector +10 · Regime +9 · Trend/Tech +8 = 64</t>
+          <t>Risk/Vol +22 · Historical +15 · Sector +10 · Trend/Tech +9 · Regime +9 = 65</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -1645,14 +1645,14 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Trend/Tech</t>
+          <t>Regime</t>
         </is>
       </c>
       <c r="F3" t="n">
         <v>50</v>
       </c>
       <c r="G3" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="H3" t="n">
         <v>88</v>
@@ -1674,11 +1674,11 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>183.9</v>
+        <v>187.6</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>179 - 189</t>
+          <t>183 - 192</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -1696,11 +1696,11 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-4.9%)</t>
+          <t>Below 200-DMA (-3.0%)</t>
         </is>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -1709,17 +1709,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="V3" t="n">
-        <v>22436</v>
+        <v>24951</v>
       </c>
       <c r="W3" t="n">
-        <v>122</v>
+        <v>133</v>
       </c>
       <c r="X3" t="n">
-        <v>7.5</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
@@ -1733,12 +1733,12 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — TATASTEEL: 64; COALINDIA: 62, HINDZINC: 62, SAIL: 52</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — TATASTEEL: 65; HINDZINC: 62, COALINDIA: 61, SAIL: 52</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>Low-risk Metal holding (low vol) • below 200-dma (-4.9%) • sector strength 100/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
+          <t>Low-risk Metal holding (low vol) • below 200-dma (-3.0%) • sector strength 100/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
         </is>
       </c>
     </row>
@@ -1749,11 +1749,11 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Risk/Vol +20 · Historical +15 · Sector +10 · Regime +9 · Trend/Tech +8 = 62</t>
+          <t>Risk/Vol +19 · Historical +15 · Sector +10 · Regime +9 · Trend/Tech +8 = 61</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1770,10 +1770,10 @@
         <v>51</v>
       </c>
       <c r="G4" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H4" t="n">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="I4" t="n">
         <v>100</v>
@@ -1792,11 +1792,11 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>426.1</v>
+        <v>424.4</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>415 - 438</t>
+          <t>413 - 436</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -1810,15 +1810,15 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-1.2%)</t>
+          <t>Below 200-DMA (-1.7%)</t>
         </is>
       </c>
       <c r="S4" t="n">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1827,17 +1827,17 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="V4" t="n">
-        <v>30257</v>
+        <v>29708</v>
       </c>
       <c r="W4" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="X4" t="n">
-        <v>10.2</v>
+        <v>9.9</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -1851,12 +1851,12 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — COALINDIA: 62; TATASTEEL: 64, HINDZINC: 62, SAIL: 52. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — COALINDIA: 61; TATASTEEL: 65, HINDZINC: 62, SAIL: 52. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>Low-risk Metal holding (low vol) • below 200-dma (-1.2%) • sector strength 100/100 • regime cautious (partial deploy) • 3 similar past recs: 67% positive, median +0.8%</t>
+          <t>Low-risk Metal holding (low vol) • below 200-dma (-1.7%) • sector strength 100/100 • regime cautious (partial deploy) • 3 similar past recs: 67% positive, median +0.8%</t>
         </is>
       </c>
     </row>
@@ -1871,7 +1871,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Historical +20 · Risk/Vol +17 · Regime +9 · Sector +9 · Trend/Tech +6 = 61</t>
+          <t>Historical +20 · Risk/Vol +18 · Regime +9 · Sector +9 · Trend/Tech +5 = 61</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1888,10 +1888,10 @@
         <v>65</v>
       </c>
       <c r="G5" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="H5" t="n">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="I5" t="n">
         <v>88</v>
@@ -1910,11 +1910,11 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>988.5</v>
+        <v>990.5</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>960 - 1017</t>
+          <t>963 - 1018</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -1932,11 +1932,11 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-5.0%)</t>
+          <t>Below 200-DMA (-4.8%)</t>
         </is>
       </c>
       <c r="S5" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1945,17 +1945,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="V5" t="n">
-        <v>18782</v>
+        <v>26744</v>
       </c>
       <c r="W5" t="n">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="X5" t="n">
-        <v>6.3</v>
+        <v>9.1</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -1969,12 +1969,12 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — SBIN: 61; ICICIBANK: 67, PNB: 66, IDFCFIRSTB: 64. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — SBIN: 61; ICICIBANK: 67, PNB: 66, IDFCFIRSTB: 62. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>Low-risk Financials holding (low vol) • below 200-dma (-5.0%) • sector strength 88/100 • regime cautious (partial deploy) • 2 similar past recs: 100% positive, median +8.9%</t>
+          <t>Low-risk Financials holding (low vol) • below 200-dma (-4.8%) • sector strength 88/100 • regime cautious (partial deploy) • 2 similar past recs: 100% positive, median +8.9%</t>
         </is>
       </c>
     </row>
@@ -1989,7 +1989,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Risk/Vol +19 · Historical +15 · Regime +9 · Trend/Tech +8 · Sector +8 = 59</t>
+          <t>Risk/Vol +17 · Historical +16 · Trend/Tech +9 · Regime +9 · Sector +8 = 59</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -2003,13 +2003,13 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="G6" t="n">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="H6" t="n">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="I6" t="n">
         <v>75</v>
@@ -2019,20 +2019,20 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>BEL</t>
+          <t>ONGC</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="M6" t="n">
-        <v>397.5</v>
+        <v>235.5</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>387 - 408</t>
+          <t>229 - 242</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -2046,15 +2046,15 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-4.9%)</t>
+          <t>Below 200-DMA (-8.3%)</t>
         </is>
       </c>
       <c r="S6" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -2063,21 +2063,21 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="V6" t="n">
-        <v>27828</v>
+        <v>28024</v>
       </c>
       <c r="W6" t="n">
-        <v>70</v>
+        <v>119</v>
       </c>
       <c r="X6" t="n">
         <v>9.4</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Industrials name under the sector cap</t>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Energy name under the sector cap</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -2087,12 +2087,12 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>No same-sector peer in the universe.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ONGC: 59; IOC: 53</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>Low-risk Industrials holding (low vol) • below 200-dma (-4.9%) • sector strength 75/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
+          <t>Low-risk Energy holding (low vol) • below 200-dma (-8.3%) • outperforming Nifty • sector strength 75/100 • regime cautious (partial deploy) • 2 similar past recs: 50% positive, median +9.0%</t>
         </is>
       </c>
     </row>
@@ -2103,11 +2103,11 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Risk/Vol +24 · Historical +13 · Regime +9 · Trend/Tech +6 · Sector +5 = 57</t>
+          <t>Risk/Vol +20 · Historical +15 · Regime +9 · Trend/Tech +8 · Sector +6 = 58</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -2121,58 +2121,58 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="G7" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="H7" t="n">
-        <v>96</v>
+        <v>81</v>
       </c>
       <c r="I7" t="n">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="J7" t="n">
         <v>60</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>ITC</t>
+          <t>BEL</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>266.3</v>
+        <v>396.5</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>260 - 272</t>
+          <t>386 - 407</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-4% to +3%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>56%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-13.5%)</t>
+          <t>Below 200-DMA (-5.1%)</t>
         </is>
       </c>
       <c r="S7" t="n">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -2181,21 +2181,21 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="V7" t="n">
-        <v>36749</v>
+        <v>28948</v>
       </c>
       <c r="W7" t="n">
-        <v>138</v>
+        <v>73</v>
       </c>
       <c r="X7" t="n">
-        <v>12.3</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility FMCG name under the sector cap</t>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Industrials name under the sector cap</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -2205,12 +2205,12 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ITC: 57; DABUR: 51</t>
+          <t>No same-sector peer in the universe.</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>Low-risk FMCG holding (low vol) • below 200-dma (-13.5%) • sector strength 50/100 • regime cautious (partial deploy) • 9 similar past recs: 56% positive, median +0.3%</t>
+          <t>Low-risk Industrials holding (low vol) • below 200-dma (-5.1%) • sector strength 62/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
         </is>
       </c>
     </row>
@@ -2225,7 +2225,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Risk/Vol +18 · Historical +16 · Regime +9 · Trend/Tech +8 · Sector +6 = 57</t>
+          <t>Risk/Vol +24 · Historical +13 · Regime +9 · Trend/Tech +6 · Sector +5 = 57</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -2239,58 +2239,58 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="G8" t="n">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="H8" t="n">
-        <v>73</v>
+        <v>96</v>
       </c>
       <c r="I8" t="n">
-        <v>62</v>
+        <v>50</v>
       </c>
       <c r="J8" t="n">
         <v>60</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>ONGC</t>
+          <t>ITC</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="M8" t="n">
-        <v>234.1</v>
+        <v>267.2</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>227 - 241</t>
+          <t>261 - 273</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-4% to +3%</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>56%</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-8.9%)</t>
+          <t>Below 200-DMA (-13.0%)</t>
         </is>
       </c>
       <c r="S8" t="n">
-        <v>43</v>
+        <v>58</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -2299,21 +2299,21 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="V8" t="n">
-        <v>28554</v>
+        <v>37415</v>
       </c>
       <c r="W8" t="n">
-        <v>122</v>
+        <v>140</v>
       </c>
       <c r="X8" t="n">
-        <v>9.5</v>
+        <v>12.6</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Energy name under the sector cap</t>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility FMCG name under the sector cap</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
@@ -2323,12 +2323,12 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ONGC: 57; IOC: 50</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ITC: 57; DABUR: 51</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>Low-risk Energy holding (low vol) • below 200-dma (-8.9%) • sector strength 62/100 • regime cautious (partial deploy) • 2 similar past recs: 50% positive, median +9.0%</t>
+          <t>Low-risk FMCG holding (low vol) • below 200-dma (-13.0%) • sector strength 50/100 • regime cautious (partial deploy) • 9 similar past recs: 56% positive, median +0.3%</t>
         </is>
       </c>
     </row>
@@ -2339,11 +2339,11 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Risk/Vol +21 · Historical +15 · Regime +9 · Trend/Tech +7 · Sector +1 = 53</t>
+          <t>Risk/Vol +21 · Historical +15 · Regime +9 · Trend/Tech +7 · Sector +2 = 54</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2360,13 +2360,13 @@
         <v>50</v>
       </c>
       <c r="G9" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="H9" t="n">
         <v>85</v>
       </c>
       <c r="I9" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="J9" t="n">
         <v>60</v>
@@ -2382,11 +2382,11 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>366.2</v>
+        <v>367.6</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>357 - 376</t>
+          <t>358 - 377</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -2404,11 +2404,11 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-5.3%)</t>
+          <t>Below 200-DMA (-4.9%)</t>
         </is>
       </c>
       <c r="S9" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -2417,17 +2417,17 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="V9" t="n">
-        <v>28568</v>
+        <v>23159</v>
       </c>
       <c r="W9" t="n">
-        <v>78</v>
+        <v>63</v>
       </c>
       <c r="X9" t="n">
-        <v>9.6</v>
+        <v>7.8</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -2441,12 +2441,12 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — TATAPOWER: 53; NHPC: 49, ADANIPOWER: 44, NLCINDIA: 28</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — TATAPOWER: 54; NHPC: 50, ADANIPOWER: 44, NLCINDIA: 31</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>Low-risk Power holding (low vol) • below 200-dma (-5.3%) • sector strength 12/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
+          <t>Low-risk Power holding (low vol) • below 200-dma (-4.9%) • sector strength 25/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
         </is>
       </c>
     </row>
@@ -2457,16 +2457,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Risk/Vol +16 · Historical +15 · Regime +9 · Trend/Tech +6 · Sector +5 = 51</t>
+          <t>Historical +16 · Risk/Vol +12 · Regime +9 · Trend/Tech +8 · Sector +8 = 53</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Risk/Vol</t>
+          <t>Historical</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -2475,36 +2475,36 @@
         </is>
       </c>
       <c r="F10" t="n">
+        <v>52</v>
+      </c>
+      <c r="G10" t="n">
+        <v>38</v>
+      </c>
+      <c r="H10" t="n">
         <v>50</v>
       </c>
-      <c r="G10" t="n">
-        <v>30</v>
-      </c>
-      <c r="H10" t="n">
-        <v>65</v>
-      </c>
       <c r="I10" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="J10" t="n">
         <v>60</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>DABUR</t>
+          <t>IOC</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>386.2</v>
+        <v>138.1</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>375 - 397</t>
+          <t>134 - 143</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -2518,15 +2518,15 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-14.8%)</t>
+          <t>Below 200-DMA (-7.5%)</t>
         </is>
       </c>
       <c r="S10" t="n">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -2535,21 +2535,21 @@
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="V10" t="n">
-        <v>25103</v>
+        <v>16577</v>
       </c>
       <c r="W10" t="n">
-        <v>65</v>
+        <v>120</v>
       </c>
       <c r="X10" t="n">
-        <v>8.4</v>
+        <v>5.6</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility FMCG name under the sector cap</t>
+          <t>Historical + Risk/Vol strongest; chosen as a lowest-volatility Energy name under the sector cap</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
@@ -2559,12 +2559,12 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — DABUR: 51; ITC: 57. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — IOC: 53; ONGC: 59. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>Low-risk FMCG holding (medium vol) • below 200-dma (-14.8%) • sector strength 50/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
+          <t>Low-risk Energy holding (medium vol) • below 200-dma (-7.5%) • sector strength 75/100 • regime cautious (partial deploy) • 2 similar past recs: 50% positive, median +8.1%</t>
         </is>
       </c>
     </row>
@@ -2575,54 +2575,54 @@
         </is>
       </c>
       <c r="B11" t="n">
+        <v>51</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Risk/Vol +16 · Historical +15 · Regime +9 · Trend/Tech +6 · Sector +5 = 51</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Risk/Vol</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Sector</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
         <v>50</v>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Historical +16 · Risk/Vol +12 · Regime +9 · Trend/Tech +7 · Sector +6 = 50</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Historical</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Sector</t>
-        </is>
-      </c>
-      <c r="F11" t="n">
-        <v>52</v>
-      </c>
       <c r="G11" t="n">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="H11" t="n">
+        <v>65</v>
+      </c>
+      <c r="I11" t="n">
         <v>50</v>
-      </c>
-      <c r="I11" t="n">
-        <v>62</v>
       </c>
       <c r="J11" t="n">
         <v>60</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>IOC</t>
+          <t>DABUR</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="M11" t="n">
-        <v>138.4</v>
+        <v>392.3</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>134 - 143</t>
+          <t>381 - 404</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -2636,15 +2636,15 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-7.4%)</t>
+          <t>Below 200-DMA (-13.3%)</t>
         </is>
       </c>
       <c r="S11" t="n">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -2653,21 +2653,21 @@
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="V11" t="n">
-        <v>27680</v>
+        <v>25107</v>
       </c>
       <c r="W11" t="n">
-        <v>200</v>
+        <v>64</v>
       </c>
       <c r="X11" t="n">
-        <v>9.300000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>Historical + Risk/Vol strongest; chosen as a lowest-volatility Energy name under the sector cap</t>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility FMCG name under the sector cap</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
@@ -2677,12 +2677,12 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — IOC: 50; ONGC: 57. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — DABUR: 51; ITC: 57. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>Low-risk Energy holding (medium vol) • below 200-dma (-7.4%) • sector strength 62/100 • regime cautious (partial deploy) • 2 similar past recs: 50% positive, median +8.1%</t>
+          <t>Low-risk FMCG holding (medium vol) • below 200-dma (-13.3%) • sector strength 50/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
         </is>
       </c>
     </row>
@@ -2693,11 +2693,11 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Historical +17 · Risk/Vol +14 · Regime +9 · Trend/Tech +8 · Sector +1 = 49</t>
+          <t>Historical +17 · Risk/Vol +14 · Regime +9 · Trend/Tech +8 · Sector +2 = 50</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2714,13 +2714,13 @@
         <v>57</v>
       </c>
       <c r="G12" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H12" t="n">
         <v>54</v>
       </c>
       <c r="I12" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="J12" t="n">
         <v>60</v>
@@ -2736,11 +2736,11 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>76.09999999999999</v>
+        <v>76.7</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>74 - 78</t>
+          <t>74 - 79</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -2754,15 +2754,15 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-2.1%)</t>
+          <t>Below 200-DMA (-1.4%)</t>
         </is>
       </c>
       <c r="S12" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2771,17 +2771,17 @@
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="V12" t="n">
-        <v>20014</v>
+        <v>29825</v>
       </c>
       <c r="W12" t="n">
-        <v>263</v>
+        <v>389</v>
       </c>
       <c r="X12" t="n">
-        <v>6.7</v>
+        <v>10</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -2795,12 +2795,12 @@
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — NHPC: 49; TATAPOWER: 53, ADANIPOWER: 44, NLCINDIA: 28. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — NHPC: 50; TATAPOWER: 54, ADANIPOWER: 44, NLCINDIA: 31. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>Low-risk Power holding (medium vol) • below 200-dma (-2.1%) • sector strength 12/100 • regime cautious (partial deploy) • 1 similar past recs: 100% positive, median +7.2%</t>
+          <t>Low-risk Power holding (medium vol) • below 200-dma (-1.4%) • sector strength 25/100 • regime cautious (partial deploy) • 1 similar past recs: 100% positive, median +7.2%</t>
         </is>
       </c>
     </row>
@@ -27605,7 +27605,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>12.4%</t>
+          <t>12.6%</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -27615,12 +27615,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>11.3%</t>
+          <t>11.0%</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -27635,7 +27635,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>10.6%</t>
+          <t>11.0%</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -27645,12 +27645,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Power</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>10.3%</t>
+          <t>10.7%</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -27660,12 +27660,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Power</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>9.7%</t>
+          <t>9.0%</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -27680,7 +27680,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>5.8%</t>
         </is>
       </c>
       <c r="C7" t="n">

--- a/reports/AEGIS_LATEST.xlsx
+++ b/reports/AEGIS_LATEST.xlsx
@@ -444,7 +444,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
     </row>
@@ -512,7 +512,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
     </row>
@@ -524,7 +524,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ICICIBANK (67)</t>
+          <t>ICICIBANK (66)</t>
         </is>
       </c>
     </row>
@@ -536,7 +536,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>NHPC (50)</t>
+          <t>WIPRO (47)</t>
         </is>
       </c>
     </row>
@@ -548,7 +548,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>WIPRO</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>IOC</t>
         </is>
       </c>
     </row>
@@ -571,7 +571,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -688,7 +688,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-23  /  2026-09-23</t>
+          <t>2026-09-24  /  2026-09-24</t>
         </is>
       </c>
     </row>
@@ -760,7 +760,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
     </row>
@@ -908,7 +908,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>15.3%</t>
+          <t>15.2%</t>
         </is>
       </c>
     </row>
@@ -920,7 +920,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>1.91</t>
         </is>
       </c>
     </row>
@@ -1513,11 +1513,11 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Risk/Vol +23 · Historical +20 · Regime +9 · Sector +9 · Trend/Tech +6 = 67</t>
+          <t>Risk/Vol +23 · Historical +20 · Regime +9 · Sector +8 · Trend/Tech +6 = 66</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -1534,13 +1534,13 @@
         <v>66</v>
       </c>
       <c r="G2" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H2" t="n">
         <v>92</v>
       </c>
       <c r="I2" t="n">
-        <v>88</v>
+        <v>75</v>
       </c>
       <c r="J2" t="n">
         <v>60</v>
@@ -1556,11 +1556,11 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>1338</v>
+        <v>1336.3</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>1306 - 1370</t>
+          <t>1304 - 1368</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -1578,7 +1578,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-1.3%)</t>
+          <t>Below 200-DMA (-1.4%)</t>
         </is>
       </c>
       <c r="S2" t="n">
@@ -1591,17 +1591,17 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="V2" t="n">
-        <v>26760</v>
+        <v>32071</v>
       </c>
       <c r="W2" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="X2" t="n">
-        <v>9.199999999999999</v>
+        <v>10.8</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
@@ -1615,12 +1615,12 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ICICIBANK: 67; PNB: 66, IDFCFIRSTB: 62, SBIN: 61</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ICICIBANK: 66; PNB: 65, SBIN: 60, IDFCFIRSTB: 59</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>Low-risk Financials holding (low vol) • below 200-dma (-1.3%) • sector strength 88/100 • regime cautious (partial deploy) • 8 similar past recs: 75% positive, median +5.3%</t>
+          <t>Low-risk Financials holding (low vol) • below 200-dma (-1.4%) • sector strength 75/100 • regime cautious (partial deploy) • 8 similar past recs: 75% positive, median +5.3%</t>
         </is>
       </c>
     </row>
@@ -1652,7 +1652,7 @@
         <v>50</v>
       </c>
       <c r="G3" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H3" t="n">
         <v>88</v>
@@ -1674,11 +1674,11 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>187.6</v>
+        <v>190.5</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>183 - 192</t>
+          <t>186 - 195</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -1696,11 +1696,11 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-3.0%)</t>
+          <t>Below 200-DMA (-1.6%)</t>
         </is>
       </c>
       <c r="S3" t="n">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -1709,17 +1709,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="V3" t="n">
-        <v>24951</v>
+        <v>29524</v>
       </c>
       <c r="W3" t="n">
-        <v>133</v>
+        <v>155</v>
       </c>
       <c r="X3" t="n">
-        <v>8.300000000000001</v>
+        <v>9.9</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
@@ -1733,12 +1733,12 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — TATASTEEL: 65; HINDZINC: 62, COALINDIA: 61, SAIL: 52</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — TATASTEEL: 65; HINDZINC: 62, COALINDIA: 61, SAIL: 55</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>Low-risk Metal holding (low vol) • below 200-dma (-3.0%) • sector strength 100/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
+          <t>Low-risk Metal holding (low vol) • below 200-dma (-1.6%) • outperforming Nifty • sector strength 100/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
         </is>
       </c>
     </row>
@@ -1792,11 +1792,11 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>424.4</v>
+        <v>421.1</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>413 - 436</t>
+          <t>410 - 433</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -1814,11 +1814,11 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-1.7%)</t>
+          <t>Below 200-DMA (-2.5%)</t>
         </is>
       </c>
       <c r="S4" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1827,17 +1827,17 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="V4" t="n">
-        <v>29708</v>
+        <v>32429</v>
       </c>
       <c r="W4" t="n">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="X4" t="n">
-        <v>9.9</v>
+        <v>10.9</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -1851,12 +1851,12 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — COALINDIA: 61; TATASTEEL: 65, HINDZINC: 62, SAIL: 52. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — COALINDIA: 61; TATASTEEL: 65, HINDZINC: 62, SAIL: 55. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>Low-risk Metal holding (low vol) • below 200-dma (-1.7%) • sector strength 100/100 • regime cautious (partial deploy) • 3 similar past recs: 67% positive, median +0.8%</t>
+          <t>Low-risk Metal holding (low vol) • below 200-dma (-2.5%) • sector strength 100/100 • regime cautious (partial deploy) • 3 similar past recs: 67% positive, median +0.8%</t>
         </is>
       </c>
     </row>
@@ -1867,31 +1867,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Historical +20 · Risk/Vol +18 · Regime +9 · Sector +9 · Trend/Tech +5 = 61</t>
+          <t>Risk/Vol +17 · Historical +16 · Trend/Tech +9 · Regime +9 · Sector +9 = 60</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Historical</t>
+          <t>Risk/Vol</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Trend/Tech</t>
+          <t>Sector</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>65</v>
+        <v>53</v>
       </c>
       <c r="G5" t="n">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="H5" t="n">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="I5" t="n">
         <v>88</v>
@@ -1901,20 +1901,20 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>SBIN</t>
+          <t>ONGC</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="M5" t="n">
-        <v>990.5</v>
+        <v>235.9</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>963 - 1018</t>
+          <t>229 - 243</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -1932,11 +1932,11 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-4.8%)</t>
+          <t>Below 200-DMA (-8.1%)</t>
         </is>
       </c>
       <c r="S5" t="n">
-        <v>34</v>
+        <v>52</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1945,21 +1945,21 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="V5" t="n">
-        <v>26744</v>
+        <v>31136</v>
       </c>
       <c r="W5" t="n">
-        <v>27</v>
+        <v>132</v>
       </c>
       <c r="X5" t="n">
-        <v>9.1</v>
+        <v>10.4</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>Historical + Risk/Vol strongest; chosen as a lowest-volatility Financials name under the sector cap</t>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Energy name under the sector cap</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1969,12 +1969,12 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — SBIN: 61; ICICIBANK: 67, PNB: 66, IDFCFIRSTB: 62. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ONGC: 60; IOC: 54</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>Low-risk Financials holding (low vol) • below 200-dma (-4.8%) • sector strength 88/100 • regime cautious (partial deploy) • 2 similar past recs: 100% positive, median +8.9%</t>
+          <t>Low-risk Energy holding (low vol) • below 200-dma (-8.1%) • sector strength 88/100 • regime cautious (partial deploy) • 2 similar past recs: 50% positive, median +9.0%</t>
         </is>
       </c>
     </row>
@@ -1985,31 +1985,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Risk/Vol +17 · Historical +16 · Trend/Tech +9 · Regime +9 · Sector +8 = 59</t>
+          <t>Historical +20 · Risk/Vol +18 · Regime +9 · Sector +8 · Trend/Tech +5 = 60</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Risk/Vol</t>
+          <t>Historical</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Sector</t>
+          <t>Trend/Tech</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="G6" t="n">
-        <v>46</v>
+        <v>27</v>
       </c>
       <c r="H6" t="n">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="I6" t="n">
         <v>75</v>
@@ -2019,20 +2019,20 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>ONGC</t>
+          <t>SBIN</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="M6" t="n">
-        <v>235.5</v>
+        <v>986.8</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>229 - 242</t>
+          <t>960 - 1014</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -2050,11 +2050,11 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-8.3%)</t>
+          <t>Below 200-DMA (-5.2%)</t>
         </is>
       </c>
       <c r="S6" t="n">
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -2063,21 +2063,21 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="V6" t="n">
-        <v>28024</v>
+        <v>24670</v>
       </c>
       <c r="W6" t="n">
-        <v>119</v>
+        <v>25</v>
       </c>
       <c r="X6" t="n">
-        <v>9.4</v>
+        <v>8.4</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Energy name under the sector cap</t>
+          <t>Historical + Risk/Vol strongest; chosen as a lowest-volatility Financials name under the sector cap</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -2087,12 +2087,12 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ONGC: 59; IOC: 53</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — SBIN: 60; ICICIBANK: 66, PNB: 65, IDFCFIRSTB: 59. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>Low-risk Energy holding (low vol) • below 200-dma (-8.3%) • outperforming Nifty • sector strength 75/100 • regime cautious (partial deploy) • 2 similar past recs: 50% positive, median +9.0%</t>
+          <t>Low-risk Financials holding (low vol) • below 200-dma (-5.2%) • sector strength 75/100 • regime cautious (partial deploy) • 2 similar past recs: 100% positive, median +8.9%</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>396.5</v>
+        <v>396.4</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -2168,11 +2168,11 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-5.1%)</t>
+          <t>Below 200-DMA (-5.2%)</t>
         </is>
       </c>
       <c r="S7" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -2181,17 +2181,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="V7" t="n">
-        <v>28948</v>
+        <v>24574</v>
       </c>
       <c r="W7" t="n">
-        <v>73</v>
+        <v>62</v>
       </c>
       <c r="X7" t="n">
-        <v>9.699999999999999</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -2210,7 +2210,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>Low-risk Industrials holding (low vol) • below 200-dma (-5.1%) • sector strength 62/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
+          <t>Low-risk Industrials holding (low vol) • below 200-dma (-5.2%) • sector strength 62/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
         </is>
       </c>
     </row>
@@ -2225,7 +2225,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Risk/Vol +24 · Historical +13 · Regime +9 · Trend/Tech +6 · Sector +5 = 57</t>
+          <t>Risk/Vol +24 · Historical +13 · Regime +9 · Trend/Tech +7 · Sector +4 = 57</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -2242,13 +2242,13 @@
         <v>44</v>
       </c>
       <c r="G8" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="H8" t="n">
         <v>96</v>
       </c>
       <c r="I8" t="n">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="J8" t="n">
         <v>60</v>
@@ -2264,11 +2264,11 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>267.2</v>
+        <v>268.8</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>261 - 273</t>
+          <t>263 - 275</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -2286,11 +2286,11 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-13.0%)</t>
+          <t>Below 200-DMA (-12.3%)</t>
         </is>
       </c>
       <c r="S8" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -2299,17 +2299,17 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="V8" t="n">
-        <v>37415</v>
+        <v>29568</v>
       </c>
       <c r="W8" t="n">
-        <v>140</v>
+        <v>110</v>
       </c>
       <c r="X8" t="n">
-        <v>12.6</v>
+        <v>9.9</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -2323,12 +2323,12 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ITC: 57; DABUR: 51</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ITC: 57; DABUR: 50</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>Low-risk FMCG holding (low vol) • below 200-dma (-13.0%) • sector strength 50/100 • regime cautious (partial deploy) • 9 similar past recs: 56% positive, median +0.3%</t>
+          <t>Low-risk FMCG holding (low vol) • below 200-dma (-12.3%) • sector strength 38/100 • regime cautious (partial deploy) • 9 similar past recs: 56% positive, median +0.3%</t>
         </is>
       </c>
     </row>
@@ -2339,11 +2339,11 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Risk/Vol +21 · Historical +15 · Regime +9 · Trend/Tech +7 · Sector +2 = 54</t>
+          <t>Risk/Vol +21 · Historical +15 · Regime +9 · Trend/Tech +7 · Sector +1 = 53</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2360,13 +2360,13 @@
         <v>50</v>
       </c>
       <c r="G9" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H9" t="n">
         <v>85</v>
       </c>
       <c r="I9" t="n">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="J9" t="n">
         <v>60</v>
@@ -2382,11 +2382,11 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>367.6</v>
+        <v>366.1</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>358 - 377</t>
+          <t>357 - 376</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -2404,11 +2404,11 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-4.9%)</t>
+          <t>Below 200-DMA (-5.3%)</t>
         </is>
       </c>
       <c r="S9" t="n">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -2417,17 +2417,17 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="V9" t="n">
-        <v>23159</v>
+        <v>20502</v>
       </c>
       <c r="W9" t="n">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="X9" t="n">
-        <v>7.8</v>
+        <v>6.9</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -2441,12 +2441,12 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — TATAPOWER: 54; NHPC: 50, ADANIPOWER: 44, NLCINDIA: 31</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — TATAPOWER: 53; NHPC: 49, ADANIPOWER: 44, NLCINDIA: 28</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>Low-risk Power holding (low vol) • below 200-dma (-4.9%) • sector strength 25/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
+          <t>Low-risk Power holding (low vol) • below 200-dma (-5.3%) • sector strength 12/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
         </is>
       </c>
     </row>
@@ -2457,16 +2457,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Historical +16 · Risk/Vol +12 · Regime +9 · Trend/Tech +8 · Sector +8 = 53</t>
+          <t>Risk/Vol +16 · Historical +15 · Regime +9 · Trend/Tech +6 · Sector +4 = 50</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Historical</t>
+          <t>Risk/Vol</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -2475,36 +2475,36 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="G10" t="n">
+        <v>29</v>
+      </c>
+      <c r="H10" t="n">
+        <v>65</v>
+      </c>
+      <c r="I10" t="n">
         <v>38</v>
-      </c>
-      <c r="H10" t="n">
-        <v>50</v>
-      </c>
-      <c r="I10" t="n">
-        <v>75</v>
       </c>
       <c r="J10" t="n">
         <v>60</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>IOC</t>
+          <t>DABUR</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>138.1</v>
+        <v>386.4</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>134 - 143</t>
+          <t>375 - 398</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -2518,15 +2518,15 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-7.5%)</t>
+          <t>Below 200-DMA (-14.5%)</t>
         </is>
       </c>
       <c r="S10" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -2535,21 +2535,21 @@
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="V10" t="n">
-        <v>16577</v>
+        <v>34772</v>
       </c>
       <c r="W10" t="n">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="X10" t="n">
-        <v>5.6</v>
+        <v>11.6</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>Historical + Risk/Vol strongest; chosen as a lowest-volatility Energy name under the sector cap</t>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility FMCG name under the sector cap</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
@@ -2559,12 +2559,12 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — IOC: 53; ONGC: 59. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — DABUR: 50; ITC: 57. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>Low-risk Energy holding (medium vol) • below 200-dma (-7.5%) • sector strength 75/100 • regime cautious (partial deploy) • 2 similar past recs: 50% positive, median +8.1%</t>
+          <t>Low-risk FMCG holding (medium vol) • below 200-dma (-14.5%) • sector strength 38/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
         </is>
       </c>
     </row>
@@ -2575,16 +2575,16 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Risk/Vol +16 · Historical +15 · Regime +9 · Trend/Tech +6 · Sector +5 = 51</t>
+          <t>Historical +17 · Risk/Vol +14 · Regime +9 · Trend/Tech +8 · Sector +1 = 49</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Risk/Vol</t>
+          <t>Historical</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -2593,36 +2593,36 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="G11" t="n">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="H11" t="n">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="I11" t="n">
-        <v>50</v>
+        <v>12</v>
       </c>
       <c r="J11" t="n">
         <v>60</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>DABUR</t>
+          <t>NHPC</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>Power</t>
         </is>
       </c>
       <c r="M11" t="n">
-        <v>392.3</v>
+        <v>76.3</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>381 - 404</t>
+          <t>74 - 79</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -2636,15 +2636,15 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-13.3%)</t>
+          <t>Below 200-DMA (-1.9%)</t>
         </is>
       </c>
       <c r="S11" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -2653,21 +2653,21 @@
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="V11" t="n">
-        <v>25107</v>
+        <v>16710</v>
       </c>
       <c r="W11" t="n">
-        <v>64</v>
+        <v>219</v>
       </c>
       <c r="X11" t="n">
-        <v>8.4</v>
+        <v>5.6</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility FMCG name under the sector cap</t>
+          <t>Historical + Risk/Vol strongest; chosen as a lowest-volatility Power name under the sector cap</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
@@ -2677,12 +2677,12 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — DABUR: 51; ITC: 57. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — NHPC: 49; TATAPOWER: 53, ADANIPOWER: 44, NLCINDIA: 28. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>Low-risk FMCG holding (medium vol) • below 200-dma (-13.3%) • sector strength 50/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
+          <t>Low-risk Power holding (medium vol) • below 200-dma (-1.9%) • sector strength 12/100 • regime cautious (partial deploy) • 1 similar past recs: 100% positive, median +7.2%</t>
         </is>
       </c>
     </row>
@@ -2693,31 +2693,31 @@
         </is>
       </c>
       <c r="B12" t="n">
+        <v>47</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Historical +19 · Risk/Vol +12 · Regime +9 · Trend/Tech +5 · Sector +2 = 47</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Historical</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Sector</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>62</v>
+      </c>
+      <c r="G12" t="n">
+        <v>26</v>
+      </c>
+      <c r="H12" t="n">
         <v>50</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Historical +17 · Risk/Vol +14 · Regime +9 · Trend/Tech +8 · Sector +2 = 50</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Historical</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Sector</t>
-        </is>
-      </c>
-      <c r="F12" t="n">
-        <v>57</v>
-      </c>
-      <c r="G12" t="n">
-        <v>39</v>
-      </c>
-      <c r="H12" t="n">
-        <v>54</v>
       </c>
       <c r="I12" t="n">
         <v>25</v>
@@ -2727,20 +2727,20 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>NHPC</t>
+          <t>WIPRO</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Power</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="M12" t="n">
-        <v>76.7</v>
+        <v>164.9</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>74 - 79</t>
+          <t>160 - 170</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -2754,15 +2754,15 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-1.4%)</t>
+          <t>Below 200-DMA (-19.1%)</t>
         </is>
       </c>
       <c r="S12" t="n">
-        <v>51</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2771,21 +2771,21 @@
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="V12" t="n">
-        <v>29825</v>
+        <v>21925</v>
       </c>
       <c r="W12" t="n">
-        <v>389</v>
+        <v>133</v>
       </c>
       <c r="X12" t="n">
-        <v>10</v>
+        <v>7.3</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>Historical + Risk/Vol strongest; chosen as a lowest-volatility Power name under the sector cap</t>
+          <t>Historical + Risk/Vol strongest; chosen as a lowest-volatility IT name under the sector cap</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
@@ -2795,12 +2795,12 @@
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — NHPC: 50; TATAPOWER: 54, ADANIPOWER: 44, NLCINDIA: 31. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — WIPRO: 47; TCS: 35, INFY: 33, KPITTECH: 28</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>Low-risk Power holding (medium vol) • below 200-dma (-1.4%) • sector strength 25/100 • regime cautious (partial deploy) • 1 similar past recs: 100% positive, median +7.2%</t>
+          <t>Low-risk IT holding (medium vol) • below 200-dma (-19.1%) • sector strength 25/100 • regime cautious (partial deploy) • 2 similar past recs: 100% positive, median +5.1%</t>
         </is>
       </c>
     </row>
@@ -27577,7 +27577,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27605,7 +27605,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>12.6%</t>
+          <t>12.9%</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -27615,12 +27615,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Metal</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>11.0%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -27630,12 +27630,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Metal</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>11.0%</t>
+          <t>11.5%</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -27650,7 +27650,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>10.7%</t>
+          <t>7.5%</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -27665,11 +27665,11 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>9.0%</t>
+          <t>6.3%</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -27680,7 +27680,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>5.8%</t>
+          <t>4.9%</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -27690,32 +27690,47 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CASH (intentional)</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>4.4%</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>CASH (intentional)</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>40.0%</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>11 stocks / 6 sectors</t>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>11 stocks / 7 sectors</t>
         </is>
       </c>
     </row>

--- a/reports/AEGIS_LATEST.xlsx
+++ b/reports/AEGIS_LATEST.xlsx
@@ -444,7 +444,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
     </row>
@@ -512,7 +512,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -536,7 +536,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>WIPRO (47)</t>
+          <t>NHPC (48)</t>
         </is>
       </c>
     </row>
@@ -548,7 +548,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>WIPRO</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>IOC</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -571,7 +571,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -688,7 +688,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-24  /  2026-09-24</t>
+          <t>2026-09-25  /  2026-09-25</t>
         </is>
       </c>
     </row>
@@ -760,7 +760,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -908,7 +908,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>15.2%</t>
+          <t>15.1%</t>
         </is>
       </c>
     </row>
@@ -920,7 +920,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>1.90</t>
         </is>
       </c>
     </row>
@@ -1534,7 +1534,7 @@
         <v>66</v>
       </c>
       <c r="G2" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H2" t="n">
         <v>92</v>
@@ -1556,11 +1556,11 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>1336.3</v>
+        <v>1327.4</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>1304 - 1368</t>
+          <t>1296 - 1359</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -1578,11 +1578,11 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-1.4%)</t>
+          <t>Below 200-DMA (-2.0%)</t>
         </is>
       </c>
       <c r="S2" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -1591,17 +1591,17 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="V2" t="n">
-        <v>32071</v>
+        <v>26548</v>
       </c>
       <c r="W2" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="X2" t="n">
-        <v>10.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
@@ -1615,12 +1615,12 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ICICIBANK: 66; PNB: 65, SBIN: 60, IDFCFIRSTB: 59</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ICICIBANK: 66; PNB: 65, SBIN: 60, IDFCFIRSTB: 57</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>Low-risk Financials holding (low vol) • below 200-dma (-1.4%) • sector strength 75/100 • regime cautious (partial deploy) • 8 similar past recs: 75% positive, median +5.3%</t>
+          <t>Low-risk Financials holding (low vol) • below 200-dma (-2.0%) • sector strength 75/100 • regime cautious (partial deploy) • 8 similar past recs: 75% positive, median +5.3%</t>
         </is>
       </c>
     </row>
@@ -1652,7 +1652,7 @@
         <v>50</v>
       </c>
       <c r="G3" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H3" t="n">
         <v>88</v>
@@ -1674,11 +1674,11 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>190.5</v>
+        <v>188.9</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>186 - 195</t>
+          <t>184 - 194</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -1696,11 +1696,11 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-1.6%)</t>
+          <t>Below 200-DMA (-2.4%)</t>
         </is>
       </c>
       <c r="S3" t="n">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -1709,17 +1709,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="V3" t="n">
-        <v>29524</v>
+        <v>20022</v>
       </c>
       <c r="W3" t="n">
-        <v>155</v>
+        <v>106</v>
       </c>
       <c r="X3" t="n">
-        <v>9.9</v>
+        <v>6.7</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
@@ -1733,12 +1733,12 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — TATASTEEL: 65; HINDZINC: 62, COALINDIA: 61, SAIL: 55</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — TATASTEEL: 65; HINDZINC: 62, COALINDIA: 61, SAIL: 54</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>Low-risk Metal holding (low vol) • below 200-dma (-1.6%) • outperforming Nifty • sector strength 100/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
+          <t>Low-risk Metal holding (low vol) • below 200-dma (-2.4%) • outperforming Nifty • sector strength 100/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
         </is>
       </c>
     </row>
@@ -1792,11 +1792,11 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>421.1</v>
+        <v>424.1</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>410 - 433</t>
+          <t>413 - 436</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -1814,7 +1814,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-2.5%)</t>
+          <t>Below 200-DMA (-1.8%)</t>
         </is>
       </c>
       <c r="S4" t="n">
@@ -1827,17 +1827,17 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="V4" t="n">
-        <v>32429</v>
+        <v>37321</v>
       </c>
       <c r="W4" t="n">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="X4" t="n">
-        <v>10.9</v>
+        <v>12.5</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -1851,12 +1851,12 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — COALINDIA: 61; TATASTEEL: 65, HINDZINC: 62, SAIL: 55. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — COALINDIA: 61; TATASTEEL: 65, HINDZINC: 62, SAIL: 54. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>Low-risk Metal holding (low vol) • below 200-dma (-2.5%) • sector strength 100/100 • regime cautious (partial deploy) • 3 similar past recs: 67% positive, median +0.8%</t>
+          <t>Low-risk Metal holding (low vol) • below 200-dma (-1.8%) • sector strength 100/100 • regime cautious (partial deploy) • 3 similar past recs: 67% positive, median +0.8%</t>
         </is>
       </c>
     </row>
@@ -1888,7 +1888,7 @@
         <v>53</v>
       </c>
       <c r="G5" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="H5" t="n">
         <v>69</v>
@@ -1910,11 +1910,11 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>235.9</v>
+        <v>236.1</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>229 - 243</t>
+          <t>230 - 243</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -1932,11 +1932,11 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-8.1%)</t>
+          <t>Below 200-DMA (-8.0%)</t>
         </is>
       </c>
       <c r="S5" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1945,17 +1945,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="V5" t="n">
-        <v>31136</v>
+        <v>35418</v>
       </c>
       <c r="W5" t="n">
-        <v>132</v>
+        <v>150</v>
       </c>
       <c r="X5" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>Low-risk Energy holding (low vol) • below 200-dma (-8.1%) • sector strength 88/100 • regime cautious (partial deploy) • 2 similar past recs: 50% positive, median +9.0%</t>
+          <t>Low-risk Energy holding (low vol) • below 200-dma (-8.0%) • outperforming Nifty • sector strength 88/100 • regime cautious (partial deploy) • 2 similar past recs: 50% positive, median +9.0%</t>
         </is>
       </c>
     </row>
@@ -2028,11 +2028,11 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>986.8</v>
+        <v>979.9</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>960 - 1014</t>
+          <t>953 - 1007</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -2050,11 +2050,11 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-5.2%)</t>
+          <t>Below 200-DMA (-5.9%)</t>
         </is>
       </c>
       <c r="S6" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -2063,17 +2063,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="V6" t="n">
-        <v>24670</v>
+        <v>19598</v>
       </c>
       <c r="W6" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="X6" t="n">
-        <v>8.4</v>
+        <v>6.7</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -2087,12 +2087,12 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — SBIN: 60; ICICIBANK: 66, PNB: 65, IDFCFIRSTB: 59. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — SBIN: 60; ICICIBANK: 66, PNB: 65, IDFCFIRSTB: 57. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>Low-risk Financials holding (low vol) • below 200-dma (-5.2%) • sector strength 75/100 • regime cautious (partial deploy) • 2 similar past recs: 100% positive, median +8.9%</t>
+          <t>Low-risk Financials holding (low vol) • below 200-dma (-5.9%) • sector strength 75/100 • regime cautious (partial deploy) • 2 similar past recs: 100% positive, median +8.9%</t>
         </is>
       </c>
     </row>
@@ -2124,7 +2124,7 @@
         <v>50</v>
       </c>
       <c r="G7" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="H7" t="n">
         <v>81</v>
@@ -2146,11 +2146,11 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>396.4</v>
+        <v>391.7</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>386 - 407</t>
+          <t>381 - 402</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -2168,11 +2168,11 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-5.2%)</t>
+          <t>Below 200-DMA (-6.3%)</t>
         </is>
       </c>
       <c r="S7" t="n">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -2181,17 +2181,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="V7" t="n">
-        <v>24574</v>
+        <v>19585</v>
       </c>
       <c r="W7" t="n">
-        <v>62</v>
+        <v>50</v>
       </c>
       <c r="X7" t="n">
-        <v>8.199999999999999</v>
+        <v>6.6</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -2210,7 +2210,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>Low-risk Industrials holding (low vol) • below 200-dma (-5.2%) • sector strength 62/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
+          <t>Low-risk Industrials holding (low vol) • below 200-dma (-6.3%) • sector strength 62/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
         </is>
       </c>
     </row>
@@ -2242,7 +2242,7 @@
         <v>44</v>
       </c>
       <c r="G8" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="H8" t="n">
         <v>96</v>
@@ -2264,11 +2264,11 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>268.8</v>
+        <v>267.1</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>263 - 275</t>
+          <t>261 - 273</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -2286,11 +2286,11 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-12.3%)</t>
+          <t>Below 200-DMA (-12.7%)</t>
         </is>
       </c>
       <c r="S8" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -2299,17 +2299,17 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="V8" t="n">
-        <v>29568</v>
+        <v>39798</v>
       </c>
       <c r="W8" t="n">
-        <v>110</v>
+        <v>149</v>
       </c>
       <c r="X8" t="n">
-        <v>9.9</v>
+        <v>13.3</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -2328,7 +2328,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>Low-risk FMCG holding (low vol) • below 200-dma (-12.3%) • sector strength 38/100 • regime cautious (partial deploy) • 9 similar past recs: 56% positive, median +0.3%</t>
+          <t>Low-risk FMCG holding (low vol) • below 200-dma (-12.7%) • sector strength 38/100 • regime cautious (partial deploy) • 9 similar past recs: 56% positive, median +0.3%</t>
         </is>
       </c>
     </row>
@@ -2382,11 +2382,11 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>366.1</v>
+        <v>365.4</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>357 - 376</t>
+          <t>356 - 375</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -2404,11 +2404,11 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-5.3%)</t>
+          <t>Below 200-DMA (-5.4%)</t>
         </is>
       </c>
       <c r="S9" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -2417,17 +2417,17 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="V9" t="n">
-        <v>20502</v>
+        <v>21559</v>
       </c>
       <c r="W9" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="X9" t="n">
-        <v>6.9</v>
+        <v>7.2</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -2441,12 +2441,12 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — TATAPOWER: 53; NHPC: 49, ADANIPOWER: 44, NLCINDIA: 28</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — TATAPOWER: 53; NHPC: 48, ADANIPOWER: 44, NLCINDIA: 28</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>Low-risk Power holding (low vol) • below 200-dma (-5.3%) • sector strength 12/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
+          <t>Low-risk Power holding (low vol) • below 200-dma (-5.4%) • sector strength 12/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
         </is>
       </c>
     </row>
@@ -2457,16 +2457,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Risk/Vol +16 · Historical +15 · Regime +9 · Trend/Tech +6 · Sector +4 = 50</t>
+          <t>Historical +19 · Risk/Vol +12 · Regime +9 · Trend/Tech +6 · Sector +5 = 51</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Risk/Vol</t>
+          <t>Historical</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -2475,36 +2475,36 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="G10" t="n">
         <v>29</v>
       </c>
       <c r="H10" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="I10" t="n">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="J10" t="n">
         <v>60</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>DABUR</t>
+          <t>WIPRO</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>386.4</v>
+        <v>163.3</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>375 - 398</t>
+          <t>158 - 168</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -2518,15 +2518,15 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-14.5%)</t>
+          <t>Below 200-DMA (-19.7%)</t>
         </is>
       </c>
       <c r="S10" t="n">
-        <v>54</v>
+        <v>27</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -2535,21 +2535,21 @@
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="V10" t="n">
-        <v>34772</v>
+        <v>29880</v>
       </c>
       <c r="W10" t="n">
-        <v>90</v>
+        <v>183</v>
       </c>
       <c r="X10" t="n">
-        <v>11.6</v>
+        <v>10</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility FMCG name under the sector cap</t>
+          <t>Historical + Risk/Vol strongest; chosen as a lowest-volatility IT name under the sector cap</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
@@ -2559,12 +2559,12 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — DABUR: 50; ITC: 57. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — WIPRO: 51; TCS: 39, INFY: 37, KPITTECH: 31</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>Low-risk FMCG holding (medium vol) • below 200-dma (-14.5%) • sector strength 38/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
+          <t>Low-risk IT holding (medium vol) • below 200-dma (-19.7%) • sector strength 50/100 • regime cautious (partial deploy) • 2 similar past recs: 100% positive, median +5.1%</t>
         </is>
       </c>
     </row>
@@ -2575,16 +2575,16 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Historical +17 · Risk/Vol +14 · Regime +9 · Trend/Tech +8 · Sector +1 = 49</t>
+          <t>Risk/Vol +16 · Historical +15 · Regime +9 · Trend/Tech +6 · Sector +4 = 50</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Historical</t>
+          <t>Risk/Vol</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -2593,36 +2593,36 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="G11" t="n">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="H11" t="n">
-        <v>54</v>
+        <v>65</v>
       </c>
       <c r="I11" t="n">
-        <v>12</v>
+        <v>38</v>
       </c>
       <c r="J11" t="n">
         <v>60</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>NHPC</t>
+          <t>DABUR</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Power</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="M11" t="n">
-        <v>76.3</v>
+        <v>384.2</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>74 - 79</t>
+          <t>373 - 395</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -2636,15 +2636,15 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-1.9%)</t>
+          <t>Below 200-DMA (-14.9%)</t>
         </is>
       </c>
       <c r="S11" t="n">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -2653,21 +2653,21 @@
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="V11" t="n">
-        <v>16710</v>
+        <v>28434</v>
       </c>
       <c r="W11" t="n">
-        <v>219</v>
+        <v>74</v>
       </c>
       <c r="X11" t="n">
-        <v>5.6</v>
+        <v>9.5</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>Historical + Risk/Vol strongest; chosen as a lowest-volatility Power name under the sector cap</t>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility FMCG name under the sector cap</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
@@ -2677,12 +2677,12 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — NHPC: 49; TATAPOWER: 53, ADANIPOWER: 44, NLCINDIA: 28. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — DABUR: 50; ITC: 57. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>Low-risk Power holding (medium vol) • below 200-dma (-1.9%) • sector strength 12/100 • regime cautious (partial deploy) • 1 similar past recs: 100% positive, median +7.2%</t>
+          <t>Low-risk FMCG holding (medium vol) • below 200-dma (-14.9%) • sector strength 38/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
         </is>
       </c>
     </row>
@@ -2693,11 +2693,11 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Historical +19 · Risk/Vol +12 · Regime +9 · Trend/Tech +5 · Sector +2 = 47</t>
+          <t>Historical +17 · Risk/Vol +14 · Regime +9 · Trend/Tech +7 · Sector +1 = 48</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2711,36 +2711,36 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="G12" t="n">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="H12" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="I12" t="n">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="J12" t="n">
         <v>60</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>WIPRO</t>
+          <t>NHPC</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>Power</t>
         </is>
       </c>
       <c r="M12" t="n">
-        <v>164.9</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>160 - 170</t>
+          <t>74 - 78</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -2754,15 +2754,15 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-19.1%)</t>
+          <t>Below 200-DMA (-2.4%)</t>
         </is>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>49</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2771,21 +2771,21 @@
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="V12" t="n">
-        <v>21925</v>
+        <v>19501</v>
       </c>
       <c r="W12" t="n">
-        <v>133</v>
+        <v>257</v>
       </c>
       <c r="X12" t="n">
-        <v>7.3</v>
+        <v>6.5</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>Historical + Risk/Vol strongest; chosen as a lowest-volatility IT name under the sector cap</t>
+          <t>Historical + Risk/Vol strongest; chosen as a lowest-volatility Power name under the sector cap</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
@@ -2795,12 +2795,12 @@
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — WIPRO: 47; TCS: 35, INFY: 33, KPITTECH: 28</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — NHPC: 48; TATAPOWER: 53, ADANIPOWER: 44, NLCINDIA: 28. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>Low-risk IT holding (medium vol) • below 200-dma (-19.1%) • sector strength 25/100 • regime cautious (partial deploy) • 2 similar past recs: 100% positive, median +5.1%</t>
+          <t>Low-risk Power holding (medium vol) • below 200-dma (-2.4%) • sector strength 12/100 • regime cautious (partial deploy) • 1 similar past recs: 100% positive, median +7.2%</t>
         </is>
       </c>
     </row>
@@ -27605,7 +27605,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>12.9%</t>
+          <t>13.7%</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -27620,7 +27620,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>11.5%</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -27635,7 +27635,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>11.5%</t>
+          <t>9.6%</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -27650,7 +27650,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>8.2%</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -27665,7 +27665,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>6.3%</t>
+          <t>7.1%</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -27675,12 +27675,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>4.9%</t>
+          <t>6.0%</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -27690,12 +27690,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>4.4%</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="C8" t="n">

--- a/reports/AEGIS_LATEST.xlsx
+++ b/reports/AEGIS_LATEST.xlsx
@@ -444,7 +444,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -479,7 +479,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6">
@@ -512,7 +512,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
@@ -524,7 +524,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ICICIBANK (66)</t>
+          <t>TATASTEEL (66)</t>
         </is>
       </c>
     </row>
@@ -536,7 +536,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>NHPC (48)</t>
+          <t>DABUR (47)</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>NHPC, WIPRO</t>
         </is>
       </c>
     </row>
@@ -571,7 +571,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -664,7 +664,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Hold a 11-stock risk-managed portfolio</t>
+          <t>Hold a 9-stock risk-managed portfolio</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-25  /  2026-09-25</t>
+          <t>2026-09-28  /  2026-09-28</t>
         </is>
       </c>
     </row>
@@ -760,7 +760,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
@@ -908,7 +908,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>15.1%</t>
+          <t>15.0%</t>
         </is>
       </c>
     </row>
@@ -920,7 +920,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>1.89</t>
         </is>
       </c>
     </row>
@@ -1361,7 +1361,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB12"/>
+  <dimension ref="A1:AB10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1517,7 +1517,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Risk/Vol +23 · Historical +20 · Regime +9 · Sector +8 · Trend/Tech +6 = 66</t>
+          <t>Risk/Vol +22 · Historical +15 · Trend/Tech +10 · Sector +10 · Regime +9 = 66</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -1527,62 +1527,62 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Trend/Tech</t>
+          <t>Regime</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="G2" t="n">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="H2" t="n">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="I2" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="J2" t="n">
         <v>60</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>ICICIBANK</t>
+          <t>TATASTEEL</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Metal</t>
         </is>
       </c>
       <c r="M2" t="n">
-        <v>1327.4</v>
+        <v>187.5</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>1296 - 1359</t>
+          <t>183 - 192</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>+2% to +8%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>75%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-2.0%)</t>
+          <t>Below 200-DMA (-3.2%)</t>
         </is>
       </c>
       <c r="S2" t="n">
-        <v>9</v>
+        <v>54</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -1591,21 +1591,21 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="V2" t="n">
-        <v>26548</v>
+        <v>33375</v>
       </c>
       <c r="W2" t="n">
-        <v>20</v>
+        <v>178</v>
       </c>
       <c r="X2" t="n">
-        <v>9.199999999999999</v>
+        <v>11.1</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Financials name under the sector cap</t>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Metal name under the sector cap</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
@@ -1615,27 +1615,27 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ICICIBANK: 66; PNB: 65, SBIN: 60, IDFCFIRSTB: 57</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — TATASTEEL: 66; COALINDIA: 62, SAIL: 55, HINDZINC: 54</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>Low-risk Financials holding (low vol) • below 200-dma (-2.0%) • sector strength 75/100 • regime cautious (partial deploy) • 8 similar past recs: 75% positive, median +5.3%</t>
+          <t>Low-risk Metal holding (low vol) • below 200-dma (-3.2%) • outperforming Nifty • sector strength 100/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>STRONG BUY</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Risk/Vol +22 · Historical +15 · Sector +10 · Trend/Tech +9 · Regime +9 = 65</t>
+          <t>Risk/Vol +23 · Historical +20 · Regime +9 · Trend/Tech +6 · Sector +6 = 64</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -1645,62 +1645,62 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Regime</t>
+          <t>Sector</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>50</v>
+        <v>66</v>
       </c>
       <c r="G3" t="n">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="H3" t="n">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="I3" t="n">
-        <v>100</v>
+        <v>62</v>
       </c>
       <c r="J3" t="n">
         <v>60</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>TATASTEEL</t>
+          <t>ICICIBANK</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Metal</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="M3" t="n">
-        <v>188.9</v>
+        <v>1303.2</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>184 - 194</t>
+          <t>1272 - 1334</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+2% to +8%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>75%</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-2.4%)</t>
+          <t>Below 200-DMA (-3.8%)</t>
         </is>
       </c>
       <c r="S3" t="n">
-        <v>57</v>
+        <v>8</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -1709,21 +1709,21 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="V3" t="n">
-        <v>20022</v>
+        <v>33883</v>
       </c>
       <c r="W3" t="n">
-        <v>106</v>
+        <v>26</v>
       </c>
       <c r="X3" t="n">
-        <v>6.7</v>
+        <v>11.5</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Metal name under the sector cap</t>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Financials name under the sector cap</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -1733,12 +1733,12 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — TATASTEEL: 65; HINDZINC: 62, COALINDIA: 61, SAIL: 54</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ICICIBANK: 64; SBIN: 58, IDFCFIRSTB: 55, PNB: 54</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>Low-risk Metal holding (low vol) • below 200-dma (-2.4%) • outperforming Nifty • sector strength 100/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
+          <t>Low-risk Financials holding (low vol) • below 200-dma (-3.8%) • sector strength 62/100 • regime cautious (partial deploy) • 8 similar past recs: 75% positive, median +5.3%</t>
         </is>
       </c>
     </row>
@@ -1749,11 +1749,11 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Risk/Vol +19 · Historical +15 · Sector +10 · Regime +9 · Trend/Tech +8 = 61</t>
+          <t>Risk/Vol +19 · Historical +15 · Sector +10 · Trend/Tech +9 · Regime +9 = 62</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1763,14 +1763,14 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Trend/Tech</t>
+          <t>Regime</t>
         </is>
       </c>
       <c r="F4" t="n">
         <v>51</v>
       </c>
       <c r="G4" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="H4" t="n">
         <v>77</v>
@@ -1792,11 +1792,11 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>424.1</v>
+        <v>427.3</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>413 - 436</t>
+          <t>416 - 439</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -1810,11 +1810,11 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-1.8%)</t>
+          <t>Below 200-DMA (-1.2%)</t>
         </is>
       </c>
       <c r="S4" t="n">
@@ -1827,17 +1827,17 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="V4" t="n">
-        <v>37321</v>
+        <v>31620</v>
       </c>
       <c r="W4" t="n">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="X4" t="n">
-        <v>12.5</v>
+        <v>10.6</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -1851,12 +1851,12 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — COALINDIA: 61; TATASTEEL: 65, HINDZINC: 62, SAIL: 54. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — COALINDIA: 62; TATASTEEL: 66, SAIL: 55, HINDZINC: 54. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>Low-risk Metal holding (low vol) • below 200-dma (-1.8%) • sector strength 100/100 • regime cautious (partial deploy) • 3 similar past recs: 67% positive, median +0.8%</t>
+          <t>Low-risk Metal holding (low vol) • below 200-dma (-1.2%) • outperforming Nifty • sector strength 100/100 • regime cautious (partial deploy) • 3 similar past recs: 67% positive, median +0.8%</t>
         </is>
       </c>
     </row>
@@ -1910,11 +1910,11 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>236.1</v>
+        <v>232.5</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>230 - 243</t>
+          <t>226 - 239</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -1932,11 +1932,11 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-8.0%)</t>
+          <t>Below 200-DMA (-9.4%)</t>
         </is>
       </c>
       <c r="S5" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1945,17 +1945,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="V5" t="n">
-        <v>35418</v>
+        <v>30225</v>
       </c>
       <c r="W5" t="n">
-        <v>150</v>
+        <v>130</v>
       </c>
       <c r="X5" t="n">
-        <v>11.8</v>
+        <v>10.1</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>Low-risk Energy holding (low vol) • below 200-dma (-8.0%) • outperforming Nifty • sector strength 88/100 • regime cautious (partial deploy) • 2 similar past recs: 50% positive, median +9.0%</t>
+          <t>Low-risk Energy holding (low vol) • below 200-dma (-9.4%) • outperforming Nifty • sector strength 88/100 • regime cautious (partial deploy) • 2 similar past recs: 50% positive, median +9.0%</t>
         </is>
       </c>
     </row>
@@ -1985,11 +1985,11 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Historical +20 · Risk/Vol +18 · Regime +9 · Sector +8 · Trend/Tech +5 = 60</t>
+          <t>Historical +20 · Risk/Vol +18 · Regime +9 · Sector +6 · Trend/Tech +5 = 58</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -2006,13 +2006,13 @@
         <v>65</v>
       </c>
       <c r="G6" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H6" t="n">
         <v>73</v>
       </c>
       <c r="I6" t="n">
-        <v>75</v>
+        <v>62</v>
       </c>
       <c r="J6" t="n">
         <v>60</v>
@@ -2028,11 +2028,11 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>979.9</v>
+        <v>965.7</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>953 - 1007</t>
+          <t>939 - 992</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -2046,15 +2046,15 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-5.9%)</t>
+          <t>Below 200-DMA (-7.2%)</t>
         </is>
       </c>
       <c r="S6" t="n">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -2063,17 +2063,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="V6" t="n">
-        <v>19598</v>
+        <v>28971</v>
       </c>
       <c r="W6" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="X6" t="n">
-        <v>6.7</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -2087,12 +2087,12 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — SBIN: 60; ICICIBANK: 66, PNB: 65, IDFCFIRSTB: 57. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — SBIN: 58; ICICIBANK: 64, IDFCFIRSTB: 55, PNB: 54. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>Low-risk Financials holding (low vol) • below 200-dma (-5.9%) • sector strength 75/100 • regime cautious (partial deploy) • 2 similar past recs: 100% positive, median +8.9%</t>
+          <t>Low-risk Financials holding (low vol) • below 200-dma (-7.2%) • sector strength 62/100 • regime cautious (partial deploy) • 2 similar past recs: 100% positive, median +8.9%</t>
         </is>
       </c>
     </row>
@@ -2103,11 +2103,11 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Risk/Vol +20 · Historical +15 · Regime +9 · Trend/Tech +8 · Sector +6 = 58</t>
+          <t>Risk/Vol +21 · Historical +15 · Regime +9 · Trend/Tech +8 · Sector +4 = 57</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -2124,33 +2124,33 @@
         <v>50</v>
       </c>
       <c r="G7" t="n">
+        <v>42</v>
+      </c>
+      <c r="H7" t="n">
+        <v>85</v>
+      </c>
+      <c r="I7" t="n">
         <v>38</v>
-      </c>
-      <c r="H7" t="n">
-        <v>81</v>
-      </c>
-      <c r="I7" t="n">
-        <v>62</v>
       </c>
       <c r="J7" t="n">
         <v>60</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>BEL</t>
+          <t>TATAPOWER</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Power</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>391.7</v>
+        <v>363</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>381 - 402</t>
+          <t>354 - 372</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -2168,11 +2168,11 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-6.3%)</t>
+          <t>Below 200-DMA (-6.0%)</t>
         </is>
       </c>
       <c r="S7" t="n">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -2181,21 +2181,21 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="V7" t="n">
-        <v>19585</v>
+        <v>32670</v>
       </c>
       <c r="W7" t="n">
-        <v>50</v>
+        <v>90</v>
       </c>
       <c r="X7" t="n">
-        <v>6.6</v>
+        <v>11</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Industrials name under the sector cap</t>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Power name under the sector cap</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -2205,12 +2205,12 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>No same-sector peer in the universe.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — TATAPOWER: 57; NHPC: 52, ADANIPOWER: 46, NLCINDIA: 31</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>Low-risk Industrials holding (low vol) • below 200-dma (-6.3%) • sector strength 62/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
+          <t>Low-risk Power holding (low vol) • below 200-dma (-6.0%) • sector strength 38/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
         </is>
       </c>
     </row>
@@ -2221,11 +2221,11 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Risk/Vol +24 · Historical +13 · Regime +9 · Trend/Tech +7 · Sector +4 = 57</t>
+          <t>Risk/Vol +24 · Historical +13 · Regime +9 · Trend/Tech +7 · Sector +2 = 55</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -2248,7 +2248,7 @@
         <v>96</v>
       </c>
       <c r="I8" t="n">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="J8" t="n">
         <v>60</v>
@@ -2264,11 +2264,11 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>267.1</v>
+        <v>266.1</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>261 - 273</t>
+          <t>260 - 272</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -2282,15 +2282,15 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-12.7%)</t>
+          <t>Below 200-DMA (-12.8%)</t>
         </is>
       </c>
       <c r="S8" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -2299,17 +2299,17 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="V8" t="n">
-        <v>39798</v>
+        <v>40189</v>
       </c>
       <c r="W8" t="n">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="X8" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -2323,12 +2323,12 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ITC: 57; DABUR: 50</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ITC: 55; DABUR: 47</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>Low-risk FMCG holding (low vol) • below 200-dma (-12.7%) • sector strength 38/100 • regime cautious (partial deploy) • 9 similar past recs: 56% positive, median +0.3%</t>
+          <t>Low-risk FMCG holding (low vol) • below 200-dma (-12.8%) • sector strength 25/100 • regime cautious (partial deploy) • 9 similar past recs: 56% positive, median +0.3%</t>
         </is>
       </c>
     </row>
@@ -2339,11 +2339,11 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Risk/Vol +21 · Historical +15 · Regime +9 · Trend/Tech +7 · Sector +1 = 53</t>
+          <t>Risk/Vol +20 · Historical +15 · Regime +9 · Trend/Tech +5 · Sector +5 = 54</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2360,33 +2360,33 @@
         <v>50</v>
       </c>
       <c r="G9" t="n">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="H9" t="n">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="I9" t="n">
-        <v>12</v>
+        <v>50</v>
       </c>
       <c r="J9" t="n">
         <v>60</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>TATAPOWER</t>
+          <t>BEL</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Power</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="M9" t="n">
-        <v>365.4</v>
+        <v>385.5</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>356 - 375</t>
+          <t>375 - 396</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -2404,11 +2404,11 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-5.4%)</t>
+          <t>Below 200-DMA (-7.8%)</t>
         </is>
       </c>
       <c r="S9" t="n">
-        <v>50</v>
+        <v>31</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -2417,21 +2417,21 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="V9" t="n">
-        <v>21559</v>
+        <v>38930</v>
       </c>
       <c r="W9" t="n">
-        <v>59</v>
+        <v>101</v>
       </c>
       <c r="X9" t="n">
-        <v>7.2</v>
+        <v>13</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Power name under the sector cap</t>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Industrials name under the sector cap</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
@@ -2441,12 +2441,12 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — TATAPOWER: 53; NHPC: 48, ADANIPOWER: 44, NLCINDIA: 28</t>
+          <t>No same-sector peer in the universe.</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>Low-risk Power holding (low vol) • below 200-dma (-5.4%) • sector strength 12/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
+          <t>Low-risk Industrials holding (low vol) • below 200-dma (-7.8%) • sector strength 50/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
         </is>
       </c>
     </row>
@@ -2457,16 +2457,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Historical +19 · Risk/Vol +12 · Regime +9 · Trend/Tech +6 · Sector +5 = 51</t>
+          <t>Risk/Vol +16 · Historical +15 · Regime +9 · Trend/Tech +5 · Sector +2 = 47</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Historical</t>
+          <t>Risk/Vol</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -2475,36 +2475,36 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>62</v>
+        <v>50</v>
       </c>
       <c r="G10" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="H10" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="I10" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="J10" t="n">
         <v>60</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>WIPRO</t>
+          <t>DABUR</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>163.3</v>
+        <v>383.5</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>158 - 168</t>
+          <t>372 - 395</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -2518,15 +2518,15 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-19.7%)</t>
+          <t>Below 200-DMA (-14.9%)</t>
         </is>
       </c>
       <c r="S10" t="n">
-        <v>27</v>
+        <v>57</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -2535,21 +2535,21 @@
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="V10" t="n">
-        <v>29880</v>
+        <v>28379</v>
       </c>
       <c r="W10" t="n">
-        <v>183</v>
+        <v>74</v>
       </c>
       <c r="X10" t="n">
-        <v>10</v>
+        <v>9.5</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>Historical + Risk/Vol strongest; chosen as a lowest-volatility IT name under the sector cap</t>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility FMCG name under the sector cap</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
@@ -2559,248 +2559,12 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — WIPRO: 51; TCS: 39, INFY: 37, KPITTECH: 31</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — DABUR: 47; ITC: 55. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>Low-risk IT holding (medium vol) • below 200-dma (-19.7%) • sector strength 50/100 • regime cautious (partial deploy) • 2 similar past recs: 100% positive, median +5.1%</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>ACCUMULATE</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>50</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Risk/Vol +16 · Historical +15 · Regime +9 · Trend/Tech +6 · Sector +4 = 50</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Risk/Vol</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Sector</t>
-        </is>
-      </c>
-      <c r="F11" t="n">
-        <v>50</v>
-      </c>
-      <c r="G11" t="n">
-        <v>30</v>
-      </c>
-      <c r="H11" t="n">
-        <v>65</v>
-      </c>
-      <c r="I11" t="n">
-        <v>38</v>
-      </c>
-      <c r="J11" t="n">
-        <v>60</v>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>DABUR</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>FMCG</t>
-        </is>
-      </c>
-      <c r="M11" t="n">
-        <v>384.2</v>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>373 - 395</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Q11" t="n">
-        <v>62</v>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>Below 200-DMA (-14.9%)</t>
-        </is>
-      </c>
-      <c r="S11" t="n">
-        <v>57</v>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>2 months (2M)</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>2026-10-25</t>
-        </is>
-      </c>
-      <c r="V11" t="n">
-        <v>28434</v>
-      </c>
-      <c r="W11" t="n">
-        <v>74</v>
-      </c>
-      <c r="X11" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility FMCG name under the sector cap</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>Fundamentals · Earnings · News · Flows</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — DABUR: 50; ITC: 57. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>Low-risk FMCG holding (medium vol) • below 200-dma (-14.9%) • sector strength 38/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>ACCUMULATE</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>48</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Historical +17 · Risk/Vol +14 · Regime +9 · Trend/Tech +7 · Sector +1 = 48</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Historical</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Sector</t>
-        </is>
-      </c>
-      <c r="F12" t="n">
-        <v>57</v>
-      </c>
-      <c r="G12" t="n">
-        <v>35</v>
-      </c>
-      <c r="H12" t="n">
-        <v>54</v>
-      </c>
-      <c r="I12" t="n">
-        <v>12</v>
-      </c>
-      <c r="J12" t="n">
-        <v>60</v>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>NHPC</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>Power</t>
-        </is>
-      </c>
-      <c r="M12" t="n">
-        <v>75.90000000000001</v>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>74 - 78</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Q12" t="n">
-        <v>65</v>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>Below 200-DMA (-2.4%)</t>
-        </is>
-      </c>
-      <c r="S12" t="n">
-        <v>49</v>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>2 months (2M)</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>2026-10-25</t>
-        </is>
-      </c>
-      <c r="V12" t="n">
-        <v>19501</v>
-      </c>
-      <c r="W12" t="n">
-        <v>257</v>
-      </c>
-      <c r="X12" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>Historical + Risk/Vol strongest; chosen as a lowest-volatility Power name under the sector cap</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>Fundamentals · Earnings · News · Flows</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — NHPC: 48; TATAPOWER: 53, ADANIPOWER: 44, NLCINDIA: 28. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>Low-risk Power holding (medium vol) • below 200-dma (-2.4%) • sector strength 12/100 • regime cautious (partial deploy) • 1 similar past recs: 100% positive, median +7.2%</t>
+          <t>Low-risk FMCG holding (medium vol) • below 200-dma (-14.9%) • sector strength 25/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
         </is>
       </c>
     </row>
@@ -26418,13 +26182,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D2" t="n">
         <v>0.6</v>
       </c>
       <c r="E2" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F2" t="n">
         <v>-5.6</v>
@@ -27577,7 +27341,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27605,7 +27369,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>13.7%</t>
+          <t>13.8%</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -27620,7 +27384,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>11.5%</t>
+          <t>13.1%</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -27635,7 +27399,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>9.6%</t>
+          <t>12.7%</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -27645,27 +27409,27 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Power</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>8.2%</t>
+          <t>7.8%</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Power</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>7.1%</t>
+          <t>6.6%</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -27675,12 +27439,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>6.0%</t>
+          <t>6.1%</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -27690,47 +27454,32 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>CASH (intentional)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CASH (intentional)</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>40.0%</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
           <t>100.0%</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>11 stocks / 7 sectors</t>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>9 stocks / 6 sectors</t>
         </is>
       </c>
     </row>

--- a/reports/AEGIS_LATEST.xlsx
+++ b/reports/AEGIS_LATEST.xlsx
@@ -444,7 +444,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
     </row>
@@ -479,7 +479,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6">
@@ -512,7 +512,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -536,7 +536,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>DABUR (47)</t>
+          <t>ITC (54)</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>NHPC, WIPRO</t>
+          <t>DABUR</t>
         </is>
       </c>
     </row>
@@ -571,7 +571,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -664,7 +664,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Hold a 9-stock risk-managed portfolio</t>
+          <t>Hold a 8-stock risk-managed portfolio</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-28  /  2026-09-28</t>
+          <t>2026-09-29  /  2026-09-29</t>
         </is>
       </c>
     </row>
@@ -760,7 +760,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -920,7 +920,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>1.89</t>
+          <t>1.88</t>
         </is>
       </c>
     </row>
@@ -1361,7 +1361,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB10"/>
+  <dimension ref="A1:AB9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1534,7 +1534,7 @@
         <v>50</v>
       </c>
       <c r="G2" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H2" t="n">
         <v>88</v>
@@ -1556,11 +1556,11 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>187.5</v>
+        <v>186.2</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>183 - 192</t>
+          <t>182 - 191</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -1578,11 +1578,11 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-3.2%)</t>
+          <t>Below 200-DMA (-3.9%)</t>
         </is>
       </c>
       <c r="S2" t="n">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -1591,17 +1591,17 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="V2" t="n">
-        <v>33375</v>
+        <v>37622</v>
       </c>
       <c r="W2" t="n">
-        <v>178</v>
+        <v>202</v>
       </c>
       <c r="X2" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
@@ -1615,27 +1615,27 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — TATASTEEL: 66; COALINDIA: 62, SAIL: 55, HINDZINC: 54</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — TATASTEEL: 66; COALINDIA: 62, SAIL: 55, HINDZINC: 51</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>Low-risk Metal holding (low vol) • below 200-dma (-3.2%) • outperforming Nifty • sector strength 100/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
+          <t>Low-risk Metal holding (low vol) • below 200-dma (-3.9%) • outperforming Nifty • sector strength 100/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>STRONG BUY</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Risk/Vol +23 · Historical +20 · Regime +9 · Trend/Tech +6 · Sector +6 = 64</t>
+          <t>Risk/Vol +24 · Historical +20 · Regime +9 · Trend/Tech +6 · Sector +6 = 65</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -1652,10 +1652,10 @@
         <v>66</v>
       </c>
       <c r="G3" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H3" t="n">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="I3" t="n">
         <v>62</v>
@@ -1674,11 +1674,11 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>1303.2</v>
+        <v>1302.7</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>1272 - 1334</t>
+          <t>1274 - 1331</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -1700,7 +1700,7 @@
         </is>
       </c>
       <c r="S3" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -1709,17 +1709,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="V3" t="n">
-        <v>33883</v>
+        <v>42989</v>
       </c>
       <c r="W3" t="n">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="X3" t="n">
-        <v>11.5</v>
+        <v>14.7</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
@@ -1733,7 +1733,7 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ICICIBANK: 64; SBIN: 58, IDFCFIRSTB: 55, PNB: 54</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ICICIBANK: 65; SBIN: 58, IDFCFIRSTB: 56, PNB: 55</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1770,7 +1770,7 @@
         <v>51</v>
       </c>
       <c r="G4" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H4" t="n">
         <v>77</v>
@@ -1792,11 +1792,11 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>427.3</v>
+        <v>425.5</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>416 - 439</t>
+          <t>414 - 437</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -1814,11 +1814,11 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-1.2%)</t>
+          <t>Below 200-DMA (-1.6%)</t>
         </is>
       </c>
       <c r="S4" t="n">
-        <v>54</v>
+        <v>43</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1827,17 +1827,17 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="V4" t="n">
-        <v>31620</v>
+        <v>36172</v>
       </c>
       <c r="W4" t="n">
-        <v>74</v>
+        <v>85</v>
       </c>
       <c r="X4" t="n">
-        <v>10.6</v>
+        <v>12.1</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -1851,12 +1851,12 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — COALINDIA: 62; TATASTEEL: 66, SAIL: 55, HINDZINC: 54. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — COALINDIA: 62; TATASTEEL: 66, SAIL: 55, HINDZINC: 51. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>Low-risk Metal holding (low vol) • below 200-dma (-1.2%) • outperforming Nifty • sector strength 100/100 • regime cautious (partial deploy) • 3 similar past recs: 67% positive, median +0.8%</t>
+          <t>Low-risk Metal holding (low vol) • below 200-dma (-1.6%) • outperforming Nifty • sector strength 100/100 • regime cautious (partial deploy) • 3 similar past recs: 67% positive, median +0.8%</t>
         </is>
       </c>
     </row>
@@ -1867,54 +1867,54 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Risk/Vol +17 · Historical +16 · Trend/Tech +9 · Regime +9 · Sector +9 = 60</t>
+          <t>Historical +20 · Risk/Vol +18 · Regime +9 · Sector +6 · Trend/Tech +5 = 58</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Risk/Vol</t>
+          <t>Historical</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Sector</t>
+          <t>Trend/Tech</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="G5" t="n">
-        <v>46</v>
+        <v>26</v>
       </c>
       <c r="H5" t="n">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="I5" t="n">
-        <v>88</v>
+        <v>62</v>
       </c>
       <c r="J5" t="n">
         <v>60</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>ONGC</t>
+          <t>SBIN</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="M5" t="n">
-        <v>232.5</v>
+        <v>959.7</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>226 - 239</t>
+          <t>934 - 986</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -1928,15 +1928,15 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-9.4%)</t>
+          <t>Below 200-DMA (-7.8%)</t>
         </is>
       </c>
       <c r="S5" t="n">
-        <v>48</v>
+        <v>29</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1945,21 +1945,21 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="V5" t="n">
-        <v>30225</v>
+        <v>32630</v>
       </c>
       <c r="W5" t="n">
-        <v>130</v>
+        <v>34</v>
       </c>
       <c r="X5" t="n">
-        <v>10.1</v>
+        <v>11.1</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Energy name under the sector cap</t>
+          <t>Historical + Risk/Vol strongest; chosen as a lowest-volatility Financials name under the sector cap</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1969,12 +1969,12 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ONGC: 60; IOC: 54</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — SBIN: 58; ICICIBANK: 65, IDFCFIRSTB: 56, PNB: 55. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>Low-risk Energy holding (low vol) • below 200-dma (-9.4%) • outperforming Nifty • sector strength 88/100 • regime cautious (partial deploy) • 2 similar past recs: 50% positive, median +9.0%</t>
+          <t>Low-risk Financials holding (low vol) • below 200-dma (-7.8%) • sector strength 62/100 • regime cautious (partial deploy) • 2 similar past recs: 100% positive, median +8.9%</t>
         </is>
       </c>
     </row>
@@ -1985,11 +1985,11 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Historical +20 · Risk/Vol +18 · Regime +9 · Sector +6 · Trend/Tech +5 = 58</t>
+          <t>Historical +16 · Risk/Vol +16 · Regime +9 · Sector +9 · Trend/Tech +7 = 57</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -2003,36 +2003,36 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>65</v>
+        <v>53</v>
       </c>
       <c r="G6" t="n">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="H6" t="n">
-        <v>73</v>
+        <v>62</v>
       </c>
       <c r="I6" t="n">
-        <v>62</v>
+        <v>88</v>
       </c>
       <c r="J6" t="n">
         <v>60</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>SBIN</t>
+          <t>ONGC</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="M6" t="n">
-        <v>965.7</v>
+        <v>231</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>939 - 992</t>
+          <t>225 - 237</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -2050,11 +2050,11 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-7.2%)</t>
+          <t>Below 200-DMA (-10.0%)</t>
         </is>
       </c>
       <c r="S6" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -2063,21 +2063,21 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="V6" t="n">
-        <v>28971</v>
+        <v>33496</v>
       </c>
       <c r="W6" t="n">
-        <v>30</v>
+        <v>145</v>
       </c>
       <c r="X6" t="n">
-        <v>9.699999999999999</v>
+        <v>11.2</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>Historical + Risk/Vol strongest; chosen as a lowest-volatility Financials name under the sector cap</t>
+          <t>Historical + Risk/Vol strongest; chosen as a lowest-volatility Energy name under the sector cap</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -2087,12 +2087,12 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — SBIN: 58; ICICIBANK: 64, IDFCFIRSTB: 55, PNB: 54. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ONGC: 57; IOC: 56</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>Low-risk Financials holding (low vol) • below 200-dma (-7.2%) • sector strength 62/100 • regime cautious (partial deploy) • 2 similar past recs: 100% positive, median +8.9%</t>
+          <t>Low-risk Energy holding (medium vol) • below 200-dma (-10.0%) • outperforming Nifty • sector strength 88/100 • regime cautious (partial deploy) • 2 similar past recs: 50% positive, median +9.0%</t>
         </is>
       </c>
     </row>
@@ -2103,11 +2103,11 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Risk/Vol +21 · Historical +15 · Regime +9 · Trend/Tech +8 · Sector +4 = 57</t>
+          <t>Risk/Vol +21 · Historical +15 · Regime +9 · Trend/Tech +7 · Sector +4 = 56</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -2124,7 +2124,7 @@
         <v>50</v>
       </c>
       <c r="G7" t="n">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="H7" t="n">
         <v>85</v>
@@ -2146,11 +2146,11 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>363</v>
+        <v>359.1</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>354 - 372</t>
+          <t>350 - 368</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -2164,15 +2164,15 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-6.0%)</t>
+          <t>Below 200-DMA (-7.0%)</t>
         </is>
       </c>
       <c r="S7" t="n">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -2181,17 +2181,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="V7" t="n">
-        <v>32670</v>
+        <v>35192</v>
       </c>
       <c r="W7" t="n">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="X7" t="n">
-        <v>11</v>
+        <v>11.8</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -2205,12 +2205,12 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — TATAPOWER: 57; NHPC: 52, ADANIPOWER: 46, NLCINDIA: 31</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — TATAPOWER: 56; NHPC: 48, ADANIPOWER: 43, NLCINDIA: 32</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>Low-risk Power holding (low vol) • below 200-dma (-6.0%) • sector strength 38/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
+          <t>Low-risk Power holding (low vol) • below 200-dma (-7.0%) • sector strength 38/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
         </is>
       </c>
     </row>
@@ -2225,7 +2225,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Risk/Vol +24 · Historical +13 · Regime +9 · Trend/Tech +7 · Sector +2 = 55</t>
+          <t>Risk/Vol +20 · Historical +15 · Regime +9 · Trend/Tech +6 · Sector +5 = 55</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -2239,58 +2239,58 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="G8" t="n">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="H8" t="n">
-        <v>96</v>
+        <v>81</v>
       </c>
       <c r="I8" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="J8" t="n">
         <v>60</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>ITC</t>
+          <t>BEL</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="M8" t="n">
-        <v>266.1</v>
+        <v>386.9</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>260 - 272</t>
+          <t>377 - 397</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>-4% to +3%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>56%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-12.8%)</t>
+          <t>Below 200-DMA (-7.4%)</t>
         </is>
       </c>
       <c r="S8" t="n">
-        <v>55</v>
+        <v>33</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -2299,21 +2299,21 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="V8" t="n">
-        <v>40189</v>
+        <v>35595</v>
       </c>
       <c r="W8" t="n">
-        <v>151</v>
+        <v>92</v>
       </c>
       <c r="X8" t="n">
-        <v>13.4</v>
+        <v>11.9</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility FMCG name under the sector cap</t>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Industrials name under the sector cap</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
@@ -2323,12 +2323,12 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ITC: 55; DABUR: 47</t>
+          <t>No same-sector peer in the universe.</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>Low-risk FMCG holding (low vol) • below 200-dma (-12.8%) • sector strength 25/100 • regime cautious (partial deploy) • 9 similar past recs: 56% positive, median +0.3%</t>
+          <t>Low-risk Industrials holding (low vol) • below 200-dma (-7.4%) • sector strength 50/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
         </is>
       </c>
     </row>
@@ -2343,7 +2343,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Risk/Vol +20 · Historical +15 · Regime +9 · Trend/Tech +5 · Sector +5 = 54</t>
+          <t>Risk/Vol +23 · Historical +13 · Regime +9 · Trend/Tech +7 · Sector +2 = 54</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2357,58 +2357,58 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="G9" t="n">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="H9" t="n">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="I9" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="J9" t="n">
         <v>60</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>BEL</t>
+          <t>ITC</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="M9" t="n">
-        <v>385.5</v>
+        <v>264.2</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>375 - 396</t>
+          <t>258 - 270</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-4% to +3%</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>56%</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-7.8%)</t>
+          <t>Below 200-DMA (-13.2%)</t>
         </is>
       </c>
       <c r="S9" t="n">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -2417,21 +2417,21 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="V9" t="n">
-        <v>38930</v>
+        <v>43857</v>
       </c>
       <c r="W9" t="n">
-        <v>101</v>
+        <v>166</v>
       </c>
       <c r="X9" t="n">
-        <v>13</v>
+        <v>14.6</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Industrials name under the sector cap</t>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility FMCG name under the sector cap</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
@@ -2441,130 +2441,12 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>No same-sector peer in the universe.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ITC: 54; DABUR: 45</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>Low-risk Industrials holding (low vol) • below 200-dma (-7.8%) • sector strength 50/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>ACCUMULATE</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>47</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Risk/Vol +16 · Historical +15 · Regime +9 · Trend/Tech +5 · Sector +2 = 47</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Risk/Vol</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Sector</t>
-        </is>
-      </c>
-      <c r="F10" t="n">
-        <v>50</v>
-      </c>
-      <c r="G10" t="n">
-        <v>27</v>
-      </c>
-      <c r="H10" t="n">
-        <v>65</v>
-      </c>
-      <c r="I10" t="n">
-        <v>25</v>
-      </c>
-      <c r="J10" t="n">
-        <v>60</v>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>DABUR</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>FMCG</t>
-        </is>
-      </c>
-      <c r="M10" t="n">
-        <v>383.5</v>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>372 - 395</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Q10" t="n">
-        <v>61</v>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>Below 200-DMA (-14.9%)</t>
-        </is>
-      </c>
-      <c r="S10" t="n">
-        <v>57</v>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>2 months (2M)</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>2026-10-28</t>
-        </is>
-      </c>
-      <c r="V10" t="n">
-        <v>28379</v>
-      </c>
-      <c r="W10" t="n">
-        <v>74</v>
-      </c>
-      <c r="X10" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility FMCG name under the sector cap</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>Fundamentals · Earnings · News · Flows</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — DABUR: 47; ITC: 55. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>Low-risk FMCG holding (medium vol) • below 200-dma (-14.9%) • sector strength 25/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
+          <t>Low-risk FMCG holding (low vol) • below 200-dma (-13.2%) • sector strength 25/100 • regime cautious (partial deploy) • 9 similar past recs: 56% positive, median +0.3%</t>
         </is>
       </c>
     </row>
@@ -27364,12 +27246,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>13.8%</t>
+          <t>15.5%</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -27384,7 +27266,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>13.1%</t>
+          <t>14.8%</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -27394,16 +27276,16 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>12.7%</t>
+          <t>8.8%</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -27414,7 +27296,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>7.8%</t>
+          <t>7.1%</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -27429,7 +27311,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>6.6%</t>
+          <t>7.1%</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -27444,7 +27326,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>6.1%</t>
+          <t>6.7%</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -27479,7 +27361,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>9 stocks / 6 sectors</t>
+          <t>8 stocks / 6 sectors</t>
         </is>
       </c>
     </row>

--- a/reports/AEGIS_LATEST.xlsx
+++ b/reports/AEGIS_LATEST.xlsx
@@ -444,7 +444,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -489,7 +489,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7">
@@ -512,7 +512,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -536,7 +536,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ITC (54)</t>
+          <t>ITC (55)</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>DABUR</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -571,7 +571,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -688,7 +688,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-29  /  2026-09-29</t>
+          <t>2026-09-30  /  2026-09-30</t>
         </is>
       </c>
     </row>
@@ -760,7 +760,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -908,7 +908,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>15.0%</t>
+          <t>14.9%</t>
         </is>
       </c>
     </row>
@@ -1534,7 +1534,7 @@
         <v>50</v>
       </c>
       <c r="G2" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="H2" t="n">
         <v>88</v>
@@ -1556,11 +1556,11 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>186.2</v>
+        <v>187.3</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>182 - 191</t>
+          <t>183 - 192</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -1578,11 +1578,11 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-3.9%)</t>
+          <t>Below 200-DMA (-3.4%)</t>
         </is>
       </c>
       <c r="S2" t="n">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -1591,14 +1591,14 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="V2" t="n">
-        <v>37622</v>
+        <v>37460</v>
       </c>
       <c r="W2" t="n">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="X2" t="n">
         <v>12.5</v>
@@ -1615,12 +1615,12 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — TATASTEEL: 66; COALINDIA: 62, SAIL: 55, HINDZINC: 51</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — TATASTEEL: 66; COALINDIA: 62, SAIL: 55, HINDZINC: 53</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>Low-risk Metal holding (low vol) • below 200-dma (-3.9%) • outperforming Nifty • sector strength 100/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
+          <t>Low-risk Metal holding (low vol) • below 200-dma (-3.4%) • outperforming Nifty • sector strength 100/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
         </is>
       </c>
     </row>
@@ -1652,7 +1652,7 @@
         <v>66</v>
       </c>
       <c r="G3" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="H3" t="n">
         <v>96</v>
@@ -1674,11 +1674,11 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>1302.7</v>
+        <v>1324</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>1274 - 1331</t>
+          <t>1295 - 1353</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -1696,11 +1696,11 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-3.8%)</t>
+          <t>Below 200-DMA (-2.2%)</t>
         </is>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -1709,17 +1709,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="V3" t="n">
-        <v>42989</v>
+        <v>38396</v>
       </c>
       <c r="W3" t="n">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="X3" t="n">
-        <v>14.7</v>
+        <v>13.2</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
@@ -1733,12 +1733,12 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ICICIBANK: 65; SBIN: 58, IDFCFIRSTB: 56, PNB: 55</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ICICIBANK: 65; SBIN: 59, IDFCFIRSTB: 56, PNB: 55</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>Low-risk Financials holding (low vol) • below 200-dma (-3.8%) • sector strength 62/100 • regime cautious (partial deploy) • 8 similar past recs: 75% positive, median +5.3%</t>
+          <t>Low-risk Financials holding (low vol) • below 200-dma (-2.2%) • sector strength 62/100 • regime cautious (partial deploy) • 8 similar past recs: 75% positive, median +5.3%</t>
         </is>
       </c>
     </row>
@@ -1770,7 +1770,7 @@
         <v>51</v>
       </c>
       <c r="G4" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H4" t="n">
         <v>77</v>
@@ -1792,11 +1792,11 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>425.5</v>
+        <v>430.9</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>414 - 437</t>
+          <t>419 - 442</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -1814,11 +1814,11 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-1.6%)</t>
+          <t>Below 200-DMA (-0.4%)</t>
         </is>
       </c>
       <c r="S4" t="n">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1827,14 +1827,14 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="V4" t="n">
-        <v>36172</v>
+        <v>36191</v>
       </c>
       <c r="W4" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="X4" t="n">
         <v>12.1</v>
@@ -1851,12 +1851,12 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — COALINDIA: 62; TATASTEEL: 66, SAIL: 55, HINDZINC: 51. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — COALINDIA: 62; TATASTEEL: 66, SAIL: 55, HINDZINC: 53. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>Low-risk Metal holding (low vol) • below 200-dma (-1.6%) • outperforming Nifty • sector strength 100/100 • regime cautious (partial deploy) • 3 similar past recs: 67% positive, median +0.8%</t>
+          <t>Low-risk Metal holding (low vol) • below 200-dma (-0.4%) • outperforming Nifty • sector strength 100/100 • regime cautious (partial deploy) • 3 similar past recs: 67% positive, median +0.8%</t>
         </is>
       </c>
     </row>
@@ -1867,11 +1867,11 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Historical +20 · Risk/Vol +18 · Regime +9 · Sector +6 · Trend/Tech +5 = 58</t>
+          <t>Historical +20 · Risk/Vol +18 · Regime +9 · Trend/Tech +6 · Sector +6 = 59</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1881,14 +1881,14 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Trend/Tech</t>
+          <t>Sector</t>
         </is>
       </c>
       <c r="F5" t="n">
         <v>65</v>
       </c>
       <c r="G5" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="H5" t="n">
         <v>73</v>
@@ -1910,11 +1910,11 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>959.7</v>
+        <v>968.1</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>934 - 986</t>
+          <t>942 - 994</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -1928,15 +1928,15 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-7.8%)</t>
+          <t>Below 200-DMA (-7.0%)</t>
         </is>
       </c>
       <c r="S5" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1945,17 +1945,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="V5" t="n">
-        <v>32630</v>
+        <v>30979</v>
       </c>
       <c r="W5" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="X5" t="n">
-        <v>11.1</v>
+        <v>10.3</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -1969,12 +1969,12 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — SBIN: 58; ICICIBANK: 65, IDFCFIRSTB: 56, PNB: 55. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — SBIN: 59; ICICIBANK: 65, IDFCFIRSTB: 56, PNB: 55. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>Low-risk Financials holding (low vol) • below 200-dma (-7.8%) • sector strength 62/100 • regime cautious (partial deploy) • 2 similar past recs: 100% positive, median +8.9%</t>
+          <t>Low-risk Financials holding (low vol) • below 200-dma (-7.0%) • sector strength 62/100 • regime cautious (partial deploy) • 2 similar past recs: 100% positive, median +8.9%</t>
         </is>
       </c>
     </row>
@@ -2006,7 +2006,7 @@
         <v>53</v>
       </c>
       <c r="G6" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H6" t="n">
         <v>62</v>
@@ -2028,11 +2028,11 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>231</v>
+        <v>228.7</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>225 - 237</t>
+          <t>222 - 235</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -2050,11 +2050,11 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-10.0%)</t>
+          <t>Below 200-DMA (-10.9%)</t>
         </is>
       </c>
       <c r="S6" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -2063,17 +2063,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="V6" t="n">
-        <v>33496</v>
+        <v>33846</v>
       </c>
       <c r="W6" t="n">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="X6" t="n">
-        <v>11.2</v>
+        <v>11.3</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -2087,12 +2087,12 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ONGC: 57; IOC: 56</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ONGC: 57; IOC: 57</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>Low-risk Energy holding (medium vol) • below 200-dma (-10.0%) • outperforming Nifty • sector strength 88/100 • regime cautious (partial deploy) • 2 similar past recs: 50% positive, median +9.0%</t>
+          <t>Low-risk Energy holding (medium vol) • below 200-dma (-10.9%) • outperforming Nifty • sector strength 88/100 • regime cautious (partial deploy) • 2 similar past recs: 50% positive, median +9.0%</t>
         </is>
       </c>
     </row>
@@ -2146,11 +2146,11 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>359.1</v>
+        <v>356.9</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>350 - 368</t>
+          <t>348 - 366</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -2168,7 +2168,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-7.0%)</t>
+          <t>Below 200-DMA (-7.6%)</t>
         </is>
       </c>
       <c r="S7" t="n">
@@ -2181,17 +2181,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="V7" t="n">
-        <v>35192</v>
+        <v>38902</v>
       </c>
       <c r="W7" t="n">
-        <v>98</v>
+        <v>109</v>
       </c>
       <c r="X7" t="n">
-        <v>11.8</v>
+        <v>13</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -2205,12 +2205,12 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — TATAPOWER: 56; NHPC: 48, ADANIPOWER: 43, NLCINDIA: 32</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — TATAPOWER: 56; NHPC: 47, ADANIPOWER: 45, NLCINDIA: 32</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>Low-risk Power holding (low vol) • below 200-dma (-7.0%) • sector strength 38/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
+          <t>Low-risk Power holding (low vol) • below 200-dma (-7.6%) • sector strength 38/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
         </is>
       </c>
     </row>
@@ -2225,7 +2225,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Risk/Vol +20 · Historical +15 · Regime +9 · Trend/Tech +6 · Sector +5 = 55</t>
+          <t>Risk/Vol +23 · Historical +13 · Regime +9 · Trend/Tech +8 · Sector +2 = 55</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -2239,58 +2239,58 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="G8" t="n">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="H8" t="n">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="I8" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="J8" t="n">
         <v>60</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>BEL</t>
+          <t>ITC</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="M8" t="n">
-        <v>386.9</v>
+        <v>266</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>377 - 397</t>
+          <t>260 - 272</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-4% to +3%</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>56%</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-7.4%)</t>
+          <t>Below 200-DMA (-12.5%)</t>
         </is>
       </c>
       <c r="S8" t="n">
-        <v>33</v>
+        <v>62</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -2299,21 +2299,21 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="V8" t="n">
-        <v>35595</v>
+        <v>46550</v>
       </c>
       <c r="W8" t="n">
-        <v>92</v>
+        <v>175</v>
       </c>
       <c r="X8" t="n">
-        <v>11.9</v>
+        <v>15.5</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Industrials name under the sector cap</t>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility FMCG name under the sector cap</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
@@ -2323,27 +2323,27 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>No same-sector peer in the universe.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ITC: 55; DABUR: 45</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>Low-risk Industrials holding (low vol) • below 200-dma (-7.4%) • sector strength 50/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
+          <t>Low-risk FMCG holding (low vol) • below 200-dma (-12.5%) • sector strength 25/100 • regime cautious (partial deploy) • 9 similar past recs: 56% positive, median +0.3%</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ACCUMULATE</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Risk/Vol +23 · Historical +13 · Regime +9 · Trend/Tech +7 · Sector +2 = 54</t>
+          <t>Risk/Vol +20 · Historical +15 · Regime +9 · Trend/Tech +6 · Sector +5 = 55</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2357,58 +2357,58 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="G9" t="n">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="H9" t="n">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="I9" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="J9" t="n">
         <v>60</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>ITC</t>
+          <t>BEL</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="M9" t="n">
-        <v>264.2</v>
+        <v>387.1</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>258 - 270</t>
+          <t>377 - 397</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>-4% to +3%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>56%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-13.2%)</t>
+          <t>Below 200-DMA (-7.4%)</t>
         </is>
       </c>
       <c r="S9" t="n">
-        <v>56</v>
+        <v>35</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -2417,21 +2417,21 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="V9" t="n">
-        <v>43857</v>
+        <v>35613</v>
       </c>
       <c r="W9" t="n">
-        <v>166</v>
+        <v>92</v>
       </c>
       <c r="X9" t="n">
-        <v>14.6</v>
+        <v>12</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility FMCG name under the sector cap</t>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Industrials name under the sector cap</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
@@ -2441,12 +2441,12 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ITC: 54; DABUR: 45</t>
+          <t>No same-sector peer in the universe.</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>Low-risk FMCG holding (low vol) • below 200-dma (-13.2%) • sector strength 25/100 • regime cautious (partial deploy) • 9 similar past recs: 56% positive, median +0.3%</t>
+          <t>Low-risk Industrials holding (low vol) • below 200-dma (-7.4%) • sector strength 50/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
         </is>
       </c>
     </row>
@@ -27246,12 +27246,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Metal</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>15.5%</t>
+          <t>14.8%</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -27261,12 +27261,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Metal</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>14.8%</t>
+          <t>14.1%</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -27281,7 +27281,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>8.8%</t>
+          <t>9.3%</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -27291,12 +27291,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Power</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>7.1%</t>
+          <t>7.8%</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -27306,12 +27306,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Power</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>7.1%</t>
+          <t>7.2%</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -27326,7 +27326,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>6.7%</t>
+          <t>6.8%</t>
         </is>
       </c>
       <c r="C7" t="n">

--- a/reports/AEGIS_LATEST.xlsx
+++ b/reports/AEGIS_LATEST.xlsx
@@ -444,7 +444,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
     </row>
@@ -489,7 +489,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7">
@@ -512,7 +512,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
     </row>
@@ -524,7 +524,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>TATASTEEL (66)</t>
+          <t>ICICIBANK (67)</t>
         </is>
       </c>
     </row>
@@ -536,7 +536,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ITC (55)</t>
+          <t>BEL (53)</t>
         </is>
       </c>
     </row>
@@ -582,7 +582,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>94%</t>
+          <t>84%</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-30  /  2026-09-30</t>
+          <t>2026-10-01  /  2026-10-01</t>
         </is>
       </c>
     </row>
@@ -760,7 +760,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
     </row>
@@ -908,7 +908,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>14.9%</t>
+          <t>14.8%</t>
         </is>
       </c>
     </row>
@@ -920,7 +920,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>1.87</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>94% (validated process)</t>
+          <t>84% (validated process)</t>
         </is>
       </c>
     </row>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Portfolio grade A (validated) · stock-alpha experimental</t>
+          <t>Portfolio grade B (validated) · stock-alpha experimental</t>
         </is>
       </c>
     </row>
@@ -1513,76 +1513,76 @@
         </is>
       </c>
       <c r="B2" t="n">
+        <v>67</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Risk/Vol +24 · Historical +20 · Regime +9 · Sector +8 · Trend/Tech +6 = 67</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Risk/Vol</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Trend/Tech</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
         <v>66</v>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Risk/Vol +22 · Historical +15 · Trend/Tech +10 · Sector +10 · Regime +9 = 66</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Risk/Vol</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Regime</t>
-        </is>
-      </c>
-      <c r="F2" t="n">
-        <v>50</v>
-      </c>
       <c r="G2" t="n">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="H2" t="n">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="I2" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="J2" t="n">
         <v>60</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>TATASTEEL</t>
+          <t>ICICIBANK</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Metal</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="M2" t="n">
-        <v>187.3</v>
+        <v>1325.3</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>183 - 192</t>
+          <t>1297 - 1353</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+2% to +8%</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>75%</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-3.4%)</t>
+          <t>Below 200-DMA (-2.1%)</t>
         </is>
       </c>
       <c r="S2" t="n">
-        <v>51</v>
+        <v>30</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -1591,21 +1591,21 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="V2" t="n">
-        <v>37460</v>
+        <v>42410</v>
       </c>
       <c r="W2" t="n">
-        <v>200</v>
+        <v>32</v>
       </c>
       <c r="X2" t="n">
-        <v>12.5</v>
+        <v>14.2</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Metal name under the sector cap</t>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Financials name under the sector cap</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
@@ -1615,12 +1615,12 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — TATASTEEL: 66; COALINDIA: 62, SAIL: 55, HINDZINC: 53</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ICICIBANK: 67; SBIN: 61, PNB: 59, IDFCFIRSTB: 58</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>Low-risk Metal holding (low vol) • below 200-dma (-3.4%) • outperforming Nifty • sector strength 100/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
+          <t>Low-risk Financials holding (low vol) • below 200-dma (-2.1%) • sector strength 75/100 • regime cautious (partial deploy) • 8 similar past recs: 75% positive, median +5.3%</t>
         </is>
       </c>
     </row>
@@ -1635,7 +1635,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Risk/Vol +24 · Historical +20 · Regime +9 · Trend/Tech +6 · Sector +6 = 65</t>
+          <t>Risk/Vol +22 · Historical +15 · Sector +10 · Trend/Tech +9 · Regime +9 = 65</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -1645,62 +1645,62 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sector</t>
+          <t>Regime</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>66</v>
+        <v>51</v>
       </c>
       <c r="G3" t="n">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="H3" t="n">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="I3" t="n">
-        <v>62</v>
+        <v>100</v>
       </c>
       <c r="J3" t="n">
         <v>60</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>ICICIBANK</t>
+          <t>COALINDIA</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Metal</t>
         </is>
       </c>
       <c r="M3" t="n">
-        <v>1324</v>
+        <v>421.2</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>1295 - 1353</t>
+          <t>410 - 432</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>+2% to +8%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>75%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-2.2%)</t>
+          <t>Below 200-DMA (-2.7%)</t>
         </is>
       </c>
       <c r="S3" t="n">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -1709,21 +1709,21 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="V3" t="n">
-        <v>38396</v>
+        <v>36644</v>
       </c>
       <c r="W3" t="n">
-        <v>29</v>
+        <v>87</v>
       </c>
       <c r="X3" t="n">
-        <v>13.2</v>
+        <v>12.2</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Financials name under the sector cap</t>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Metal name under the sector cap</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -1733,12 +1733,12 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ICICIBANK: 65; SBIN: 59, IDFCFIRSTB: 56, PNB: 55</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — COALINDIA: 65; TATASTEEL: 64, SAIL: 55, HINDZINC: 53</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>Low-risk Financials holding (low vol) • below 200-dma (-2.2%) • sector strength 62/100 • regime cautious (partial deploy) • 8 similar past recs: 75% positive, median +5.3%</t>
+          <t>Low-risk Metal holding (low vol) • below 200-dma (-2.7%) • outperforming Nifty • sector strength 100/100 • regime cautious (partial deploy) • 3 similar past recs: 67% positive, median +0.8%</t>
         </is>
       </c>
     </row>
@@ -1749,11 +1749,11 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Risk/Vol +19 · Historical +15 · Sector +10 · Trend/Tech +9 · Regime +9 = 62</t>
+          <t>Risk/Vol +21 · Historical +15 · Sector +10 · Trend/Tech +9 · Regime +9 = 64</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1767,13 +1767,13 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G4" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H4" t="n">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="I4" t="n">
         <v>100</v>
@@ -1783,7 +1783,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>COALINDIA</t>
+          <t>TATASTEEL</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -1792,11 +1792,11 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>430.9</v>
+        <v>182</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>419 - 442</t>
+          <t>177 - 187</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -1810,15 +1810,15 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-0.4%)</t>
+          <t>Below 200-DMA (-6.2%)</t>
         </is>
       </c>
       <c r="S4" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1827,17 +1827,17 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="V4" t="n">
-        <v>36191</v>
+        <v>35486</v>
       </c>
       <c r="W4" t="n">
-        <v>84</v>
+        <v>195</v>
       </c>
       <c r="X4" t="n">
-        <v>12.1</v>
+        <v>11.9</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -1851,12 +1851,12 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — COALINDIA: 62; TATASTEEL: 66, SAIL: 55, HINDZINC: 53. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — TATASTEEL: 64; COALINDIA: 65, SAIL: 55, HINDZINC: 53. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>Low-risk Metal holding (low vol) • below 200-dma (-0.4%) • outperforming Nifty • sector strength 100/100 • regime cautious (partial deploy) • 3 similar past recs: 67% positive, median +0.8%</t>
+          <t>Low-risk Metal holding (low vol) • below 200-dma (-6.2%) • outperforming Nifty • sector strength 100/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
         </is>
       </c>
     </row>
@@ -1867,11 +1867,11 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Historical +20 · Risk/Vol +18 · Regime +9 · Trend/Tech +6 · Sector +6 = 59</t>
+          <t>Historical +20 · Risk/Vol +18 · Regime +9 · Sector +8 · Trend/Tech +6 = 61</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1881,7 +1881,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Sector</t>
+          <t>Trend/Tech</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1894,7 +1894,7 @@
         <v>73</v>
       </c>
       <c r="I5" t="n">
-        <v>62</v>
+        <v>75</v>
       </c>
       <c r="J5" t="n">
         <v>60</v>
@@ -1910,11 +1910,11 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>968.1</v>
+        <v>962.5</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>942 - 994</t>
+          <t>937 - 988</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -1932,11 +1932,11 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-7.0%)</t>
+          <t>Below 200-DMA (-7.5%)</t>
         </is>
       </c>
       <c r="S5" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1945,17 +1945,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="V5" t="n">
-        <v>30979</v>
+        <v>31762</v>
       </c>
       <c r="W5" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="X5" t="n">
-        <v>10.3</v>
+        <v>10.9</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -1969,12 +1969,12 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — SBIN: 59; ICICIBANK: 65, IDFCFIRSTB: 56, PNB: 55. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — SBIN: 61; ICICIBANK: 67, PNB: 59, IDFCFIRSTB: 58. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>Low-risk Financials holding (low vol) • below 200-dma (-7.0%) • sector strength 62/100 • regime cautious (partial deploy) • 2 similar past recs: 100% positive, median +8.9%</t>
+          <t>Low-risk Financials holding (low vol) • below 200-dma (-7.5%) • sector strength 75/100 • regime cautious (partial deploy) • 2 similar past recs: 100% positive, median +8.9%</t>
         </is>
       </c>
     </row>
@@ -1985,54 +1985,54 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Historical +16 · Risk/Vol +16 · Regime +9 · Sector +9 · Trend/Tech +7 = 57</t>
+          <t>Risk/Vol +20 · Historical +15 · Regime +9 · Trend/Tech +7 · Sector +4 = 55</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Historical</t>
+          <t>Risk/Vol</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Trend/Tech</t>
+          <t>Sector</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="G6" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="H6" t="n">
-        <v>62</v>
+        <v>81</v>
       </c>
       <c r="I6" t="n">
-        <v>88</v>
+        <v>38</v>
       </c>
       <c r="J6" t="n">
         <v>60</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>ONGC</t>
+          <t>TATAPOWER</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Power</t>
         </is>
       </c>
       <c r="M6" t="n">
-        <v>228.7</v>
+        <v>354.1</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>222 - 235</t>
+          <t>345 - 363</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -2046,15 +2046,15 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-10.9%)</t>
+          <t>Below 200-DMA (-8.3%)</t>
         </is>
       </c>
       <c r="S6" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -2063,21 +2063,21 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="V6" t="n">
-        <v>33846</v>
+        <v>39305</v>
       </c>
       <c r="W6" t="n">
-        <v>148</v>
+        <v>111</v>
       </c>
       <c r="X6" t="n">
-        <v>11.3</v>
+        <v>13.2</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>Historical + Risk/Vol strongest; chosen as a lowest-volatility Energy name under the sector cap</t>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Power name under the sector cap</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -2087,27 +2087,27 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ONGC: 57; IOC: 57</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — TATAPOWER: 55; NHPC: 47, ADANIPOWER: 45, NLCINDIA: 32</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>Low-risk Energy holding (medium vol) • below 200-dma (-10.9%) • outperforming Nifty • sector strength 88/100 • regime cautious (partial deploy) • 2 similar past recs: 50% positive, median +9.0%</t>
+          <t>Low-risk Power holding (low vol) • below 200-dma (-8.3%) • sector strength 38/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>ACCUMULATE</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Risk/Vol +21 · Historical +15 · Regime +9 · Trend/Tech +7 · Sector +4 = 56</t>
+          <t>Risk/Vol +23 · Historical +13 · Regime +9 · Trend/Tech +7 · Sector +2 = 54</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -2121,58 +2121,58 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="G7" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="H7" t="n">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="I7" t="n">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="J7" t="n">
         <v>60</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>TATAPOWER</t>
+          <t>ITC</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Power</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>356.9</v>
+        <v>258.5</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>348 - 366</t>
+          <t>253 - 264</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-4% to +3%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>56%</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-7.6%)</t>
+          <t>Below 200-DMA (-14.7%)</t>
         </is>
       </c>
       <c r="S7" t="n">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -2181,21 +2181,21 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="V7" t="n">
-        <v>38902</v>
+        <v>45746</v>
       </c>
       <c r="W7" t="n">
-        <v>109</v>
+        <v>177</v>
       </c>
       <c r="X7" t="n">
-        <v>13</v>
+        <v>15.3</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Power name under the sector cap</t>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility FMCG name under the sector cap</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -2205,27 +2205,27 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — TATAPOWER: 56; NHPC: 47, ADANIPOWER: 45, NLCINDIA: 32</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ITC: 54; DABUR: 46</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>Low-risk Power holding (low vol) • below 200-dma (-7.6%) • sector strength 38/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
+          <t>Low-risk FMCG holding (low vol) • below 200-dma (-14.7%) • sector strength 25/100 • regime cautious (partial deploy) • 9 similar past recs: 56% positive, median +0.3%</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>ACCUMULATE</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Risk/Vol +23 · Historical +13 · Regime +9 · Trend/Tech +8 · Sector +2 = 55</t>
+          <t>Risk/Vol +19 · Historical +15 · Regime +9 · Trend/Tech +5 · Sector +5 = 53</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -2239,58 +2239,58 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="G8" t="n">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="H8" t="n">
-        <v>92</v>
+        <v>77</v>
       </c>
       <c r="I8" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="J8" t="n">
         <v>60</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>ITC</t>
+          <t>BEL</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="M8" t="n">
-        <v>266</v>
+        <v>384.2</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>260 - 272</t>
+          <t>374 - 394</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>-4% to +3%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>56%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-12.5%)</t>
+          <t>Below 200-DMA (-8.1%)</t>
         </is>
       </c>
       <c r="S8" t="n">
-        <v>62</v>
+        <v>36</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -2299,21 +2299,21 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="V8" t="n">
-        <v>46550</v>
+        <v>34578</v>
       </c>
       <c r="W8" t="n">
-        <v>175</v>
+        <v>90</v>
       </c>
       <c r="X8" t="n">
-        <v>15.5</v>
+        <v>11.6</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility FMCG name under the sector cap</t>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Industrials name under the sector cap</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
@@ -2323,32 +2323,32 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ITC: 55; DABUR: 45</t>
+          <t>No same-sector peer in the universe.</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>Low-risk FMCG holding (low vol) • below 200-dma (-12.5%) • sector strength 25/100 • regime cautious (partial deploy) • 9 similar past recs: 56% positive, median +0.3%</t>
+          <t>Low-risk Industrials holding (low vol) • below 200-dma (-8.1%) • sector strength 50/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>ACCUMULATE</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Risk/Vol +20 · Historical +15 · Regime +9 · Trend/Tech +6 · Sector +5 = 55</t>
+          <t>Historical +16 · Risk/Vol +16 · Regime +9 · Trend/Tech +6 · Sector +6 = 53</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Risk/Vol</t>
+          <t>Historical</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -2357,36 +2357,36 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="G9" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H9" t="n">
-        <v>81</v>
+        <v>62</v>
       </c>
       <c r="I9" t="n">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="J9" t="n">
         <v>60</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>BEL</t>
+          <t>ONGC</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="M9" t="n">
-        <v>387.1</v>
+        <v>223.4</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>377 - 397</t>
+          <t>217 - 230</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -2400,15 +2400,15 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-7.4%)</t>
+          <t>Below 200-DMA (-12.9%)</t>
         </is>
       </c>
       <c r="S9" t="n">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -2417,21 +2417,21 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="V9" t="n">
-        <v>35613</v>
+        <v>31945</v>
       </c>
       <c r="W9" t="n">
-        <v>92</v>
+        <v>143</v>
       </c>
       <c r="X9" t="n">
-        <v>12</v>
+        <v>10.7</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Industrials name under the sector cap</t>
+          <t>Historical + Risk/Vol strongest; chosen as a lowest-volatility Energy name under the sector cap</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
@@ -2441,12 +2441,12 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>No same-sector peer in the universe.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ONGC: 53; IOC: 52</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>Low-risk Industrials holding (low vol) • below 200-dma (-7.4%) • sector strength 50/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
+          <t>Low-risk Energy holding (medium vol) • below 200-dma (-12.9%) • sector strength 62/100 • regime cautious (partial deploy) • 2 similar past recs: 50% positive, median +9.0%</t>
         </is>
       </c>
     </row>
@@ -27246,12 +27246,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Metal</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>14.8%</t>
+          <t>15.0%</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -27261,12 +27261,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Metal</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>14.1%</t>
+          <t>14.5%</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -27281,7 +27281,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>9.3%</t>
+          <t>9.2%</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -27296,7 +27296,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>7.8%</t>
+          <t>7.9%</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -27311,7 +27311,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>7.2%</t>
+          <t>7.0%</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -27326,7 +27326,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>6.8%</t>
+          <t>6.4%</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -27607,7 +27607,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>The PORTFOLIO process (grade A): beat Nifty 68% of cycles, ~half the drawdown, higher risk-adjusted return. Out-of-sample tested.</t>
+          <t>The PORTFOLIO process (grade B): beat Nifty 68% of cycles, ~half the drawdown, higher risk-adjusted return. Out-of-sample tested.</t>
         </is>
       </c>
     </row>
@@ -27703,7 +27703,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>VALIDATED — grade A · beat Nifty 68% of cycles</t>
+          <t>VALIDATED — grade B · beat Nifty 68% of cycles</t>
         </is>
       </c>
     </row>

--- a/reports/AEGIS_LATEST.xlsx
+++ b/reports/AEGIS_LATEST.xlsx
@@ -444,7 +444,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-01  /  2026-10-01</t>
+          <t>2026-10-02  /  2026-10-01</t>
         </is>
       </c>
     </row>

--- a/reports/AEGIS_LATEST.xlsx
+++ b/reports/AEGIS_LATEST.xlsx
@@ -444,7 +444,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-05</t>
         </is>
       </c>
     </row>
@@ -512,7 +512,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-04</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-02  /  2026-10-01</t>
+          <t>2026-10-05  /  2026-10-05</t>
         </is>
       </c>
     </row>
@@ -760,7 +760,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-04</t>
         </is>
       </c>
     </row>
@@ -1534,7 +1534,7 @@
         <v>66</v>
       </c>
       <c r="G2" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H2" t="n">
         <v>96</v>
@@ -1556,11 +1556,11 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>1325.3</v>
+        <v>1318.3</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>1297 - 1353</t>
+          <t>1291 - 1346</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -1578,11 +1578,11 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-2.1%)</t>
+          <t>Below 200-DMA (-2.6%)</t>
         </is>
       </c>
       <c r="S2" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -1591,17 +1591,17 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="V2" t="n">
-        <v>42410</v>
+        <v>42186</v>
       </c>
       <c r="W2" t="n">
         <v>32</v>
       </c>
       <c r="X2" t="n">
-        <v>14.2</v>
+        <v>14.5</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
@@ -1615,12 +1615,12 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ICICIBANK: 67; SBIN: 61, PNB: 59, IDFCFIRSTB: 58</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ICICIBANK: 67; SBIN: 61, IDFCFIRSTB: 60, PNB: 57</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>Low-risk Financials holding (low vol) • below 200-dma (-2.1%) • sector strength 75/100 • regime cautious (partial deploy) • 8 similar past recs: 75% positive, median +5.3%</t>
+          <t>Low-risk Financials holding (low vol) • below 200-dma (-2.6%) • sector strength 75/100 • regime cautious (partial deploy) • 8 similar past recs: 75% positive, median +5.3%</t>
         </is>
       </c>
     </row>
@@ -1635,7 +1635,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Risk/Vol +22 · Historical +15 · Sector +10 · Trend/Tech +9 · Regime +9 = 65</t>
+          <t>Risk/Vol +21 · Historical +15 · Trend/Tech +10 · Sector +10 · Regime +9 = 65</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -1652,10 +1652,10 @@
         <v>51</v>
       </c>
       <c r="G3" t="n">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="H3" t="n">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="I3" t="n">
         <v>100</v>
@@ -1674,11 +1674,11 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>421.2</v>
+        <v>424.8</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>410 - 432</t>
+          <t>414 - 436</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -1696,11 +1696,11 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-2.7%)</t>
+          <t>Below 200-DMA (-1.9%)</t>
         </is>
       </c>
       <c r="S3" t="n">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -1709,14 +1709,14 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="V3" t="n">
-        <v>36644</v>
+        <v>36528</v>
       </c>
       <c r="W3" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="X3" t="n">
         <v>12.2</v>
@@ -1733,12 +1733,12 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — COALINDIA: 65; TATASTEEL: 64, SAIL: 55, HINDZINC: 53</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — COALINDIA: 65; TATASTEEL: 63, SAIL: 55, HINDZINC: 53</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>Low-risk Metal holding (low vol) • below 200-dma (-2.7%) • outperforming Nifty • sector strength 100/100 • regime cautious (partial deploy) • 3 similar past recs: 67% positive, median +0.8%</t>
+          <t>Low-risk Metal holding (low vol) • below 200-dma (-1.9%) • outperforming Nifty • sector strength 100/100 • regime cautious (partial deploy) • 3 similar past recs: 67% positive, median +0.8%</t>
         </is>
       </c>
     </row>
@@ -1749,11 +1749,11 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Risk/Vol +21 · Historical +15 · Sector +10 · Trend/Tech +9 · Regime +9 = 64</t>
+          <t>Risk/Vol +20 · Historical +15 · Sector +10 · Trend/Tech +9 · Regime +9 = 63</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1770,10 +1770,10 @@
         <v>50</v>
       </c>
       <c r="G4" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H4" t="n">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="I4" t="n">
         <v>100</v>
@@ -1792,11 +1792,11 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>182</v>
+        <v>177.9</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>177 - 187</t>
+          <t>173 - 183</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -1810,15 +1810,15 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-6.2%)</t>
+          <t>Below 200-DMA (-8.3%)</t>
         </is>
       </c>
       <c r="S4" t="n">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1827,17 +1827,17 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="V4" t="n">
-        <v>35486</v>
+        <v>34874</v>
       </c>
       <c r="W4" t="n">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="X4" t="n">
-        <v>11.9</v>
+        <v>11.7</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -1851,12 +1851,12 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — TATASTEEL: 64; COALINDIA: 65, SAIL: 55, HINDZINC: 53. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — TATASTEEL: 63; COALINDIA: 65, SAIL: 55, HINDZINC: 53. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>Low-risk Metal holding (low vol) • below 200-dma (-6.2%) • outperforming Nifty • sector strength 100/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
+          <t>Low-risk Metal holding (low vol) • below 200-dma (-8.3%) • outperforming Nifty • sector strength 100/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
         </is>
       </c>
     </row>
@@ -1910,11 +1910,11 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>962.5</v>
+        <v>961</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>937 - 988</t>
+          <t>936 - 986</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-7.5%)</t>
+          <t>Below 200-DMA (-7.7%)</t>
         </is>
       </c>
       <c r="S5" t="n">
@@ -1945,17 +1945,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="V5" t="n">
-        <v>31762</v>
+        <v>31713</v>
       </c>
       <c r="W5" t="n">
         <v>33</v>
       </c>
       <c r="X5" t="n">
-        <v>10.9</v>
+        <v>10.8</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -1969,12 +1969,12 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — SBIN: 61; ICICIBANK: 67, PNB: 59, IDFCFIRSTB: 58. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — SBIN: 61; ICICIBANK: 67, IDFCFIRSTB: 60, PNB: 57. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>Low-risk Financials holding (low vol) • below 200-dma (-7.5%) • sector strength 75/100 • regime cautious (partial deploy) • 2 similar past recs: 100% positive, median +8.9%</t>
+          <t>Low-risk Financials holding (low vol) • below 200-dma (-7.7%) • sector strength 75/100 • regime cautious (partial deploy) • 2 similar past recs: 100% positive, median +8.9%</t>
         </is>
       </c>
     </row>
@@ -1985,11 +1985,11 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Risk/Vol +20 · Historical +15 · Regime +9 · Trend/Tech +7 · Sector +4 = 55</t>
+          <t>Risk/Vol +22 · Historical +15 · Regime +9 · Trend/Tech +7 · Sector +4 = 57</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -2009,7 +2009,7 @@
         <v>33</v>
       </c>
       <c r="H6" t="n">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="I6" t="n">
         <v>38</v>
@@ -2028,11 +2028,11 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>354.1</v>
+        <v>350.3</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>345 - 363</t>
+          <t>341 - 359</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -2046,15 +2046,15 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-8.3%)</t>
+          <t>Below 200-DMA (-9.2%)</t>
         </is>
       </c>
       <c r="S6" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -2063,17 +2063,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="V6" t="n">
-        <v>39305</v>
+        <v>39934</v>
       </c>
       <c r="W6" t="n">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="X6" t="n">
-        <v>13.2</v>
+        <v>13.3</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -2087,12 +2087,12 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — TATAPOWER: 55; NHPC: 47, ADANIPOWER: 45, NLCINDIA: 32</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — TATAPOWER: 57; ADANIPOWER: 46, NHPC: 45, NLCINDIA: 32</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>Low-risk Power holding (low vol) • below 200-dma (-8.3%) • sector strength 38/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
+          <t>Low-risk Power holding (low vol) • below 200-dma (-9.2%) • sector strength 38/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
         </is>
       </c>
     </row>
@@ -2124,7 +2124,7 @@
         <v>44</v>
       </c>
       <c r="G7" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="H7" t="n">
         <v>92</v>
@@ -2146,11 +2146,11 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>258.5</v>
+        <v>262.4</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>253 - 264</t>
+          <t>256 - 268</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -2168,11 +2168,11 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-14.7%)</t>
+          <t>Below 200-DMA (-13.2%)</t>
         </is>
       </c>
       <c r="S7" t="n">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -2181,17 +2181,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="V7" t="n">
-        <v>45746</v>
+        <v>45395</v>
       </c>
       <c r="W7" t="n">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="X7" t="n">
-        <v>15.3</v>
+        <v>15.2</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -2205,12 +2205,12 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ITC: 54; DABUR: 46</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ITC: 54; DABUR: 45</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>Low-risk FMCG holding (low vol) • below 200-dma (-14.7%) • sector strength 25/100 • regime cautious (partial deploy) • 9 similar past recs: 56% positive, median +0.3%</t>
+          <t>Low-risk FMCG holding (low vol) • below 200-dma (-13.2%) • sector strength 25/100 • regime cautious (partial deploy) • 9 similar past recs: 56% positive, median +0.3%</t>
         </is>
       </c>
     </row>
@@ -2242,7 +2242,7 @@
         <v>50</v>
       </c>
       <c r="G8" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H8" t="n">
         <v>77</v>
@@ -2264,11 +2264,11 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>384.2</v>
+        <v>380</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>374 - 394</t>
+          <t>370 - 390</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -2286,11 +2286,11 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-8.1%)</t>
+          <t>Below 200-DMA (-9.0%)</t>
         </is>
       </c>
       <c r="S8" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -2299,14 +2299,14 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="V8" t="n">
-        <v>34578</v>
+        <v>34585</v>
       </c>
       <c r="W8" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="X8" t="n">
         <v>11.6</v>
@@ -2328,7 +2328,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>Low-risk Industrials holding (low vol) • below 200-dma (-8.1%) • sector strength 50/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
+          <t>Low-risk Industrials holding (low vol) • below 200-dma (-9.0%) • sector strength 50/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
         </is>
       </c>
     </row>
@@ -2382,11 +2382,11 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>223.4</v>
+        <v>222.7</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>217 - 230</t>
+          <t>216 - 229</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -2404,11 +2404,11 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-12.9%)</t>
+          <t>Below 200-DMA (-13.2%)</t>
         </is>
       </c>
       <c r="S9" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -2417,14 +2417,14 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="V9" t="n">
-        <v>31945</v>
+        <v>32063</v>
       </c>
       <c r="W9" t="n">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="X9" t="n">
         <v>10.7</v>
@@ -2441,12 +2441,12 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ONGC: 53; IOC: 52</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ONGC: 53; IOC: 49</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>Low-risk Energy holding (medium vol) • below 200-dma (-12.9%) • sector strength 62/100 • regime cautious (partial deploy) • 2 similar past recs: 50% positive, median +9.0%</t>
+          <t>Low-risk Energy holding (medium vol) • below 200-dma (-13.2%) • sector strength 62/100 • regime cautious (partial deploy) • 2 similar past recs: 50% positive, median +9.0%</t>
         </is>
       </c>
     </row>
@@ -27251,7 +27251,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>15.0%</t>
+          <t>15.2%</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -27266,7 +27266,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>14.5%</t>
+          <t>14.3%</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -27281,7 +27281,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>9.2%</t>
+          <t>9.1%</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -27296,7 +27296,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>7.9%</t>
+          <t>8.0%</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -27311,7 +27311,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>7.0%</t>
+          <t>6.9%</t>
         </is>
       </c>
       <c r="C6" t="n">

--- a/reports/AEGIS_LATEST.xlsx
+++ b/reports/AEGIS_LATEST.xlsx
@@ -444,7 +444,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
     </row>
@@ -489,7 +489,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7">
@@ -512,7 +512,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-05</t>
         </is>
       </c>
     </row>
@@ -524,7 +524,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ICICIBANK (67)</t>
+          <t>ICICIBANK (71)</t>
         </is>
       </c>
     </row>
@@ -536,7 +536,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>BEL (53)</t>
+          <t>ONGC (51)</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-05  /  2026-10-05</t>
+          <t>2026-10-06  /  2026-10-06</t>
         </is>
       </c>
     </row>
@@ -760,7 +760,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-05</t>
         </is>
       </c>
     </row>
@@ -908,7 +908,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>14.8%</t>
+          <t>14.9%</t>
         </is>
       </c>
     </row>
@@ -1513,11 +1513,11 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Risk/Vol +24 · Historical +20 · Regime +9 · Sector +8 · Trend/Tech +6 = 67</t>
+          <t>Risk/Vol +24 · Historical +20 · Trend/Tech +9 · Regime +9 · Sector +9 = 71</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -1527,20 +1527,20 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Trend/Tech</t>
+          <t>Sector</t>
         </is>
       </c>
       <c r="F2" t="n">
         <v>66</v>
       </c>
       <c r="G2" t="n">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="H2" t="n">
         <v>96</v>
       </c>
       <c r="I2" t="n">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="J2" t="n">
         <v>60</v>
@@ -1556,11 +1556,11 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>1318.3</v>
+        <v>1334.3</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>1291 - 1346</t>
+          <t>1306 - 1362</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -1574,15 +1574,15 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-2.6%)</t>
+          <t>Below 200-DMA (-1.4%)</t>
         </is>
       </c>
       <c r="S2" t="n">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -1591,17 +1591,17 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="V2" t="n">
-        <v>42186</v>
+        <v>45366</v>
       </c>
       <c r="W2" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="X2" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
@@ -1615,27 +1615,27 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ICICIBANK: 67; SBIN: 61, IDFCFIRSTB: 60, PNB: 57</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ICICIBANK: 71; SBIN: 64, IDFCFIRSTB: 59, PNB: 58</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>Low-risk Financials holding (low vol) • below 200-dma (-2.6%) • sector strength 75/100 • regime cautious (partial deploy) • 8 similar past recs: 75% positive, median +5.3%</t>
+          <t>Low-risk Financials holding (low vol) • below 200-dma (-1.4%) • sector strength 88/100 • regime cautious (partial deploy) • 8 similar past recs: 75% positive, median +5.3%</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>STRONG BUY</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Risk/Vol +21 · Historical +15 · Trend/Tech +10 · Sector +10 · Regime +9 = 65</t>
+          <t>Risk/Vol +21 · Historical +15 · Sector +10 · Trend/Tech +9 · Regime +9 = 64</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -1649,10 +1649,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G3" t="n">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="H3" t="n">
         <v>85</v>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>COALINDIA</t>
+          <t>TATASTEEL</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -1674,11 +1674,11 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>424.8</v>
+        <v>179.4</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>414 - 436</t>
+          <t>175 - 184</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -1692,15 +1692,15 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-1.9%)</t>
+          <t>Below 200-DMA (-7.6%)</t>
         </is>
       </c>
       <c r="S3" t="n">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -1709,17 +1709,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="V3" t="n">
-        <v>36528</v>
+        <v>35172</v>
       </c>
       <c r="W3" t="n">
-        <v>86</v>
+        <v>196</v>
       </c>
       <c r="X3" t="n">
-        <v>12.2</v>
+        <v>11.7</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
@@ -1733,12 +1733,12 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — COALINDIA: 65; TATASTEEL: 63, SAIL: 55, HINDZINC: 53</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — TATASTEEL: 64; COALINDIA: 63, SAIL: 55, HINDZINC: 53</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>Low-risk Metal holding (low vol) • below 200-dma (-1.9%) • outperforming Nifty • sector strength 100/100 • regime cautious (partial deploy) • 3 similar past recs: 67% positive, median +0.8%</t>
+          <t>Low-risk Metal holding (low vol) • below 200-dma (-7.6%) • sector strength 100/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
         </is>
       </c>
     </row>
@@ -1749,54 +1749,54 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Risk/Vol +20 · Historical +15 · Sector +10 · Trend/Tech +9 · Regime +9 = 63</t>
+          <t>Historical +20 · Risk/Vol +18 · Regime +9 · Sector +9 · Trend/Tech +8 = 64</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Risk/Vol</t>
+          <t>Historical</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Regime</t>
+          <t>Trend/Tech</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="G4" t="n">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="H4" t="n">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="I4" t="n">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="J4" t="n">
         <v>60</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>TATASTEEL</t>
+          <t>SBIN</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Metal</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>177.9</v>
+        <v>952.8</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>173 - 183</t>
+          <t>928 - 978</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -1810,15 +1810,15 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-8.3%)</t>
+          <t>Below 200-DMA (-8.5%)</t>
         </is>
       </c>
       <c r="S4" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1827,21 +1827,21 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="V4" t="n">
-        <v>34874</v>
+        <v>34299</v>
       </c>
       <c r="W4" t="n">
-        <v>196</v>
+        <v>36</v>
       </c>
       <c r="X4" t="n">
         <v>11.7</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Metal name under the sector cap</t>
+          <t>Historical + Risk/Vol strongest; chosen as a lowest-volatility Financials name under the sector cap</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1851,12 +1851,12 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — TATASTEEL: 63; COALINDIA: 65, SAIL: 55, HINDZINC: 53. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — SBIN: 64; ICICIBANK: 71, IDFCFIRSTB: 59, PNB: 58. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>Low-risk Metal holding (low vol) • below 200-dma (-8.3%) • outperforming Nifty • sector strength 100/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
+          <t>Low-risk Financials holding (low vol) • below 200-dma (-8.5%) • sector strength 88/100 • regime cautious (partial deploy) • 2 similar past recs: 100% positive, median +8.9%</t>
         </is>
       </c>
     </row>
@@ -1867,54 +1867,54 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Historical +20 · Risk/Vol +18 · Regime +9 · Sector +8 · Trend/Tech +6 = 61</t>
+          <t>Risk/Vol +20 · Historical +15 · Sector +10 · Trend/Tech +9 · Regime +9 = 63</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Historical</t>
+          <t>Risk/Vol</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Trend/Tech</t>
+          <t>Regime</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>65</v>
+        <v>51</v>
       </c>
       <c r="G5" t="n">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="H5" t="n">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="I5" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="J5" t="n">
         <v>60</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>SBIN</t>
+          <t>COALINDIA</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Metal</t>
         </is>
       </c>
       <c r="M5" t="n">
-        <v>961</v>
+        <v>416.8</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>936 - 986</t>
+          <t>406 - 427</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -1928,15 +1928,15 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-7.7%)</t>
+          <t>Below 200-DMA (-3.8%)</t>
         </is>
       </c>
       <c r="S5" t="n">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1945,21 +1945,21 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="V5" t="n">
-        <v>31713</v>
+        <v>36257</v>
       </c>
       <c r="W5" t="n">
-        <v>33</v>
+        <v>87</v>
       </c>
       <c r="X5" t="n">
-        <v>10.8</v>
+        <v>12.1</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>Historical + Risk/Vol strongest; chosen as a lowest-volatility Financials name under the sector cap</t>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Metal name under the sector cap</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1969,12 +1969,12 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — SBIN: 61; ICICIBANK: 67, IDFCFIRSTB: 60, PNB: 57. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — COALINDIA: 63; TATASTEEL: 64, SAIL: 55, HINDZINC: 53. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>Low-risk Financials holding (low vol) • below 200-dma (-7.7%) • sector strength 75/100 • regime cautious (partial deploy) • 2 similar past recs: 100% positive, median +8.9%</t>
+          <t>Low-risk Metal holding (low vol) • below 200-dma (-3.8%) • outperforming Nifty • sector strength 100/100 • regime cautious (partial deploy) • 3 similar past recs: 67% positive, median +0.8%</t>
         </is>
       </c>
     </row>
@@ -1985,11 +1985,11 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Risk/Vol +22 · Historical +15 · Regime +9 · Trend/Tech +7 · Sector +4 = 57</t>
+          <t>Risk/Vol +22 · Historical +15 · Trend/Tech +9 · Regime +9 · Sector +4 = 59</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -2006,7 +2006,7 @@
         <v>50</v>
       </c>
       <c r="G6" t="n">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="H6" t="n">
         <v>88</v>
@@ -2028,11 +2028,11 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>350.3</v>
+        <v>355.6</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>341 - 359</t>
+          <t>347 - 364</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -2046,15 +2046,15 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-9.2%)</t>
+          <t>Below 200-DMA (-7.8%)</t>
         </is>
       </c>
       <c r="S6" t="n">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -2063,17 +2063,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="V6" t="n">
-        <v>39934</v>
+        <v>37694</v>
       </c>
       <c r="W6" t="n">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="X6" t="n">
-        <v>13.3</v>
+        <v>12.6</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -2087,27 +2087,27 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — TATAPOWER: 57; ADANIPOWER: 46, NHPC: 45, NLCINDIA: 32</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — TATAPOWER: 59; ADANIPOWER: 47, NHPC: 46, NLCINDIA: 34</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>Low-risk Power holding (low vol) • below 200-dma (-9.2%) • sector strength 38/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
+          <t>Low-risk Power holding (low vol) • below 200-dma (-7.8%) • sector strength 38/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ACCUMULATE</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Risk/Vol +23 · Historical +13 · Regime +9 · Trend/Tech +7 · Sector +2 = 54</t>
+          <t>Risk/Vol +19 · Historical +15 · Regime +9 · Trend/Tech +8 · Sector +6 = 57</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -2121,54 +2121,54 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="G7" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="H7" t="n">
-        <v>92</v>
+        <v>77</v>
       </c>
       <c r="I7" t="n">
-        <v>25</v>
+        <v>62</v>
       </c>
       <c r="J7" t="n">
         <v>60</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>ITC</t>
+          <t>BEL</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>262.4</v>
+        <v>386</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>256 - 268</t>
+          <t>376 - 396</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-4% to +3%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>56%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-13.2%)</t>
+          <t>Below 200-DMA (-7.6%)</t>
         </is>
       </c>
       <c r="S7" t="n">
@@ -2181,21 +2181,21 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="V7" t="n">
-        <v>45395</v>
+        <v>34358</v>
       </c>
       <c r="W7" t="n">
-        <v>173</v>
+        <v>89</v>
       </c>
       <c r="X7" t="n">
-        <v>15.2</v>
+        <v>11.6</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility FMCG name under the sector cap</t>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Industrials name under the sector cap</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -2205,27 +2205,27 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ITC: 54; DABUR: 45</t>
+          <t>No same-sector peer in the universe.</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>Low-risk FMCG holding (low vol) • below 200-dma (-13.2%) • sector strength 25/100 • regime cautious (partial deploy) • 9 similar past recs: 56% positive, median +0.3%</t>
+          <t>Low-risk Industrials holding (low vol) • below 200-dma (-7.6%) • sector strength 62/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ACCUMULATE</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Risk/Vol +19 · Historical +15 · Regime +9 · Trend/Tech +5 · Sector +5 = 53</t>
+          <t>Risk/Vol +23 · Historical +13 · Regime +9 · Trend/Tech +8 · Sector +2 = 55</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -2239,58 +2239,58 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="G8" t="n">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="H8" t="n">
-        <v>77</v>
+        <v>92</v>
       </c>
       <c r="I8" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="J8" t="n">
         <v>60</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>BEL</t>
+          <t>ITC</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="M8" t="n">
-        <v>380</v>
+        <v>265.1</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>370 - 390</t>
+          <t>259 - 271</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-4% to +3%</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>56%</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-9.0%)</t>
+          <t>Below 200-DMA (-12.2%)</t>
         </is>
       </c>
       <c r="S8" t="n">
-        <v>30</v>
+        <v>59</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -2299,21 +2299,21 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="V8" t="n">
-        <v>34585</v>
+        <v>42151</v>
       </c>
       <c r="W8" t="n">
-        <v>91</v>
+        <v>159</v>
       </c>
       <c r="X8" t="n">
-        <v>11.6</v>
+        <v>14.1</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Industrials name under the sector cap</t>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility FMCG name under the sector cap</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
@@ -2323,12 +2323,12 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>No same-sector peer in the universe.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ITC: 55; DABUR: 46</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>Low-risk Industrials holding (low vol) • below 200-dma (-9.0%) • sector strength 50/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
+          <t>Low-risk FMCG holding (low vol) • below 200-dma (-12.2%) • sector strength 25/100 • regime cautious (partial deploy) • 9 similar past recs: 56% positive, median +0.3%</t>
         </is>
       </c>
     </row>
@@ -2339,11 +2339,11 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Historical +16 · Risk/Vol +16 · Regime +9 · Trend/Tech +6 · Sector +6 = 53</t>
+          <t>Historical +16 · Risk/Vol +16 · Regime +9 · Trend/Tech +5 · Sector +5 = 51</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2360,13 +2360,13 @@
         <v>53</v>
       </c>
       <c r="G9" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="H9" t="n">
         <v>62</v>
       </c>
       <c r="I9" t="n">
-        <v>62</v>
+        <v>50</v>
       </c>
       <c r="J9" t="n">
         <v>60</v>
@@ -2382,11 +2382,11 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>222.7</v>
+        <v>221.9</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>216 - 229</t>
+          <t>216 - 228</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -2400,15 +2400,15 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-13.2%)</t>
+          <t>Below 200-DMA (-13.4%)</t>
         </is>
       </c>
       <c r="S9" t="n">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -2417,17 +2417,17 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="V9" t="n">
-        <v>32063</v>
+        <v>32178</v>
       </c>
       <c r="W9" t="n">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="X9" t="n">
-        <v>10.7</v>
+        <v>10.8</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -2441,12 +2441,12 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ONGC: 53; IOC: 49</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ONGC: 51; IOC: 50</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>Low-risk Energy holding (medium vol) • below 200-dma (-13.2%) • sector strength 62/100 • regime cautious (partial deploy) • 2 similar past recs: 50% positive, median +9.0%</t>
+          <t>Low-risk Energy holding (medium vol) • below 200-dma (-13.4%) • sector strength 50/100 • regime cautious (partial deploy) • 2 similar past recs: 50% positive, median +9.0%</t>
         </is>
       </c>
     </row>
@@ -26097,13 +26097,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D3" t="n">
         <v>0.6</v>
       </c>
       <c r="E3" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F3" t="n">
         <v>-5.9</v>
@@ -26113,7 +26113,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -27251,7 +27251,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>15.2%</t>
+          <t>16.3%</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -27281,7 +27281,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>9.1%</t>
+          <t>8.4%</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -27296,7 +27296,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>8.0%</t>
+          <t>7.6%</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -27326,7 +27326,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>6.4%</t>
+          <t>6.5%</t>
         </is>
       </c>
       <c r="C7" t="n">

--- a/reports/AEGIS_LATEST.xlsx
+++ b/reports/AEGIS_LATEST.xlsx
@@ -444,7 +444,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
     </row>
@@ -512,7 +512,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-06</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-06  /  2026-10-06</t>
+          <t>2026-10-07  /  2026-10-07</t>
         </is>
       </c>
     </row>
@@ -760,7 +760,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-06</t>
         </is>
       </c>
     </row>
@@ -908,7 +908,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>14.9%</t>
+          <t>14.8%</t>
         </is>
       </c>
     </row>
@@ -1322,7 +1322,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>-5.8%</t>
+          <t>-5.9%</t>
         </is>
       </c>
     </row>
@@ -1517,7 +1517,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Risk/Vol +24 · Historical +20 · Trend/Tech +9 · Regime +9 · Sector +9 = 71</t>
+          <t>Risk/Vol +24 · Historical +20 · Trend/Tech +10 · Regime +9 · Sector +8 = 71</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -1534,13 +1534,13 @@
         <v>66</v>
       </c>
       <c r="G2" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="H2" t="n">
         <v>96</v>
       </c>
       <c r="I2" t="n">
-        <v>88</v>
+        <v>75</v>
       </c>
       <c r="J2" t="n">
         <v>60</v>
@@ -1556,11 +1556,11 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>1334.3</v>
+        <v>1349.9</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>1306 - 1362</t>
+          <t>1322 - 1378</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -1578,11 +1578,11 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-1.4%)</t>
+          <t>Below 200-DMA (-0.3%)</t>
         </is>
       </c>
       <c r="S2" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -1591,17 +1591,17 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="V2" t="n">
-        <v>45366</v>
+        <v>53996</v>
       </c>
       <c r="W2" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="X2" t="n">
-        <v>15.5</v>
+        <v>18.2</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
@@ -1615,12 +1615,12 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ICICIBANK: 71; SBIN: 64, IDFCFIRSTB: 59, PNB: 58</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ICICIBANK: 71; PNB: 67, SBIN: 61, IDFCFIRSTB: 58</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>Low-risk Financials holding (low vol) • below 200-dma (-1.4%) • sector strength 88/100 • regime cautious (partial deploy) • 8 similar past recs: 75% positive, median +5.3%</t>
+          <t>Low-risk Financials holding (low vol) • below 200-dma (-0.3%) • outperforming Nifty • sector strength 75/100 • regime cautious (partial deploy) • 8 similar past recs: 75% positive, median +5.3%</t>
         </is>
       </c>
     </row>
@@ -1649,10 +1649,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G3" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="H3" t="n">
         <v>85</v>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>TATASTEEL</t>
+          <t>COALINDIA</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -1674,11 +1674,11 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>179.4</v>
+        <v>414.9</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>175 - 184</t>
+          <t>404 - 426</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -1692,15 +1692,15 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-7.6%)</t>
+          <t>Below 200-DMA (-4.3%)</t>
         </is>
       </c>
       <c r="S3" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -1709,17 +1709,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="V3" t="n">
-        <v>35172</v>
+        <v>40660</v>
       </c>
       <c r="W3" t="n">
-        <v>196</v>
+        <v>98</v>
       </c>
       <c r="X3" t="n">
-        <v>11.7</v>
+        <v>13.6</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
@@ -1733,12 +1733,12 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — TATASTEEL: 64; COALINDIA: 63, SAIL: 55, HINDZINC: 53</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — COALINDIA: 64; TATASTEEL: 60, SAIL: 54, HINDZINC: 53</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>Low-risk Metal holding (low vol) • below 200-dma (-7.6%) • sector strength 100/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
+          <t>Low-risk Metal holding (low vol) • below 200-dma (-4.3%) • outperforming Nifty • sector strength 100/100 • regime cautious (partial deploy) • 3 similar past recs: 67% positive, median +0.8%</t>
         </is>
       </c>
     </row>
@@ -1749,11 +1749,11 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Historical +20 · Risk/Vol +18 · Regime +9 · Sector +9 · Trend/Tech +8 = 64</t>
+          <t>Historical +20 · Risk/Vol +18 · Regime +9 · Sector +8 · Trend/Tech +6 = 61</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1770,13 +1770,13 @@
         <v>65</v>
       </c>
       <c r="G4" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="H4" t="n">
         <v>73</v>
       </c>
       <c r="I4" t="n">
-        <v>88</v>
+        <v>75</v>
       </c>
       <c r="J4" t="n">
         <v>60</v>
@@ -1792,11 +1792,11 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>952.8</v>
+        <v>959.5</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>928 - 978</t>
+          <t>934 - 985</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -1810,15 +1810,15 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-8.5%)</t>
+          <t>Below 200-DMA (-7.8%)</t>
         </is>
       </c>
       <c r="S4" t="n">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1827,17 +1827,17 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="V4" t="n">
-        <v>34299</v>
+        <v>29746</v>
       </c>
       <c r="W4" t="n">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="X4" t="n">
-        <v>11.7</v>
+        <v>10</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -1851,12 +1851,12 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — SBIN: 64; ICICIBANK: 71, IDFCFIRSTB: 59, PNB: 58. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — SBIN: 61; ICICIBANK: 71, PNB: 67, IDFCFIRSTB: 58. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>Low-risk Financials holding (low vol) • below 200-dma (-8.5%) • sector strength 88/100 • regime cautious (partial deploy) • 2 similar past recs: 100% positive, median +8.9%</t>
+          <t>Low-risk Financials holding (low vol) • below 200-dma (-7.8%) • sector strength 75/100 • regime cautious (partial deploy) • 2 similar past recs: 100% positive, median +8.9%</t>
         </is>
       </c>
     </row>
@@ -1867,11 +1867,11 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Risk/Vol +20 · Historical +15 · Sector +10 · Trend/Tech +9 · Regime +9 = 63</t>
+          <t>Risk/Vol +20 · Historical +15 · Sector +10 · Regime +9 · Trend/Tech +6 = 60</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1881,14 +1881,14 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Regime</t>
+          <t>Trend/Tech</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G5" t="n">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="H5" t="n">
         <v>81</v>
@@ -1901,7 +1901,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>COALINDIA</t>
+          <t>TATASTEEL</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1910,11 +1910,11 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>416.8</v>
+        <v>176.5</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>406 - 427</t>
+          <t>172 - 181</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -1928,15 +1928,15 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-3.8%)</t>
+          <t>Below 200-DMA (-9.1%)</t>
         </is>
       </c>
       <c r="S5" t="n">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1945,17 +1945,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="V5" t="n">
-        <v>36257</v>
+        <v>28246</v>
       </c>
       <c r="W5" t="n">
-        <v>87</v>
+        <v>160</v>
       </c>
       <c r="X5" t="n">
-        <v>12.1</v>
+        <v>9.4</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -1969,12 +1969,12 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — COALINDIA: 63; TATASTEEL: 64, SAIL: 55, HINDZINC: 53. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — TATASTEEL: 60; COALINDIA: 64, SAIL: 54, HINDZINC: 53. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>Low-risk Metal holding (low vol) • below 200-dma (-3.8%) • outperforming Nifty • sector strength 100/100 • regime cautious (partial deploy) • 3 similar past recs: 67% positive, median +0.8%</t>
+          <t>Low-risk Metal holding (low vol) • below 200-dma (-9.1%) • sector strength 100/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
         </is>
       </c>
     </row>
@@ -1985,11 +1985,11 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Risk/Vol +22 · Historical +15 · Trend/Tech +9 · Regime +9 · Sector +4 = 59</t>
+          <t>Risk/Vol +23 · Historical +13 · Regime +9 · Trend/Tech +8 · Sector +2 = 55</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -2003,58 +2003,58 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="G6" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="H6" t="n">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="I6" t="n">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="J6" t="n">
         <v>60</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>TATAPOWER</t>
+          <t>ITC</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Power</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="M6" t="n">
-        <v>355.6</v>
+        <v>265.9</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>347 - 364</t>
+          <t>260 - 272</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-4% to +3%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>56%</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-7.8%)</t>
+          <t>Below 200-DMA (-11.7%)</t>
         </is>
       </c>
       <c r="S6" t="n">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -2063,21 +2063,21 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="V6" t="n">
-        <v>37694</v>
+        <v>49714</v>
       </c>
       <c r="W6" t="n">
-        <v>106</v>
+        <v>187</v>
       </c>
       <c r="X6" t="n">
-        <v>12.6</v>
+        <v>16.6</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Power name under the sector cap</t>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility FMCG name under the sector cap</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -2087,12 +2087,12 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — TATAPOWER: 59; ADANIPOWER: 47, NHPC: 46, NLCINDIA: 34</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ITC: 55; DABUR: 45</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>Low-risk Power holding (low vol) • below 200-dma (-7.8%) • sector strength 38/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
+          <t>Low-risk FMCG holding (low vol) • below 200-dma (-11.7%) • sector strength 25/100 • regime cautious (partial deploy) • 9 similar past recs: 56% positive, median +0.3%</t>
         </is>
       </c>
     </row>
@@ -2103,11 +2103,11 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Risk/Vol +19 · Historical +15 · Regime +9 · Trend/Tech +8 · Sector +6 = 57</t>
+          <t>Risk/Vol +22 · Historical +15 · Regime +9 · Trend/Tech +5 · Sector +4 = 55</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -2124,33 +2124,33 @@
         <v>50</v>
       </c>
       <c r="G7" t="n">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="H7" t="n">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="I7" t="n">
-        <v>62</v>
+        <v>38</v>
       </c>
       <c r="J7" t="n">
         <v>60</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>BEL</t>
+          <t>TATAPOWER</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Power</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>386</v>
+        <v>346</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>376 - 396</t>
+          <t>337 - 355</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -2164,15 +2164,15 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-7.6%)</t>
+          <t>Below 200-DMA (-10.2%)</t>
         </is>
       </c>
       <c r="S7" t="n">
-        <v>53</v>
+        <v>34</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -2181,21 +2181,21 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="V7" t="n">
-        <v>34358</v>
+        <v>31837</v>
       </c>
       <c r="W7" t="n">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="X7" t="n">
-        <v>11.6</v>
+        <v>10.7</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Industrials name under the sector cap</t>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Power name under the sector cap</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -2205,12 +2205,12 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>No same-sector peer in the universe.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — TATAPOWER: 55; ADANIPOWER: 47, NHPC: 45, NLCINDIA: 35</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>Low-risk Industrials holding (low vol) • below 200-dma (-7.6%) • sector strength 62/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
+          <t>Low-risk Power holding (low vol) • below 200-dma (-10.2%) • sector strength 38/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
         </is>
       </c>
     </row>
@@ -2225,7 +2225,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Risk/Vol +23 · Historical +13 · Regime +9 · Trend/Tech +8 · Sector +2 = 55</t>
+          <t>Risk/Vol +19 · Historical +15 · Regime +9 · Trend/Tech +6 · Sector +6 = 55</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -2239,58 +2239,58 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="G8" t="n">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="H8" t="n">
-        <v>92</v>
+        <v>77</v>
       </c>
       <c r="I8" t="n">
-        <v>25</v>
+        <v>62</v>
       </c>
       <c r="J8" t="n">
         <v>60</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>ITC</t>
+          <t>BEL</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="M8" t="n">
-        <v>265.1</v>
+        <v>380.1</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>259 - 271</t>
+          <t>370 - 390</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>-4% to +3%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>56%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-12.2%)</t>
+          <t>Below 200-DMA (-9.0%)</t>
         </is>
       </c>
       <c r="S8" t="n">
-        <v>59</v>
+        <v>40</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -2299,21 +2299,21 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="V8" t="n">
-        <v>42151</v>
+        <v>28127</v>
       </c>
       <c r="W8" t="n">
-        <v>159</v>
+        <v>74</v>
       </c>
       <c r="X8" t="n">
-        <v>14.1</v>
+        <v>9.4</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility FMCG name under the sector cap</t>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Industrials name under the sector cap</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
@@ -2323,12 +2323,12 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ITC: 55; DABUR: 46</t>
+          <t>No same-sector peer in the universe.</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>Low-risk FMCG holding (low vol) • below 200-dma (-12.2%) • sector strength 25/100 • regime cautious (partial deploy) • 9 similar past recs: 56% positive, median +0.3%</t>
+          <t>Low-risk Industrials holding (low vol) • below 200-dma (-9.0%) • sector strength 62/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
         </is>
       </c>
     </row>
@@ -2360,7 +2360,7 @@
         <v>53</v>
       </c>
       <c r="G9" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H9" t="n">
         <v>62</v>
@@ -2382,11 +2382,11 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>221.9</v>
+        <v>221.1</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>216 - 228</t>
+          <t>215 - 227</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-13.4%)</t>
+          <t>Below 200-DMA (-13.8%)</t>
         </is>
       </c>
       <c r="S9" t="n">
@@ -2417,17 +2417,17 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="V9" t="n">
-        <v>32178</v>
+        <v>36254</v>
       </c>
       <c r="W9" t="n">
-        <v>145</v>
+        <v>164</v>
       </c>
       <c r="X9" t="n">
-        <v>10.8</v>
+        <v>12.1</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -2441,12 +2441,12 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ONGC: 51; IOC: 50</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ONGC: 51; IOC: 48</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>Low-risk Energy holding (medium vol) • below 200-dma (-13.4%) • sector strength 50/100 • regime cautious (partial deploy) • 2 similar past recs: 50% positive, median +9.0%</t>
+          <t>Low-risk Energy holding (medium vol) • below 200-dma (-13.8%) • sector strength 50/100 • regime cautious (partial deploy) • 2 similar past recs: 50% positive, median +9.0%</t>
         </is>
       </c>
     </row>
@@ -11411,15 +11411,9 @@
       <c r="L106" t="n">
         <v>-1.05</v>
       </c>
-      <c r="M106" t="n">
-        <v>1</v>
-      </c>
-      <c r="N106" t="n">
-        <v>-17.4</v>
-      </c>
-      <c r="O106" t="n">
-        <v>-1645</v>
-      </c>
+      <c r="M106" t="inlineStr"/>
+      <c r="N106" t="inlineStr"/>
+      <c r="O106" t="inlineStr"/>
       <c r="P106" t="n">
         <v>-51.4</v>
       </c>
@@ -25388,15 +25382,9 @@
       <c r="L279" t="n">
         <v>0.27</v>
       </c>
-      <c r="M279" t="n">
-        <v>23.5</v>
-      </c>
-      <c r="N279" t="n">
-        <v>0</v>
-      </c>
-      <c r="O279" t="n">
-        <v>10</v>
-      </c>
+      <c r="M279" t="inlineStr"/>
+      <c r="N279" t="inlineStr"/>
+      <c r="O279" t="inlineStr"/>
       <c r="P279" t="n">
         <v>10.2</v>
       </c>
@@ -27171,7 +27159,7 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>-11.8</v>
+        <v>-12.6</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -27251,7 +27239,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>16.3%</t>
+          <t>16.9%</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -27266,7 +27254,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>13.8%</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -27281,7 +27269,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>8.4%</t>
+          <t>10.0%</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -27291,12 +27279,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Power</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>7.6%</t>
+          <t>7.3%</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -27306,12 +27294,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Power</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>6.9%</t>
+          <t>6.4%</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -27321,12 +27309,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>6.5%</t>
+          <t>5.6%</t>
         </is>
       </c>
       <c r="C7" t="n">

--- a/reports/AEGIS_LATEST.xlsx
+++ b/reports/AEGIS_LATEST.xlsx
@@ -444,7 +444,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
     </row>
@@ -489,7 +489,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7">
@@ -512,7 +512,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-07</t>
         </is>
       </c>
     </row>
@@ -524,7 +524,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ICICIBANK (71)</t>
+          <t>ICICIBANK (79)</t>
         </is>
       </c>
     </row>
@@ -536,7 +536,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ONGC (51)</t>
+          <t>DABUR (50)</t>
         </is>
       </c>
     </row>
@@ -548,7 +548,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>DABUR</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>ONGC</t>
         </is>
       </c>
     </row>
@@ -571,7 +571,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -688,7 +688,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-07  /  2026-10-07</t>
+          <t>2026-10-08  /  2026-10-08</t>
         </is>
       </c>
     </row>
@@ -760,7 +760,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-07</t>
         </is>
       </c>
     </row>
@@ -908,7 +908,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>14.8%</t>
+          <t>14.7%</t>
         </is>
       </c>
     </row>
@@ -920,7 +920,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>1.85</t>
         </is>
       </c>
     </row>
@@ -1322,7 +1322,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>-5.9%</t>
+          <t>-5.8%</t>
         </is>
       </c>
     </row>
@@ -1513,11 +1513,11 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Risk/Vol +24 · Historical +20 · Trend/Tech +10 · Regime +9 · Sector +8 = 71</t>
+          <t>Risk/Vol +24 · Historical +20 · Trend/Tech +18 · Regime +9 · Sector +8 = 79</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -1534,7 +1534,7 @@
         <v>66</v>
       </c>
       <c r="G2" t="n">
-        <v>48</v>
+        <v>89</v>
       </c>
       <c r="H2" t="n">
         <v>96</v>
@@ -1556,11 +1556,11 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>1349.9</v>
+        <v>1356.6</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>1322 - 1378</t>
+          <t>1328 - 1385</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -1574,15 +1574,15 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-0.3%)</t>
+          <t>Above 200-DMA (+0.2%)</t>
         </is>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -1591,17 +1591,17 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-07</t>
         </is>
       </c>
       <c r="V2" t="n">
-        <v>53996</v>
+        <v>44768</v>
       </c>
       <c r="W2" t="n">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="X2" t="n">
-        <v>18.2</v>
+        <v>15.3</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
@@ -1615,12 +1615,12 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ICICIBANK: 71; PNB: 67, SBIN: 61, IDFCFIRSTB: 58</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ICICIBANK: 79; PNB: 67, SBIN: 61, IDFCFIRSTB: 57</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>Low-risk Financials holding (low vol) • below 200-dma (-0.3%) • outperforming Nifty • sector strength 75/100 • regime cautious (partial deploy) • 8 similar past recs: 75% positive, median +5.3%</t>
+          <t>Low-risk Financials holding (low vol) • above 200-dma (+0.2%) • outperforming Nifty • sector strength 75/100 • regime cautious (partial deploy) • 8 similar past recs: 75% positive, median +5.3%</t>
         </is>
       </c>
     </row>
@@ -1652,7 +1652,7 @@
         <v>51</v>
       </c>
       <c r="G3" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H3" t="n">
         <v>85</v>
@@ -1674,11 +1674,11 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>414.9</v>
+        <v>406.2</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>404 - 426</t>
+          <t>396 - 417</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -1696,11 +1696,11 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-4.3%)</t>
+          <t>Below 200-DMA (-6.3%)</t>
         </is>
       </c>
       <c r="S3" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -1709,17 +1709,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-07</t>
         </is>
       </c>
       <c r="V3" t="n">
-        <v>40660</v>
+        <v>50375</v>
       </c>
       <c r="W3" t="n">
-        <v>98</v>
+        <v>124</v>
       </c>
       <c r="X3" t="n">
-        <v>13.6</v>
+        <v>16.9</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
@@ -1733,12 +1733,12 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — COALINDIA: 64; TATASTEEL: 60, SAIL: 54, HINDZINC: 53</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — COALINDIA: 64; TATASTEEL: 59, HINDZINC: 50, SAIL: 45</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>Low-risk Metal holding (low vol) • below 200-dma (-4.3%) • outperforming Nifty • sector strength 100/100 • regime cautious (partial deploy) • 3 similar past recs: 67% positive, median +0.8%</t>
+          <t>Low-risk Metal holding (low vol) • below 200-dma (-6.3%) • outperforming Nifty • sector strength 100/100 • regime cautious (partial deploy) • 3 similar past recs: 67% positive, median +0.8%</t>
         </is>
       </c>
     </row>
@@ -1770,7 +1770,7 @@
         <v>65</v>
       </c>
       <c r="G4" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="H4" t="n">
         <v>73</v>
@@ -1792,11 +1792,11 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>959.5</v>
+        <v>947.5</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>934 - 985</t>
+          <t>922 - 972</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -1814,11 +1814,11 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-7.8%)</t>
+          <t>Below 200-DMA (-9.0%)</t>
         </is>
       </c>
       <c r="S4" t="n">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1827,11 +1827,11 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-07</t>
         </is>
       </c>
       <c r="V4" t="n">
-        <v>29746</v>
+        <v>29371</v>
       </c>
       <c r="W4" t="n">
         <v>31</v>
@@ -1851,12 +1851,12 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — SBIN: 61; ICICIBANK: 71, PNB: 67, IDFCFIRSTB: 58. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — SBIN: 61; ICICIBANK: 79, PNB: 67, IDFCFIRSTB: 57. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>Low-risk Financials holding (low vol) • below 200-dma (-7.8%) • sector strength 75/100 • regime cautious (partial deploy) • 2 similar past recs: 100% positive, median +8.9%</t>
+          <t>Low-risk Financials holding (low vol) • below 200-dma (-9.0%) • sector strength 75/100 • regime cautious (partial deploy) • 2 similar past recs: 100% positive, median +8.9%</t>
         </is>
       </c>
     </row>
@@ -1867,11 +1867,11 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Risk/Vol +20 · Historical +15 · Sector +10 · Regime +9 · Trend/Tech +6 = 60</t>
+          <t>Risk/Vol +19 · Historical +15 · Sector +10 · Regime +9 · Trend/Tech +6 = 59</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1888,10 +1888,10 @@
         <v>50</v>
       </c>
       <c r="G5" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H5" t="n">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="I5" t="n">
         <v>100</v>
@@ -1910,11 +1910,11 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>176.5</v>
+        <v>172.6</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>172 - 181</t>
+          <t>168 - 177</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -1932,11 +1932,11 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-9.1%)</t>
+          <t>Below 200-DMA (-11.1%)</t>
         </is>
       </c>
       <c r="S5" t="n">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1945,17 +1945,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-07</t>
         </is>
       </c>
       <c r="V5" t="n">
-        <v>28246</v>
+        <v>27781</v>
       </c>
       <c r="W5" t="n">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="X5" t="n">
-        <v>9.4</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -1969,12 +1969,12 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — TATASTEEL: 60; COALINDIA: 64, SAIL: 54, HINDZINC: 53. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — TATASTEEL: 59; COALINDIA: 64, HINDZINC: 50, SAIL: 45. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>Low-risk Metal holding (low vol) • below 200-dma (-9.1%) • sector strength 100/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
+          <t>Low-risk Metal holding (low vol) • below 200-dma (-11.1%) • sector strength 100/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
         </is>
       </c>
     </row>
@@ -1989,7 +1989,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Risk/Vol +23 · Historical +13 · Regime +9 · Trend/Tech +8 · Sector +2 = 55</t>
+          <t>Risk/Vol +23 · Historical +13 · Regime +9 · Trend/Tech +6 · Sector +4 = 55</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -2006,13 +2006,13 @@
         <v>44</v>
       </c>
       <c r="G6" t="n">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="H6" t="n">
         <v>92</v>
       </c>
       <c r="I6" t="n">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="J6" t="n">
         <v>60</v>
@@ -2028,11 +2028,11 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>265.9</v>
+        <v>255.4</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>260 - 272</t>
+          <t>249 - 261</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -2050,11 +2050,11 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-11.7%)</t>
+          <t>Below 200-DMA (-15.0%)</t>
         </is>
       </c>
       <c r="S6" t="n">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -2063,17 +2063,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-07</t>
         </is>
       </c>
       <c r="V6" t="n">
-        <v>49714</v>
+        <v>39579</v>
       </c>
       <c r="W6" t="n">
-        <v>187</v>
+        <v>155</v>
       </c>
       <c r="X6" t="n">
-        <v>16.6</v>
+        <v>13.2</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -2087,27 +2087,27 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ITC: 55; DABUR: 45</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ITC: 55; DABUR: 50</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>Low-risk FMCG holding (low vol) • below 200-dma (-11.7%) • sector strength 25/100 • regime cautious (partial deploy) • 9 similar past recs: 56% positive, median +0.3%</t>
+          <t>Low-risk FMCG holding (low vol) • below 200-dma (-15.0%) • sector strength 38/100 • regime cautious (partial deploy) • 9 similar past recs: 56% positive, median +0.3%</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>ACCUMULATE</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Risk/Vol +22 · Historical +15 · Regime +9 · Trend/Tech +5 · Sector +4 = 55</t>
+          <t>Risk/Vol +20 · Historical +15 · Regime +9 · Trend/Tech +5 · Sector +5 = 54</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -2127,30 +2127,30 @@
         <v>26</v>
       </c>
       <c r="H7" t="n">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="I7" t="n">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="J7" t="n">
         <v>60</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>TATAPOWER</t>
+          <t>BEL</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Power</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>346</v>
+        <v>372.5</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>337 - 355</t>
+          <t>363 - 382</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -2164,15 +2164,15 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-10.2%)</t>
+          <t>Below 200-DMA (-10.8%)</t>
         </is>
       </c>
       <c r="S7" t="n">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -2181,21 +2181,21 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-07</t>
         </is>
       </c>
       <c r="V7" t="n">
-        <v>31837</v>
+        <v>27938</v>
       </c>
       <c r="W7" t="n">
-        <v>92</v>
+        <v>75</v>
       </c>
       <c r="X7" t="n">
-        <v>10.7</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Power name under the sector cap</t>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Industrials name under the sector cap</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -2205,27 +2205,27 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — TATAPOWER: 55; ADANIPOWER: 47, NHPC: 45, NLCINDIA: 35</t>
+          <t>No same-sector peer in the universe.</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>Low-risk Power holding (low vol) • below 200-dma (-10.2%) • sector strength 38/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
+          <t>Low-risk Industrials holding (low vol) • below 200-dma (-10.8%) • sector strength 50/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>ACCUMULATE</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Risk/Vol +19 · Historical +15 · Regime +9 · Trend/Tech +6 · Sector +6 = 55</t>
+          <t>Risk/Vol +22 · Historical +15 · Regime +9 · Trend/Tech +5 · Sector +2 = 53</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -2242,33 +2242,33 @@
         <v>50</v>
       </c>
       <c r="G8" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="H8" t="n">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="I8" t="n">
-        <v>62</v>
+        <v>25</v>
       </c>
       <c r="J8" t="n">
         <v>60</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>BEL</t>
+          <t>TATAPOWER</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Power</t>
         </is>
       </c>
       <c r="M8" t="n">
-        <v>380.1</v>
+        <v>338.5</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>370 - 390</t>
+          <t>330 - 347</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -2282,15 +2282,15 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-9.0%)</t>
+          <t>Below 200-DMA (-12.1%)</t>
         </is>
       </c>
       <c r="S8" t="n">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -2299,21 +2299,21 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-07</t>
         </is>
       </c>
       <c r="V8" t="n">
-        <v>28127</v>
+        <v>31485</v>
       </c>
       <c r="W8" t="n">
-        <v>74</v>
+        <v>93</v>
       </c>
       <c r="X8" t="n">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Industrials name under the sector cap</t>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Power name under the sector cap</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
@@ -2323,12 +2323,12 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>No same-sector peer in the universe.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — TATAPOWER: 53; NHPC: 46, ADANIPOWER: 34, NLCINDIA: 30</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>Low-risk Industrials holding (low vol) • below 200-dma (-9.0%) • sector strength 62/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
+          <t>Low-risk Power holding (low vol) • below 200-dma (-12.1%) • sector strength 25/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
         </is>
       </c>
     </row>
@@ -2339,16 +2339,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Historical +16 · Risk/Vol +16 · Regime +9 · Trend/Tech +5 · Sector +5 = 51</t>
+          <t>Risk/Vol +16 · Historical +15 · Regime +9 · Trend/Tech +6 · Sector +4 = 50</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Historical</t>
+          <t>Risk/Vol</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -2357,36 +2357,36 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="G9" t="n">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="H9" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="I9" t="n">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="J9" t="n">
         <v>60</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>ONGC</t>
+          <t>DABUR</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="M9" t="n">
-        <v>221.1</v>
+        <v>383.4</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>215 - 227</t>
+          <t>373 - 394</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -2400,15 +2400,15 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-13.8%)</t>
+          <t>Below 200-DMA (-14.2%)</t>
         </is>
       </c>
       <c r="S9" t="n">
-        <v>17</v>
+        <v>49</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -2417,21 +2417,21 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-07</t>
         </is>
       </c>
       <c r="V9" t="n">
-        <v>36254</v>
+        <v>46008</v>
       </c>
       <c r="W9" t="n">
-        <v>164</v>
+        <v>120</v>
       </c>
       <c r="X9" t="n">
-        <v>12.1</v>
+        <v>15.4</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>Historical + Risk/Vol strongest; chosen as a lowest-volatility Energy name under the sector cap</t>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility FMCG name under the sector cap</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
@@ -2441,12 +2441,12 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ONGC: 51; IOC: 48</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — DABUR: 50; ITC: 55. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>Low-risk Energy holding (medium vol) • below 200-dma (-13.8%) • sector strength 50/100 • regime cautious (partial deploy) • 2 similar past recs: 50% positive, median +9.0%</t>
+          <t>Low-risk FMCG holding (medium vol) • below 200-dma (-14.2%) • sector strength 38/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
         </is>
       </c>
     </row>
@@ -11411,9 +11411,15 @@
       <c r="L106" t="n">
         <v>-1.05</v>
       </c>
-      <c r="M106" t="inlineStr"/>
-      <c r="N106" t="inlineStr"/>
-      <c r="O106" t="inlineStr"/>
+      <c r="M106" t="n">
+        <v>1</v>
+      </c>
+      <c r="N106" t="n">
+        <v>-17.4</v>
+      </c>
+      <c r="O106" t="n">
+        <v>-1645</v>
+      </c>
       <c r="P106" t="n">
         <v>-51.4</v>
       </c>
@@ -25382,9 +25388,15 @@
       <c r="L279" t="n">
         <v>0.27</v>
       </c>
-      <c r="M279" t="inlineStr"/>
-      <c r="N279" t="inlineStr"/>
-      <c r="O279" t="inlineStr"/>
+      <c r="M279" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="N279" t="n">
+        <v>0</v>
+      </c>
+      <c r="O279" t="n">
+        <v>10</v>
+      </c>
       <c r="P279" t="n">
         <v>10.2</v>
       </c>
@@ -27159,7 +27171,7 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>-12.6</v>
+        <v>-11.8</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -27211,7 +27223,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27234,12 +27246,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>16.9%</t>
+          <t>17.2%</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -27254,7 +27266,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>13.8%</t>
+          <t>15.7%</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -27264,27 +27276,27 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>15.2%</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Power</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>7.3%</t>
+          <t>6.3%</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -27294,12 +27306,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Power</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>6.4%</t>
+          <t>5.6%</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -27309,47 +27321,32 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>CASH (intentional)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CASH (intentional)</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>40.0%</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
           <t>100.0%</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>8 stocks / 6 sectors</t>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>8 stocks / 5 sectors</t>
         </is>
       </c>
     </row>

--- a/reports/AEGIS_LATEST.xlsx
+++ b/reports/AEGIS_LATEST.xlsx
@@ -444,7 +444,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
     </row>
@@ -512,7 +512,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-11-07</t>
+          <t>2026-11-08</t>
         </is>
       </c>
     </row>
@@ -524,7 +524,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ICICIBANK (79)</t>
+          <t>ICICIBANK (72)</t>
         </is>
       </c>
     </row>
@@ -548,7 +548,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>DABUR</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>ONGC</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -571,7 +571,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -688,7 +688,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-08  /  2026-10-08</t>
+          <t>2026-10-09  /  2026-10-09</t>
         </is>
       </c>
     </row>
@@ -760,7 +760,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-11-07</t>
+          <t>2026-11-08</t>
         </is>
       </c>
     </row>
@@ -1322,7 +1322,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>-5.8%</t>
+          <t>-5.9%</t>
         </is>
       </c>
     </row>
@@ -1513,11 +1513,11 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Risk/Vol +24 · Historical +20 · Trend/Tech +18 · Regime +9 · Sector +8 = 79</t>
+          <t>Risk/Vol +24 · Historical +20 · Trend/Tech +10 · Regime +9 · Sector +9 = 72</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -1534,13 +1534,13 @@
         <v>66</v>
       </c>
       <c r="G2" t="n">
-        <v>89</v>
+        <v>48</v>
       </c>
       <c r="H2" t="n">
         <v>96</v>
       </c>
       <c r="I2" t="n">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="J2" t="n">
         <v>60</v>
@@ -1556,11 +1556,11 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>1356.6</v>
+        <v>1348.6</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>1328 - 1385</t>
+          <t>1320 - 1377</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -1574,11 +1574,11 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>Above 200-DMA (+0.2%)</t>
+          <t>Below 200-DMA (-0.4%)</t>
         </is>
       </c>
       <c r="S2" t="n">
@@ -1591,17 +1591,17 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>2026-11-07</t>
+          <t>2026-11-08</t>
         </is>
       </c>
       <c r="V2" t="n">
-        <v>44768</v>
+        <v>45852</v>
       </c>
       <c r="W2" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="X2" t="n">
-        <v>15.3</v>
+        <v>15.4</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
@@ -1615,27 +1615,27 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ICICIBANK: 79; PNB: 67, SBIN: 61, IDFCFIRSTB: 57</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ICICIBANK: 72; PNB: 69, SBIN: 65, IDFCFIRSTB: 59</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>Low-risk Financials holding (low vol) • above 200-dma (+0.2%) • outperforming Nifty • sector strength 75/100 • regime cautious (partial deploy) • 8 similar past recs: 75% positive, median +5.3%</t>
+          <t>Low-risk Financials holding (low vol) • below 200-dma (-0.4%) • outperforming Nifty • sector strength 88/100 • regime cautious (partial deploy) • 8 similar past recs: 75% positive, median +5.3%</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>STRONG BUY</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Risk/Vol +21 · Historical +15 · Sector +10 · Trend/Tech +9 · Regime +9 = 64</t>
+          <t>Risk/Vol +21 · Historical +20 · Regime +9 · Sector +9 · Trend/Tech +6 = 65</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -1645,40 +1645,40 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Regime</t>
+          <t>Trend/Tech</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="G3" t="n">
-        <v>47</v>
+        <v>31</v>
       </c>
       <c r="H3" t="n">
         <v>85</v>
       </c>
       <c r="I3" t="n">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="J3" t="n">
         <v>60</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>COALINDIA</t>
+          <t>SBIN</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Metal</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="M3" t="n">
-        <v>406.2</v>
+        <v>952.2</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>396 - 417</t>
+          <t>928 - 977</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -1696,11 +1696,11 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-6.3%)</t>
+          <t>Below 200-DMA (-8.5%)</t>
         </is>
       </c>
       <c r="S3" t="n">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -1709,21 +1709,21 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>2026-11-07</t>
+          <t>2026-11-08</t>
         </is>
       </c>
       <c r="V3" t="n">
-        <v>50375</v>
+        <v>30472</v>
       </c>
       <c r="W3" t="n">
-        <v>124</v>
+        <v>32</v>
       </c>
       <c r="X3" t="n">
-        <v>16.9</v>
+        <v>10.3</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Metal name under the sector cap</t>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Financials name under the sector cap</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -1733,12 +1733,12 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — COALINDIA: 64; TATASTEEL: 59, HINDZINC: 50, SAIL: 45</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — SBIN: 65; ICICIBANK: 72, PNB: 69, IDFCFIRSTB: 59. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>Low-risk Metal holding (low vol) • below 200-dma (-6.3%) • outperforming Nifty • sector strength 100/100 • regime cautious (partial deploy) • 3 similar past recs: 67% positive, median +0.8%</t>
+          <t>Low-risk Financials holding (low vol) • below 200-dma (-8.5%) • sector strength 88/100 • regime cautious (partial deploy) • 2 similar past recs: 100% positive, median +8.9%</t>
         </is>
       </c>
     </row>
@@ -1749,54 +1749,54 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Historical +20 · Risk/Vol +18 · Regime +9 · Sector +8 · Trend/Tech +6 = 61</t>
+          <t>Risk/Vol +20 · Historical +15 · Trend/Tech +10 · Sector +10 · Regime +9 = 64</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Historical</t>
+          <t>Risk/Vol</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Trend/Tech</t>
+          <t>Regime</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>65</v>
+        <v>51</v>
       </c>
       <c r="G4" t="n">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="H4" t="n">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="I4" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="J4" t="n">
         <v>60</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>SBIN</t>
+          <t>COALINDIA</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Metal</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>947.5</v>
+        <v>411</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>922 - 972</t>
+          <t>400 - 422</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -1810,15 +1810,15 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-9.0%)</t>
+          <t>Below 200-DMA (-5.3%)</t>
         </is>
       </c>
       <c r="S4" t="n">
-        <v>27</v>
+        <v>51</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1827,21 +1827,21 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>2026-11-07</t>
+          <t>2026-11-08</t>
         </is>
       </c>
       <c r="V4" t="n">
-        <v>29371</v>
+        <v>50136</v>
       </c>
       <c r="W4" t="n">
-        <v>31</v>
+        <v>122</v>
       </c>
       <c r="X4" t="n">
-        <v>10</v>
+        <v>16.7</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>Historical + Risk/Vol strongest; chosen as a lowest-volatility Financials name under the sector cap</t>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Metal name under the sector cap</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1851,12 +1851,12 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — SBIN: 61; ICICIBANK: 79, PNB: 67, IDFCFIRSTB: 57. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — COALINDIA: 64; TATASTEEL: 58, SAIL: 54, HINDZINC: 51</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>Low-risk Financials holding (low vol) • below 200-dma (-9.0%) • sector strength 75/100 • regime cautious (partial deploy) • 2 similar past recs: 100% positive, median +8.9%</t>
+          <t>Low-risk Metal holding (low vol) • below 200-dma (-5.3%) • outperforming Nifty • sector strength 100/100 • regime cautious (partial deploy) • 3 similar past recs: 67% positive, median +0.8%</t>
         </is>
       </c>
     </row>
@@ -1867,11 +1867,11 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Risk/Vol +19 · Historical +15 · Sector +10 · Regime +9 · Trend/Tech +6 = 59</t>
+          <t>Risk/Vol +23 · Historical +13 · Trend/Tech +9 · Regime +9 · Sector +6 = 60</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1881,62 +1881,62 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Trend/Tech</t>
+          <t>Sector</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="G5" t="n">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="H5" t="n">
-        <v>77</v>
+        <v>92</v>
       </c>
       <c r="I5" t="n">
-        <v>100</v>
+        <v>62</v>
       </c>
       <c r="J5" t="n">
         <v>60</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>TATASTEEL</t>
+          <t>ITC</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Metal</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="M5" t="n">
-        <v>172.6</v>
+        <v>262.2</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>168 - 177</t>
+          <t>256 - 269</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-4% to +3%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>56%</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-11.1%)</t>
+          <t>Below 200-DMA (-12.5%)</t>
         </is>
       </c>
       <c r="S5" t="n">
-        <v>28</v>
+        <v>50</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1945,21 +1945,21 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>2026-11-07</t>
+          <t>2026-11-08</t>
         </is>
       </c>
       <c r="V5" t="n">
-        <v>27781</v>
+        <v>38813</v>
       </c>
       <c r="W5" t="n">
-        <v>161</v>
+        <v>148</v>
       </c>
       <c r="X5" t="n">
-        <v>9.300000000000001</v>
+        <v>12.9</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Metal name under the sector cap</t>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility FMCG name under the sector cap</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1969,12 +1969,12 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — TATASTEEL: 59; COALINDIA: 64, HINDZINC: 50, SAIL: 45. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ITC: 60; DABUR: 50</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>Low-risk Metal holding (low vol) • below 200-dma (-11.1%) • sector strength 100/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
+          <t>Low-risk FMCG holding (low vol) • below 200-dma (-12.5%) • outperforming Nifty • sector strength 62/100 • regime cautious (partial deploy) • 9 similar past recs: 56% positive, median +0.3%</t>
         </is>
       </c>
     </row>
@@ -1985,11 +1985,11 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Risk/Vol +23 · Historical +13 · Regime +9 · Trend/Tech +6 · Sector +4 = 55</t>
+          <t>Risk/Vol +18 · Historical +15 · Sector +10 · Regime +9 · Trend/Tech +6 = 58</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1999,62 +1999,62 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Sector</t>
+          <t>Trend/Tech</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="G6" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="H6" t="n">
-        <v>92</v>
+        <v>73</v>
       </c>
       <c r="I6" t="n">
-        <v>38</v>
+        <v>100</v>
       </c>
       <c r="J6" t="n">
         <v>60</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>ITC</t>
+          <t>TATASTEEL</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>Metal</t>
         </is>
       </c>
       <c r="M6" t="n">
-        <v>255.4</v>
+        <v>172.6</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>249 - 261</t>
+          <t>168 - 177</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-4% to +3%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>56%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-15.0%)</t>
+          <t>Below 200-DMA (-11.1%)</t>
         </is>
       </c>
       <c r="S6" t="n">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -2063,21 +2063,21 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>2026-11-07</t>
+          <t>2026-11-08</t>
         </is>
       </c>
       <c r="V6" t="n">
-        <v>39579</v>
+        <v>27613</v>
       </c>
       <c r="W6" t="n">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="X6" t="n">
-        <v>13.2</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility FMCG name under the sector cap</t>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Metal name under the sector cap</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -2087,12 +2087,12 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ITC: 55; DABUR: 50</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — TATASTEEL: 58; COALINDIA: 64, SAIL: 54, HINDZINC: 51. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>Low-risk FMCG holding (low vol) • below 200-dma (-15.0%) • sector strength 38/100 • regime cautious (partial deploy) • 9 similar past recs: 56% positive, median +0.3%</t>
+          <t>Low-risk Metal holding (low vol) • below 200-dma (-11.1%) • sector strength 100/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
         </is>
       </c>
     </row>
@@ -2103,11 +2103,11 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Risk/Vol +20 · Historical +15 · Regime +9 · Trend/Tech +5 · Sector +5 = 54</t>
+          <t>Risk/Vol +22 · Historical +15 · Regime +9 · Trend/Tech +5 · Sector +2 = 53</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -2124,33 +2124,33 @@
         <v>50</v>
       </c>
       <c r="G7" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H7" t="n">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="I7" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="J7" t="n">
         <v>60</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>BEL</t>
+          <t>TATAPOWER</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Power</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>372.5</v>
+        <v>340</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>363 - 382</t>
+          <t>331 - 349</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -2168,11 +2168,11 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-10.8%)</t>
+          <t>Below 200-DMA (-11.7%)</t>
         </is>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -2181,21 +2181,21 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>2026-11-07</t>
+          <t>2026-11-08</t>
         </is>
       </c>
       <c r="V7" t="n">
-        <v>27938</v>
+        <v>31960</v>
       </c>
       <c r="W7" t="n">
-        <v>75</v>
+        <v>94</v>
       </c>
       <c r="X7" t="n">
-        <v>9.300000000000001</v>
+        <v>10.7</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Industrials name under the sector cap</t>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Power name under the sector cap</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -2205,12 +2205,12 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>No same-sector peer in the universe.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — TATAPOWER: 53; NHPC: 46, ADANIPOWER: 34, NLCINDIA: 31</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>Low-risk Industrials holding (low vol) • below 200-dma (-10.8%) • sector strength 50/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
+          <t>Low-risk Power holding (low vol) • below 200-dma (-11.7%) • sector strength 25/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
         </is>
       </c>
     </row>
@@ -2221,11 +2221,11 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Risk/Vol +22 · Historical +15 · Regime +9 · Trend/Tech +5 · Sector +2 = 53</t>
+          <t>Risk/Vol +19 · Historical +15 · Regime +9 · Trend/Tech +5 · Sector +4 = 52</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -2242,33 +2242,33 @@
         <v>50</v>
       </c>
       <c r="G8" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H8" t="n">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="I8" t="n">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="J8" t="n">
         <v>60</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>TATAPOWER</t>
+          <t>BEL</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Power</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="M8" t="n">
-        <v>338.5</v>
+        <v>367.9</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>330 - 347</t>
+          <t>358 - 377</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -2282,15 +2282,15 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-12.1%)</t>
+          <t>Below 200-DMA (-11.9%)</t>
         </is>
       </c>
       <c r="S8" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -2299,21 +2299,21 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>2026-11-07</t>
+          <t>2026-11-08</t>
         </is>
       </c>
       <c r="V8" t="n">
-        <v>31485</v>
+        <v>27589</v>
       </c>
       <c r="W8" t="n">
-        <v>93</v>
+        <v>75</v>
       </c>
       <c r="X8" t="n">
-        <v>10.5</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Power name under the sector cap</t>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Industrials name under the sector cap</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
@@ -2323,12 +2323,12 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — TATAPOWER: 53; NHPC: 46, ADANIPOWER: 34, NLCINDIA: 30</t>
+          <t>No same-sector peer in the universe.</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>Low-risk Power holding (low vol) • below 200-dma (-12.1%) • sector strength 25/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
+          <t>Low-risk Industrials holding (low vol) • below 200-dma (-11.9%) • sector strength 38/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
         </is>
       </c>
     </row>
@@ -2343,7 +2343,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Risk/Vol +16 · Historical +15 · Regime +9 · Trend/Tech +6 · Sector +4 = 50</t>
+          <t>Risk/Vol +16 · Historical +15 · Regime +9 · Sector +6 · Trend/Tech +4 = 50</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2353,20 +2353,20 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Sector</t>
+          <t>Trend/Tech</t>
         </is>
       </c>
       <c r="F9" t="n">
         <v>50</v>
       </c>
       <c r="G9" t="n">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="H9" t="n">
         <v>65</v>
       </c>
       <c r="I9" t="n">
-        <v>38</v>
+        <v>62</v>
       </c>
       <c r="J9" t="n">
         <v>60</v>
@@ -2382,11 +2382,11 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>383.4</v>
+        <v>384.4</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>373 - 394</t>
+          <t>374 - 395</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -2404,11 +2404,11 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-14.2%)</t>
+          <t>Below 200-DMA (-13.8%)</t>
         </is>
       </c>
       <c r="S9" t="n">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -2417,11 +2417,11 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>2026-11-07</t>
+          <t>2026-11-08</t>
         </is>
       </c>
       <c r="V9" t="n">
-        <v>46008</v>
+        <v>46122</v>
       </c>
       <c r="W9" t="n">
         <v>120</v>
@@ -2441,12 +2441,12 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — DABUR: 50; ITC: 55. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — DABUR: 50; ITC: 60. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>Low-risk FMCG holding (medium vol) • below 200-dma (-14.2%) • sector strength 38/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
+          <t>Low-risk FMCG holding (medium vol) • below 200-dma (-13.8%) • sector strength 62/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
         </is>
       </c>
     </row>
@@ -11411,15 +11411,9 @@
       <c r="L106" t="n">
         <v>-1.05</v>
       </c>
-      <c r="M106" t="n">
-        <v>1</v>
-      </c>
-      <c r="N106" t="n">
-        <v>-17.4</v>
-      </c>
-      <c r="O106" t="n">
-        <v>-1645</v>
-      </c>
+      <c r="M106" t="inlineStr"/>
+      <c r="N106" t="inlineStr"/>
+      <c r="O106" t="inlineStr"/>
       <c r="P106" t="n">
         <v>-51.4</v>
       </c>
@@ -25388,15 +25382,9 @@
       <c r="L279" t="n">
         <v>0.27</v>
       </c>
-      <c r="M279" t="n">
-        <v>23.5</v>
-      </c>
-      <c r="N279" t="n">
-        <v>0</v>
-      </c>
-      <c r="O279" t="n">
-        <v>10</v>
-      </c>
+      <c r="M279" t="inlineStr"/>
+      <c r="N279" t="inlineStr"/>
+      <c r="O279" t="inlineStr"/>
       <c r="P279" t="n">
         <v>10.2</v>
       </c>
@@ -27171,7 +27159,7 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>-11.8</v>
+        <v>-12.6</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -27251,7 +27239,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>17.2%</t>
+          <t>17.0%</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -27266,7 +27254,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>15.7%</t>
+          <t>15.6%</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -27281,7 +27269,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>15.2%</t>
+          <t>15.4%</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -27296,7 +27284,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>6.3%</t>
+          <t>6.4%</t>
         </is>
       </c>
       <c r="C5" t="n">

--- a/reports/AEGIS_LATEST.xlsx
+++ b/reports/AEGIS_LATEST.xlsx
@@ -444,7 +444,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>
@@ -489,7 +489,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7">
@@ -512,7 +512,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-11-08</t>
+          <t>2026-11-11</t>
         </is>
       </c>
     </row>
@@ -524,7 +524,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ICICIBANK (72)</t>
+          <t>ICICIBANK (71)</t>
         </is>
       </c>
     </row>
@@ -536,7 +536,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>DABUR (50)</t>
+          <t>DABUR (48)</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-09  /  2026-10-09</t>
+          <t>2026-10-12  /  2026-10-12</t>
         </is>
       </c>
     </row>
@@ -760,7 +760,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-11-08</t>
+          <t>2026-11-11</t>
         </is>
       </c>
     </row>
@@ -908,7 +908,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>14.7%</t>
+          <t>14.6%</t>
         </is>
       </c>
     </row>
@@ -920,7 +920,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.84</t>
         </is>
       </c>
     </row>
@@ -1513,11 +1513,11 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Risk/Vol +24 · Historical +20 · Trend/Tech +10 · Regime +9 · Sector +9 = 72</t>
+          <t>Risk/Vol +24 · Historical +20 · Trend/Tech +9 · Regime +9 · Sector +9 = 71</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -1534,7 +1534,7 @@
         <v>66</v>
       </c>
       <c r="G2" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H2" t="n">
         <v>96</v>
@@ -1556,11 +1556,11 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>1348.6</v>
+        <v>1336.4</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>1320 - 1377</t>
+          <t>1309 - 1364</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -1578,11 +1578,11 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-0.4%)</t>
+          <t>Below 200-DMA (-1.3%)</t>
         </is>
       </c>
       <c r="S2" t="n">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -1591,17 +1591,17 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>2026-11-08</t>
+          <t>2026-11-11</t>
         </is>
       </c>
       <c r="V2" t="n">
-        <v>45852</v>
+        <v>46774</v>
       </c>
       <c r="W2" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="X2" t="n">
-        <v>15.4</v>
+        <v>15.8</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
@@ -1615,32 +1615,32 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ICICIBANK: 72; PNB: 69, SBIN: 65, IDFCFIRSTB: 59</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ICICIBANK: 71; PNB: 68, SBIN: 64, IDFCFIRSTB: 58</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>Low-risk Financials holding (low vol) • below 200-dma (-0.4%) • outperforming Nifty • sector strength 88/100 • regime cautious (partial deploy) • 8 similar past recs: 75% positive, median +5.3%</t>
+          <t>Low-risk Financials holding (low vol) • below 200-dma (-1.3%) • outperforming Nifty • sector strength 88/100 • regime cautious (partial deploy) • 8 similar past recs: 75% positive, median +5.3%</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>STRONG BUY</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Risk/Vol +21 · Historical +20 · Regime +9 · Sector +9 · Trend/Tech +6 = 65</t>
+          <t>Historical +20 · Risk/Vol +20 · Regime +9 · Sector +9 · Trend/Tech +6 = 64</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Risk/Vol</t>
+          <t>Historical</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1652,10 +1652,10 @@
         <v>65</v>
       </c>
       <c r="G3" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="H3" t="n">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="I3" t="n">
         <v>88</v>
@@ -1674,11 +1674,11 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>952.2</v>
+        <v>940.5</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>928 - 977</t>
+          <t>916 - 965</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -1696,11 +1696,11 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-8.5%)</t>
+          <t>Below 200-DMA (-9.6%)</t>
         </is>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -1709,21 +1709,21 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>2026-11-08</t>
+          <t>2026-11-11</t>
         </is>
       </c>
       <c r="V3" t="n">
-        <v>30472</v>
+        <v>30098</v>
       </c>
       <c r="W3" t="n">
         <v>32</v>
       </c>
       <c r="X3" t="n">
-        <v>10.3</v>
+        <v>10.2</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Financials name under the sector cap</t>
+          <t>Historical + Risk/Vol strongest; chosen as a lowest-volatility Financials name under the sector cap</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -1733,12 +1733,12 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — SBIN: 65; ICICIBANK: 72, PNB: 69, IDFCFIRSTB: 59. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — SBIN: 64; ICICIBANK: 71, PNB: 68, IDFCFIRSTB: 58. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>Low-risk Financials holding (low vol) • below 200-dma (-8.5%) • sector strength 88/100 • regime cautious (partial deploy) • 2 similar past recs: 100% positive, median +8.9%</t>
+          <t>Low-risk Financials holding (low vol) • below 200-dma (-9.6%) • sector strength 88/100 • regime cautious (partial deploy) • 2 similar past recs: 100% positive, median +8.9%</t>
         </is>
       </c>
     </row>
@@ -1749,11 +1749,11 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Risk/Vol +20 · Historical +15 · Trend/Tech +10 · Sector +10 · Regime +9 = 64</t>
+          <t>Risk/Vol +19 · Historical +15 · Sector +10 · Trend/Tech +9 · Regime +9 = 62</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1770,10 +1770,10 @@
         <v>51</v>
       </c>
       <c r="G4" t="n">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="H4" t="n">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="I4" t="n">
         <v>100</v>
@@ -1792,11 +1792,11 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>411</v>
+        <v>404.8</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>400 - 422</t>
+          <t>394 - 415</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -1810,15 +1810,15 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-5.3%)</t>
+          <t>Below 200-DMA (-6.7%)</t>
         </is>
       </c>
       <c r="S4" t="n">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1827,17 +1827,17 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>2026-11-08</t>
+          <t>2026-11-11</t>
         </is>
       </c>
       <c r="V4" t="n">
-        <v>50136</v>
+        <v>49386</v>
       </c>
       <c r="W4" t="n">
         <v>122</v>
       </c>
       <c r="X4" t="n">
-        <v>16.7</v>
+        <v>16.5</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -1851,12 +1851,12 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — COALINDIA: 64; TATASTEEL: 58, SAIL: 54, HINDZINC: 51</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — COALINDIA: 62; TATASTEEL: 58, SAIL: 54, HINDZINC: 51</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>Low-risk Metal holding (low vol) • below 200-dma (-5.3%) • outperforming Nifty • sector strength 100/100 • regime cautious (partial deploy) • 3 similar past recs: 67% positive, median +0.8%</t>
+          <t>Low-risk Metal holding (low vol) • below 200-dma (-6.7%) • sector strength 100/100 • regime cautious (partial deploy) • 3 similar past recs: 67% positive, median +0.8%</t>
         </is>
       </c>
     </row>
@@ -1867,11 +1867,11 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Risk/Vol +23 · Historical +13 · Trend/Tech +9 · Regime +9 · Sector +6 = 60</t>
+          <t>Risk/Vol +18 · Historical +15 · Sector +10 · Regime +9 · Trend/Tech +6 = 58</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1881,62 +1881,62 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Sector</t>
+          <t>Trend/Tech</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="G5" t="n">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="H5" t="n">
-        <v>92</v>
+        <v>73</v>
       </c>
       <c r="I5" t="n">
-        <v>62</v>
+        <v>100</v>
       </c>
       <c r="J5" t="n">
         <v>60</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>ITC</t>
+          <t>TATASTEEL</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>Metal</t>
         </is>
       </c>
       <c r="M5" t="n">
-        <v>262.2</v>
+        <v>173.3</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>256 - 269</t>
+          <t>169 - 178</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-4% to +3%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>56%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-12.5%)</t>
+          <t>Below 200-DMA (-10.8%)</t>
         </is>
       </c>
       <c r="S5" t="n">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1945,21 +1945,21 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>2026-11-08</t>
+          <t>2026-11-11</t>
         </is>
       </c>
       <c r="V5" t="n">
-        <v>38813</v>
+        <v>27214</v>
       </c>
       <c r="W5" t="n">
-        <v>148</v>
+        <v>157</v>
       </c>
       <c r="X5" t="n">
-        <v>12.9</v>
+        <v>9.1</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility FMCG name under the sector cap</t>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Metal name under the sector cap</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1969,12 +1969,12 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ITC: 60; DABUR: 50</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — TATASTEEL: 58; COALINDIA: 62, SAIL: 54, HINDZINC: 51. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>Low-risk FMCG holding (low vol) • below 200-dma (-12.5%) • outperforming Nifty • sector strength 62/100 • regime cautious (partial deploy) • 9 similar past recs: 56% positive, median +0.3%</t>
+          <t>Low-risk Metal holding (low vol) • below 200-dma (-10.8%) • sector strength 100/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
         </is>
       </c>
     </row>
@@ -1985,11 +1985,11 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Risk/Vol +18 · Historical +15 · Sector +10 · Regime +9 · Trend/Tech +6 = 58</t>
+          <t>Risk/Vol +23 · Historical +13 · Regime +9 · Trend/Tech +8 · Sector +4 = 57</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1999,62 +1999,62 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Trend/Tech</t>
+          <t>Sector</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="G6" t="n">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="H6" t="n">
-        <v>73</v>
+        <v>92</v>
       </c>
       <c r="I6" t="n">
-        <v>100</v>
+        <v>38</v>
       </c>
       <c r="J6" t="n">
         <v>60</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>TATASTEEL</t>
+          <t>ITC</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Metal</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="M6" t="n">
-        <v>172.6</v>
+        <v>258.5</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>168 - 177</t>
+          <t>252 - 265</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-4% to +3%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>56%</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-11.1%)</t>
+          <t>Below 200-DMA (-13.6%)</t>
         </is>
       </c>
       <c r="S6" t="n">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -2063,21 +2063,21 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>2026-11-08</t>
+          <t>2026-11-11</t>
         </is>
       </c>
       <c r="V6" t="n">
-        <v>27613</v>
+        <v>39284</v>
       </c>
       <c r="W6" t="n">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="X6" t="n">
-        <v>9.300000000000001</v>
+        <v>13.1</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Metal name under the sector cap</t>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility FMCG name under the sector cap</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -2087,27 +2087,27 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — TATASTEEL: 58; COALINDIA: 64, SAIL: 54, HINDZINC: 51. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ITC: 57; DABUR: 48</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>Low-risk Metal holding (low vol) • below 200-dma (-11.1%) • sector strength 100/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
+          <t>Low-risk FMCG holding (low vol) • below 200-dma (-13.6%) • sector strength 38/100 • regime cautious (partial deploy) • 9 similar past recs: 56% positive, median +0.3%</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ACCUMULATE</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Risk/Vol +22 · Historical +15 · Regime +9 · Trend/Tech +5 · Sector +2 = 53</t>
+          <t>Risk/Vol +21 · Historical +15 · Regime +9 · Sector +6 · Trend/Tech +5 = 56</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -2117,40 +2117,40 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Sector</t>
+          <t>Trend/Tech</t>
         </is>
       </c>
       <c r="F7" t="n">
         <v>50</v>
       </c>
       <c r="G7" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H7" t="n">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="I7" t="n">
-        <v>25</v>
+        <v>62</v>
       </c>
       <c r="J7" t="n">
         <v>60</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>TATAPOWER</t>
+          <t>BEL</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Power</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>340</v>
+        <v>370.4</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>331 - 349</t>
+          <t>361 - 380</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -2164,15 +2164,15 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-11.7%)</t>
+          <t>Below 200-DMA (-11.3%)</t>
         </is>
       </c>
       <c r="S7" t="n">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -2181,21 +2181,21 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>2026-11-08</t>
+          <t>2026-11-11</t>
         </is>
       </c>
       <c r="V7" t="n">
-        <v>31960</v>
+        <v>27410</v>
       </c>
       <c r="W7" t="n">
-        <v>94</v>
+        <v>74</v>
       </c>
       <c r="X7" t="n">
-        <v>10.7</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Power name under the sector cap</t>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Industrials name under the sector cap</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -2205,12 +2205,12 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — TATAPOWER: 53; NHPC: 46, ADANIPOWER: 34, NLCINDIA: 31</t>
+          <t>No same-sector peer in the universe.</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>Low-risk Power holding (low vol) • below 200-dma (-11.7%) • sector strength 25/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
+          <t>Low-risk Industrials holding (low vol) • below 200-dma (-11.3%) • sector strength 62/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
         </is>
       </c>
     </row>
@@ -2221,11 +2221,11 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Risk/Vol +19 · Historical +15 · Regime +9 · Trend/Tech +5 · Sector +4 = 52</t>
+          <t>Risk/Vol +22 · Historical +15 · Regime +9 · Trend/Tech +5 · Sector +2 = 53</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -2245,30 +2245,30 @@
         <v>26</v>
       </c>
       <c r="H8" t="n">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="I8" t="n">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="J8" t="n">
         <v>60</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>BEL</t>
+          <t>TATAPOWER</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Power</t>
         </is>
       </c>
       <c r="M8" t="n">
-        <v>367.9</v>
+        <v>341.5</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>358 - 377</t>
+          <t>333 - 350</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -2282,15 +2282,15 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-11.9%)</t>
+          <t>Below 200-DMA (-11.3%)</t>
         </is>
       </c>
       <c r="S8" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -2299,21 +2299,21 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>2026-11-08</t>
+          <t>2026-11-11</t>
         </is>
       </c>
       <c r="V8" t="n">
-        <v>27589</v>
+        <v>31755</v>
       </c>
       <c r="W8" t="n">
-        <v>75</v>
+        <v>93</v>
       </c>
       <c r="X8" t="n">
-        <v>9.300000000000001</v>
+        <v>10.6</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Industrials name under the sector cap</t>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Power name under the sector cap</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
@@ -2323,12 +2323,12 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>No same-sector peer in the universe.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — TATAPOWER: 53; NHPC: 46, ADANIPOWER: 34, NLCINDIA: 31</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>Low-risk Industrials holding (low vol) • below 200-dma (-11.9%) • sector strength 38/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
+          <t>Low-risk Power holding (low vol) • below 200-dma (-11.3%) • sector strength 25/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
         </is>
       </c>
     </row>
@@ -2339,11 +2339,11 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Risk/Vol +16 · Historical +15 · Regime +9 · Sector +6 · Trend/Tech +4 = 50</t>
+          <t>Risk/Vol +16 · Historical +15 · Regime +9 · Trend/Tech +4 · Sector +4 = 48</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2353,7 +2353,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Trend/Tech</t>
+          <t>Sector</t>
         </is>
       </c>
       <c r="F9" t="n">
@@ -2366,7 +2366,7 @@
         <v>65</v>
       </c>
       <c r="I9" t="n">
-        <v>62</v>
+        <v>38</v>
       </c>
       <c r="J9" t="n">
         <v>60</v>
@@ -2382,11 +2382,11 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>384.4</v>
+        <v>377.9</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>374 - 395</t>
+          <t>368 - 388</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -2404,11 +2404,11 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-13.8%)</t>
+          <t>Below 200-DMA (-15.2%)</t>
         </is>
       </c>
       <c r="S9" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -2417,17 +2417,17 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>2026-11-08</t>
+          <t>2026-11-11</t>
         </is>
       </c>
       <c r="V9" t="n">
-        <v>46122</v>
+        <v>46104</v>
       </c>
       <c r="W9" t="n">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="X9" t="n">
-        <v>15.4</v>
+        <v>15.5</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -2441,12 +2441,12 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — DABUR: 50; ITC: 60. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — DABUR: 48; ITC: 57. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>Low-risk FMCG holding (medium vol) • below 200-dma (-13.8%) • sector strength 62/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
+          <t>Low-risk FMCG holding (medium vol) • below 200-dma (-15.2%) • sector strength 38/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
         </is>
       </c>
     </row>
@@ -27239,7 +27239,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>17.0%</t>
+          <t>17.1%</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -27249,7 +27249,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Metal</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -27264,7 +27264,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Metal</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -27299,7 +27299,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>5.5%</t>
         </is>
       </c>
       <c r="C6" t="n">

--- a/reports/AEGIS_LATEST.xlsx
+++ b/reports/AEGIS_LATEST.xlsx
@@ -444,7 +444,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -512,7 +512,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-11-11</t>
+          <t>2026-11-12</t>
         </is>
       </c>
     </row>
@@ -524,7 +524,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ICICIBANK (71)</t>
+          <t>ICICIBANK (70)</t>
         </is>
       </c>
     </row>
@@ -536,7 +536,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>DABUR (48)</t>
+          <t>DABUR (51)</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-12  /  2026-10-12</t>
+          <t>2026-10-13  /  2026-10-13</t>
         </is>
       </c>
     </row>
@@ -760,7 +760,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-11-11</t>
+          <t>2026-11-12</t>
         </is>
       </c>
     </row>
@@ -908,7 +908,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>14.6%</t>
+          <t>14.7%</t>
         </is>
       </c>
     </row>
@@ -920,7 +920,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>1.85</t>
         </is>
       </c>
     </row>
@@ -1513,11 +1513,11 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Risk/Vol +24 · Historical +20 · Trend/Tech +9 · Regime +9 · Sector +9 = 71</t>
+          <t>Risk/Vol +24 · Historical +20 · Trend/Tech +9 · Regime +9 · Sector +8 = 70</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -1534,13 +1534,13 @@
         <v>66</v>
       </c>
       <c r="G2" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H2" t="n">
         <v>96</v>
       </c>
       <c r="I2" t="n">
-        <v>88</v>
+        <v>75</v>
       </c>
       <c r="J2" t="n">
         <v>60</v>
@@ -1556,11 +1556,11 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>1336.4</v>
+        <v>1349.8</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>1309 - 1364</t>
+          <t>1322 - 1378</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -1578,11 +1578,11 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-1.3%)</t>
+          <t>Below 200-DMA (-0.3%)</t>
         </is>
       </c>
       <c r="S2" t="n">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -1591,17 +1591,17 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>2026-11-11</t>
+          <t>2026-11-12</t>
         </is>
       </c>
       <c r="V2" t="n">
-        <v>46774</v>
+        <v>47243</v>
       </c>
       <c r="W2" t="n">
         <v>35</v>
       </c>
       <c r="X2" t="n">
-        <v>15.8</v>
+        <v>15.9</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
@@ -1615,12 +1615,12 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ICICIBANK: 71; PNB: 68, SBIN: 64, IDFCFIRSTB: 58</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ICICIBANK: 70; PNB: 67, SBIN: 64, IDFCFIRSTB: 58</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>Low-risk Financials holding (low vol) • below 200-dma (-1.3%) • outperforming Nifty • sector strength 88/100 • regime cautious (partial deploy) • 8 similar past recs: 75% positive, median +5.3%</t>
+          <t>Low-risk Financials holding (low vol) • below 200-dma (-0.3%) • outperforming Nifty • sector strength 75/100 • regime cautious (partial deploy) • 8 similar past recs: 75% positive, median +5.3%</t>
         </is>
       </c>
     </row>
@@ -1635,12 +1635,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Historical +20 · Risk/Vol +20 · Regime +9 · Sector +9 · Trend/Tech +6 = 64</t>
+          <t>Risk/Vol +21 · Historical +20 · Regime +9 · Sector +8 · Trend/Tech +6 = 64</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Historical</t>
+          <t>Risk/Vol</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1652,13 +1652,13 @@
         <v>65</v>
       </c>
       <c r="G3" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="H3" t="n">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="I3" t="n">
-        <v>88</v>
+        <v>75</v>
       </c>
       <c r="J3" t="n">
         <v>60</v>
@@ -1674,11 +1674,11 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>940.5</v>
+        <v>942.8</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>916 - 965</t>
+          <t>918 - 967</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -1696,11 +1696,11 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-9.6%)</t>
+          <t>Below 200-DMA (-9.4%)</t>
         </is>
       </c>
       <c r="S3" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -1709,11 +1709,11 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>2026-11-11</t>
+          <t>2026-11-12</t>
         </is>
       </c>
       <c r="V3" t="n">
-        <v>30098</v>
+        <v>30170</v>
       </c>
       <c r="W3" t="n">
         <v>32</v>
@@ -1723,7 +1723,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>Historical + Risk/Vol strongest; chosen as a lowest-volatility Financials name under the sector cap</t>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Financials name under the sector cap</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -1733,12 +1733,12 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — SBIN: 64; ICICIBANK: 71, PNB: 68, IDFCFIRSTB: 58. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — SBIN: 64; ICICIBANK: 70, PNB: 67, IDFCFIRSTB: 58. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>Low-risk Financials holding (low vol) • below 200-dma (-9.6%) • sector strength 88/100 • regime cautious (partial deploy) • 2 similar past recs: 100% positive, median +8.9%</t>
+          <t>Low-risk Financials holding (low vol) • below 200-dma (-9.4%) • sector strength 75/100 • regime cautious (partial deploy) • 2 similar past recs: 100% positive, median +8.9%</t>
         </is>
       </c>
     </row>
@@ -1749,11 +1749,11 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Risk/Vol +19 · Historical +15 · Sector +10 · Trend/Tech +9 · Regime +9 = 62</t>
+          <t>Risk/Vol +23 · Historical +13 · Trend/Tech +9 · Regime +9 · Sector +5 = 59</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1763,62 +1763,62 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Regime</t>
+          <t>Sector</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="G4" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H4" t="n">
-        <v>77</v>
+        <v>92</v>
       </c>
       <c r="I4" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="J4" t="n">
         <v>60</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>COALINDIA</t>
+          <t>ITC</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Metal</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>404.8</v>
+        <v>260.2</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>394 - 415</t>
+          <t>254 - 266</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-4% to +3%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>56%</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-6.7%)</t>
+          <t>Below 200-DMA (-12.8%)</t>
         </is>
       </c>
       <c r="S4" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1827,21 +1827,21 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>2026-11-11</t>
+          <t>2026-11-12</t>
         </is>
       </c>
       <c r="V4" t="n">
-        <v>49386</v>
+        <v>39030</v>
       </c>
       <c r="W4" t="n">
-        <v>122</v>
+        <v>150</v>
       </c>
       <c r="X4" t="n">
-        <v>16.5</v>
+        <v>13.1</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Metal name under the sector cap</t>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility FMCG name under the sector cap</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1851,12 +1851,12 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — COALINDIA: 62; TATASTEEL: 58, SAIL: 54, HINDZINC: 51</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ITC: 59; DABUR: 51</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>Low-risk Metal holding (low vol) • below 200-dma (-6.7%) • sector strength 100/100 • regime cautious (partial deploy) • 3 similar past recs: 67% positive, median +0.8%</t>
+          <t>Low-risk FMCG holding (low vol) • below 200-dma (-12.8%) • outperforming Nifty • sector strength 50/100 • regime cautious (partial deploy) • 9 similar past recs: 56% positive, median +0.3%</t>
         </is>
       </c>
     </row>
@@ -1867,11 +1867,11 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Risk/Vol +18 · Historical +15 · Sector +10 · Regime +9 · Trend/Tech +6 = 58</t>
+          <t>Risk/Vol +20 · Historical +15 · Regime +9 · Sector +9 · Trend/Tech +6 = 59</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1888,13 +1888,13 @@
         <v>50</v>
       </c>
       <c r="G5" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H5" t="n">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="I5" t="n">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="J5" t="n">
         <v>60</v>
@@ -1910,7 +1910,7 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>173.3</v>
+        <v>173.7</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -1928,15 +1928,15 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-10.8%)</t>
+          <t>Below 200-DMA (-10.6%)</t>
         </is>
       </c>
       <c r="S5" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1945,11 +1945,11 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>2026-11-11</t>
+          <t>2026-11-12</t>
         </is>
       </c>
       <c r="V5" t="n">
-        <v>27214</v>
+        <v>27268</v>
       </c>
       <c r="W5" t="n">
         <v>157</v>
@@ -1969,12 +1969,12 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — TATASTEEL: 58; COALINDIA: 62, SAIL: 54, HINDZINC: 51. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — TATASTEEL: 59; COALINDIA: 58, SAIL: 53, HINDZINC: 49</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>Low-risk Metal holding (low vol) • below 200-dma (-10.8%) • sector strength 100/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
+          <t>Low-risk Metal holding (low vol) • below 200-dma (-10.6%) • sector strength 88/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
         </is>
       </c>
     </row>
@@ -1985,11 +1985,11 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Risk/Vol +23 · Historical +13 · Regime +9 · Trend/Tech +8 · Sector +4 = 57</t>
+          <t>Risk/Vol +18 · Historical +15 · Regime +9 · Sector +9 · Trend/Tech +7 = 58</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1999,62 +1999,62 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Sector</t>
+          <t>Trend/Tech</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="G6" t="n">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="H6" t="n">
-        <v>92</v>
+        <v>73</v>
       </c>
       <c r="I6" t="n">
-        <v>38</v>
+        <v>88</v>
       </c>
       <c r="J6" t="n">
         <v>60</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>ITC</t>
+          <t>COALINDIA</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>Metal</t>
         </is>
       </c>
       <c r="M6" t="n">
-        <v>258.5</v>
+        <v>408.9</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>252 - 265</t>
+          <t>398 - 420</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-4% to +3%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>56%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-13.6%)</t>
+          <t>Below 200-DMA (-5.8%)</t>
         </is>
       </c>
       <c r="S6" t="n">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -2063,21 +2063,21 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>2026-11-11</t>
+          <t>2026-11-12</t>
         </is>
       </c>
       <c r="V6" t="n">
-        <v>39284</v>
+        <v>49068</v>
       </c>
       <c r="W6" t="n">
-        <v>152</v>
+        <v>120</v>
       </c>
       <c r="X6" t="n">
-        <v>13.1</v>
+        <v>16.5</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility FMCG name under the sector cap</t>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Metal name under the sector cap</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -2087,12 +2087,12 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ITC: 57; DABUR: 48</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — COALINDIA: 58; TATASTEEL: 59, SAIL: 53, HINDZINC: 49. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>Low-risk FMCG holding (low vol) • below 200-dma (-13.6%) • sector strength 38/100 • regime cautious (partial deploy) • 9 similar past recs: 56% positive, median +0.3%</t>
+          <t>Low-risk Metal holding (low vol) • below 200-dma (-5.8%) • outperforming Nifty • sector strength 88/100 • regime cautious (partial deploy) • 3 similar past recs: 67% positive, median +0.8%</t>
         </is>
       </c>
     </row>
@@ -2103,11 +2103,11 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Risk/Vol +21 · Historical +15 · Regime +9 · Sector +6 · Trend/Tech +5 = 56</t>
+          <t>Risk/Vol +19 · Historical +15 · Regime +9 · Trend/Tech +6 · Sector +6 = 55</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -2117,17 +2117,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Trend/Tech</t>
+          <t>Sector</t>
         </is>
       </c>
       <c r="F7" t="n">
         <v>50</v>
       </c>
       <c r="G7" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="H7" t="n">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="I7" t="n">
         <v>62</v>
@@ -2146,11 +2146,11 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>370.4</v>
+        <v>376.2</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>361 - 380</t>
+          <t>366 - 386</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -2168,11 +2168,11 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-11.3%)</t>
+          <t>Below 200-DMA (-9.9%)</t>
         </is>
       </c>
       <c r="S7" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -2181,17 +2181,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>2026-11-11</t>
+          <t>2026-11-12</t>
         </is>
       </c>
       <c r="V7" t="n">
-        <v>27410</v>
+        <v>27086</v>
       </c>
       <c r="W7" t="n">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="X7" t="n">
-        <v>9.199999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -2210,7 +2210,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>Low-risk Industrials holding (low vol) • below 200-dma (-11.3%) • sector strength 62/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
+          <t>Low-risk Industrials holding (low vol) • below 200-dma (-9.9%) • sector strength 62/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
         </is>
       </c>
     </row>
@@ -2242,7 +2242,7 @@
         <v>50</v>
       </c>
       <c r="G8" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H8" t="n">
         <v>88</v>
@@ -2264,11 +2264,11 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>341.5</v>
+        <v>343</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>333 - 350</t>
+          <t>334 - 352</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -2286,11 +2286,11 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-11.3%)</t>
+          <t>Below 200-DMA (-10.9%)</t>
         </is>
       </c>
       <c r="S8" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -2299,14 +2299,14 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>2026-11-11</t>
+          <t>2026-11-12</t>
         </is>
       </c>
       <c r="V8" t="n">
-        <v>31755</v>
+        <v>31556</v>
       </c>
       <c r="W8" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="X8" t="n">
         <v>10.6</v>
@@ -2323,12 +2323,12 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — TATAPOWER: 53; NHPC: 46, ADANIPOWER: 34, NLCINDIA: 31</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — TATAPOWER: 53; NHPC: 46, ADANIPOWER: 35, NLCINDIA: 31</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>Low-risk Power holding (low vol) • below 200-dma (-11.3%) • sector strength 25/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
+          <t>Low-risk Power holding (low vol) • below 200-dma (-10.9%) • sector strength 25/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
         </is>
       </c>
     </row>
@@ -2339,11 +2339,11 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Risk/Vol +16 · Historical +15 · Regime +9 · Trend/Tech +4 · Sector +4 = 48</t>
+          <t>Risk/Vol +16 · Historical +15 · Regime +9 · Trend/Tech +6 · Sector +5 = 51</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2360,13 +2360,13 @@
         <v>50</v>
       </c>
       <c r="G9" t="n">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="H9" t="n">
         <v>65</v>
       </c>
       <c r="I9" t="n">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="J9" t="n">
         <v>60</v>
@@ -2382,11 +2382,11 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>377.9</v>
+        <v>375.6</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>368 - 388</t>
+          <t>365 - 386</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -2400,15 +2400,15 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-15.2%)</t>
+          <t>Below 200-DMA (-15.6%)</t>
         </is>
       </c>
       <c r="S9" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -2417,17 +2417,17 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>2026-11-11</t>
+          <t>2026-11-12</t>
         </is>
       </c>
       <c r="V9" t="n">
-        <v>46104</v>
+        <v>46574</v>
       </c>
       <c r="W9" t="n">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="X9" t="n">
-        <v>15.5</v>
+        <v>15.6</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -2441,12 +2441,12 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — DABUR: 48; ITC: 57. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — DABUR: 51; ITC: 59. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>Low-risk FMCG holding (medium vol) • below 200-dma (-15.2%) • sector strength 38/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
+          <t>Low-risk FMCG holding (medium vol) • below 200-dma (-15.6%) • sector strength 50/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
         </is>
       </c>
     </row>
@@ -27239,7 +27239,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>17.1%</t>
+          <t>17.2%</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -27269,7 +27269,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>15.4%</t>
+          <t>15.3%</t>
         </is>
       </c>
       <c r="C4" t="n">

--- a/reports/AEGIS_LATEST.xlsx
+++ b/reports/AEGIS_LATEST.xlsx
@@ -444,7 +444,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -512,7 +512,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-11-13</t>
         </is>
       </c>
     </row>
@@ -536,7 +536,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>DABUR (51)</t>
+          <t>DABUR (49)</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-13  /  2026-10-13</t>
+          <t>2026-10-14  /  2026-10-14</t>
         </is>
       </c>
     </row>
@@ -760,7 +760,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-11-13</t>
         </is>
       </c>
     </row>
@@ -908,7 +908,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>14.7%</t>
+          <t>14.8%</t>
         </is>
       </c>
     </row>
@@ -920,7 +920,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.86</t>
         </is>
       </c>
     </row>
@@ -1322,7 +1322,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>-5.9%</t>
+          <t>-5.8%</t>
         </is>
       </c>
     </row>
@@ -1534,7 +1534,7 @@
         <v>66</v>
       </c>
       <c r="G2" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H2" t="n">
         <v>96</v>
@@ -1556,11 +1556,11 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>1349.8</v>
+        <v>1349.4</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>1322 - 1378</t>
+          <t>1322 - 1377</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -1591,17 +1591,17 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-11-13</t>
         </is>
       </c>
       <c r="V2" t="n">
-        <v>47243</v>
+        <v>47229</v>
       </c>
       <c r="W2" t="n">
         <v>35</v>
       </c>
       <c r="X2" t="n">
-        <v>15.9</v>
+        <v>16.2</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
@@ -1615,7 +1615,7 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ICICIBANK: 70; PNB: 67, SBIN: 64, IDFCFIRSTB: 58</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ICICIBANK: 70; PNB: 67, SBIN: 63, IDFCFIRSTB: 58</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1631,11 +1631,11 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Risk/Vol +21 · Historical +20 · Regime +9 · Sector +8 · Trend/Tech +6 = 64</t>
+          <t>Risk/Vol +19 · Historical +15 · Trend/Tech +10 · Sector +10 · Regime +9 = 63</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -1645,40 +1645,40 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Trend/Tech</t>
+          <t>Regime</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>65</v>
+        <v>51</v>
       </c>
       <c r="G3" t="n">
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="H3" t="n">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="I3" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="J3" t="n">
         <v>60</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>SBIN</t>
+          <t>COALINDIA</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Metal</t>
         </is>
       </c>
       <c r="M3" t="n">
-        <v>942.8</v>
+        <v>416.7</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>918 - 967</t>
+          <t>406 - 428</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -1692,15 +1692,15 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-9.4%)</t>
+          <t>Below 200-DMA (-4.0%)</t>
         </is>
       </c>
       <c r="S3" t="n">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -1709,21 +1709,21 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-11-13</t>
         </is>
       </c>
       <c r="V3" t="n">
-        <v>30170</v>
+        <v>48754</v>
       </c>
       <c r="W3" t="n">
-        <v>32</v>
+        <v>117</v>
       </c>
       <c r="X3" t="n">
-        <v>10.2</v>
+        <v>16.4</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Financials name under the sector cap</t>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Metal name under the sector cap</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -1733,12 +1733,12 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — SBIN: 64; ICICIBANK: 70, PNB: 67, IDFCFIRSTB: 58. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — COALINDIA: 63; TATASTEEL: 61, SAIL: 54, HINDZINC: 51</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>Low-risk Financials holding (low vol) • below 200-dma (-9.4%) • sector strength 75/100 • regime cautious (partial deploy) • 2 similar past recs: 100% positive, median +8.9%</t>
+          <t>Low-risk Metal holding (low vol) • below 200-dma (-4.0%) • outperforming Nifty • sector strength 100/100 • regime cautious (partial deploy) • 3 similar past recs: 67% positive, median +0.8%</t>
         </is>
       </c>
     </row>
@@ -1749,11 +1749,11 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Risk/Vol +23 · Historical +13 · Trend/Tech +9 · Regime +9 · Sector +5 = 59</t>
+          <t>Risk/Vol +21 · Historical +20 · Regime +9 · Sector +8 · Trend/Tech +5 = 63</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1763,62 +1763,62 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sector</t>
+          <t>Trend/Tech</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>44</v>
+        <v>65</v>
       </c>
       <c r="G4" t="n">
-        <v>45</v>
+        <v>26</v>
       </c>
       <c r="H4" t="n">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="I4" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="J4" t="n">
         <v>60</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>ITC</t>
+          <t>SBIN</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>260.2</v>
+        <v>947</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>254 - 266</t>
+          <t>922 - 972</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-4% to +3%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>56%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-12.8%)</t>
+          <t>Below 200-DMA (-9.0%)</t>
         </is>
       </c>
       <c r="S4" t="n">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1827,21 +1827,21 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-11-13</t>
         </is>
       </c>
       <c r="V4" t="n">
-        <v>39030</v>
+        <v>30304</v>
       </c>
       <c r="W4" t="n">
-        <v>150</v>
+        <v>32</v>
       </c>
       <c r="X4" t="n">
-        <v>13.1</v>
+        <v>10.2</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility FMCG name under the sector cap</t>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Financials name under the sector cap</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1851,12 +1851,12 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ITC: 59; DABUR: 51</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — SBIN: 63; ICICIBANK: 70, PNB: 67, IDFCFIRSTB: 58. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>Low-risk FMCG holding (low vol) • below 200-dma (-12.8%) • outperforming Nifty • sector strength 50/100 • regime cautious (partial deploy) • 9 similar past recs: 56% positive, median +0.3%</t>
+          <t>Low-risk Financials holding (low vol) • below 200-dma (-9.0%) • sector strength 75/100 • regime cautious (partial deploy) • 2 similar past recs: 100% positive, median +8.9%</t>
         </is>
       </c>
     </row>
@@ -1867,11 +1867,11 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Risk/Vol +20 · Historical +15 · Regime +9 · Sector +9 · Trend/Tech +6 = 59</t>
+          <t>Risk/Vol +20 · Historical +15 · Sector +10 · Regime +9 · Trend/Tech +7 = 61</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1888,13 +1888,13 @@
         <v>50</v>
       </c>
       <c r="G5" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H5" t="n">
         <v>81</v>
       </c>
       <c r="I5" t="n">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="J5" t="n">
         <v>60</v>
@@ -1910,11 +1910,11 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>173.7</v>
+        <v>175.4</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>169 - 178</t>
+          <t>171 - 180</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -1932,11 +1932,11 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-10.6%)</t>
+          <t>Below 200-DMA (-9.7%)</t>
         </is>
       </c>
       <c r="S5" t="n">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1945,17 +1945,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-11-13</t>
         </is>
       </c>
       <c r="V5" t="n">
-        <v>27268</v>
+        <v>27018</v>
       </c>
       <c r="W5" t="n">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="X5" t="n">
-        <v>9.1</v>
+        <v>9</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -1969,12 +1969,12 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — TATASTEEL: 59; COALINDIA: 58, SAIL: 53, HINDZINC: 49</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — TATASTEEL: 61; COALINDIA: 63, SAIL: 54, HINDZINC: 51. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>Low-risk Metal holding (low vol) • below 200-dma (-10.6%) • sector strength 88/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
+          <t>Low-risk Metal holding (low vol) • below 200-dma (-9.7%) • outperforming Nifty • sector strength 100/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
         </is>
       </c>
     </row>
@@ -1989,7 +1989,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Risk/Vol +18 · Historical +15 · Regime +9 · Sector +9 · Trend/Tech +7 = 58</t>
+          <t>Risk/Vol +23 · Historical +13 · Regime +9 · Trend/Tech +8 · Sector +5 = 58</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1999,62 +1999,62 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Trend/Tech</t>
+          <t>Sector</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="G6" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="H6" t="n">
-        <v>73</v>
+        <v>92</v>
       </c>
       <c r="I6" t="n">
-        <v>88</v>
+        <v>50</v>
       </c>
       <c r="J6" t="n">
         <v>60</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>COALINDIA</t>
+          <t>ITC</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Metal</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="M6" t="n">
-        <v>408.9</v>
+        <v>260.1</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>398 - 420</t>
+          <t>254 - 266</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-4% to +3%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>56%</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-5.8%)</t>
+          <t>Below 200-DMA (-12.6%)</t>
         </is>
       </c>
       <c r="S6" t="n">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -2063,21 +2063,21 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-11-13</t>
         </is>
       </c>
       <c r="V6" t="n">
-        <v>49068</v>
+        <v>39275</v>
       </c>
       <c r="W6" t="n">
-        <v>120</v>
+        <v>151</v>
       </c>
       <c r="X6" t="n">
-        <v>16.5</v>
+        <v>13.1</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Metal name under the sector cap</t>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility FMCG name under the sector cap</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -2087,12 +2087,12 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — COALINDIA: 58; TATASTEEL: 59, SAIL: 53, HINDZINC: 49. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ITC: 58; DABUR: 49</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>Low-risk Metal holding (low vol) • below 200-dma (-5.8%) • outperforming Nifty • sector strength 88/100 • regime cautious (partial deploy) • 3 similar past recs: 67% positive, median +0.8%</t>
+          <t>Low-risk FMCG holding (low vol) • below 200-dma (-12.6%) • sector strength 50/100 • regime cautious (partial deploy) • 9 similar past recs: 56% positive, median +0.3%</t>
         </is>
       </c>
     </row>
@@ -2107,7 +2107,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Risk/Vol +19 · Historical +15 · Regime +9 · Trend/Tech +6 · Sector +6 = 55</t>
+          <t>Risk/Vol +18 · Historical +15 · Regime +9 · Trend/Tech +7 · Sector +6 = 55</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -2124,10 +2124,10 @@
         <v>50</v>
       </c>
       <c r="G7" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="H7" t="n">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="I7" t="n">
         <v>62</v>
@@ -2146,11 +2146,11 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>376.2</v>
+        <v>381.6</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>366 - 386</t>
+          <t>372 - 392</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -2168,11 +2168,11 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-9.9%)</t>
+          <t>Below 200-DMA (-8.6%)</t>
         </is>
       </c>
       <c r="S7" t="n">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -2181,17 +2181,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-11-13</t>
         </is>
       </c>
       <c r="V7" t="n">
-        <v>27086</v>
+        <v>26712</v>
       </c>
       <c r="W7" t="n">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="X7" t="n">
-        <v>9.1</v>
+        <v>9</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -2210,7 +2210,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>Low-risk Industrials holding (low vol) • below 200-dma (-9.9%) • sector strength 62/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
+          <t>Low-risk Industrials holding (low vol) • below 200-dma (-8.6%) • sector strength 62/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
         </is>
       </c>
     </row>
@@ -2221,11 +2221,11 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Risk/Vol +22 · Historical +15 · Regime +9 · Trend/Tech +5 · Sector +2 = 53</t>
+          <t>Risk/Vol +22 · Historical +15 · Regime +9 · Trend/Tech +6 · Sector +2 = 54</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -2242,7 +2242,7 @@
         <v>50</v>
       </c>
       <c r="G8" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="H8" t="n">
         <v>88</v>
@@ -2264,11 +2264,11 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>343</v>
+        <v>349.1</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>334 - 352</t>
+          <t>340 - 358</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -2286,11 +2286,11 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-10.9%)</t>
+          <t>Below 200-DMA (-9.2%)</t>
         </is>
       </c>
       <c r="S8" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -2299,17 +2299,17 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-11-13</t>
         </is>
       </c>
       <c r="V8" t="n">
-        <v>31556</v>
+        <v>31423</v>
       </c>
       <c r="W8" t="n">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="X8" t="n">
-        <v>10.6</v>
+        <v>10.5</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -2323,12 +2323,12 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — TATAPOWER: 53; NHPC: 46, ADANIPOWER: 35, NLCINDIA: 31</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — TATAPOWER: 54; NHPC: 46, ADANIPOWER: 35, NLCINDIA: 31</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>Low-risk Power holding (low vol) • below 200-dma (-10.9%) • sector strength 25/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
+          <t>Low-risk Power holding (low vol) • below 200-dma (-9.2%) • sector strength 25/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
         </is>
       </c>
     </row>
@@ -2339,11 +2339,11 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Risk/Vol +16 · Historical +15 · Regime +9 · Trend/Tech +6 · Sector +5 = 51</t>
+          <t>Risk/Vol +16 · Historical +15 · Regime +9 · Sector +5 · Trend/Tech +4 = 49</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2353,14 +2353,14 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Sector</t>
+          <t>Trend/Tech</t>
         </is>
       </c>
       <c r="F9" t="n">
         <v>50</v>
       </c>
       <c r="G9" t="n">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="H9" t="n">
         <v>65</v>
@@ -2382,11 +2382,11 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>375.6</v>
+        <v>379.9</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>365 - 386</t>
+          <t>370 - 390</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -2400,15 +2400,15 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-15.6%)</t>
+          <t>Below 200-DMA (-14.5%)</t>
         </is>
       </c>
       <c r="S9" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -2417,17 +2417,17 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-11-13</t>
         </is>
       </c>
       <c r="V9" t="n">
-        <v>46574</v>
+        <v>46348</v>
       </c>
       <c r="W9" t="n">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="X9" t="n">
-        <v>15.6</v>
+        <v>15.5</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -2441,12 +2441,12 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — DABUR: 51; ITC: 59. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — DABUR: 49; ITC: 58. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>Low-risk FMCG holding (medium vol) • below 200-dma (-15.6%) • sector strength 50/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
+          <t>Low-risk FMCG holding (medium vol) • below 200-dma (-14.5%) • sector strength 50/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
         </is>
       </c>
     </row>
@@ -4297,15 +4297,9 @@
       <c r="L18" t="n">
         <v>0.41</v>
       </c>
-      <c r="M18" t="n">
-        <v>14.6</v>
-      </c>
-      <c r="N18" t="n">
-        <v>-3.2</v>
-      </c>
-      <c r="O18" t="n">
-        <v>61</v>
-      </c>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
       <c r="P18" t="n">
         <v>41.1</v>
       </c>
@@ -7851,15 +7845,9 @@
       <c r="L62" t="n">
         <v>0.92</v>
       </c>
-      <c r="M62" t="n">
-        <v>22.1</v>
-      </c>
-      <c r="N62" t="n">
-        <v>0</v>
-      </c>
-      <c r="O62" t="n">
-        <v>93</v>
-      </c>
+      <c r="M62" t="inlineStr"/>
+      <c r="N62" t="inlineStr"/>
+      <c r="O62" t="inlineStr"/>
       <c r="P62" t="n">
         <v>112</v>
       </c>
@@ -9471,15 +9459,9 @@
       <c r="L82" t="n">
         <v>0.4</v>
       </c>
-      <c r="M82" t="n">
-        <v>25.7</v>
-      </c>
-      <c r="N82" t="n">
-        <v>-5.4</v>
-      </c>
-      <c r="O82" t="n">
-        <v>21</v>
-      </c>
+      <c r="M82" t="inlineStr"/>
+      <c r="N82" t="inlineStr"/>
+      <c r="O82" t="inlineStr"/>
       <c r="P82" t="n">
         <v>23.2</v>
       </c>
@@ -26445,7 +26427,7 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>-10.7</v>
+        <v>-10.4</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -26571,7 +26553,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>-4.5</v>
+        <v>-4.6</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -26613,7 +26595,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>-9.300000000000001</v>
+        <v>-8.6</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -27254,7 +27236,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>15.6%</t>
+          <t>15.8%</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -27284,7 +27266,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>6.4%</t>
+          <t>6.3%</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -27299,7 +27281,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>5.5%</t>
+          <t>5.4%</t>
         </is>
       </c>
       <c r="C6" t="n">

--- a/reports/AEGIS_LATEST.xlsx
+++ b/reports/AEGIS_LATEST.xlsx
@@ -444,7 +444,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -489,7 +489,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7">
@@ -512,7 +512,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-11-13</t>
+          <t>2026-11-14</t>
         </is>
       </c>
     </row>
@@ -524,7 +524,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ICICIBANK (70)</t>
+          <t>ICICIBANK (77)</t>
         </is>
       </c>
     </row>
@@ -536,7 +536,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>DABUR (49)</t>
+          <t>DABUR (53)</t>
         </is>
       </c>
     </row>
@@ -582,7 +582,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>84%</t>
+          <t>94%</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-14  /  2026-10-14</t>
+          <t>2026-10-15  /  2026-10-15</t>
         </is>
       </c>
     </row>
@@ -760,7 +760,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-11-13</t>
+          <t>2026-11-14</t>
         </is>
       </c>
     </row>
@@ -920,7 +920,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>1.87</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>84% (validated process)</t>
+          <t>94% (validated process)</t>
         </is>
       </c>
     </row>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Portfolio grade B (validated) · stock-alpha experimental</t>
+          <t>Portfolio grade A (validated) · stock-alpha experimental</t>
         </is>
       </c>
     </row>
@@ -1513,11 +1513,11 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Risk/Vol +24 · Historical +20 · Trend/Tech +9 · Regime +9 · Sector +8 = 70</t>
+          <t>Risk/Vol +24 · Historical +20 · Trend/Tech +16 · Regime +9 · Sector +8 = 77</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -1534,7 +1534,7 @@
         <v>66</v>
       </c>
       <c r="G2" t="n">
-        <v>45</v>
+        <v>81</v>
       </c>
       <c r="H2" t="n">
         <v>96</v>
@@ -1556,11 +1556,11 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>1349.4</v>
+        <v>1361.2</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>1322 - 1377</t>
+          <t>1334 - 1389</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -1574,15 +1574,15 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-0.3%)</t>
+          <t>Above 200-DMA (+0.6%)</t>
         </is>
       </c>
       <c r="S2" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -1591,17 +1591,17 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>2026-11-13</t>
+          <t>2026-11-14</t>
         </is>
       </c>
       <c r="V2" t="n">
-        <v>47229</v>
+        <v>49003</v>
       </c>
       <c r="W2" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="X2" t="n">
-        <v>16.2</v>
+        <v>16.4</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
@@ -1615,12 +1615,12 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ICICIBANK: 70; PNB: 67, SBIN: 63, IDFCFIRSTB: 58</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ICICIBANK: 77; PNB: 67, SBIN: 63, IDFCFIRSTB: 58</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>Low-risk Financials holding (low vol) • below 200-dma (-0.3%) • outperforming Nifty • sector strength 75/100 • regime cautious (partial deploy) • 8 similar past recs: 75% positive, median +5.3%</t>
+          <t>Low-risk Financials holding (low vol) • above 200-dma (+0.6%) • sector strength 75/100 • regime cautious (partial deploy) • 8 similar past recs: 75% positive, median +5.3%</t>
         </is>
       </c>
     </row>
@@ -1635,7 +1635,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Risk/Vol +19 · Historical +15 · Trend/Tech +10 · Sector +10 · Regime +9 = 63</t>
+          <t>Risk/Vol +21 · Historical +20 · Regime +9 · Sector +8 · Trend/Tech +5 = 63</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -1645,40 +1645,40 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Regime</t>
+          <t>Trend/Tech</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="G3" t="n">
-        <v>48</v>
+        <v>25</v>
       </c>
       <c r="H3" t="n">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="I3" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="J3" t="n">
         <v>60</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>COALINDIA</t>
+          <t>SBIN</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Metal</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="M3" t="n">
-        <v>416.7</v>
+        <v>956.1</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>406 - 428</t>
+          <t>931 - 981</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -1696,11 +1696,11 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-4.0%)</t>
+          <t>Below 200-DMA (-8.1%)</t>
         </is>
       </c>
       <c r="S3" t="n">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -1709,21 +1709,21 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>2026-11-13</t>
+          <t>2026-11-14</t>
         </is>
       </c>
       <c r="V3" t="n">
-        <v>48754</v>
+        <v>30595</v>
       </c>
       <c r="W3" t="n">
-        <v>117</v>
+        <v>32</v>
       </c>
       <c r="X3" t="n">
-        <v>16.4</v>
+        <v>10.3</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Metal name under the sector cap</t>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Financials name under the sector cap</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -1733,12 +1733,12 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — COALINDIA: 63; TATASTEEL: 61, SAIL: 54, HINDZINC: 51</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — SBIN: 63; ICICIBANK: 77, PNB: 67, IDFCFIRSTB: 58. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>Low-risk Metal holding (low vol) • below 200-dma (-4.0%) • outperforming Nifty • sector strength 100/100 • regime cautious (partial deploy) • 3 similar past recs: 67% positive, median +0.8%</t>
+          <t>Low-risk Financials holding (low vol) • below 200-dma (-8.1%) • sector strength 75/100 • regime cautious (partial deploy) • 2 similar past recs: 100% positive, median +8.9%</t>
         </is>
       </c>
     </row>
@@ -1749,11 +1749,11 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Risk/Vol +21 · Historical +20 · Regime +9 · Sector +8 · Trend/Tech +5 = 63</t>
+          <t>Risk/Vol +19 · Historical +15 · Trend/Tech +9 · Regime +9 · Sector +9 = 61</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1763,40 +1763,40 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Trend/Tech</t>
+          <t>Sector</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>65</v>
+        <v>51</v>
       </c>
       <c r="G4" t="n">
-        <v>26</v>
+        <v>47</v>
       </c>
       <c r="H4" t="n">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="I4" t="n">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="J4" t="n">
         <v>60</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>SBIN</t>
+          <t>COALINDIA</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Metal</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>947</v>
+        <v>418</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>922 - 972</t>
+          <t>407 - 429</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -1810,15 +1810,15 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-9.0%)</t>
+          <t>Below 200-DMA (-3.7%)</t>
         </is>
       </c>
       <c r="S4" t="n">
-        <v>27</v>
+        <v>48</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1827,21 +1827,21 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>2026-11-13</t>
+          <t>2026-11-14</t>
         </is>
       </c>
       <c r="V4" t="n">
-        <v>30304</v>
+        <v>48494</v>
       </c>
       <c r="W4" t="n">
-        <v>32</v>
+        <v>116</v>
       </c>
       <c r="X4" t="n">
-        <v>10.2</v>
+        <v>16.3</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Financials name under the sector cap</t>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Metal name under the sector cap</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1851,12 +1851,12 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — SBIN: 63; ICICIBANK: 70, PNB: 67, IDFCFIRSTB: 58. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — COALINDIA: 61; TATASTEEL: 59, HINDZINC: 49, SAIL: 43</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>Low-risk Financials holding (low vol) • below 200-dma (-9.0%) • sector strength 75/100 • regime cautious (partial deploy) • 2 similar past recs: 100% positive, median +8.9%</t>
+          <t>Low-risk Metal holding (low vol) • below 200-dma (-3.7%) • outperforming Nifty • sector strength 88/100 • regime cautious (partial deploy) • 3 similar past recs: 67% positive, median +0.8%</t>
         </is>
       </c>
     </row>
@@ -1867,11 +1867,11 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Risk/Vol +20 · Historical +15 · Sector +10 · Regime +9 · Trend/Tech +7 = 61</t>
+          <t>Risk/Vol +23 · Historical +13 · Regime +9 · Trend/Tech +8 · Sector +6 = 59</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1881,62 +1881,62 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Trend/Tech</t>
+          <t>Sector</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="G5" t="n">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="H5" t="n">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="I5" t="n">
-        <v>100</v>
+        <v>62</v>
       </c>
       <c r="J5" t="n">
         <v>60</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>TATASTEEL</t>
+          <t>ITC</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Metal</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="M5" t="n">
-        <v>175.4</v>
+        <v>265.1</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>171 - 180</t>
+          <t>259 - 272</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-4% to +3%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>56%</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-9.7%)</t>
+          <t>Below 200-DMA (-10.7%)</t>
         </is>
       </c>
       <c r="S5" t="n">
-        <v>29</v>
+        <v>46</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1945,21 +1945,21 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>2026-11-13</t>
+          <t>2026-11-14</t>
         </is>
       </c>
       <c r="V5" t="n">
-        <v>27018</v>
+        <v>38970</v>
       </c>
       <c r="W5" t="n">
-        <v>154</v>
+        <v>147</v>
       </c>
       <c r="X5" t="n">
-        <v>9</v>
+        <v>13.1</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Metal name under the sector cap</t>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility FMCG name under the sector cap</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1969,12 +1969,12 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — TATASTEEL: 61; COALINDIA: 63, SAIL: 54, HINDZINC: 51. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ITC: 59; DABUR: 53</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>Low-risk Metal holding (low vol) • below 200-dma (-9.7%) • outperforming Nifty • sector strength 100/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
+          <t>Low-risk FMCG holding (low vol) • below 200-dma (-10.7%) • sector strength 62/100 • regime cautious (partial deploy) • 9 similar past recs: 56% positive, median +0.3%</t>
         </is>
       </c>
     </row>
@@ -1985,11 +1985,11 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Risk/Vol +23 · Historical +13 · Regime +9 · Trend/Tech +8 · Sector +5 = 58</t>
+          <t>Risk/Vol +20 · Historical +15 · Regime +9 · Sector +9 · Trend/Tech +6 = 59</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1999,62 +1999,62 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Sector</t>
+          <t>Trend/Tech</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="G6" t="n">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="H6" t="n">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="I6" t="n">
-        <v>50</v>
+        <v>88</v>
       </c>
       <c r="J6" t="n">
         <v>60</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>ITC</t>
+          <t>TATASTEEL</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>Metal</t>
         </is>
       </c>
       <c r="M6" t="n">
-        <v>260.1</v>
+        <v>175.7</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>254 - 266</t>
+          <t>171 - 180</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-4% to +3%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>56%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-12.6%)</t>
+          <t>Below 200-DMA (-9.6%)</t>
         </is>
       </c>
       <c r="S6" t="n">
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -2063,21 +2063,21 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>2026-11-13</t>
+          <t>2026-11-14</t>
         </is>
       </c>
       <c r="V6" t="n">
-        <v>39275</v>
+        <v>27233</v>
       </c>
       <c r="W6" t="n">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="X6" t="n">
-        <v>13.1</v>
+        <v>9.1</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility FMCG name under the sector cap</t>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Metal name under the sector cap</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -2087,27 +2087,27 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ITC: 58; DABUR: 49</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — TATASTEEL: 59; COALINDIA: 61, HINDZINC: 49, SAIL: 43. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>Low-risk FMCG holding (low vol) • below 200-dma (-12.6%) • sector strength 50/100 • regime cautious (partial deploy) • 9 similar past recs: 56% positive, median +0.3%</t>
+          <t>Low-risk Metal holding (low vol) • below 200-dma (-9.6%) • sector strength 88/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>ACCUMULATE</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Risk/Vol +18 · Historical +15 · Regime +9 · Trend/Tech +7 · Sector +6 = 55</t>
+          <t>Risk/Vol +22 · Historical +15 · Regime +9 · Trend/Tech +6 · Sector +2 = 54</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -2124,33 +2124,33 @@
         <v>50</v>
       </c>
       <c r="G7" t="n">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="H7" t="n">
-        <v>73</v>
+        <v>88</v>
       </c>
       <c r="I7" t="n">
-        <v>62</v>
+        <v>25</v>
       </c>
       <c r="J7" t="n">
         <v>60</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>BEL</t>
+          <t>TATAPOWER</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Power</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>381.6</v>
+        <v>351</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>372 - 392</t>
+          <t>342 - 360</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -2164,15 +2164,15 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-8.6%)</t>
+          <t>Below 200-DMA (-8.7%)</t>
         </is>
       </c>
       <c r="S7" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -2181,21 +2181,21 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>2026-11-13</t>
+          <t>2026-11-14</t>
         </is>
       </c>
       <c r="V7" t="n">
-        <v>26712</v>
+        <v>31590</v>
       </c>
       <c r="W7" t="n">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="X7" t="n">
-        <v>9</v>
+        <v>10.6</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Industrials name under the sector cap</t>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Power name under the sector cap</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -2205,12 +2205,12 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>No same-sector peer in the universe.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — TATAPOWER: 54; ADANIPOWER: 45, NHPC: 45, NLCINDIA: 31</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>Low-risk Industrials holding (low vol) • below 200-dma (-8.6%) • sector strength 62/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
+          <t>Low-risk Power holding (low vol) • below 200-dma (-8.7%) • sector strength 25/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
         </is>
       </c>
     </row>
@@ -2221,11 +2221,11 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Risk/Vol +22 · Historical +15 · Regime +9 · Trend/Tech +6 · Sector +2 = 54</t>
+          <t>Risk/Vol +16 · Historical +15 · Regime +9 · Trend/Tech +7 · Sector +6 = 53</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -2242,33 +2242,33 @@
         <v>50</v>
       </c>
       <c r="G8" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="H8" t="n">
-        <v>88</v>
+        <v>65</v>
       </c>
       <c r="I8" t="n">
-        <v>25</v>
+        <v>62</v>
       </c>
       <c r="J8" t="n">
         <v>60</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>TATAPOWER</t>
+          <t>DABUR</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Power</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="M8" t="n">
-        <v>349.1</v>
+        <v>390.1</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>340 - 358</t>
+          <t>379 - 401</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -2286,11 +2286,11 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-9.2%)</t>
+          <t>Below 200-DMA (-12.1%)</t>
         </is>
       </c>
       <c r="S8" t="n">
-        <v>32</v>
+        <v>53</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -2299,21 +2299,21 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>2026-11-13</t>
+          <t>2026-11-14</t>
         </is>
       </c>
       <c r="V8" t="n">
-        <v>31423</v>
+        <v>45257</v>
       </c>
       <c r="W8" t="n">
-        <v>90</v>
+        <v>116</v>
       </c>
       <c r="X8" t="n">
-        <v>10.5</v>
+        <v>15.1</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Power name under the sector cap</t>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility FMCG name under the sector cap</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
@@ -2323,12 +2323,12 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — TATAPOWER: 54; NHPC: 46, ADANIPOWER: 35, NLCINDIA: 31</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — DABUR: 53; ITC: 59. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>Low-risk Power holding (low vol) • below 200-dma (-9.2%) • sector strength 25/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
+          <t>Low-risk FMCG holding (medium vol) • below 200-dma (-12.1%) • sector strength 62/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
         </is>
       </c>
     </row>
@@ -2339,11 +2339,11 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Risk/Vol +16 · Historical +15 · Regime +9 · Sector +5 · Trend/Tech +4 = 49</t>
+          <t>Risk/Vol +18 · Historical +15 · Regime +9 · Trend/Tech +6 · Sector +5 = 53</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2353,17 +2353,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Trend/Tech</t>
+          <t>Sector</t>
         </is>
       </c>
       <c r="F9" t="n">
         <v>50</v>
       </c>
       <c r="G9" t="n">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="H9" t="n">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="I9" t="n">
         <v>50</v>
@@ -2373,20 +2373,20 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>DABUR</t>
+          <t>BEL</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="M9" t="n">
-        <v>379.9</v>
+        <v>380.8</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>370 - 390</t>
+          <t>371 - 391</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -2400,15 +2400,15 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-14.5%)</t>
+          <t>Below 200-DMA (-8.7%)</t>
         </is>
       </c>
       <c r="S9" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -2417,21 +2417,21 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>2026-11-13</t>
+          <t>2026-11-14</t>
         </is>
       </c>
       <c r="V9" t="n">
-        <v>46348</v>
+        <v>27037</v>
       </c>
       <c r="W9" t="n">
-        <v>122</v>
+        <v>71</v>
       </c>
       <c r="X9" t="n">
-        <v>15.5</v>
+        <v>9.1</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility FMCG name under the sector cap</t>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Industrials name under the sector cap</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
@@ -2441,12 +2441,12 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — DABUR: 49; ITC: 58. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>No same-sector peer in the universe.</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>Low-risk FMCG holding (medium vol) • below 200-dma (-14.5%) • sector strength 50/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
+          <t>Low-risk Industrials holding (low vol) • below 200-dma (-8.7%) • sector strength 50/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
         </is>
       </c>
     </row>
@@ -27221,7 +27221,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>17.2%</t>
+          <t>16.9%</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -27236,7 +27236,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>15.8%</t>
+          <t>16.0%</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -27251,7 +27251,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>15.3%</t>
+          <t>15.2%</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -27266,7 +27266,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>6.3%</t>
+          <t>6.4%</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -27562,7 +27562,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>The PORTFOLIO process (grade B): beat Nifty 68% of cycles, ~half the drawdown, higher risk-adjusted return. Out-of-sample tested.</t>
+          <t>The PORTFOLIO process (grade A): beat Nifty 68% of cycles, ~half the drawdown, higher risk-adjusted return. Out-of-sample tested.</t>
         </is>
       </c>
     </row>
@@ -27658,7 +27658,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>VALIDATED — grade B · beat Nifty 68% of cycles</t>
+          <t>VALIDATED — grade A · beat Nifty 68% of cycles</t>
         </is>
       </c>
     </row>

--- a/reports/AEGIS_LATEST.xlsx
+++ b/reports/AEGIS_LATEST.xlsx
@@ -444,7 +444,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
     </row>
@@ -489,7 +489,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7">
@@ -512,7 +512,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-11-14</t>
+          <t>2026-11-15</t>
         </is>
       </c>
     </row>
@@ -524,7 +524,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ICICIBANK (77)</t>
+          <t>ICICIBANK (76)</t>
         </is>
       </c>
     </row>
@@ -536,7 +536,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>DABUR (53)</t>
+          <t>DABUR (52)</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-15  /  2026-10-15</t>
+          <t>2026-10-16  /  2026-10-16</t>
         </is>
       </c>
     </row>
@@ -760,7 +760,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-11-14</t>
+          <t>2026-11-15</t>
         </is>
       </c>
     </row>
@@ -908,7 +908,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>14.8%</t>
+          <t>14.9%</t>
         </is>
       </c>
     </row>
@@ -920,7 +920,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>1.88</t>
         </is>
       </c>
     </row>
@@ -1513,11 +1513,11 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Risk/Vol +24 · Historical +20 · Trend/Tech +16 · Regime +9 · Sector +8 = 77</t>
+          <t>Risk/Vol +24 · Historical +20 · Trend/Tech +17 · Regime +9 · Sector +6 = 76</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -1534,13 +1534,13 @@
         <v>66</v>
       </c>
       <c r="G2" t="n">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="H2" t="n">
         <v>96</v>
       </c>
       <c r="I2" t="n">
-        <v>75</v>
+        <v>62</v>
       </c>
       <c r="J2" t="n">
         <v>60</v>
@@ -1556,11 +1556,11 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>1361.2</v>
+        <v>1387.7</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>1334 - 1389</t>
+          <t>1359 - 1416</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -1574,15 +1574,15 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>Above 200-DMA (+0.6%)</t>
+          <t>Above 200-DMA (+2.5%)</t>
         </is>
       </c>
       <c r="S2" t="n">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -1591,17 +1591,17 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>2026-11-14</t>
+          <t>2026-11-15</t>
         </is>
       </c>
       <c r="V2" t="n">
-        <v>49003</v>
+        <v>41631</v>
       </c>
       <c r="W2" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="X2" t="n">
-        <v>16.4</v>
+        <v>14.1</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
@@ -1615,12 +1615,12 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ICICIBANK: 77; PNB: 67, SBIN: 63, IDFCFIRSTB: 58</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ICICIBANK: 76; PNB: 64, SBIN: 61, IDFCFIRSTB: 57</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>Low-risk Financials holding (low vol) • above 200-dma (+0.6%) • sector strength 75/100 • regime cautious (partial deploy) • 8 similar past recs: 75% positive, median +5.3%</t>
+          <t>Low-risk Financials holding (low vol) • above 200-dma (+2.5%) • sector strength 62/100 • regime cautious (partial deploy) • 8 similar past recs: 75% positive, median +5.3%</t>
         </is>
       </c>
     </row>
@@ -1631,11 +1631,11 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Risk/Vol +21 · Historical +20 · Regime +9 · Sector +8 · Trend/Tech +5 = 63</t>
+          <t>Risk/Vol +21 · Historical +20 · Regime +9 · Sector +6 · Trend/Tech +5 = 61</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -1658,7 +1658,7 @@
         <v>85</v>
       </c>
       <c r="I3" t="n">
-        <v>75</v>
+        <v>62</v>
       </c>
       <c r="J3" t="n">
         <v>60</v>
@@ -1674,11 +1674,11 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>956.1</v>
+        <v>959.4</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>931 - 981</t>
+          <t>935 - 984</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -1692,15 +1692,15 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-8.1%)</t>
+          <t>Below 200-DMA (-7.8%)</t>
         </is>
       </c>
       <c r="S3" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -1709,11 +1709,11 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>2026-11-14</t>
+          <t>2026-11-15</t>
         </is>
       </c>
       <c r="V3" t="n">
-        <v>30595</v>
+        <v>30701</v>
       </c>
       <c r="W3" t="n">
         <v>32</v>
@@ -1733,12 +1733,12 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — SBIN: 63; ICICIBANK: 77, PNB: 67, IDFCFIRSTB: 58. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — SBIN: 61; ICICIBANK: 76, PNB: 64, IDFCFIRSTB: 57. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>Low-risk Financials holding (low vol) • below 200-dma (-8.1%) • sector strength 75/100 • regime cautious (partial deploy) • 2 similar past recs: 100% positive, median +8.9%</t>
+          <t>Low-risk Financials holding (low vol) • below 200-dma (-7.8%) • sector strength 62/100 • regime cautious (partial deploy) • 2 similar past recs: 100% positive, median +8.9%</t>
         </is>
       </c>
     </row>
@@ -1749,11 +1749,11 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Risk/Vol +19 · Historical +15 · Trend/Tech +9 · Regime +9 · Sector +9 = 61</t>
+          <t>Risk/Vol +18 · Historical +15 · Trend/Tech +9 · Regime +9 · Sector +9 = 60</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1773,7 +1773,7 @@
         <v>47</v>
       </c>
       <c r="H4" t="n">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="I4" t="n">
         <v>88</v>
@@ -1792,11 +1792,11 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>418</v>
+        <v>416.5</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>407 - 429</t>
+          <t>406 - 427</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -1814,11 +1814,11 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-3.7%)</t>
+          <t>Below 200-DMA (-4.1%)</t>
         </is>
       </c>
       <c r="S4" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1827,17 +1827,17 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>2026-11-14</t>
+          <t>2026-11-15</t>
         </is>
       </c>
       <c r="V4" t="n">
-        <v>48494</v>
+        <v>46226</v>
       </c>
       <c r="W4" t="n">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="X4" t="n">
-        <v>16.3</v>
+        <v>15.4</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -1851,12 +1851,12 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — COALINDIA: 61; TATASTEEL: 59, HINDZINC: 49, SAIL: 43</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — COALINDIA: 60; TATASTEEL: 59, HINDZINC: 52, SAIL: 43</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>Low-risk Metal holding (low vol) • below 200-dma (-3.7%) • outperforming Nifty • sector strength 88/100 • regime cautious (partial deploy) • 3 similar past recs: 67% positive, median +0.8%</t>
+          <t>Low-risk Metal holding (low vol) • below 200-dma (-4.1%) • outperforming Nifty • sector strength 88/100 • regime cautious (partial deploy) • 3 similar past recs: 67% positive, median +0.8%</t>
         </is>
       </c>
     </row>
@@ -1871,7 +1871,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Risk/Vol +23 · Historical +13 · Regime +9 · Trend/Tech +8 · Sector +6 = 59</t>
+          <t>Risk/Vol +19 · Historical +15 · Regime +9 · Sector +9 · Trend/Tech +7 = 59</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1881,62 +1881,62 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Sector</t>
+          <t>Trend/Tech</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="G5" t="n">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="H5" t="n">
-        <v>92</v>
+        <v>77</v>
       </c>
       <c r="I5" t="n">
-        <v>62</v>
+        <v>88</v>
       </c>
       <c r="J5" t="n">
         <v>60</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>ITC</t>
+          <t>TATASTEEL</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>Metal</t>
         </is>
       </c>
       <c r="M5" t="n">
-        <v>265.1</v>
+        <v>177.9</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>259 - 272</t>
+          <t>173 - 183</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-4% to +3%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>56%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-10.7%)</t>
+          <t>Below 200-DMA (-8.4%)</t>
         </is>
       </c>
       <c r="S5" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1945,21 +1945,21 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>2026-11-14</t>
+          <t>2026-11-15</t>
         </is>
       </c>
       <c r="V5" t="n">
-        <v>38970</v>
+        <v>29896</v>
       </c>
       <c r="W5" t="n">
-        <v>147</v>
+        <v>168</v>
       </c>
       <c r="X5" t="n">
-        <v>13.1</v>
+        <v>10</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility FMCG name under the sector cap</t>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Metal name under the sector cap</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1969,12 +1969,12 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ITC: 59; DABUR: 53</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — TATASTEEL: 59; COALINDIA: 60, HINDZINC: 52, SAIL: 43. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>Low-risk FMCG holding (low vol) • below 200-dma (-10.7%) • sector strength 62/100 • regime cautious (partial deploy) • 9 similar past recs: 56% positive, median +0.3%</t>
+          <t>Low-risk Metal holding (low vol) • below 200-dma (-8.4%) • outperforming Nifty • sector strength 88/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
         </is>
       </c>
     </row>
@@ -1985,11 +1985,11 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Risk/Vol +20 · Historical +15 · Regime +9 · Sector +9 · Trend/Tech +6 = 59</t>
+          <t>Risk/Vol +20 · Historical +15 · Regime +9 · Sector +8 · Trend/Tech +6 = 58</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -2012,27 +2012,27 @@
         <v>81</v>
       </c>
       <c r="I6" t="n">
-        <v>88</v>
+        <v>75</v>
       </c>
       <c r="J6" t="n">
         <v>60</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>TATASTEEL</t>
+          <t>BEL</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Metal</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="M6" t="n">
-        <v>175.7</v>
+        <v>379.2</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>171 - 180</t>
+          <t>369 - 389</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -2046,15 +2046,15 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-9.6%)</t>
+          <t>Below 200-DMA (-9.1%)</t>
         </is>
       </c>
       <c r="S6" t="n">
-        <v>22</v>
+        <v>39</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -2063,21 +2063,21 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>2026-11-14</t>
+          <t>2026-11-15</t>
         </is>
       </c>
       <c r="V6" t="n">
-        <v>27233</v>
+        <v>29961</v>
       </c>
       <c r="W6" t="n">
-        <v>155</v>
+        <v>79</v>
       </c>
       <c r="X6" t="n">
-        <v>9.1</v>
+        <v>10.1</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Metal name under the sector cap</t>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Industrials name under the sector cap</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -2087,27 +2087,27 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — TATASTEEL: 59; COALINDIA: 61, HINDZINC: 49, SAIL: 43. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>No same-sector peer in the universe.</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>Low-risk Metal holding (low vol) • below 200-dma (-9.6%) • sector strength 88/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
+          <t>Low-risk Industrials holding (low vol) • below 200-dma (-9.1%) • sector strength 75/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ACCUMULATE</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Risk/Vol +22 · Historical +15 · Regime +9 · Trend/Tech +6 · Sector +2 = 54</t>
+          <t>Risk/Vol +22 · Historical +13 · Regime +9 · Trend/Tech +8 · Sector +5 = 57</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -2121,58 +2121,58 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="G7" t="n">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="H7" t="n">
         <v>88</v>
       </c>
       <c r="I7" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="J7" t="n">
         <v>60</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>TATAPOWER</t>
+          <t>ITC</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Power</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>351</v>
+        <v>262.5</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>342 - 360</t>
+          <t>256 - 269</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-4% to +3%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>56%</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-8.7%)</t>
+          <t>Below 200-DMA (-11.3%)</t>
         </is>
       </c>
       <c r="S7" t="n">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -2181,21 +2181,21 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>2026-11-14</t>
+          <t>2026-11-15</t>
         </is>
       </c>
       <c r="V7" t="n">
-        <v>31590</v>
+        <v>38325</v>
       </c>
       <c r="W7" t="n">
-        <v>90</v>
+        <v>146</v>
       </c>
       <c r="X7" t="n">
-        <v>10.6</v>
+        <v>12.8</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Power name under the sector cap</t>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility FMCG name under the sector cap</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -2205,27 +2205,27 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — TATAPOWER: 54; ADANIPOWER: 45, NHPC: 45, NLCINDIA: 31</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ITC: 57; DABUR: 52</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>Low-risk Power holding (low vol) • below 200-dma (-8.7%) • sector strength 25/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
+          <t>Low-risk FMCG holding (low vol) • below 200-dma (-11.3%) • sector strength 50/100 • regime cautious (partial deploy) • 9 similar past recs: 56% positive, median +0.3%</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ACCUMULATE</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Risk/Vol +16 · Historical +15 · Regime +9 · Trend/Tech +7 · Sector +6 = 53</t>
+          <t>Risk/Vol +23 · Historical +15 · Regime +9 · Trend/Tech +6 · Sector +2 = 55</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -2242,33 +2242,33 @@
         <v>50</v>
       </c>
       <c r="G8" t="n">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="H8" t="n">
-        <v>65</v>
+        <v>92</v>
       </c>
       <c r="I8" t="n">
-        <v>62</v>
+        <v>25</v>
       </c>
       <c r="J8" t="n">
         <v>60</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>DABUR</t>
+          <t>TATAPOWER</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>Power</t>
         </is>
       </c>
       <c r="M8" t="n">
-        <v>390.1</v>
+        <v>352.2</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>379 - 401</t>
+          <t>344 - 361</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -2282,15 +2282,15 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-12.1%)</t>
+          <t>Below 200-DMA (-8.3%)</t>
         </is>
       </c>
       <c r="S8" t="n">
-        <v>53</v>
+        <v>37</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -2299,21 +2299,21 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>2026-11-14</t>
+          <t>2026-11-15</t>
         </is>
       </c>
       <c r="V8" t="n">
-        <v>45257</v>
+        <v>38748</v>
       </c>
       <c r="W8" t="n">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="X8" t="n">
-        <v>15.1</v>
+        <v>13</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility FMCG name under the sector cap</t>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Power name under the sector cap</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
@@ -2323,12 +2323,12 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — DABUR: 53; ITC: 59. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — TATAPOWER: 55; ADANIPOWER: 46, NHPC: 46, NLCINDIA: 32</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>Low-risk FMCG holding (medium vol) • below 200-dma (-12.1%) • sector strength 62/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
+          <t>Low-risk Power holding (low vol) • below 200-dma (-8.3%) • sector strength 25/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
         </is>
       </c>
     </row>
@@ -2339,11 +2339,11 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Risk/Vol +18 · Historical +15 · Regime +9 · Trend/Tech +6 · Sector +5 = 53</t>
+          <t>Risk/Vol +16 · Historical +15 · Regime +9 · Trend/Tech +7 · Sector +5 = 52</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2360,10 +2360,10 @@
         <v>50</v>
       </c>
       <c r="G9" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="H9" t="n">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="I9" t="n">
         <v>50</v>
@@ -2373,20 +2373,20 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>BEL</t>
+          <t>DABUR</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="M9" t="n">
-        <v>380.8</v>
+        <v>384.8</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>371 - 391</t>
+          <t>374 - 395</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -2400,15 +2400,15 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-8.7%)</t>
+          <t>Below 200-DMA (-13.2%)</t>
         </is>
       </c>
       <c r="S9" t="n">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -2417,21 +2417,21 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>2026-11-14</t>
+          <t>2026-11-15</t>
         </is>
       </c>
       <c r="V9" t="n">
-        <v>27037</v>
+        <v>42328</v>
       </c>
       <c r="W9" t="n">
-        <v>71</v>
+        <v>110</v>
       </c>
       <c r="X9" t="n">
-        <v>9.1</v>
+        <v>14.2</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Industrials name under the sector cap</t>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility FMCG name under the sector cap</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
@@ -2441,12 +2441,12 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>No same-sector peer in the universe.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — DABUR: 52; ITC: 57. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>Low-risk Industrials holding (low vol) • below 200-dma (-8.7%) • sector strength 50/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
+          <t>Low-risk FMCG holding (medium vol) • below 200-dma (-13.2%) • sector strength 50/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
         </is>
       </c>
     </row>
@@ -27221,7 +27221,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>16.9%</t>
+          <t>16.2%</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -27231,12 +27231,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Metal</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>16.0%</t>
+          <t>15.3%</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -27246,12 +27246,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Metal</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>15.2%</t>
+          <t>14.6%</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -27266,7 +27266,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>6.4%</t>
+          <t>7.8%</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -27281,7 +27281,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>5.4%</t>
+          <t>6.0%</t>
         </is>
       </c>
       <c r="C6" t="n">

--- a/reports/AEGIS_LATEST.xlsx
+++ b/reports/AEGIS_LATEST.xlsx
@@ -444,7 +444,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-16  /  2026-10-16</t>
+          <t>2026-10-17  /  2026-10-16</t>
         </is>
       </c>
     </row>

--- a/reports/AEGIS_LATEST.xlsx
+++ b/reports/AEGIS_LATEST.xlsx
@@ -444,7 +444,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-19</t>
         </is>
       </c>
     </row>
@@ -479,7 +479,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6">
@@ -512,7 +512,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-11-15</t>
+          <t>2026-11-18</t>
         </is>
       </c>
     </row>
@@ -536,7 +536,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>DABUR (52)</t>
+          <t>ONGC (51)</t>
         </is>
       </c>
     </row>
@@ -548,7 +548,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>ONGC</t>
         </is>
       </c>
     </row>
@@ -571,7 +571,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -664,7 +664,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Hold a 8-stock risk-managed portfolio</t>
+          <t>Hold a 9-stock risk-managed portfolio</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-17  /  2026-10-16</t>
+          <t>2026-10-19  /  2026-10-19</t>
         </is>
       </c>
     </row>
@@ -760,7 +760,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-11-15</t>
+          <t>2026-11-18</t>
         </is>
       </c>
     </row>
@@ -908,7 +908,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>14.9%</t>
+          <t>14.8%</t>
         </is>
       </c>
     </row>
@@ -920,7 +920,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>1.87</t>
         </is>
       </c>
     </row>
@@ -1361,7 +1361,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB9"/>
+  <dimension ref="A1:AB10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1517,7 +1517,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Risk/Vol +24 · Historical +20 · Trend/Tech +17 · Regime +9 · Sector +6 = 76</t>
+          <t>Risk/Vol +24 · Historical +20 · Trend/Tech +15 · Regime +9 · Sector +8 = 76</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -1534,13 +1534,13 @@
         <v>66</v>
       </c>
       <c r="G2" t="n">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="H2" t="n">
         <v>96</v>
       </c>
       <c r="I2" t="n">
-        <v>62</v>
+        <v>75</v>
       </c>
       <c r="J2" t="n">
         <v>60</v>
@@ -1556,11 +1556,11 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>1387.7</v>
+        <v>1386.1</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>1359 - 1416</t>
+          <t>1358 - 1414</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -1578,11 +1578,11 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>Above 200-DMA (+2.5%)</t>
+          <t>Above 200-DMA (+2.4%)</t>
         </is>
       </c>
       <c r="S2" t="n">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -1591,17 +1591,17 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>2026-11-15</t>
+          <t>2026-11-18</t>
         </is>
       </c>
       <c r="V2" t="n">
-        <v>41631</v>
+        <v>41583</v>
       </c>
       <c r="W2" t="n">
         <v>30</v>
       </c>
       <c r="X2" t="n">
-        <v>14.1</v>
+        <v>14.2</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
@@ -1615,50 +1615,50 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ICICIBANK: 76; PNB: 64, SBIN: 61, IDFCFIRSTB: 57</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ICICIBANK: 76; SBIN: 65, IDFCFIRSTB: 61, PNB: 61</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>Low-risk Financials holding (low vol) • above 200-dma (+2.5%) • sector strength 62/100 • regime cautious (partial deploy) • 8 similar past recs: 75% positive, median +5.3%</t>
+          <t>Low-risk Financials holding (low vol) • above 200-dma (+2.4%) • outperforming Nifty • sector strength 75/100 • regime cautious (partial deploy) • 8 similar past recs: 75% positive, median +5.3%</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>STRONG BUY</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Risk/Vol +21 · Historical +20 · Regime +9 · Sector +6 · Trend/Tech +5 = 61</t>
+          <t>Historical +20 · Risk/Vol +20 · Regime +9 · Trend/Tech +8 · Sector +8 = 65</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Risk/Vol</t>
+          <t>Historical</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Trend/Tech</t>
+          <t>Sector</t>
         </is>
       </c>
       <c r="F3" t="n">
         <v>65</v>
       </c>
       <c r="G3" t="n">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="H3" t="n">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="I3" t="n">
-        <v>62</v>
+        <v>75</v>
       </c>
       <c r="J3" t="n">
         <v>60</v>
@@ -1674,11 +1674,11 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>959.4</v>
+        <v>976.3</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>935 - 984</t>
+          <t>951 - 1002</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -1692,15 +1692,15 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-7.8%)</t>
+          <t>Below 200-DMA (-6.1%)</t>
         </is>
       </c>
       <c r="S3" t="n">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -1709,21 +1709,21 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>2026-11-15</t>
+          <t>2026-11-18</t>
         </is>
       </c>
       <c r="V3" t="n">
-        <v>30701</v>
+        <v>36125</v>
       </c>
       <c r="W3" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="X3" t="n">
-        <v>10.3</v>
+        <v>12.3</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Financials name under the sector cap</t>
+          <t>Historical + Risk/Vol strongest; chosen as a lowest-volatility Financials name under the sector cap</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -1733,12 +1733,12 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — SBIN: 61; ICICIBANK: 76, PNB: 64, IDFCFIRSTB: 57. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — SBIN: 65; ICICIBANK: 76, IDFCFIRSTB: 61, PNB: 61. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>Low-risk Financials holding (low vol) • below 200-dma (-7.8%) • sector strength 62/100 • regime cautious (partial deploy) • 2 similar past recs: 100% positive, median +8.9%</t>
+          <t>Low-risk Financials holding (low vol) • below 200-dma (-6.1%) • sector strength 75/100 • regime cautious (partial deploy) • 2 similar past recs: 100% positive, median +8.9%</t>
         </is>
       </c>
     </row>
@@ -1749,11 +1749,11 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Risk/Vol +18 · Historical +15 · Trend/Tech +9 · Regime +9 · Sector +9 = 60</t>
+          <t>Risk/Vol +21 · Historical +15 · Trend/Tech +10 · Regime +9 · Sector +9 = 64</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1770,10 +1770,10 @@
         <v>51</v>
       </c>
       <c r="G4" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="H4" t="n">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="I4" t="n">
         <v>88</v>
@@ -1792,7 +1792,7 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>416.5</v>
+        <v>416.6</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -1810,7 +1810,7 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
@@ -1818,7 +1818,7 @@
         </is>
       </c>
       <c r="S4" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1827,17 +1827,17 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>2026-11-15</t>
+          <t>2026-11-18</t>
         </is>
       </c>
       <c r="V4" t="n">
-        <v>46226</v>
+        <v>32911</v>
       </c>
       <c r="W4" t="n">
-        <v>111</v>
+        <v>79</v>
       </c>
       <c r="X4" t="n">
-        <v>15.4</v>
+        <v>11.1</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -1851,7 +1851,7 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — COALINDIA: 60; TATASTEEL: 59, HINDZINC: 52, SAIL: 43</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — COALINDIA: 64; TATASTEEL: 58, HINDZINC: 52, SAIL: 43</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1867,11 +1867,11 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Risk/Vol +19 · Historical +15 · Regime +9 · Sector +9 · Trend/Tech +7 = 59</t>
+          <t>Risk/Vol +18 · Historical +15 · Regime +9 · Sector +9 · Trend/Tech +7 = 58</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1888,10 +1888,10 @@
         <v>50</v>
       </c>
       <c r="G5" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="H5" t="n">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="I5" t="n">
         <v>88</v>
@@ -1910,11 +1910,11 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>177.9</v>
+        <v>175.8</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>173 - 183</t>
+          <t>171 - 180</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -1928,15 +1928,15 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-8.4%)</t>
+          <t>Below 200-DMA (-9.5%)</t>
         </is>
       </c>
       <c r="S5" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1945,17 +1945,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>2026-11-15</t>
+          <t>2026-11-18</t>
         </is>
       </c>
       <c r="V5" t="n">
-        <v>29896</v>
+        <v>31298</v>
       </c>
       <c r="W5" t="n">
-        <v>168</v>
+        <v>178</v>
       </c>
       <c r="X5" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -1969,12 +1969,12 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — TATASTEEL: 59; COALINDIA: 60, HINDZINC: 52, SAIL: 43. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — TATASTEEL: 58; COALINDIA: 64, HINDZINC: 52, SAIL: 43. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>Low-risk Metal holding (low vol) • below 200-dma (-8.4%) • outperforming Nifty • sector strength 88/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
+          <t>Low-risk Metal holding (low vol) • below 200-dma (-9.5%) • sector strength 88/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
         </is>
       </c>
     </row>
@@ -1985,11 +1985,11 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Risk/Vol +20 · Historical +15 · Regime +9 · Sector +8 · Trend/Tech +6 = 58</t>
+          <t>Risk/Vol +22 · Historical +13 · Regime +9 · Trend/Tech +8 · Sector +5 = 57</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1999,62 +1999,62 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Trend/Tech</t>
+          <t>Sector</t>
         </is>
       </c>
       <c r="F6" t="n">
+        <v>44</v>
+      </c>
+      <c r="G6" t="n">
+        <v>42</v>
+      </c>
+      <c r="H6" t="n">
+        <v>88</v>
+      </c>
+      <c r="I6" t="n">
         <v>50</v>
-      </c>
-      <c r="G6" t="n">
-        <v>32</v>
-      </c>
-      <c r="H6" t="n">
-        <v>81</v>
-      </c>
-      <c r="I6" t="n">
-        <v>75</v>
       </c>
       <c r="J6" t="n">
         <v>60</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>BEL</t>
+          <t>ITC</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="M6" t="n">
-        <v>379.2</v>
+        <v>262.6</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>369 - 389</t>
+          <t>256 - 269</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-4% to +3%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>56%</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-9.1%)</t>
+          <t>Below 200-DMA (-11.1%)</t>
         </is>
       </c>
       <c r="S6" t="n">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -2063,21 +2063,21 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>2026-11-15</t>
+          <t>2026-11-18</t>
         </is>
       </c>
       <c r="V6" t="n">
-        <v>29961</v>
+        <v>33088</v>
       </c>
       <c r="W6" t="n">
-        <v>79</v>
+        <v>126</v>
       </c>
       <c r="X6" t="n">
-        <v>10.1</v>
+        <v>11.1</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Industrials name under the sector cap</t>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility FMCG name under the sector cap</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -2087,12 +2087,12 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>No same-sector peer in the universe.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ITC: 57; DABUR: 52</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>Low-risk Industrials holding (low vol) • below 200-dma (-9.1%) • sector strength 75/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
+          <t>Low-risk FMCG holding (low vol) • below 200-dma (-11.1%) • sector strength 50/100 • regime cautious (partial deploy) • 9 similar past recs: 56% positive, median +0.3%</t>
         </is>
       </c>
     </row>
@@ -2107,7 +2107,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Risk/Vol +22 · Historical +13 · Regime +9 · Trend/Tech +8 · Sector +5 = 57</t>
+          <t>Risk/Vol +19 · Historical +15 · Regime +9 · Trend/Tech +8 · Sector +6 = 57</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -2121,58 +2121,58 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="G7" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H7" t="n">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="I7" t="n">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="J7" t="n">
         <v>60</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>ITC</t>
+          <t>BEL</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>262.5</v>
+        <v>378.3</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>256 - 269</t>
+          <t>368 - 388</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-4% to +3%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>56%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-11.3%)</t>
+          <t>Below 200-DMA (-9.3%)</t>
         </is>
       </c>
       <c r="S7" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -2181,21 +2181,21 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>2026-11-15</t>
+          <t>2026-11-18</t>
         </is>
       </c>
       <c r="V7" t="n">
-        <v>38325</v>
+        <v>29507</v>
       </c>
       <c r="W7" t="n">
-        <v>146</v>
+        <v>78</v>
       </c>
       <c r="X7" t="n">
-        <v>12.8</v>
+        <v>9.9</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility FMCG name under the sector cap</t>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Industrials name under the sector cap</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -2205,12 +2205,12 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ITC: 57; DABUR: 52</t>
+          <t>No same-sector peer in the universe.</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>Low-risk FMCG holding (low vol) • below 200-dma (-11.3%) • sector strength 50/100 • regime cautious (partial deploy) • 9 similar past recs: 56% positive, median +0.3%</t>
+          <t>Low-risk Industrials holding (low vol) • below 200-dma (-9.3%) • sector strength 62/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
         </is>
       </c>
     </row>
@@ -2242,7 +2242,7 @@
         <v>50</v>
       </c>
       <c r="G8" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H8" t="n">
         <v>92</v>
@@ -2264,11 +2264,11 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>352.2</v>
+        <v>351.8</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>344 - 361</t>
+          <t>343 - 360</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -2286,11 +2286,11 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-8.3%)</t>
+          <t>Below 200-DMA (-8.4%)</t>
         </is>
       </c>
       <c r="S8" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -2299,17 +2299,17 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>2026-11-15</t>
+          <t>2026-11-18</t>
         </is>
       </c>
       <c r="V8" t="n">
-        <v>38748</v>
+        <v>33064</v>
       </c>
       <c r="W8" t="n">
-        <v>110</v>
+        <v>94</v>
       </c>
       <c r="X8" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -2323,12 +2323,12 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — TATAPOWER: 55; ADANIPOWER: 46, NHPC: 46, NLCINDIA: 32</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — TATAPOWER: 55; NHPC: 47, ADANIPOWER: 46, NLCINDIA: 32</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>Low-risk Power holding (low vol) • below 200-dma (-8.3%) • sector strength 25/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
+          <t>Low-risk Power holding (low vol) • below 200-dma (-8.4%) • sector strength 25/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
         </is>
       </c>
     </row>
@@ -2360,10 +2360,10 @@
         <v>50</v>
       </c>
       <c r="G9" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H9" t="n">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="I9" t="n">
         <v>50</v>
@@ -2382,11 +2382,11 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>384.8</v>
+        <v>382</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>374 - 395</t>
+          <t>371 - 393</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -2404,11 +2404,11 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-13.2%)</t>
+          <t>Below 200-DMA (-13.7%)</t>
         </is>
       </c>
       <c r="S9" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -2417,17 +2417,17 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>2026-11-15</t>
+          <t>2026-11-18</t>
         </is>
       </c>
       <c r="V9" t="n">
-        <v>42328</v>
+        <v>27886</v>
       </c>
       <c r="W9" t="n">
-        <v>110</v>
+        <v>73</v>
       </c>
       <c r="X9" t="n">
-        <v>14.2</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -2446,7 +2446,125 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>Low-risk FMCG holding (medium vol) • below 200-dma (-13.2%) • sector strength 50/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
+          <t>Low-risk FMCG holding (medium vol) • below 200-dma (-13.7%) • sector strength 50/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>ACCUMULATE</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>51</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Risk/Vol +17 · Historical +16 · Regime +9 · Trend/Tech +5 · Sector +4 = 51</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Risk/Vol</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Sector</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>53</v>
+      </c>
+      <c r="G10" t="n">
+        <v>25</v>
+      </c>
+      <c r="H10" t="n">
+        <v>69</v>
+      </c>
+      <c r="I10" t="n">
+        <v>38</v>
+      </c>
+      <c r="J10" t="n">
+        <v>60</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>ONGC</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="M10" t="n">
+        <v>224.9</v>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>219 - 231</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>66</v>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>Below 200-DMA (-12.1%)</t>
+        </is>
+      </c>
+      <c r="S10" t="n">
+        <v>33</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>2 months (2M)</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>2026-11-18</t>
+        </is>
+      </c>
+      <c r="V10" t="n">
+        <v>31943</v>
+      </c>
+      <c r="W10" t="n">
+        <v>142</v>
+      </c>
+      <c r="X10" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Energy name under the sector cap</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>Fundamentals · Earnings · News · Flows</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ONGC: 51; IOC: 46</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>Low-risk Energy holding (low vol) • below 200-dma (-12.1%) • sector strength 38/100 • regime cautious (partial deploy) • 2 similar past recs: 50% positive, median +9.0%</t>
         </is>
       </c>
     </row>
@@ -27193,7 +27311,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27216,12 +27334,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>16.2%</t>
+          <t>15.9%</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -27236,7 +27354,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>15.3%</t>
+          <t>12.9%</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -27246,12 +27364,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>14.6%</t>
+          <t>12.2%</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -27266,7 +27384,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>7.8%</t>
+          <t>6.6%</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -27276,12 +27394,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>6.0%</t>
+          <t>6.4%</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -27291,32 +27409,47 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CASH (intentional)</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>5.9%</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>CASH (intentional)</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>40.0%</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>8 stocks / 5 sectors</t>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>9 stocks / 6 sectors</t>
         </is>
       </c>
     </row>

--- a/reports/AEGIS_LATEST.xlsx
+++ b/reports/AEGIS_LATEST.xlsx
@@ -444,7 +444,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
     </row>
@@ -548,7 +548,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>ONGC</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -571,7 +571,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -688,7 +688,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-19  /  2026-10-19</t>
+          <t>2026-10-20  /  2026-10-19</t>
         </is>
       </c>
     </row>

--- a/reports/AEGIS_LATEST.xlsx
+++ b/reports/AEGIS_LATEST.xlsx
@@ -444,7 +444,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
     </row>
@@ -489,7 +489,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7">
@@ -512,7 +512,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-11-18</t>
+          <t>2026-11-20</t>
         </is>
       </c>
     </row>
@@ -524,7 +524,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ICICIBANK (76)</t>
+          <t>ICICIBANK (77)</t>
         </is>
       </c>
     </row>
@@ -582,7 +582,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>94%</t>
+          <t>84%</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-20  /  2026-10-19</t>
+          <t>2026-10-21  /  2026-10-21</t>
         </is>
       </c>
     </row>
@@ -760,7 +760,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-11-18</t>
+          <t>2026-11-20</t>
         </is>
       </c>
     </row>
@@ -908,7 +908,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>14.8%</t>
+          <t>14.7%</t>
         </is>
       </c>
     </row>
@@ -920,7 +920,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>1.86</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>94% (validated process)</t>
+          <t>84% (validated process)</t>
         </is>
       </c>
     </row>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Portfolio grade A (validated) · stock-alpha experimental</t>
+          <t>Portfolio grade B (validated) · stock-alpha experimental</t>
         </is>
       </c>
     </row>
@@ -1513,11 +1513,11 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Risk/Vol +24 · Historical +20 · Trend/Tech +15 · Regime +9 · Sector +8 = 76</t>
+          <t>Risk/Vol +24 · Historical +20 · Trend/Tech +16 · Regime +9 · Sector +8 = 77</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -1534,7 +1534,7 @@
         <v>66</v>
       </c>
       <c r="G2" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="H2" t="n">
         <v>96</v>
@@ -1556,11 +1556,11 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>1386.1</v>
+        <v>1406.9</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>1358 - 1414</t>
+          <t>1378 - 1435</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -1574,16 +1574,16 @@
         </is>
       </c>
       <c r="Q2" t="n">
+        <v>83</v>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>Above 200-DMA (+3.9%)</t>
+        </is>
+      </c>
+      <c r="S2" t="n">
         <v>82</v>
       </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>Above 200-DMA (+2.4%)</t>
-        </is>
-      </c>
-      <c r="S2" t="n">
-        <v>79</v>
-      </c>
       <c r="T2" t="inlineStr">
         <is>
           <t>2 months (2M)</t>
@@ -1591,17 +1591,17 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>2026-11-18</t>
+          <t>2026-11-20</t>
         </is>
       </c>
       <c r="V2" t="n">
-        <v>41583</v>
+        <v>29545</v>
       </c>
       <c r="W2" t="n">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="X2" t="n">
-        <v>14.2</v>
+        <v>10.3</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
@@ -1615,12 +1615,12 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ICICIBANK: 76; SBIN: 65, IDFCFIRSTB: 61, PNB: 61</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ICICIBANK: 77; SBIN: 66, PNB: 61, HDFCBANK: 58</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>Low-risk Financials holding (low vol) • above 200-dma (+2.4%) • outperforming Nifty • sector strength 75/100 • regime cautious (partial deploy) • 8 similar past recs: 75% positive, median +5.3%</t>
+          <t>Low-risk Financials holding (low vol) • above 200-dma (+3.9%) • outperforming Nifty • sector strength 75/100 • regime cautious (partial deploy) • 8 similar past recs: 75% positive, median +5.3%</t>
         </is>
       </c>
     </row>
@@ -1631,11 +1631,11 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Historical +20 · Risk/Vol +20 · Regime +9 · Trend/Tech +8 · Sector +8 = 65</t>
+          <t>Historical +20 · Risk/Vol +20 · Trend/Tech +9 · Regime +9 · Sector +8 = 66</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -1652,7 +1652,7 @@
         <v>65</v>
       </c>
       <c r="G3" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="H3" t="n">
         <v>81</v>
@@ -1674,11 +1674,11 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>976.3</v>
+        <v>980.2</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>951 - 1002</t>
+          <t>955 - 1006</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -1692,15 +1692,15 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-6.1%)</t>
+          <t>Below 200-DMA (-5.8%)</t>
         </is>
       </c>
       <c r="S3" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -1709,17 +1709,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>2026-11-18</t>
+          <t>2026-11-20</t>
         </is>
       </c>
       <c r="V3" t="n">
-        <v>36125</v>
+        <v>22543</v>
       </c>
       <c r="W3" t="n">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="X3" t="n">
-        <v>12.3</v>
+        <v>7.6</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
@@ -1733,12 +1733,12 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — SBIN: 65; ICICIBANK: 76, IDFCFIRSTB: 61, PNB: 61. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — SBIN: 66; ICICIBANK: 77, PNB: 61, HDFCBANK: 58. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>Low-risk Financials holding (low vol) • below 200-dma (-6.1%) • sector strength 75/100 • regime cautious (partial deploy) • 2 similar past recs: 100% positive, median +8.9%</t>
+          <t>Low-risk Financials holding (low vol) • below 200-dma (-5.8%) • outperforming Nifty • sector strength 75/100 • regime cautious (partial deploy) • 2 similar past recs: 100% positive, median +8.9%</t>
         </is>
       </c>
     </row>
@@ -1749,11 +1749,11 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Risk/Vol +21 · Historical +15 · Trend/Tech +10 · Regime +9 · Sector +9 = 64</t>
+          <t>Risk/Vol +21 · Historical +15 · Regime +9 · Sector +9 · Trend/Tech +7 = 61</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1763,14 +1763,14 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sector</t>
+          <t>Trend/Tech</t>
         </is>
       </c>
       <c r="F4" t="n">
         <v>51</v>
       </c>
       <c r="G4" t="n">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="H4" t="n">
         <v>85</v>
@@ -1792,11 +1792,11 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>416.6</v>
+        <v>410.4</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>406 - 427</t>
+          <t>400 - 421</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -1810,15 +1810,15 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-4.1%)</t>
+          <t>Below 200-DMA (-5.5%)</t>
         </is>
       </c>
       <c r="S4" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1827,17 +1827,17 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>2026-11-18</t>
+          <t>2026-11-20</t>
         </is>
       </c>
       <c r="V4" t="n">
-        <v>32911</v>
+        <v>38163</v>
       </c>
       <c r="W4" t="n">
-        <v>79</v>
+        <v>93</v>
       </c>
       <c r="X4" t="n">
-        <v>11.1</v>
+        <v>12.9</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -1851,12 +1851,12 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — COALINDIA: 64; TATASTEEL: 58, HINDZINC: 52, SAIL: 43</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — COALINDIA: 61; TATASTEEL: 57, HINDZINC: 51, SAIL: 42</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>Low-risk Metal holding (low vol) • below 200-dma (-4.1%) • outperforming Nifty • sector strength 88/100 • regime cautious (partial deploy) • 3 similar past recs: 67% positive, median +0.8%</t>
+          <t>Low-risk Metal holding (low vol) • below 200-dma (-5.5%) • outperforming Nifty • sector strength 88/100 • regime cautious (partial deploy) • 3 similar past recs: 67% positive, median +0.8%</t>
         </is>
       </c>
     </row>
@@ -1867,11 +1867,11 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Risk/Vol +18 · Historical +15 · Regime +9 · Sector +9 · Trend/Tech +7 = 58</t>
+          <t>Risk/Vol +23 · Historical +13 · Trend/Tech +9 · Regime +9 · Sector +6 = 60</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1881,62 +1881,62 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Trend/Tech</t>
+          <t>Sector</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="G5" t="n">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="H5" t="n">
-        <v>73</v>
+        <v>92</v>
       </c>
       <c r="I5" t="n">
-        <v>88</v>
+        <v>62</v>
       </c>
       <c r="J5" t="n">
         <v>60</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>TATASTEEL</t>
+          <t>ITC</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Metal</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="M5" t="n">
-        <v>175.8</v>
+        <v>264.2</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>171 - 180</t>
+          <t>258 - 270</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-4% to +3%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>56%</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-9.5%)</t>
+          <t>Below 200-DMA (-10.4%)</t>
         </is>
       </c>
       <c r="S5" t="n">
-        <v>29</v>
+        <v>50</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1945,21 +1945,21 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>2026-11-18</t>
+          <t>2026-11-20</t>
         </is>
       </c>
       <c r="V5" t="n">
-        <v>31298</v>
+        <v>42272</v>
       </c>
       <c r="W5" t="n">
-        <v>178</v>
+        <v>160</v>
       </c>
       <c r="X5" t="n">
-        <v>10.5</v>
+        <v>14.1</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Metal name under the sector cap</t>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility FMCG name under the sector cap</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1969,12 +1969,12 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — TATASTEEL: 58; COALINDIA: 64, HINDZINC: 52, SAIL: 43. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ITC: 60; DABUR: 53</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>Low-risk Metal holding (low vol) • below 200-dma (-9.5%) • sector strength 88/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
+          <t>Low-risk FMCG holding (low vol) • below 200-dma (-10.4%) • outperforming Nifty • sector strength 62/100 • regime cautious (partial deploy) • 9 similar past recs: 56% positive, median +0.3%</t>
         </is>
       </c>
     </row>
@@ -1989,7 +1989,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Risk/Vol +22 · Historical +13 · Regime +9 · Trend/Tech +8 · Sector +5 = 57</t>
+          <t>Risk/Vol +18 · Historical +15 · Regime +9 · Sector +9 · Trend/Tech +6 = 57</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1999,62 +1999,62 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Sector</t>
+          <t>Trend/Tech</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="G6" t="n">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="H6" t="n">
+        <v>73</v>
+      </c>
+      <c r="I6" t="n">
         <v>88</v>
-      </c>
-      <c r="I6" t="n">
-        <v>50</v>
       </c>
       <c r="J6" t="n">
         <v>60</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>ITC</t>
+          <t>TATASTEEL</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>Metal</t>
         </is>
       </c>
       <c r="M6" t="n">
-        <v>262.6</v>
+        <v>174.7</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>256 - 269</t>
+          <t>170 - 179</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-4% to +3%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>56%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-11.1%)</t>
+          <t>Below 200-DMA (-10.1%)</t>
         </is>
       </c>
       <c r="S6" t="n">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -2063,21 +2063,21 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>2026-11-18</t>
+          <t>2026-11-20</t>
         </is>
       </c>
       <c r="V6" t="n">
-        <v>33088</v>
+        <v>27429</v>
       </c>
       <c r="W6" t="n">
-        <v>126</v>
+        <v>157</v>
       </c>
       <c r="X6" t="n">
-        <v>11.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility FMCG name under the sector cap</t>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Metal name under the sector cap</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -2087,12 +2087,12 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ITC: 57; DABUR: 52</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — TATASTEEL: 57; COALINDIA: 61, HINDZINC: 51, SAIL: 42. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>Low-risk FMCG holding (low vol) • below 200-dma (-11.1%) • sector strength 50/100 • regime cautious (partial deploy) • 9 similar past recs: 56% positive, median +0.3%</t>
+          <t>Low-risk Metal holding (low vol) • below 200-dma (-10.1%) • sector strength 88/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
         </is>
       </c>
     </row>
@@ -2103,11 +2103,11 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Risk/Vol +19 · Historical +15 · Regime +9 · Trend/Tech +8 · Sector +6 = 57</t>
+          <t>Risk/Vol +22 · Historical +15 · Regime +9 · Trend/Tech +8 · Sector +2 = 56</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -2124,33 +2124,33 @@
         <v>50</v>
       </c>
       <c r="G7" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H7" t="n">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="I7" t="n">
-        <v>62</v>
+        <v>25</v>
       </c>
       <c r="J7" t="n">
         <v>60</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>BEL</t>
+          <t>TATAPOWER</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Power</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>378.3</v>
+        <v>351</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>368 - 388</t>
+          <t>343 - 359</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -2164,15 +2164,15 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-9.3%)</t>
+          <t>Below 200-DMA (-8.6%)</t>
         </is>
       </c>
       <c r="S7" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -2181,21 +2181,21 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>2026-11-18</t>
+          <t>2026-11-20</t>
         </is>
       </c>
       <c r="V7" t="n">
-        <v>29507</v>
+        <v>30533</v>
       </c>
       <c r="W7" t="n">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="X7" t="n">
-        <v>9.9</v>
+        <v>10.3</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Industrials name under the sector cap</t>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Power name under the sector cap</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -2205,27 +2205,27 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>No same-sector peer in the universe.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — TATAPOWER: 56; NHPC: 49, ADANIPOWER: 45, NLCINDIA: 32</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>Low-risk Industrials holding (low vol) • below 200-dma (-9.3%) • sector strength 62/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
+          <t>Low-risk Power holding (low vol) • below 200-dma (-8.6%) • sector strength 25/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>ACCUMULATE</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Risk/Vol +23 · Historical +15 · Regime +9 · Trend/Tech +6 · Sector +2 = 55</t>
+          <t>Risk/Vol +19 · Historical +15 · Regime +9 · Trend/Tech +6 · Sector +5 = 54</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -2245,30 +2245,30 @@
         <v>29</v>
       </c>
       <c r="H8" t="n">
-        <v>92</v>
+        <v>77</v>
       </c>
       <c r="I8" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="J8" t="n">
         <v>60</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>TATAPOWER</t>
+          <t>BEL</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Power</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="M8" t="n">
-        <v>351.8</v>
+        <v>374</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>343 - 360</t>
+          <t>364 - 384</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -2282,15 +2282,15 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-8.4%)</t>
+          <t>Below 200-DMA (-10.3%)</t>
         </is>
       </c>
       <c r="S8" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -2299,21 +2299,21 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>2026-11-18</t>
+          <t>2026-11-20</t>
         </is>
       </c>
       <c r="V8" t="n">
-        <v>33064</v>
+        <v>26924</v>
       </c>
       <c r="W8" t="n">
-        <v>94</v>
+        <v>72</v>
       </c>
       <c r="X8" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Power name under the sector cap</t>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Industrials name under the sector cap</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
@@ -2323,12 +2323,12 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — TATAPOWER: 55; NHPC: 47, ADANIPOWER: 46, NLCINDIA: 32</t>
+          <t>No same-sector peer in the universe.</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>Low-risk Power holding (low vol) • below 200-dma (-8.4%) • sector strength 25/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
+          <t>Low-risk Industrials holding (low vol) • below 200-dma (-10.3%) • sector strength 50/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
         </is>
       </c>
     </row>
@@ -2339,11 +2339,11 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Risk/Vol +16 · Historical +15 · Regime +9 · Trend/Tech +7 · Sector +5 = 52</t>
+          <t>Risk/Vol +16 · Historical +15 · Regime +9 · Trend/Tech +7 · Sector +6 = 53</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2360,13 +2360,13 @@
         <v>50</v>
       </c>
       <c r="G9" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H9" t="n">
         <v>62</v>
       </c>
       <c r="I9" t="n">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="J9" t="n">
         <v>60</v>
@@ -2382,11 +2382,11 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>382</v>
+        <v>376.4</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>371 - 393</t>
+          <t>366 - 387</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -2400,15 +2400,15 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-13.7%)</t>
+          <t>Below 200-DMA (-14.9%)</t>
         </is>
       </c>
       <c r="S9" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -2417,17 +2417,17 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>2026-11-18</t>
+          <t>2026-11-20</t>
         </is>
       </c>
       <c r="V9" t="n">
-        <v>27886</v>
+        <v>38388</v>
       </c>
       <c r="W9" t="n">
-        <v>73</v>
+        <v>102</v>
       </c>
       <c r="X9" t="n">
-        <v>9.300000000000001</v>
+        <v>12.9</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -2441,12 +2441,12 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — DABUR: 52; ITC: 57. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — DABUR: 53; ITC: 60. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>Low-risk FMCG holding (medium vol) • below 200-dma (-13.7%) • sector strength 50/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
+          <t>Low-risk FMCG holding (medium vol) • below 200-dma (-14.9%) • sector strength 62/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
         </is>
       </c>
     </row>
@@ -2500,11 +2500,11 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>224.9</v>
+        <v>225.6</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>219 - 231</t>
+          <t>220 - 232</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -2522,11 +2522,11 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-12.1%)</t>
+          <t>Below 200-DMA (-11.8%)</t>
         </is>
       </c>
       <c r="S10" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -2535,17 +2535,17 @@
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>2026-11-18</t>
+          <t>2026-11-20</t>
         </is>
       </c>
       <c r="V10" t="n">
-        <v>31943</v>
+        <v>41520</v>
       </c>
       <c r="W10" t="n">
-        <v>142</v>
+        <v>184</v>
       </c>
       <c r="X10" t="n">
-        <v>10.6</v>
+        <v>13.8</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -2559,12 +2559,12 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ONGC: 51; IOC: 46</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ONGC: 51; IOC: 47</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>Low-risk Energy holding (low vol) • below 200-dma (-12.1%) • sector strength 38/100 • regime cautious (partial deploy) • 2 similar past recs: 50% positive, median +9.0%</t>
+          <t>Low-risk Energy holding (low vol) • below 200-dma (-11.8%) • sector strength 38/100 • regime cautious (partial deploy) • 2 similar past recs: 50% positive, median +9.0%</t>
         </is>
       </c>
     </row>
@@ -27334,12 +27334,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>15.9%</t>
+          <t>16.2%</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -27354,7 +27354,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>12.9%</t>
+          <t>13.2%</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -27364,12 +27364,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>12.2%</t>
+          <t>10.7%</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -27379,12 +27379,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Power</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>6.6%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -27394,12 +27394,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Power</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>6.4%</t>
+          <t>6.2%</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -27414,7 +27414,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>5.9%</t>
+          <t>5.4%</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -27695,7 +27695,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>The PORTFOLIO process (grade A): beat Nifty 68% of cycles, ~half the drawdown, higher risk-adjusted return. Out-of-sample tested.</t>
+          <t>The PORTFOLIO process (grade B): beat Nifty 68% of cycles, ~half the drawdown, higher risk-adjusted return. Out-of-sample tested.</t>
         </is>
       </c>
     </row>
@@ -27791,7 +27791,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>VALIDATED — grade A · beat Nifty 68% of cycles</t>
+          <t>VALIDATED — grade B · beat Nifty 68% of cycles</t>
         </is>
       </c>
     </row>

--- a/reports/AEGIS_LATEST.xlsx
+++ b/reports/AEGIS_LATEST.xlsx
@@ -444,7 +444,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
     </row>
@@ -456,7 +456,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Weak  ·  deploy 60%  ·  cash 40%</t>
+          <t>Weak  ·  deploy 36%  ·  cash 64%</t>
         </is>
       </c>
     </row>
@@ -489,7 +489,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -512,7 +512,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-11-20</t>
+          <t>2026-11-21</t>
         </is>
       </c>
     </row>
@@ -524,7 +524,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ICICIBANK (77)</t>
+          <t>ICICIBANK (73)</t>
         </is>
       </c>
     </row>
@@ -536,7 +536,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ONGC (51)</t>
+          <t>DABUR (47)</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-21  /  2026-10-21</t>
+          <t>2026-10-22  /  2026-10-22</t>
         </is>
       </c>
     </row>
@@ -736,7 +736,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Rs300,000 (60%)</t>
+          <t>Rs180,000 (36%)</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Rs200,000 (40%)</t>
+          <t>Rs320,000 (64%)</t>
         </is>
       </c>
     </row>
@@ -760,7 +760,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-11-20</t>
+          <t>2026-11-21</t>
         </is>
       </c>
     </row>
@@ -780,7 +780,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>65%</t>
+          <t>64%</t>
         </is>
       </c>
     </row>
@@ -792,7 +792,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>+2.3%</t>
+          <t>+2.1%</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Rs511,500</t>
+          <t>Rs510,500</t>
         </is>
       </c>
     </row>
@@ -920,7 +920,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>1.85</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>60% (Weak regime)</t>
+          <t>36% (Weak regime)</t>
         </is>
       </c>
     </row>
@@ -1513,11 +1513,11 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Risk/Vol +24 · Historical +20 · Trend/Tech +16 · Regime +9 · Sector +8 = 77</t>
+          <t>Risk/Vol +24 · Historical +20 · Trend/Tech +16 · Sector +8 · Regime +5 = 73</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -1527,14 +1527,14 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Sector</t>
+          <t>Regime</t>
         </is>
       </c>
       <c r="F2" t="n">
         <v>66</v>
       </c>
       <c r="G2" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H2" t="n">
         <v>96</v>
@@ -1543,7 +1543,7 @@
         <v>75</v>
       </c>
       <c r="J2" t="n">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -1556,11 +1556,11 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>1406.9</v>
+        <v>1395.8</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>1378 - 1435</t>
+          <t>1368 - 1424</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -1574,15 +1574,15 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>Above 200-DMA (+3.9%)</t>
+          <t>Above 200-DMA (+3.1%)</t>
         </is>
       </c>
       <c r="S2" t="n">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -1591,14 +1591,14 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>2026-11-20</t>
+          <t>2026-11-21</t>
         </is>
       </c>
       <c r="V2" t="n">
-        <v>29545</v>
+        <v>18145</v>
       </c>
       <c r="W2" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="X2" t="n">
         <v>10.3</v>
@@ -1615,27 +1615,27 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ICICIBANK: 77; SBIN: 66, PNB: 61, HDFCBANK: 58</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ICICIBANK: 73; SBIN: 62, PNB: 57, HDFCBANK: 54</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>Low-risk Financials holding (low vol) • above 200-dma (+3.9%) • outperforming Nifty • sector strength 75/100 • regime cautious (partial deploy) • 8 similar past recs: 75% positive, median +5.3%</t>
+          <t>Low-risk Financials holding (low vol) • above 200-dma (+3.1%) • outperforming Nifty • sector strength 75/100 • regime cautious (partial deploy) • 8 similar past recs: 75% positive, median +5.3%</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>STRONG BUY</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Historical +20 · Risk/Vol +20 · Trend/Tech +9 · Regime +9 · Sector +8 = 66</t>
+          <t>Historical +20 · Risk/Vol +20 · Trend/Tech +9 · Sector +8 · Regime +5 = 62</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -1645,14 +1645,14 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sector</t>
+          <t>Regime</t>
         </is>
       </c>
       <c r="F3" t="n">
         <v>65</v>
       </c>
       <c r="G3" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H3" t="n">
         <v>81</v>
@@ -1661,7 +1661,7 @@
         <v>75</v>
       </c>
       <c r="J3" t="n">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -1674,11 +1674,11 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>980.2</v>
+        <v>966.6</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>955 - 1006</t>
+          <t>942 - 992</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -1692,15 +1692,15 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-5.8%)</t>
+          <t>Below 200-DMA (-7.1%)</t>
         </is>
       </c>
       <c r="S3" t="n">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -1709,14 +1709,14 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>2026-11-20</t>
+          <t>2026-11-21</t>
         </is>
       </c>
       <c r="V3" t="n">
-        <v>22543</v>
+        <v>13532</v>
       </c>
       <c r="W3" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="X3" t="n">
         <v>7.6</v>
@@ -1733,12 +1733,12 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — SBIN: 66; ICICIBANK: 77, PNB: 61, HDFCBANK: 58. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — SBIN: 62; ICICIBANK: 73, PNB: 57, HDFCBANK: 54. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>Low-risk Financials holding (low vol) • below 200-dma (-5.8%) • outperforming Nifty • sector strength 75/100 • regime cautious (partial deploy) • 2 similar past recs: 100% positive, median +8.9%</t>
+          <t>Low-risk Financials holding (low vol) • below 200-dma (-7.1%) • outperforming Nifty • sector strength 75/100 • regime cautious (partial deploy) • 2 similar past recs: 100% positive, median +8.9%</t>
         </is>
       </c>
     </row>
@@ -1749,11 +1749,11 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Risk/Vol +21 · Historical +15 · Regime +9 · Sector +9 · Trend/Tech +7 = 61</t>
+          <t>Risk/Vol +21 · Historical +15 · Sector +9 · Trend/Tech +7 · Regime +5 = 57</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1763,14 +1763,14 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Trend/Tech</t>
+          <t>Regime</t>
         </is>
       </c>
       <c r="F4" t="n">
         <v>51</v>
       </c>
       <c r="G4" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="H4" t="n">
         <v>85</v>
@@ -1779,7 +1779,7 @@
         <v>88</v>
       </c>
       <c r="J4" t="n">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -1792,11 +1792,11 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>410.4</v>
+        <v>398.5</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>400 - 421</t>
+          <t>388 - 409</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -1810,15 +1810,15 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-5.5%)</t>
+          <t>Below 200-DMA (-8.2%)</t>
         </is>
       </c>
       <c r="S4" t="n">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1827,17 +1827,17 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>2026-11-20</t>
+          <t>2026-11-21</t>
         </is>
       </c>
       <c r="V4" t="n">
-        <v>38163</v>
+        <v>21918</v>
       </c>
       <c r="W4" t="n">
-        <v>93</v>
+        <v>55</v>
       </c>
       <c r="X4" t="n">
-        <v>12.9</v>
+        <v>12.3</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -1851,27 +1851,27 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — COALINDIA: 61; TATASTEEL: 57, HINDZINC: 51, SAIL: 42</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — COALINDIA: 57; TATASTEEL: 54, HINDZINC: 46, SAIL: 39</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>Low-risk Metal holding (low vol) • below 200-dma (-5.5%) • outperforming Nifty • sector strength 88/100 • regime cautious (partial deploy) • 3 similar past recs: 67% positive, median +0.8%</t>
+          <t>Low-risk Metal holding (low vol) • below 200-dma (-8.2%) • sector strength 88/100 • regime cautious (partial deploy) • 3 similar past recs: 67% positive, median +0.8%</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>ACCUMULATE</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Risk/Vol +23 · Historical +13 · Trend/Tech +9 · Regime +9 · Sector +6 = 60</t>
+          <t>Risk/Vol +19 · Historical +15 · Sector +9 · Trend/Tech +6 · Regime +5 = 54</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1881,62 +1881,62 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Sector</t>
+          <t>Regime</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="G5" t="n">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="H5" t="n">
-        <v>92</v>
+        <v>77</v>
       </c>
       <c r="I5" t="n">
-        <v>62</v>
+        <v>88</v>
       </c>
       <c r="J5" t="n">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>ITC</t>
+          <t>TATASTEEL</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>Metal</t>
         </is>
       </c>
       <c r="M5" t="n">
-        <v>264.2</v>
+        <v>171.6</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>258 - 270</t>
+          <t>167 - 176</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-4% to +3%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>56%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>75</v>
+        <v>64</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-10.4%)</t>
+          <t>Below 200-DMA (-11.7%)</t>
         </is>
       </c>
       <c r="S5" t="n">
-        <v>50</v>
+        <v>23</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1945,21 +1945,21 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>2026-11-20</t>
+          <t>2026-11-21</t>
         </is>
       </c>
       <c r="V5" t="n">
-        <v>42272</v>
+        <v>16647</v>
       </c>
       <c r="W5" t="n">
-        <v>160</v>
+        <v>97</v>
       </c>
       <c r="X5" t="n">
-        <v>14.1</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility FMCG name under the sector cap</t>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Metal name under the sector cap</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1969,27 +1969,27 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ITC: 60; DABUR: 53</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — TATASTEEL: 54; COALINDIA: 57, HINDZINC: 46, SAIL: 39. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>Low-risk FMCG holding (low vol) • below 200-dma (-10.4%) • outperforming Nifty • sector strength 62/100 • regime cautious (partial deploy) • 9 similar past recs: 56% positive, median +0.3%</t>
+          <t>Low-risk Metal holding (low vol) • below 200-dma (-11.7%) • sector strength 88/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>ACCUMULATE</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Risk/Vol +18 · Historical +15 · Regime +9 · Sector +9 · Trend/Tech +6 = 57</t>
+          <t>Risk/Vol +23 · Historical +15 · Trend/Tech +8 · Regime +5 · Sector +2 = 53</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1999,40 +1999,40 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Trend/Tech</t>
+          <t>Sector</t>
         </is>
       </c>
       <c r="F6" t="n">
         <v>50</v>
       </c>
       <c r="G6" t="n">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="H6" t="n">
-        <v>73</v>
+        <v>92</v>
       </c>
       <c r="I6" t="n">
-        <v>88</v>
+        <v>25</v>
       </c>
       <c r="J6" t="n">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>TATASTEEL</t>
+          <t>TATAPOWER</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Metal</t>
+          <t>Power</t>
         </is>
       </c>
       <c r="M6" t="n">
-        <v>174.7</v>
+        <v>349.9</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>170 - 179</t>
+          <t>342 - 358</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -2046,15 +2046,15 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-10.1%)</t>
+          <t>Below 200-DMA (-8.9%)</t>
         </is>
       </c>
       <c r="S6" t="n">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -2063,21 +2063,21 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>2026-11-20</t>
+          <t>2026-11-21</t>
         </is>
       </c>
       <c r="V6" t="n">
-        <v>27429</v>
+        <v>19244</v>
       </c>
       <c r="W6" t="n">
-        <v>157</v>
+        <v>55</v>
       </c>
       <c r="X6" t="n">
-        <v>9.199999999999999</v>
+        <v>10.7</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Metal name under the sector cap</t>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Power name under the sector cap</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -2087,27 +2087,27 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — TATASTEEL: 57; COALINDIA: 61, HINDZINC: 51, SAIL: 42. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — TATAPOWER: 53; NHPC: 46, ADANIPOWER: 31, NLCINDIA: 28</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>Low-risk Metal holding (low vol) • below 200-dma (-10.1%) • sector strength 88/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
+          <t>Low-risk Power holding (low vol) • below 200-dma (-8.9%) • sector strength 25/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>ACCUMULATE</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Risk/Vol +22 · Historical +15 · Regime +9 · Trend/Tech +8 · Sector +2 = 56</t>
+          <t>Risk/Vol +22 · Historical +13 · Trend/Tech +8 · Regime +5 · Sector +4 = 52</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -2121,7 +2121,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="G7" t="n">
         <v>41</v>
@@ -2130,49 +2130,49 @@
         <v>88</v>
       </c>
       <c r="I7" t="n">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="J7" t="n">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>TATAPOWER</t>
+          <t>ITC</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Power</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>351</v>
+        <v>259.5</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>343 - 359</t>
+          <t>253 - 266</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-4% to +3%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>56%</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-8.6%)</t>
+          <t>Below 200-DMA (-11.7%)</t>
         </is>
       </c>
       <c r="S7" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -2181,21 +2181,21 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>2026-11-20</t>
+          <t>2026-11-21</t>
         </is>
       </c>
       <c r="V7" t="n">
-        <v>30533</v>
+        <v>24652</v>
       </c>
       <c r="W7" t="n">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="X7" t="n">
-        <v>10.3</v>
+        <v>13.7</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Power name under the sector cap</t>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility FMCG name under the sector cap</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -2205,12 +2205,12 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — TATAPOWER: 56; NHPC: 49, ADANIPOWER: 45, NLCINDIA: 32</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ITC: 52; DABUR: 47</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>Low-risk Power holding (low vol) • below 200-dma (-8.6%) • sector strength 25/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
+          <t>Low-risk FMCG holding (low vol) • below 200-dma (-11.7%) • sector strength 38/100 • regime cautious (partial deploy) • 9 similar past recs: 56% positive, median +0.3%</t>
         </is>
       </c>
     </row>
@@ -2221,11 +2221,11 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Risk/Vol +19 · Historical +15 · Regime +9 · Trend/Tech +6 · Sector +5 = 54</t>
+          <t>Risk/Vol +17 · Historical +16 · Trend/Tech +7 · Sector +6 · Regime +5 = 51</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -2235,40 +2235,40 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Sector</t>
+          <t>Regime</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="G8" t="n">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="H8" t="n">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="I8" t="n">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="J8" t="n">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>BEL</t>
+          <t>ONGC</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="M8" t="n">
-        <v>374</v>
+        <v>225.8</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>364 - 384</t>
+          <t>220 - 232</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -2282,15 +2282,15 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-10.3%)</t>
+          <t>Below 200-DMA (-11.7%)</t>
         </is>
       </c>
       <c r="S8" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -2299,21 +2299,21 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>2026-11-20</t>
+          <t>2026-11-21</t>
         </is>
       </c>
       <c r="V8" t="n">
-        <v>26924</v>
+        <v>24841</v>
       </c>
       <c r="W8" t="n">
-        <v>72</v>
+        <v>110</v>
       </c>
       <c r="X8" t="n">
-        <v>9</v>
+        <v>13.9</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Industrials name under the sector cap</t>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Energy name under the sector cap</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
@@ -2323,12 +2323,12 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>No same-sector peer in the universe.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ONGC: 51; IOC: 43</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>Low-risk Industrials holding (low vol) • below 200-dma (-10.3%) • sector strength 50/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
+          <t>Low-risk Energy holding (low vol) • below 200-dma (-11.7%) • sector strength 62/100 • regime cautious (partial deploy) • 2 similar past recs: 50% positive, median +9.0%</t>
         </is>
       </c>
     </row>
@@ -2339,11 +2339,11 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Risk/Vol +16 · Historical +15 · Regime +9 · Trend/Tech +7 · Sector +6 = 53</t>
+          <t>Risk/Vol +18 · Historical +15 · Trend/Tech +6 · Regime +5 · Sector +5 = 49</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2360,55 +2360,55 @@
         <v>50</v>
       </c>
       <c r="G9" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="H9" t="n">
+        <v>73</v>
+      </c>
+      <c r="I9" t="n">
+        <v>50</v>
+      </c>
+      <c r="J9" t="n">
+        <v>36</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>BEL</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="M9" t="n">
+        <v>366.1</v>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>357 - 376</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
         <v>62</v>
       </c>
-      <c r="I9" t="n">
-        <v>62</v>
-      </c>
-      <c r="J9" t="n">
-        <v>60</v>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>DABUR</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>FMCG</t>
-        </is>
-      </c>
-      <c r="M9" t="n">
-        <v>376.4</v>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>366 - 387</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Q9" t="n">
-        <v>64</v>
-      </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-14.9%)</t>
+          <t>Below 200-DMA (-12.1%)</t>
         </is>
       </c>
       <c r="S9" t="n">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -2417,21 +2417,21 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>2026-11-20</t>
+          <t>2026-11-21</t>
         </is>
       </c>
       <c r="V9" t="n">
-        <v>38388</v>
+        <v>16111</v>
       </c>
       <c r="W9" t="n">
-        <v>102</v>
+        <v>44</v>
       </c>
       <c r="X9" t="n">
-        <v>12.9</v>
+        <v>9</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility FMCG name under the sector cap</t>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Industrials name under the sector cap</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
@@ -2441,12 +2441,12 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — DABUR: 53; ITC: 60. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>No same-sector peer in the universe.</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>Low-risk FMCG holding (medium vol) • below 200-dma (-14.9%) • sector strength 62/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
+          <t>Low-risk Industrials holding (low vol) • below 200-dma (-12.1%) • sector strength 50/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
         </is>
       </c>
     </row>
@@ -2457,11 +2457,11 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Risk/Vol +17 · Historical +16 · Regime +9 · Trend/Tech +5 · Sector +4 = 51</t>
+          <t>Risk/Vol +16 · Historical +15 · Trend/Tech +7 · Regime +5 · Sector +4 = 47</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2475,36 +2475,36 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="G10" t="n">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="H10" t="n">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="I10" t="n">
         <v>38</v>
       </c>
       <c r="J10" t="n">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>ONGC</t>
+          <t>DABUR</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>225.6</v>
+        <v>372.2</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>220 - 232</t>
+          <t>362 - 382</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -2518,15 +2518,15 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-11.8%)</t>
+          <t>Below 200-DMA (-15.7%)</t>
         </is>
       </c>
       <c r="S10" t="n">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -2535,21 +2535,21 @@
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>2026-11-20</t>
+          <t>2026-11-21</t>
         </is>
       </c>
       <c r="V10" t="n">
-        <v>41520</v>
+        <v>23449</v>
       </c>
       <c r="W10" t="n">
-        <v>184</v>
+        <v>63</v>
       </c>
       <c r="X10" t="n">
-        <v>13.8</v>
+        <v>13.2</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Energy name under the sector cap</t>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility FMCG name under the sector cap</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
@@ -2559,12 +2559,12 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ONGC: 51; IOC: 47</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — DABUR: 47; ITC: 52. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>Low-risk Energy holding (low vol) • below 200-dma (-11.8%) • sector strength 38/100 • regime cautious (partial deploy) • 2 similar past recs: 50% positive, median +9.0%</t>
+          <t>Low-risk FMCG holding (medium vol) • below 200-dma (-15.7%) • sector strength 38/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
         </is>
       </c>
     </row>
@@ -26218,19 +26218,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D4" t="n">
         <v>0.9</v>
       </c>
       <c r="E4" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F4" t="n">
         <v>-6.7</v>
       </c>
       <c r="G4" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -26251,19 +26251,19 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D5" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="E5" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F5" t="n">
         <v>-8.4</v>
       </c>
       <c r="G5" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -26288,16 +26288,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D6" t="n">
         <v>2.6</v>
       </c>
       <c r="E6" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F6" t="n">
-        <v>-7.9</v>
+        <v>-9.300000000000001</v>
       </c>
       <c r="G6" t="n">
         <v>1.1</v>
@@ -26321,10 +26321,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D7" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="E7" t="n">
         <v>68</v>
@@ -26354,16 +26354,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D8" t="n">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="E8" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F8" t="n">
-        <v>-11.8</v>
+        <v>-11.9</v>
       </c>
       <c r="G8" t="n">
         <v>0.8</v>
@@ -26387,19 +26387,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D9" t="n">
         <v>6.6</v>
       </c>
       <c r="E9" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F9" t="n">
-        <v>-7.6</v>
+        <v>-9.9</v>
       </c>
       <c r="G9" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -27339,7 +27339,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>16.2%</t>
+          <t>9.7%</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -27354,7 +27354,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>13.2%</t>
+          <t>7.8%</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -27369,7 +27369,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>10.7%</t>
+          <t>6.4%</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -27384,7 +27384,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>5.0%</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -27399,7 +27399,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>6.2%</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -27414,7 +27414,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>5.4%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -27429,7 +27429,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>64.0%</t>
         </is>
       </c>
       <c r="C8" t="n">

--- a/reports/AEGIS_LATEST.xlsx
+++ b/reports/AEGIS_LATEST.xlsx
@@ -444,7 +444,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
     </row>
@@ -489,7 +489,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7">
@@ -512,7 +512,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-11-21</t>
+          <t>2026-11-22</t>
         </is>
       </c>
     </row>
@@ -536,7 +536,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>DABUR (47)</t>
+          <t>DABUR (44)</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-22  /  2026-10-22</t>
+          <t>2026-10-23  /  2026-10-23</t>
         </is>
       </c>
     </row>
@@ -760,7 +760,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-11-21</t>
+          <t>2026-11-22</t>
         </is>
       </c>
     </row>
@@ -908,7 +908,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>14.7%</t>
+          <t>14.6%</t>
         </is>
       </c>
     </row>
@@ -920,7 +920,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.84</t>
         </is>
       </c>
     </row>
@@ -1534,7 +1534,7 @@
         <v>66</v>
       </c>
       <c r="G2" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H2" t="n">
         <v>96</v>
@@ -1556,11 +1556,11 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>1395.8</v>
+        <v>1391.2</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>1368 - 1424</t>
+          <t>1363 - 1419</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -1578,11 +1578,11 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>Above 200-DMA (+3.1%)</t>
+          <t>Above 200-DMA (+2.7%)</t>
         </is>
       </c>
       <c r="S2" t="n">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -1591,17 +1591,17 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>2026-11-21</t>
+          <t>2026-11-22</t>
         </is>
       </c>
       <c r="V2" t="n">
-        <v>18145</v>
+        <v>18086</v>
       </c>
       <c r="W2" t="n">
         <v>13</v>
       </c>
       <c r="X2" t="n">
-        <v>10.3</v>
+        <v>10.6</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
@@ -1615,12 +1615,12 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ICICIBANK: 73; SBIN: 62, PNB: 57, HDFCBANK: 54</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ICICIBANK: 73; SBIN: 62, PNB: 59, HDFCBANK: 52</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>Low-risk Financials holding (low vol) • above 200-dma (+3.1%) • outperforming Nifty • sector strength 75/100 • regime cautious (partial deploy) • 8 similar past recs: 75% positive, median +5.3%</t>
+          <t>Low-risk Financials holding (low vol) • above 200-dma (+2.7%) • outperforming Nifty • sector strength 75/100 • regime cautious (partial deploy) • 8 similar past recs: 75% positive, median +5.3%</t>
         </is>
       </c>
     </row>
@@ -1635,7 +1635,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Historical +20 · Risk/Vol +20 · Trend/Tech +9 · Sector +8 · Regime +5 = 62</t>
+          <t>Historical +20 · Risk/Vol +19 · Trend/Tech +10 · Sector +8 · Regime +5 = 62</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -1652,10 +1652,10 @@
         <v>65</v>
       </c>
       <c r="G3" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="H3" t="n">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="I3" t="n">
         <v>75</v>
@@ -1674,11 +1674,11 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>966.6</v>
+        <v>956.2</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>942 - 992</t>
+          <t>931 - 981</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -1696,11 +1696,11 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-7.1%)</t>
+          <t>Below 200-DMA (-8.0%)</t>
         </is>
       </c>
       <c r="S3" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -1709,17 +1709,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>2026-11-21</t>
+          <t>2026-11-22</t>
         </is>
       </c>
       <c r="V3" t="n">
-        <v>13532</v>
+        <v>13387</v>
       </c>
       <c r="W3" t="n">
         <v>14</v>
       </c>
       <c r="X3" t="n">
-        <v>7.6</v>
+        <v>7.7</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
@@ -1733,12 +1733,12 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — SBIN: 62; ICICIBANK: 73, PNB: 57, HDFCBANK: 54. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — SBIN: 62; ICICIBANK: 73, PNB: 59, HDFCBANK: 52. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>Low-risk Financials holding (low vol) • below 200-dma (-7.1%) • outperforming Nifty • sector strength 75/100 • regime cautious (partial deploy) • 2 similar past recs: 100% positive, median +8.9%</t>
+          <t>Low-risk Financials holding (low vol) • below 200-dma (-8.0%) • outperforming Nifty • sector strength 75/100 • regime cautious (partial deploy) • 2 similar past recs: 100% positive, median +8.9%</t>
         </is>
       </c>
     </row>
@@ -1770,7 +1770,7 @@
         <v>51</v>
       </c>
       <c r="G4" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H4" t="n">
         <v>85</v>
@@ -1792,11 +1792,11 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>398.5</v>
+        <v>395.5</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>388 - 409</t>
+          <t>385 - 406</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -1814,11 +1814,11 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-8.2%)</t>
+          <t>Below 200-DMA (-8.9%)</t>
         </is>
       </c>
       <c r="S4" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1827,17 +1827,17 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>2026-11-21</t>
+          <t>2026-11-22</t>
         </is>
       </c>
       <c r="V4" t="n">
-        <v>21918</v>
+        <v>22151</v>
       </c>
       <c r="W4" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="X4" t="n">
-        <v>12.3</v>
+        <v>12.4</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -1851,27 +1851,27 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — COALINDIA: 57; TATASTEEL: 54, HINDZINC: 46, SAIL: 39</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — COALINDIA: 57; TATASTEEL: 52, HINDZINC: 46, SAIL: 39</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>Low-risk Metal holding (low vol) • below 200-dma (-8.2%) • sector strength 88/100 • regime cautious (partial deploy) • 3 similar past recs: 67% positive, median +0.8%</t>
+          <t>Low-risk Metal holding (low vol) • below 200-dma (-8.9%) • outperforming Nifty • sector strength 88/100 • regime cautious (partial deploy) • 3 similar past recs: 67% positive, median +0.8%</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ACCUMULATE</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Risk/Vol +19 · Historical +15 · Sector +9 · Trend/Tech +6 · Regime +5 = 54</t>
+          <t>Risk/Vol +20 · Historical +16 · Trend/Tech +8 · Sector +6 · Regime +5 = 55</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1885,36 +1885,36 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="G5" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="H5" t="n">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="I5" t="n">
-        <v>88</v>
+        <v>62</v>
       </c>
       <c r="J5" t="n">
         <v>36</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>TATASTEEL</t>
+          <t>ONGC</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Metal</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="M5" t="n">
-        <v>171.6</v>
+        <v>225.5</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>167 - 176</t>
+          <t>220 - 231</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -1928,15 +1928,15 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-11.7%)</t>
+          <t>Below 200-DMA (-11.8%)</t>
         </is>
       </c>
       <c r="S5" t="n">
-        <v>23</v>
+        <v>58</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1945,21 +1945,21 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>2026-11-21</t>
+          <t>2026-11-22</t>
         </is>
       </c>
       <c r="V5" t="n">
-        <v>16647</v>
+        <v>25483</v>
       </c>
       <c r="W5" t="n">
-        <v>97</v>
+        <v>113</v>
       </c>
       <c r="X5" t="n">
-        <v>9.300000000000001</v>
+        <v>14.2</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Metal name under the sector cap</t>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Energy name under the sector cap</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1969,12 +1969,12 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — TATASTEEL: 54; COALINDIA: 57, HINDZINC: 46, SAIL: 39. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ONGC: 55; IOC: 46</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>Low-risk Metal holding (low vol) • below 200-dma (-11.7%) • sector strength 88/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
+          <t>Low-risk Energy holding (low vol) • below 200-dma (-11.8%) • sector strength 62/100 • regime cautious (partial deploy) • 2 similar past recs: 50% positive, median +9.0%</t>
         </is>
       </c>
     </row>
@@ -1989,7 +1989,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Risk/Vol +23 · Historical +15 · Trend/Tech +8 · Regime +5 · Sector +2 = 53</t>
+          <t>Risk/Vol +23 · Historical +13 · Trend/Tech +8 · Regime +5 · Sector +4 = 53</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -2003,7 +2003,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="G6" t="n">
         <v>42</v>
@@ -2012,49 +2012,49 @@
         <v>92</v>
       </c>
       <c r="I6" t="n">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="J6" t="n">
         <v>36</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>TATAPOWER</t>
+          <t>ITC</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Power</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="M6" t="n">
-        <v>349.9</v>
+        <v>257.1</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>342 - 358</t>
+          <t>251 - 263</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-4% to +3%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>56%</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-8.9%)</t>
+          <t>Below 200-DMA (-12.4%)</t>
         </is>
       </c>
       <c r="S6" t="n">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -2063,21 +2063,21 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>2026-11-21</t>
+          <t>2026-11-22</t>
         </is>
       </c>
       <c r="V6" t="n">
-        <v>19244</v>
+        <v>24939</v>
       </c>
       <c r="W6" t="n">
-        <v>55</v>
+        <v>97</v>
       </c>
       <c r="X6" t="n">
-        <v>10.7</v>
+        <v>14</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Power name under the sector cap</t>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility FMCG name under the sector cap</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -2087,12 +2087,12 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — TATAPOWER: 53; NHPC: 46, ADANIPOWER: 31, NLCINDIA: 28</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ITC: 53; DABUR: 44</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>Low-risk Power holding (low vol) • below 200-dma (-8.9%) • sector strength 25/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
+          <t>Low-risk FMCG holding (low vol) • below 200-dma (-12.4%) • sector strength 38/100 • regime cautious (partial deploy) • 9 similar past recs: 56% positive, median +0.3%</t>
         </is>
       </c>
     </row>
@@ -2107,7 +2107,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Risk/Vol +22 · Historical +13 · Trend/Tech +8 · Regime +5 · Sector +4 = 52</t>
+          <t>Risk/Vol +17 · Historical +15 · Sector +9 · Trend/Tech +6 · Regime +5 = 52</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -2117,62 +2117,62 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Sector</t>
+          <t>Regime</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="G7" t="n">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="H7" t="n">
+        <v>69</v>
+      </c>
+      <c r="I7" t="n">
         <v>88</v>
-      </c>
-      <c r="I7" t="n">
-        <v>38</v>
       </c>
       <c r="J7" t="n">
         <v>36</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>ITC</t>
+          <t>TATASTEEL</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>Metal</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>259.5</v>
+        <v>166.5</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>253 - 266</t>
+          <t>162 - 171</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-4% to +3%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>56%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-11.7%)</t>
+          <t>Below 200-DMA (-14.3%)</t>
         </is>
       </c>
       <c r="S7" t="n">
-        <v>44</v>
+        <v>24</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -2181,21 +2181,21 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>2026-11-21</t>
+          <t>2026-11-22</t>
         </is>
       </c>
       <c r="V7" t="n">
-        <v>24652</v>
+        <v>16315</v>
       </c>
       <c r="W7" t="n">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="X7" t="n">
-        <v>13.7</v>
+        <v>9.1</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility FMCG name under the sector cap</t>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Metal name under the sector cap</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -2205,12 +2205,12 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ITC: 52; DABUR: 47</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — TATASTEEL: 52; COALINDIA: 57, HINDZINC: 46, SAIL: 39. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>Low-risk FMCG holding (low vol) • below 200-dma (-11.7%) • sector strength 38/100 • regime cautious (partial deploy) • 9 similar past recs: 56% positive, median +0.3%</t>
+          <t>Low-risk Metal holding (low vol) • below 200-dma (-14.3%) • sector strength 88/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
         </is>
       </c>
     </row>
@@ -2225,7 +2225,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Risk/Vol +17 · Historical +16 · Trend/Tech +7 · Sector +6 · Regime +5 = 51</t>
+          <t>Risk/Vol +22 · Historical +15 · Trend/Tech +7 · Regime +5 · Sector +2 = 51</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -2235,40 +2235,40 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Regime</t>
+          <t>Sector</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="G8" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="H8" t="n">
-        <v>69</v>
+        <v>88</v>
       </c>
       <c r="I8" t="n">
-        <v>62</v>
+        <v>25</v>
       </c>
       <c r="J8" t="n">
         <v>36</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>ONGC</t>
+          <t>TATAPOWER</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Power</t>
         </is>
       </c>
       <c r="M8" t="n">
-        <v>225.8</v>
+        <v>343.5</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>220 - 232</t>
+          <t>335 - 352</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -2282,15 +2282,15 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-11.7%)</t>
+          <t>Below 200-DMA (-10.5%)</t>
         </is>
       </c>
       <c r="S8" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -2299,21 +2299,21 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>2026-11-21</t>
+          <t>2026-11-22</t>
         </is>
       </c>
       <c r="V8" t="n">
-        <v>24841</v>
+        <v>18546</v>
       </c>
       <c r="W8" t="n">
-        <v>110</v>
+        <v>54</v>
       </c>
       <c r="X8" t="n">
-        <v>13.9</v>
+        <v>10.3</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Energy name under the sector cap</t>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Power name under the sector cap</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
@@ -2323,12 +2323,12 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ONGC: 51; IOC: 43</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — TATAPOWER: 51; NHPC: 45, ADANIPOWER: 31, NLCINDIA: 28</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>Low-risk Energy holding (low vol) • below 200-dma (-11.7%) • sector strength 62/100 • regime cautious (partial deploy) • 2 similar past recs: 50% positive, median +9.0%</t>
+          <t>Low-risk Power holding (low vol) • below 200-dma (-10.5%) • sector strength 25/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
         </is>
       </c>
     </row>
@@ -2339,11 +2339,11 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Risk/Vol +18 · Historical +15 · Trend/Tech +6 · Regime +5 · Sector +5 = 49</t>
+          <t>Risk/Vol +18 · Historical +15 · Trend/Tech +5 · Regime +5 · Sector +5 = 48</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2360,7 +2360,7 @@
         <v>50</v>
       </c>
       <c r="G9" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H9" t="n">
         <v>73</v>
@@ -2382,11 +2382,11 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>366.1</v>
+        <v>357.6</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>357 - 376</t>
+          <t>348 - 367</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -2404,11 +2404,11 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-12.1%)</t>
+          <t>Below 200-DMA (-14.2%)</t>
         </is>
       </c>
       <c r="S9" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -2417,17 +2417,17 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>2026-11-21</t>
+          <t>2026-11-22</t>
         </is>
       </c>
       <c r="V9" t="n">
-        <v>16111</v>
+        <v>15734</v>
       </c>
       <c r="W9" t="n">
         <v>44</v>
       </c>
       <c r="X9" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -2446,22 +2446,22 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>Low-risk Industrials holding (low vol) • below 200-dma (-12.1%) • sector strength 50/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
+          <t>Low-risk Industrials holding (low vol) • below 200-dma (-14.2%) • sector strength 50/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ACCUMULATE</t>
+          <t>WATCH</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Risk/Vol +16 · Historical +15 · Trend/Tech +7 · Regime +5 · Sector +4 = 47</t>
+          <t>Risk/Vol +16 · Historical +15 · Regime +5 · Trend/Tech +4 · Sector +4 = 44</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2478,7 +2478,7 @@
         <v>50</v>
       </c>
       <c r="G10" t="n">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="H10" t="n">
         <v>62</v>
@@ -2500,11 +2500,11 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>372.2</v>
+        <v>359.7</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>362 - 382</t>
+          <t>350 - 370</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -2518,15 +2518,15 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-15.7%)</t>
+          <t>Below 200-DMA (-18.4%)</t>
         </is>
       </c>
       <c r="S10" t="n">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -2535,17 +2535,17 @@
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>2026-11-21</t>
+          <t>2026-11-22</t>
         </is>
       </c>
       <c r="V10" t="n">
-        <v>23449</v>
+        <v>23021</v>
       </c>
       <c r="W10" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="X10" t="n">
-        <v>13.2</v>
+        <v>12.9</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -2559,12 +2559,12 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — DABUR: 47; ITC: 52. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — DABUR: 44; ITC: 53. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>Low-risk FMCG holding (medium vol) • below 200-dma (-15.7%) • sector strength 38/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
+          <t>Low-risk FMCG holding (medium vol) • below 200-dma (-18.4%) • sector strength 38/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
         </is>
       </c>
     </row>
@@ -11511,9 +11511,15 @@
       <c r="L106" t="n">
         <v>-1.05</v>
       </c>
-      <c r="M106" t="inlineStr"/>
-      <c r="N106" t="inlineStr"/>
-      <c r="O106" t="inlineStr"/>
+      <c r="M106" t="n">
+        <v>1</v>
+      </c>
+      <c r="N106" t="n">
+        <v>-17.4</v>
+      </c>
+      <c r="O106" t="n">
+        <v>-1645</v>
+      </c>
       <c r="P106" t="n">
         <v>-51.4</v>
       </c>
@@ -25482,9 +25488,15 @@
       <c r="L279" t="n">
         <v>0.27</v>
       </c>
-      <c r="M279" t="inlineStr"/>
-      <c r="N279" t="inlineStr"/>
-      <c r="O279" t="inlineStr"/>
+      <c r="M279" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="N279" t="n">
+        <v>0</v>
+      </c>
+      <c r="O279" t="n">
+        <v>10</v>
+      </c>
       <c r="P279" t="n">
         <v>10.2</v>
       </c>
@@ -27259,7 +27271,7 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>-12.6</v>
+        <v>-11.8</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -27354,7 +27366,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>7.8%</t>
+          <t>7.7%</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -27369,7 +27381,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>6.4%</t>
+          <t>6.6%</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -27384,7 +27396,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>5.0%</t>
+          <t>5.1%</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -27399,7 +27411,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>3.7%</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -27414,7 +27426,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="C7" t="n">

--- a/reports/AEGIS_LATEST.xlsx
+++ b/reports/AEGIS_LATEST.xlsx
@@ -444,7 +444,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-23  /  2026-10-23</t>
+          <t>2026-10-24  /  2026-10-23</t>
         </is>
       </c>
     </row>
@@ -11511,15 +11511,9 @@
       <c r="L106" t="n">
         <v>-1.05</v>
       </c>
-      <c r="M106" t="n">
-        <v>1</v>
-      </c>
-      <c r="N106" t="n">
-        <v>-17.4</v>
-      </c>
-      <c r="O106" t="n">
-        <v>-1645</v>
-      </c>
+      <c r="M106" t="inlineStr"/>
+      <c r="N106" t="inlineStr"/>
+      <c r="O106" t="inlineStr"/>
       <c r="P106" t="n">
         <v>-51.4</v>
       </c>
@@ -25488,15 +25482,9 @@
       <c r="L279" t="n">
         <v>0.27</v>
       </c>
-      <c r="M279" t="n">
-        <v>23.5</v>
-      </c>
-      <c r="N279" t="n">
-        <v>0</v>
-      </c>
-      <c r="O279" t="n">
-        <v>10</v>
-      </c>
+      <c r="M279" t="inlineStr"/>
+      <c r="N279" t="inlineStr"/>
+      <c r="O279" t="inlineStr"/>
       <c r="P279" t="n">
         <v>10.2</v>
       </c>
@@ -27271,7 +27259,7 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>-11.8</v>
+        <v>-12.6</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>

--- a/reports/AEGIS_LATEST.xlsx
+++ b/reports/AEGIS_LATEST.xlsx
@@ -444,7 +444,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -456,7 +456,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Weak  ·  deploy 36%  ·  cash 64%</t>
+          <t>Weak  ·  deploy 29%  ·  cash 71%</t>
         </is>
       </c>
     </row>
@@ -479,7 +479,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6">
@@ -512,7 +512,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-11-22</t>
+          <t>2026-11-25</t>
         </is>
       </c>
     </row>
@@ -524,7 +524,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ICICIBANK (73)</t>
+          <t>ICICIBANK (70)</t>
         </is>
       </c>
     </row>
@@ -536,7 +536,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>DABUR (44)</t>
+          <t>BEL (48)</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>DABUR</t>
         </is>
       </c>
     </row>
@@ -571,7 +571,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -664,7 +664,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Hold a 9-stock risk-managed portfolio</t>
+          <t>Hold a 8-stock risk-managed portfolio</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-24  /  2026-10-23</t>
+          <t>2026-10-26  /  2026-10-26</t>
         </is>
       </c>
     </row>
@@ -736,7 +736,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Rs180,000 (36%)</t>
+          <t>Rs144,000 (29%)</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Rs320,000 (64%)</t>
+          <t>Rs356,000 (71%)</t>
         </is>
       </c>
     </row>
@@ -760,7 +760,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-11-22</t>
+          <t>2026-11-25</t>
         </is>
       </c>
     </row>
@@ -920,7 +920,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>1.85</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>36% (Weak regime)</t>
+          <t>29% (Weak regime)</t>
         </is>
       </c>
     </row>
@@ -1361,7 +1361,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB10"/>
+  <dimension ref="A1:AB9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1513,11 +1513,11 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Risk/Vol +24 · Historical +20 · Trend/Tech +16 · Sector +8 · Regime +5 = 73</t>
+          <t>Risk/Vol +24 · Historical +20 · Trend/Tech +16 · Sector +6 · Regime +4 = 70</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -1534,16 +1534,16 @@
         <v>66</v>
       </c>
       <c r="G2" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H2" t="n">
         <v>96</v>
       </c>
       <c r="I2" t="n">
-        <v>75</v>
+        <v>62</v>
       </c>
       <c r="J2" t="n">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -1556,11 +1556,11 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>1391.2</v>
+        <v>1389.6</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>1363 - 1419</t>
+          <t>1362 - 1417</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -1574,15 +1574,15 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>Above 200-DMA (+2.7%)</t>
+          <t>Above 200-DMA (+2.6%)</t>
         </is>
       </c>
       <c r="S2" t="n">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -1591,17 +1591,17 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>2026-11-22</t>
+          <t>2026-11-25</t>
         </is>
       </c>
       <c r="V2" t="n">
-        <v>18086</v>
+        <v>27792</v>
       </c>
       <c r="W2" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="X2" t="n">
-        <v>10.6</v>
+        <v>19.7</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
@@ -1615,12 +1615,12 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ICICIBANK: 73; SBIN: 62, PNB: 59, HDFCBANK: 52</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ICICIBANK: 70; SBIN: 59, PNB: 56, HDFCBANK: 51</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>Low-risk Financials holding (low vol) • above 200-dma (+2.7%) • outperforming Nifty • sector strength 75/100 • regime cautious (partial deploy) • 8 similar past recs: 75% positive, median +5.3%</t>
+          <t>Low-risk Financials holding (low vol) • above 200-dma (+2.6%) • outperforming Nifty • sector strength 62/100 • regime cautious (partial deploy) • 8 similar past recs: 75% positive, median +5.3%</t>
         </is>
       </c>
     </row>
@@ -1631,11 +1631,11 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Historical +20 · Risk/Vol +19 · Trend/Tech +10 · Sector +8 · Regime +5 = 62</t>
+          <t>Historical +20 · Risk/Vol +20 · Trend/Tech +9 · Sector +6 · Regime +4 = 59</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -1652,16 +1652,16 @@
         <v>65</v>
       </c>
       <c r="G3" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="H3" t="n">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="I3" t="n">
-        <v>75</v>
+        <v>62</v>
       </c>
       <c r="J3" t="n">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -1674,11 +1674,11 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>956.2</v>
+        <v>953.5</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>931 - 981</t>
+          <t>929 - 978</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -1692,11 +1692,11 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-8.0%)</t>
+          <t>Below 200-DMA (-8.3%)</t>
         </is>
       </c>
       <c r="S3" t="n">
@@ -1709,17 +1709,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>2026-11-22</t>
+          <t>2026-11-25</t>
         </is>
       </c>
       <c r="V3" t="n">
-        <v>13387</v>
+        <v>13348</v>
       </c>
       <c r="W3" t="n">
         <v>14</v>
       </c>
       <c r="X3" t="n">
-        <v>7.7</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
@@ -1733,12 +1733,12 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — SBIN: 62; ICICIBANK: 73, PNB: 59, HDFCBANK: 52. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — SBIN: 59; ICICIBANK: 70, PNB: 56, HDFCBANK: 51. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>Low-risk Financials holding (low vol) • below 200-dma (-8.0%) • outperforming Nifty • sector strength 75/100 • regime cautious (partial deploy) • 2 similar past recs: 100% positive, median +8.9%</t>
+          <t>Low-risk Financials holding (low vol) • below 200-dma (-8.3%) • outperforming Nifty • sector strength 62/100 • regime cautious (partial deploy) • 2 similar past recs: 100% positive, median +8.9%</t>
         </is>
       </c>
     </row>
@@ -1753,7 +1753,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Risk/Vol +21 · Historical +15 · Sector +9 · Trend/Tech +7 · Regime +5 = 57</t>
+          <t>Risk/Vol +21 · Historical +15 · Sector +9 · Trend/Tech +8 · Regime +4 = 57</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1770,7 +1770,7 @@
         <v>51</v>
       </c>
       <c r="G4" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="H4" t="n">
         <v>85</v>
@@ -1779,7 +1779,7 @@
         <v>88</v>
       </c>
       <c r="J4" t="n">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -1792,11 +1792,11 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>395.5</v>
+        <v>403.4</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>385 - 406</t>
+          <t>393 - 414</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -1814,11 +1814,11 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-8.9%)</t>
+          <t>Below 200-DMA (-7.1%)</t>
         </is>
       </c>
       <c r="S4" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1827,17 +1827,17 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>2026-11-22</t>
+          <t>2026-11-25</t>
         </is>
       </c>
       <c r="V4" t="n">
-        <v>22151</v>
+        <v>19764</v>
       </c>
       <c r="W4" t="n">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="X4" t="n">
-        <v>12.4</v>
+        <v>13.8</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -1851,12 +1851,12 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — COALINDIA: 57; TATASTEEL: 52, HINDZINC: 46, SAIL: 39</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — COALINDIA: 57; TATASTEEL: 52, HINDZINC: 45, SAIL: 38</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>Low-risk Metal holding (low vol) • below 200-dma (-8.9%) • outperforming Nifty • sector strength 88/100 • regime cautious (partial deploy) • 3 similar past recs: 67% positive, median +0.8%</t>
+          <t>Low-risk Metal holding (low vol) • below 200-dma (-7.1%) • outperforming Nifty • sector strength 88/100 • regime cautious (partial deploy) • 3 similar past recs: 67% positive, median +0.8%</t>
         </is>
       </c>
     </row>
@@ -1867,11 +1867,11 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Risk/Vol +20 · Historical +16 · Trend/Tech +8 · Sector +6 · Regime +5 = 55</t>
+          <t>Risk/Vol +19 · Historical +16 · Trend/Tech +10 · Sector +8 · Regime +4 = 57</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1888,16 +1888,16 @@
         <v>53</v>
       </c>
       <c r="G5" t="n">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="H5" t="n">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="I5" t="n">
-        <v>62</v>
+        <v>75</v>
       </c>
       <c r="J5" t="n">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -1910,11 +1910,11 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>225.5</v>
+        <v>228.6</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>220 - 231</t>
+          <t>223 - 235</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -1928,15 +1928,15 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-11.8%)</t>
+          <t>Below 200-DMA (-10.6%)</t>
         </is>
       </c>
       <c r="S5" t="n">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1945,17 +1945,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>2026-11-22</t>
+          <t>2026-11-25</t>
         </is>
       </c>
       <c r="V5" t="n">
-        <v>25483</v>
+        <v>19434</v>
       </c>
       <c r="W5" t="n">
-        <v>113</v>
+        <v>85</v>
       </c>
       <c r="X5" t="n">
-        <v>14.2</v>
+        <v>13.5</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -1969,12 +1969,12 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ONGC: 55; IOC: 46</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ONGC: 57; IOC: 47</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>Low-risk Energy holding (low vol) • below 200-dma (-11.8%) • sector strength 62/100 • regime cautious (partial deploy) • 2 similar past recs: 50% positive, median +9.0%</t>
+          <t>Low-risk Energy holding (low vol) • below 200-dma (-10.6%) • outperforming Nifty • sector strength 75/100 • regime cautious (partial deploy) • 2 similar past recs: 50% positive, median +9.0%</t>
         </is>
       </c>
     </row>
@@ -1985,11 +1985,11 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Risk/Vol +23 · Historical +13 · Trend/Tech +8 · Regime +5 · Sector +4 = 53</t>
+          <t>Risk/Vol +23 · Historical +13 · Trend/Tech +8 · Regime +4 · Sector +4 = 52</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -2006,7 +2006,7 @@
         <v>44</v>
       </c>
       <c r="G6" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H6" t="n">
         <v>92</v>
@@ -2015,7 +2015,7 @@
         <v>38</v>
       </c>
       <c r="J6" t="n">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -2028,11 +2028,11 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>257.1</v>
+        <v>257.7</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>251 - 263</t>
+          <t>252 - 264</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -2046,15 +2046,15 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-12.4%)</t>
+          <t>Below 200-DMA (-12.0%)</t>
         </is>
       </c>
       <c r="S6" t="n">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -2063,17 +2063,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>2026-11-22</t>
+          <t>2026-11-25</t>
         </is>
       </c>
       <c r="V6" t="n">
-        <v>24939</v>
+        <v>22935</v>
       </c>
       <c r="W6" t="n">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="X6" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -2087,12 +2087,12 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ITC: 53; DABUR: 44</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ITC: 52; DABUR: 43</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>Low-risk FMCG holding (low vol) • below 200-dma (-12.4%) • sector strength 38/100 • regime cautious (partial deploy) • 9 similar past recs: 56% positive, median +0.3%</t>
+          <t>Low-risk FMCG holding (low vol) • below 200-dma (-12.0%) • sector strength 38/100 • regime cautious (partial deploy) • 9 similar past recs: 56% positive, median +0.3%</t>
         </is>
       </c>
     </row>
@@ -2107,7 +2107,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Risk/Vol +17 · Historical +15 · Sector +9 · Trend/Tech +6 · Regime +5 = 52</t>
+          <t>Risk/Vol +22 · Historical +15 · Trend/Tech +9 · Regime +4 · Sector +2 = 52</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -2117,40 +2117,40 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Regime</t>
+          <t>Sector</t>
         </is>
       </c>
       <c r="F7" t="n">
         <v>50</v>
       </c>
       <c r="G7" t="n">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="H7" t="n">
-        <v>69</v>
+        <v>88</v>
       </c>
       <c r="I7" t="n">
-        <v>88</v>
+        <v>25</v>
       </c>
       <c r="J7" t="n">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>TATASTEEL</t>
+          <t>TATAPOWER</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Metal</t>
+          <t>Power</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>166.5</v>
+        <v>346.8</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>162 - 171</t>
+          <t>339 - 355</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -2168,11 +2168,11 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-14.3%)</t>
+          <t>Below 200-DMA (-9.6%)</t>
         </is>
       </c>
       <c r="S7" t="n">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -2181,21 +2181,21 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>2026-11-22</t>
+          <t>2026-11-25</t>
         </is>
       </c>
       <c r="V7" t="n">
-        <v>16315</v>
+        <v>15953</v>
       </c>
       <c r="W7" t="n">
-        <v>98</v>
+        <v>46</v>
       </c>
       <c r="X7" t="n">
-        <v>9.1</v>
+        <v>11.1</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Metal name under the sector cap</t>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Power name under the sector cap</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -2205,12 +2205,12 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — TATASTEEL: 52; COALINDIA: 57, HINDZINC: 46, SAIL: 39. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — TATAPOWER: 52; NHPC: 44, ADANIPOWER: 31, NLCINDIA: 27</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>Low-risk Metal holding (low vol) • below 200-dma (-14.3%) • sector strength 88/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
+          <t>Low-risk Power holding (low vol) • below 200-dma (-9.6%) • outperforming Nifty • sector strength 25/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
         </is>
       </c>
     </row>
@@ -2221,11 +2221,11 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Risk/Vol +22 · Historical +15 · Trend/Tech +7 · Regime +5 · Sector +2 = 51</t>
+          <t>Risk/Vol +17 · Historical +15 · Sector +9 · Trend/Tech +7 · Regime +4 = 52</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -2235,40 +2235,40 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Sector</t>
+          <t>Regime</t>
         </is>
       </c>
       <c r="F8" t="n">
         <v>50</v>
       </c>
       <c r="G8" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H8" t="n">
+        <v>69</v>
+      </c>
+      <c r="I8" t="n">
         <v>88</v>
       </c>
-      <c r="I8" t="n">
-        <v>25</v>
-      </c>
       <c r="J8" t="n">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>TATAPOWER</t>
+          <t>TATASTEEL</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Power</t>
+          <t>Metal</t>
         </is>
       </c>
       <c r="M8" t="n">
-        <v>343.5</v>
+        <v>168.8</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>335 - 352</t>
+          <t>164 - 173</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -2286,11 +2286,11 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-10.5%)</t>
+          <t>Below 200-DMA (-13.0%)</t>
         </is>
       </c>
       <c r="S8" t="n">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -2299,21 +2299,21 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>2026-11-22</t>
+          <t>2026-11-25</t>
         </is>
       </c>
       <c r="V8" t="n">
-        <v>18546</v>
+        <v>11481</v>
       </c>
       <c r="W8" t="n">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="X8" t="n">
-        <v>10.3</v>
+        <v>8</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Power name under the sector cap</t>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Metal name under the sector cap</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
@@ -2323,12 +2323,12 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — TATAPOWER: 51; NHPC: 45, ADANIPOWER: 31, NLCINDIA: 28</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — TATASTEEL: 52; COALINDIA: 57, HINDZINC: 45, SAIL: 38. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>Low-risk Power holding (low vol) • below 200-dma (-10.5%) • sector strength 25/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
+          <t>Low-risk Metal holding (low vol) • below 200-dma (-13.0%) • sector strength 88/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
         </is>
       </c>
     </row>
@@ -2343,7 +2343,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Risk/Vol +18 · Historical +15 · Trend/Tech +5 · Regime +5 · Sector +5 = 48</t>
+          <t>Risk/Vol +18 · Historical +15 · Trend/Tech +6 · Sector +5 · Regime +4 = 48</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2353,14 +2353,14 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Sector</t>
+          <t>Regime</t>
         </is>
       </c>
       <c r="F9" t="n">
         <v>50</v>
       </c>
       <c r="G9" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="H9" t="n">
         <v>73</v>
@@ -2369,7 +2369,7 @@
         <v>50</v>
       </c>
       <c r="J9" t="n">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -2382,11 +2382,11 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>357.6</v>
+        <v>362.6</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>348 - 367</t>
+          <t>353 - 372</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -2404,11 +2404,11 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-14.2%)</t>
+          <t>Below 200-DMA (-12.9%)</t>
         </is>
       </c>
       <c r="S9" t="n">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -2417,17 +2417,17 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>2026-11-22</t>
+          <t>2026-11-25</t>
         </is>
       </c>
       <c r="V9" t="n">
-        <v>15734</v>
+        <v>11603</v>
       </c>
       <c r="W9" t="n">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="X9" t="n">
-        <v>8.800000000000001</v>
+        <v>8.1</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -2446,125 +2446,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>Low-risk Industrials holding (low vol) • below 200-dma (-14.2%) • sector strength 50/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>WATCH</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>44</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Risk/Vol +16 · Historical +15 · Regime +5 · Trend/Tech +4 · Sector +4 = 44</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Risk/Vol</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Sector</t>
-        </is>
-      </c>
-      <c r="F10" t="n">
-        <v>50</v>
-      </c>
-      <c r="G10" t="n">
-        <v>22</v>
-      </c>
-      <c r="H10" t="n">
-        <v>62</v>
-      </c>
-      <c r="I10" t="n">
-        <v>38</v>
-      </c>
-      <c r="J10" t="n">
-        <v>36</v>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>DABUR</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>FMCG</t>
-        </is>
-      </c>
-      <c r="M10" t="n">
-        <v>359.7</v>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>350 - 370</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Q10" t="n">
-        <v>60</v>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>Below 200-DMA (-18.4%)</t>
-        </is>
-      </c>
-      <c r="S10" t="n">
-        <v>35</v>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>2 months (2M)</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>2026-11-22</t>
-        </is>
-      </c>
-      <c r="V10" t="n">
-        <v>23021</v>
-      </c>
-      <c r="W10" t="n">
-        <v>64</v>
-      </c>
-      <c r="X10" t="n">
-        <v>12.9</v>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility FMCG name under the sector cap</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>Fundamentals · Earnings · News · Flows</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — DABUR: 44; ITC: 53. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>Low-risk FMCG holding (medium vol) • below 200-dma (-18.4%) • sector strength 38/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
+          <t>Low-risk Industrials holding (low vol) • below 200-dma (-12.9%) • sector strength 50/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
         </is>
       </c>
     </row>
@@ -11511,9 +11393,15 @@
       <c r="L106" t="n">
         <v>-1.05</v>
       </c>
-      <c r="M106" t="inlineStr"/>
-      <c r="N106" t="inlineStr"/>
-      <c r="O106" t="inlineStr"/>
+      <c r="M106" t="n">
+        <v>1</v>
+      </c>
+      <c r="N106" t="n">
+        <v>-17.4</v>
+      </c>
+      <c r="O106" t="n">
+        <v>-1645</v>
+      </c>
       <c r="P106" t="n">
         <v>-51.4</v>
       </c>
@@ -25482,9 +25370,15 @@
       <c r="L279" t="n">
         <v>0.27</v>
       </c>
-      <c r="M279" t="inlineStr"/>
-      <c r="N279" t="inlineStr"/>
-      <c r="O279" t="inlineStr"/>
+      <c r="M279" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="N279" t="n">
+        <v>0</v>
+      </c>
+      <c r="O279" t="n">
+        <v>10</v>
+      </c>
       <c r="P279" t="n">
         <v>10.2</v>
       </c>
@@ -27259,7 +27153,7 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>-12.6</v>
+        <v>-11.8</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -27334,12 +27228,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>9.7%</t>
+          <t>8.5%</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -27354,7 +27248,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>7.7%</t>
+          <t>6.3%</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -27364,16 +27258,16 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>6.6%</t>
+          <t>4.6%</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -27384,7 +27278,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>5.1%</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -27399,7 +27293,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -27414,7 +27308,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -27429,7 +27323,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>64.0%</t>
+          <t>71.2%</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -27449,7 +27343,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>9 stocks / 6 sectors</t>
+          <t>8 stocks / 6 sectors</t>
         </is>
       </c>
     </row>

--- a/reports/AEGIS_LATEST.xlsx
+++ b/reports/AEGIS_LATEST.xlsx
@@ -560,7 +560,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>DABUR</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -571,7 +571,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">

--- a/reports/AEGIS_LATEST.xlsx
+++ b/reports/AEGIS_LATEST.xlsx
@@ -444,7 +444,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
     </row>
@@ -512,7 +512,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-11-25</t>
+          <t>2026-11-26</t>
         </is>
       </c>
     </row>
@@ -524,7 +524,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ICICIBANK (70)</t>
+          <t>ICICIBANK (69)</t>
         </is>
       </c>
     </row>
@@ -536,7 +536,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>BEL (48)</t>
+          <t>ITC (50)</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-26  /  2026-10-26</t>
+          <t>2026-10-27  /  2026-10-27</t>
         </is>
       </c>
     </row>
@@ -760,7 +760,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-11-25</t>
+          <t>2026-11-26</t>
         </is>
       </c>
     </row>
@@ -908,7 +908,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>14.6%</t>
+          <t>14.7%</t>
         </is>
       </c>
     </row>
@@ -1322,7 +1322,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>-5.8%</t>
+          <t>-5.9%</t>
         </is>
       </c>
     </row>
@@ -1513,11 +1513,11 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Risk/Vol +24 · Historical +20 · Trend/Tech +16 · Sector +6 · Regime +4 = 70</t>
+          <t>Risk/Vol +24 · Historical +20 · Trend/Tech +16 · Sector +5 · Regime +4 = 69</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -1534,13 +1534,13 @@
         <v>66</v>
       </c>
       <c r="G2" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H2" t="n">
         <v>96</v>
       </c>
       <c r="I2" t="n">
-        <v>62</v>
+        <v>50</v>
       </c>
       <c r="J2" t="n">
         <v>29</v>
@@ -1556,11 +1556,11 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>1389.6</v>
+        <v>1397.2</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>1362 - 1417</t>
+          <t>1370 - 1425</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -1574,15 +1574,15 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>Above 200-DMA (+2.6%)</t>
+          <t>Above 200-DMA (+3.1%)</t>
         </is>
       </c>
       <c r="S2" t="n">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -1591,17 +1591,17 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>2026-11-25</t>
+          <t>2026-11-26</t>
         </is>
       </c>
       <c r="V2" t="n">
-        <v>27792</v>
+        <v>20958</v>
       </c>
       <c r="W2" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="X2" t="n">
-        <v>19.7</v>
+        <v>15.3</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
@@ -1615,12 +1615,12 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ICICIBANK: 70; SBIN: 59, PNB: 56, HDFCBANK: 51</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ICICIBANK: 69; SBIN: 59, PNB: 55, HDFCBANK: 50</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>Low-risk Financials holding (low vol) • above 200-dma (+2.6%) • outperforming Nifty • sector strength 62/100 • regime cautious (partial deploy) • 8 similar past recs: 75% positive, median +5.3%</t>
+          <t>Low-risk Financials holding (low vol) • above 200-dma (+3.1%) • outperforming Nifty • sector strength 50/100 • regime cautious (partial deploy) • 8 similar past recs: 75% positive, median +5.3%</t>
         </is>
       </c>
     </row>
@@ -1635,12 +1635,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Historical +20 · Risk/Vol +20 · Trend/Tech +9 · Sector +6 · Regime +4 = 59</t>
+          <t>Risk/Vol +21 · Historical +20 · Trend/Tech +9 · Sector +5 · Regime +4 = 59</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Historical</t>
+          <t>Risk/Vol</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1655,10 +1655,10 @@
         <v>46</v>
       </c>
       <c r="H3" t="n">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="I3" t="n">
-        <v>62</v>
+        <v>50</v>
       </c>
       <c r="J3" t="n">
         <v>29</v>
@@ -1674,11 +1674,11 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>953.5</v>
+        <v>964</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>929 - 978</t>
+          <t>940 - 988</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -1696,11 +1696,11 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-8.3%)</t>
+          <t>Below 200-DMA (-7.3%)</t>
         </is>
       </c>
       <c r="S3" t="n">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -1709,21 +1709,21 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>2026-11-25</t>
+          <t>2026-11-26</t>
         </is>
       </c>
       <c r="V3" t="n">
-        <v>13348</v>
+        <v>15424</v>
       </c>
       <c r="W3" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="X3" t="n">
-        <v>9.699999999999999</v>
+        <v>10.9</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>Historical + Risk/Vol strongest; chosen as a lowest-volatility Financials name under the sector cap</t>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Financials name under the sector cap</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -1733,12 +1733,12 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — SBIN: 59; ICICIBANK: 70, PNB: 56, HDFCBANK: 51. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — SBIN: 59; ICICIBANK: 69, PNB: 55, HDFCBANK: 50. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>Low-risk Financials holding (low vol) • below 200-dma (-8.3%) • outperforming Nifty • sector strength 62/100 • regime cautious (partial deploy) • 2 similar past recs: 100% positive, median +8.9%</t>
+          <t>Low-risk Financials holding (low vol) • below 200-dma (-7.3%) • outperforming Nifty • sector strength 50/100 • regime cautious (partial deploy) • 2 similar past recs: 100% positive, median +8.9%</t>
         </is>
       </c>
     </row>
@@ -1753,7 +1753,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Risk/Vol +21 · Historical +15 · Sector +9 · Trend/Tech +8 · Regime +4 = 57</t>
+          <t>Risk/Vol +19 · Historical +15 · Trend/Tech +10 · Sector +9 · Regime +4 = 57</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1770,10 +1770,10 @@
         <v>51</v>
       </c>
       <c r="G4" t="n">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="H4" t="n">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="I4" t="n">
         <v>88</v>
@@ -1792,11 +1792,11 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>403.4</v>
+        <v>404</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>393 - 414</t>
+          <t>394 - 414</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -1814,11 +1814,11 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-7.1%)</t>
+          <t>Below 200-DMA (-6.9%)</t>
         </is>
       </c>
       <c r="S4" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1827,17 +1827,17 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>2026-11-25</t>
+          <t>2026-11-26</t>
         </is>
       </c>
       <c r="V4" t="n">
-        <v>19764</v>
+        <v>17776</v>
       </c>
       <c r="W4" t="n">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="X4" t="n">
-        <v>13.8</v>
+        <v>12.5</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -1851,12 +1851,12 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — COALINDIA: 57; TATASTEEL: 52, HINDZINC: 45, SAIL: 38</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — COALINDIA: 57; TATASTEEL: 52, HINDZINC: 45, SAIL: 40</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>Low-risk Metal holding (low vol) • below 200-dma (-7.1%) • outperforming Nifty • sector strength 88/100 • regime cautious (partial deploy) • 3 similar past recs: 67% positive, median +0.8%</t>
+          <t>Low-risk Metal holding (low vol) • below 200-dma (-6.9%) • outperforming Nifty • sector strength 88/100 • regime cautious (partial deploy) • 3 similar past recs: 67% positive, median +0.8%</t>
         </is>
       </c>
     </row>
@@ -1867,11 +1867,11 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Risk/Vol +19 · Historical +16 · Trend/Tech +10 · Sector +8 · Regime +4 = 57</t>
+          <t>Risk/Vol +20 · Historical +16 · Trend/Tech +9 · Sector +6 · Regime +4 = 55</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1888,13 +1888,13 @@
         <v>53</v>
       </c>
       <c r="G5" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="H5" t="n">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="I5" t="n">
-        <v>75</v>
+        <v>62</v>
       </c>
       <c r="J5" t="n">
         <v>29</v>
@@ -1910,11 +1910,11 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>228.6</v>
+        <v>227.4</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>223 - 235</t>
+          <t>222 - 233</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -1928,15 +1928,15 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-10.6%)</t>
+          <t>Below 200-DMA (-11.0%)</t>
         </is>
       </c>
       <c r="S5" t="n">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1945,17 +1945,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>2026-11-25</t>
+          <t>2026-11-26</t>
         </is>
       </c>
       <c r="V5" t="n">
-        <v>19434</v>
+        <v>18190</v>
       </c>
       <c r="W5" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="X5" t="n">
-        <v>13.5</v>
+        <v>12.7</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -1969,12 +1969,12 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ONGC: 57; IOC: 47</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ONGC: 55; IOC: 49</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>Low-risk Energy holding (low vol) • below 200-dma (-10.6%) • outperforming Nifty • sector strength 75/100 • regime cautious (partial deploy) • 2 similar past recs: 50% positive, median +9.0%</t>
+          <t>Low-risk Energy holding (low vol) • below 200-dma (-11.0%) • outperforming Nifty • sector strength 62/100 • regime cautious (partial deploy) • 2 similar past recs: 50% positive, median +9.0%</t>
         </is>
       </c>
     </row>
@@ -1989,7 +1989,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Risk/Vol +23 · Historical +13 · Trend/Tech +8 · Regime +4 · Sector +4 = 52</t>
+          <t>Risk/Vol +17 · Historical +15 · Sector +9 · Trend/Tech +7 · Regime +4 = 52</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1999,62 +1999,62 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Sector</t>
+          <t>Regime</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="G6" t="n">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="H6" t="n">
-        <v>92</v>
+        <v>69</v>
       </c>
       <c r="I6" t="n">
-        <v>38</v>
+        <v>88</v>
       </c>
       <c r="J6" t="n">
         <v>29</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>ITC</t>
+          <t>TATASTEEL</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>Metal</t>
         </is>
       </c>
       <c r="M6" t="n">
-        <v>257.7</v>
+        <v>172</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>252 - 264</t>
+          <t>167 - 177</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-4% to +3%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>56%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-12.0%)</t>
+          <t>Below 200-DMA (-11.4%)</t>
         </is>
       </c>
       <c r="S6" t="n">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -2063,21 +2063,21 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>2026-11-25</t>
+          <t>2026-11-26</t>
         </is>
       </c>
       <c r="V6" t="n">
-        <v>22935</v>
+        <v>13418</v>
       </c>
       <c r="W6" t="n">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="X6" t="n">
-        <v>16</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility FMCG name under the sector cap</t>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Metal name under the sector cap</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -2087,12 +2087,12 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ITC: 52; DABUR: 43</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — TATASTEEL: 52; COALINDIA: 57, HINDZINC: 45, SAIL: 40. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>Low-risk FMCG holding (low vol) • below 200-dma (-12.0%) • sector strength 38/100 • regime cautious (partial deploy) • 9 similar past recs: 56% positive, median +0.3%</t>
+          <t>Low-risk Metal holding (low vol) • below 200-dma (-11.4%) • outperforming Nifty • sector strength 88/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
         </is>
       </c>
     </row>
@@ -2103,11 +2103,11 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Risk/Vol +22 · Historical +15 · Trend/Tech +9 · Regime +4 · Sector +2 = 52</t>
+          <t>Risk/Vol +22 · Historical +15 · Trend/Tech +6 · Regime +4 · Sector +4 = 51</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -2124,13 +2124,13 @@
         <v>50</v>
       </c>
       <c r="G7" t="n">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="H7" t="n">
         <v>88</v>
       </c>
       <c r="I7" t="n">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="J7" t="n">
         <v>29</v>
@@ -2146,11 +2146,11 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>346.8</v>
+        <v>340.5</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>339 - 355</t>
+          <t>332 - 349</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -2168,11 +2168,11 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-9.6%)</t>
+          <t>Below 200-DMA (-11.2%)</t>
         </is>
       </c>
       <c r="S7" t="n">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -2181,17 +2181,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>2026-11-25</t>
+          <t>2026-11-26</t>
         </is>
       </c>
       <c r="V7" t="n">
-        <v>15953</v>
+        <v>21111</v>
       </c>
       <c r="W7" t="n">
-        <v>46</v>
+        <v>62</v>
       </c>
       <c r="X7" t="n">
-        <v>11.1</v>
+        <v>14.8</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -2205,12 +2205,12 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — TATAPOWER: 52; NHPC: 44, ADANIPOWER: 31, NLCINDIA: 27</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — TATAPOWER: 51; NHPC: 44, ADANIPOWER: 34, NLCINDIA: 27</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>Low-risk Power holding (low vol) • below 200-dma (-9.6%) • outperforming Nifty • sector strength 25/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
+          <t>Low-risk Power holding (low vol) • below 200-dma (-11.2%) • sector strength 38/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
         </is>
       </c>
     </row>
@@ -2221,11 +2221,11 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Risk/Vol +17 · Historical +15 · Sector +9 · Trend/Tech +7 · Regime +4 = 52</t>
+          <t>Risk/Vol +23 · Historical +13 · Trend/Tech +8 · Regime +4 · Sector +2 = 50</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -2235,62 +2235,62 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Regime</t>
+          <t>Sector</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="G8" t="n">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="H8" t="n">
-        <v>69</v>
+        <v>92</v>
       </c>
       <c r="I8" t="n">
-        <v>88</v>
+        <v>25</v>
       </c>
       <c r="J8" t="n">
         <v>29</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>TATASTEEL</t>
+          <t>ITC</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Metal</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="M8" t="n">
-        <v>168.8</v>
+        <v>259.5</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>164 - 173</t>
+          <t>253 - 266</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-4% to +3%</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>56%</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-13.0%)</t>
+          <t>Below 200-DMA (-11.3%)</t>
         </is>
       </c>
       <c r="S8" t="n">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -2299,21 +2299,21 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>2026-11-25</t>
+          <t>2026-11-26</t>
         </is>
       </c>
       <c r="V8" t="n">
-        <v>11481</v>
+        <v>21534</v>
       </c>
       <c r="W8" t="n">
-        <v>68</v>
+        <v>83</v>
       </c>
       <c r="X8" t="n">
-        <v>8</v>
+        <v>15.1</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Metal name under the sector cap</t>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility FMCG name under the sector cap</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
@@ -2323,12 +2323,12 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — TATASTEEL: 52; COALINDIA: 57, HINDZINC: 45, SAIL: 38. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ITC: 50; DABUR: 41</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>Low-risk Metal holding (low vol) • below 200-dma (-13.0%) • sector strength 88/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
+          <t>Low-risk FMCG holding (low vol) • below 200-dma (-11.3%) • sector strength 25/100 • regime cautious (partial deploy) • 9 similar past recs: 56% positive, median +0.3%</t>
         </is>
       </c>
     </row>
@@ -2339,11 +2339,11 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Risk/Vol +18 · Historical +15 · Trend/Tech +6 · Sector +5 · Regime +4 = 48</t>
+          <t>Risk/Vol +16 · Historical +15 · Sector +8 · Trend/Tech +7 · Regime +4 = 50</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2360,13 +2360,13 @@
         <v>50</v>
       </c>
       <c r="G9" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="H9" t="n">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="I9" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="J9" t="n">
         <v>29</v>
@@ -2382,11 +2382,11 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>362.6</v>
+        <v>370</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>353 - 372</t>
+          <t>360 - 380</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -2404,11 +2404,11 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-12.9%)</t>
+          <t>Below 200-DMA (-11.1%)</t>
         </is>
       </c>
       <c r="S9" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -2417,17 +2417,17 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>2026-11-25</t>
+          <t>2026-11-26</t>
         </is>
       </c>
       <c r="V9" t="n">
-        <v>11603</v>
+        <v>13320</v>
       </c>
       <c r="W9" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="X9" t="n">
-        <v>8.1</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -2446,7 +2446,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>Low-risk Industrials holding (low vol) • below 200-dma (-12.9%) • sector strength 50/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
+          <t>Low-risk Industrials holding (medium vol) • below 200-dma (-11.1%) • outperforming Nifty • sector strength 75/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
         </is>
       </c>
     </row>
@@ -4297,9 +4297,15 @@
       <c r="L18" t="n">
         <v>0.41</v>
       </c>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
-      <c r="O18" t="inlineStr"/>
+      <c r="M18" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="N18" t="n">
+        <v>-3.2</v>
+      </c>
+      <c r="O18" t="n">
+        <v>61</v>
+      </c>
       <c r="P18" t="n">
         <v>41.1</v>
       </c>
@@ -7845,9 +7851,15 @@
       <c r="L62" t="n">
         <v>0.92</v>
       </c>
-      <c r="M62" t="inlineStr"/>
-      <c r="N62" t="inlineStr"/>
-      <c r="O62" t="inlineStr"/>
+      <c r="M62" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="N62" t="n">
+        <v>0</v>
+      </c>
+      <c r="O62" t="n">
+        <v>93</v>
+      </c>
       <c r="P62" t="n">
         <v>112</v>
       </c>
@@ -9459,9 +9471,15 @@
       <c r="L82" t="n">
         <v>0.4</v>
       </c>
-      <c r="M82" t="inlineStr"/>
-      <c r="N82" t="inlineStr"/>
-      <c r="O82" t="inlineStr"/>
+      <c r="M82" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="N82" t="n">
+        <v>-5.4</v>
+      </c>
+      <c r="O82" t="n">
+        <v>21</v>
+      </c>
       <c r="P82" t="n">
         <v>23.2</v>
       </c>
@@ -11393,15 +11411,9 @@
       <c r="L106" t="n">
         <v>-1.05</v>
       </c>
-      <c r="M106" t="n">
-        <v>1</v>
-      </c>
-      <c r="N106" t="n">
-        <v>-17.4</v>
-      </c>
-      <c r="O106" t="n">
-        <v>-1645</v>
-      </c>
+      <c r="M106" t="inlineStr"/>
+      <c r="N106" t="inlineStr"/>
+      <c r="O106" t="inlineStr"/>
       <c r="P106" t="n">
         <v>-51.4</v>
       </c>
@@ -25370,15 +25382,9 @@
       <c r="L279" t="n">
         <v>0.27</v>
       </c>
-      <c r="M279" t="n">
-        <v>23.5</v>
-      </c>
-      <c r="N279" t="n">
-        <v>0</v>
-      </c>
-      <c r="O279" t="n">
-        <v>10</v>
-      </c>
+      <c r="M279" t="inlineStr"/>
+      <c r="N279" t="inlineStr"/>
+      <c r="O279" t="inlineStr"/>
       <c r="P279" t="n">
         <v>10.2</v>
       </c>
@@ -26439,7 +26445,7 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>-10.4</v>
+        <v>-10.7</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -26565,7 +26571,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>-4.6</v>
+        <v>-4.5</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -26607,7 +26613,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>-8.6</v>
+        <v>-9.300000000000001</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -27153,7 +27159,7 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>-11.8</v>
+        <v>-12.6</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -27233,7 +27239,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>8.5%</t>
+          <t>7.6%</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -27263,7 +27269,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>4.6%</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -27273,12 +27279,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Power</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -27288,12 +27294,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Power</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>3.7%</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -27308,7 +27314,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>2.7%</t>
         </is>
       </c>
       <c r="C7" t="n">

--- a/reports/AEGIS_LATEST.xlsx
+++ b/reports/AEGIS_LATEST.xlsx
@@ -444,7 +444,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
@@ -489,7 +489,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7">
@@ -512,7 +512,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-11-26</t>
+          <t>2026-11-27</t>
         </is>
       </c>
     </row>
@@ -524,7 +524,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ICICIBANK (69)</t>
+          <t>ICICIBANK (70)</t>
         </is>
       </c>
     </row>
@@ -536,7 +536,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ITC (50)</t>
+          <t>ITC (48)</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-27  /  2026-10-27</t>
+          <t>2026-10-28  /  2026-10-28</t>
         </is>
       </c>
     </row>
@@ -760,7 +760,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-11-26</t>
+          <t>2026-11-27</t>
         </is>
       </c>
     </row>
@@ -908,7 +908,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>14.7%</t>
+          <t>14.6%</t>
         </is>
       </c>
     </row>
@@ -1322,7 +1322,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>-5.9%</t>
+          <t>-5.8%</t>
         </is>
       </c>
     </row>
@@ -1513,11 +1513,11 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Risk/Vol +24 · Historical +20 · Trend/Tech +16 · Sector +5 · Regime +4 = 69</t>
+          <t>Risk/Vol +24 · Historical +20 · Trend/Tech +17 · Sector +5 · Regime +4 = 70</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -1534,7 +1534,7 @@
         <v>66</v>
       </c>
       <c r="G2" t="n">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H2" t="n">
         <v>96</v>
@@ -1556,11 +1556,11 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>1397.2</v>
+        <v>1370.9</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>1370 - 1425</t>
+          <t>1344 - 1398</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -1574,15 +1574,15 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>Above 200-DMA (+3.1%)</t>
+          <t>Above 200-DMA (+1.2%)</t>
         </is>
       </c>
       <c r="S2" t="n">
-        <v>72</v>
+        <v>57</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -1591,17 +1591,17 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>2026-11-26</t>
+          <t>2026-11-27</t>
         </is>
       </c>
       <c r="V2" t="n">
-        <v>20958</v>
+        <v>20564</v>
       </c>
       <c r="W2" t="n">
         <v>15</v>
       </c>
       <c r="X2" t="n">
-        <v>15.3</v>
+        <v>15.2</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
@@ -1615,12 +1615,12 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ICICIBANK: 69; SBIN: 59, PNB: 55, HDFCBANK: 50</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ICICIBANK: 70; SBIN: 59, PNB: 55, HDFCBANK: 49</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>Low-risk Financials holding (low vol) • above 200-dma (+3.1%) • outperforming Nifty • sector strength 50/100 • regime cautious (partial deploy) • 8 similar past recs: 75% positive, median +5.3%</t>
+          <t>Low-risk Financials holding (low vol) • above 200-dma (+1.2%) • outperforming Nifty • sector strength 50/100 • regime cautious (partial deploy) • 8 similar past recs: 75% positive, median +5.3%</t>
         </is>
       </c>
     </row>
@@ -1652,7 +1652,7 @@
         <v>65</v>
       </c>
       <c r="G3" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H3" t="n">
         <v>85</v>
@@ -1674,11 +1674,11 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>964</v>
+        <v>953</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>940 - 988</t>
+          <t>929 - 977</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -1696,11 +1696,11 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-7.3%)</t>
+          <t>Below 200-DMA (-8.3%)</t>
         </is>
       </c>
       <c r="S3" t="n">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -1709,17 +1709,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>2026-11-26</t>
+          <t>2026-11-27</t>
         </is>
       </c>
       <c r="V3" t="n">
-        <v>15424</v>
+        <v>15248</v>
       </c>
       <c r="W3" t="n">
         <v>16</v>
       </c>
       <c r="X3" t="n">
-        <v>10.9</v>
+        <v>11</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
@@ -1733,12 +1733,12 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — SBIN: 59; ICICIBANK: 69, PNB: 55, HDFCBANK: 50. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — SBIN: 59; ICICIBANK: 70, PNB: 55, HDFCBANK: 49. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>Low-risk Financials holding (low vol) • below 200-dma (-7.3%) • outperforming Nifty • sector strength 50/100 • regime cautious (partial deploy) • 2 similar past recs: 100% positive, median +8.9%</t>
+          <t>Low-risk Financials holding (low vol) • below 200-dma (-8.3%) • outperforming Nifty • sector strength 50/100 • regime cautious (partial deploy) • 2 similar past recs: 100% positive, median +8.9%</t>
         </is>
       </c>
     </row>
@@ -1749,11 +1749,11 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Risk/Vol +19 · Historical +15 · Trend/Tech +10 · Sector +9 · Regime +4 = 57</t>
+          <t>Risk/Vol +20 · Historical +16 · Trend/Tech +9 · Sector +6 · Regime +4 = 55</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1767,36 +1767,36 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="G4" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="H4" t="n">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="I4" t="n">
-        <v>88</v>
+        <v>62</v>
       </c>
       <c r="J4" t="n">
         <v>29</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>COALINDIA</t>
+          <t>ONGC</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Metal</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>404</v>
+        <v>224.4</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>394 - 414</t>
+          <t>219 - 230</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -1810,15 +1810,15 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-6.9%)</t>
+          <t>Below 200-DMA (-12.2%)</t>
         </is>
       </c>
       <c r="S4" t="n">
-        <v>40</v>
+        <v>59</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1827,21 +1827,21 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>2026-11-26</t>
+          <t>2026-11-27</t>
         </is>
       </c>
       <c r="V4" t="n">
-        <v>17776</v>
+        <v>18176</v>
       </c>
       <c r="W4" t="n">
-        <v>44</v>
+        <v>81</v>
       </c>
       <c r="X4" t="n">
-        <v>12.5</v>
+        <v>12.7</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Metal name under the sector cap</t>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Energy name under the sector cap</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1851,12 +1851,12 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — COALINDIA: 57; TATASTEEL: 52, HINDZINC: 45, SAIL: 40</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ONGC: 55; IOC: 49</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>Low-risk Metal holding (low vol) • below 200-dma (-6.9%) • outperforming Nifty • sector strength 88/100 • regime cautious (partial deploy) • 3 similar past recs: 67% positive, median +0.8%</t>
+          <t>Low-risk Energy holding (low vol) • below 200-dma (-12.2%) • outperforming Nifty • sector strength 62/100 • regime cautious (partial deploy) • 2 similar past recs: 50% positive, median +9.0%</t>
         </is>
       </c>
     </row>
@@ -1871,7 +1871,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Risk/Vol +20 · Historical +16 · Trend/Tech +9 · Sector +6 · Regime +4 = 55</t>
+          <t>Risk/Vol +19 · Historical +15 · Sector +9 · Trend/Tech +8 · Regime +4 = 55</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1885,36 +1885,36 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="G5" t="n">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="H5" t="n">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="I5" t="n">
-        <v>62</v>
+        <v>88</v>
       </c>
       <c r="J5" t="n">
         <v>29</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>ONGC</t>
+          <t>COALINDIA</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Metal</t>
         </is>
       </c>
       <c r="M5" t="n">
-        <v>227.4</v>
+        <v>395.5</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>222 - 233</t>
+          <t>385 - 406</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -1932,11 +1932,11 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-11.0%)</t>
+          <t>Below 200-DMA (-8.8%)</t>
         </is>
       </c>
       <c r="S5" t="n">
-        <v>66</v>
+        <v>37</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1945,21 +1945,21 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>2026-11-26</t>
+          <t>2026-11-27</t>
         </is>
       </c>
       <c r="V5" t="n">
-        <v>18190</v>
+        <v>17798</v>
       </c>
       <c r="W5" t="n">
-        <v>80</v>
+        <v>45</v>
       </c>
       <c r="X5" t="n">
-        <v>12.7</v>
+        <v>12.4</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Energy name under the sector cap</t>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Metal name under the sector cap</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1969,27 +1969,27 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ONGC: 55; IOC: 49</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — COALINDIA: 55; TATASTEEL: 51, HINDZINC: 45, SAIL: 39</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>Low-risk Energy holding (low vol) • below 200-dma (-11.0%) • outperforming Nifty • sector strength 62/100 • regime cautious (partial deploy) • 2 similar past recs: 50% positive, median +9.0%</t>
+          <t>Low-risk Metal holding (low vol) • below 200-dma (-8.8%) • outperforming Nifty • sector strength 88/100 • regime cautious (partial deploy) • 3 similar past recs: 67% positive, median +0.8%</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ACCUMULATE</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Risk/Vol +17 · Historical +15 · Sector +9 · Trend/Tech +7 · Regime +4 = 52</t>
+          <t>Risk/Vol +16 · Historical +15 · Trend/Tech +10 · Sector +10 · Regime +4 = 55</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -2006,33 +2006,33 @@
         <v>50</v>
       </c>
       <c r="G6" t="n">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="H6" t="n">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="I6" t="n">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="J6" t="n">
         <v>29</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>TATASTEEL</t>
+          <t>BEL</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Metal</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="M6" t="n">
-        <v>172</v>
+        <v>367.6</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>167 - 177</t>
+          <t>358 - 377</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -2046,15 +2046,15 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-11.4%)</t>
+          <t>Below 200-DMA (-11.6%)</t>
         </is>
       </c>
       <c r="S6" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -2063,21 +2063,21 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>2026-11-26</t>
+          <t>2026-11-27</t>
         </is>
       </c>
       <c r="V6" t="n">
-        <v>13418</v>
+        <v>13234</v>
       </c>
       <c r="W6" t="n">
-        <v>78</v>
+        <v>36</v>
       </c>
       <c r="X6" t="n">
         <v>9.300000000000001</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Metal name under the sector cap</t>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Industrials name under the sector cap</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -2087,12 +2087,12 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — TATASTEEL: 52; COALINDIA: 57, HINDZINC: 45, SAIL: 40. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>No same-sector peer in the universe.</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>Low-risk Metal holding (low vol) • below 200-dma (-11.4%) • outperforming Nifty • sector strength 88/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
+          <t>Low-risk Industrials holding (medium vol) • below 200-dma (-11.6%) • outperforming Nifty • sector strength 100/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
         </is>
       </c>
     </row>
@@ -2103,11 +2103,11 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Risk/Vol +22 · Historical +15 · Trend/Tech +6 · Regime +4 · Sector +4 = 51</t>
+          <t>Risk/Vol +22 · Historical +15 · Trend/Tech +8 · Regime +4 · Sector +4 = 53</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -2124,7 +2124,7 @@
         <v>50</v>
       </c>
       <c r="G7" t="n">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="H7" t="n">
         <v>88</v>
@@ -2146,11 +2146,11 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>340.5</v>
+        <v>338</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>332 - 349</t>
+          <t>330 - 346</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -2164,15 +2164,15 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-11.2%)</t>
+          <t>Below 200-DMA (-11.8%)</t>
         </is>
       </c>
       <c r="S7" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -2181,17 +2181,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>2026-11-26</t>
+          <t>2026-11-27</t>
         </is>
       </c>
       <c r="V7" t="n">
-        <v>21111</v>
+        <v>21294</v>
       </c>
       <c r="W7" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="X7" t="n">
-        <v>14.8</v>
+        <v>14.9</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -2205,12 +2205,12 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — TATAPOWER: 51; NHPC: 44, ADANIPOWER: 34, NLCINDIA: 27</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — TATAPOWER: 53; NHPC: 44, ADANIPOWER: 34, NLCINDIA: 28</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>Low-risk Power holding (low vol) • below 200-dma (-11.2%) • sector strength 38/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
+          <t>Low-risk Power holding (low vol) • below 200-dma (-11.8%) • sector strength 38/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
         </is>
       </c>
     </row>
@@ -2221,76 +2221,76 @@
         </is>
       </c>
       <c r="B8" t="n">
+        <v>51</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Risk/Vol +17 · Historical +15 · Sector +9 · Trend/Tech +6 · Regime +4 = 51</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Risk/Vol</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Regime</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
         <v>50</v>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Risk/Vol +23 · Historical +13 · Trend/Tech +8 · Regime +4 · Sector +2 = 50</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Risk/Vol</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Sector</t>
-        </is>
-      </c>
-      <c r="F8" t="n">
-        <v>44</v>
-      </c>
       <c r="G8" t="n">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="H8" t="n">
-        <v>92</v>
+        <v>69</v>
       </c>
       <c r="I8" t="n">
-        <v>25</v>
+        <v>88</v>
       </c>
       <c r="J8" t="n">
         <v>29</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>ITC</t>
+          <t>TATASTEEL</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>Metal</t>
         </is>
       </c>
       <c r="M8" t="n">
-        <v>259.5</v>
+        <v>169.3</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>253 - 266</t>
+          <t>165 - 174</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>-4% to +3%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>56%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-11.3%)</t>
+          <t>Below 200-DMA (-12.7%)</t>
         </is>
       </c>
       <c r="S8" t="n">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -2299,21 +2299,21 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>2026-11-26</t>
+          <t>2026-11-27</t>
         </is>
       </c>
       <c r="V8" t="n">
-        <v>21534</v>
+        <v>13376</v>
       </c>
       <c r="W8" t="n">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="X8" t="n">
-        <v>15.1</v>
+        <v>9.4</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility FMCG name under the sector cap</t>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Metal name under the sector cap</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
@@ -2323,12 +2323,12 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ITC: 50; DABUR: 41</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — TATASTEEL: 51; COALINDIA: 55, HINDZINC: 45, SAIL: 39. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>Low-risk FMCG holding (low vol) • below 200-dma (-11.3%) • sector strength 25/100 • regime cautious (partial deploy) • 9 similar past recs: 56% positive, median +0.3%</t>
+          <t>Low-risk Metal holding (low vol) • below 200-dma (-12.7%) • sector strength 88/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
         </is>
       </c>
     </row>
@@ -2339,11 +2339,11 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Risk/Vol +16 · Historical +15 · Sector +8 · Trend/Tech +7 · Regime +4 = 50</t>
+          <t>Risk/Vol +23 · Historical +13 · Trend/Tech +6 · Regime +4 · Sector +2 = 48</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2353,58 +2353,58 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Regime</t>
+          <t>Sector</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="G9" t="n">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="H9" t="n">
-        <v>65</v>
+        <v>92</v>
       </c>
       <c r="I9" t="n">
-        <v>75</v>
+        <v>25</v>
       </c>
       <c r="J9" t="n">
         <v>29</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>BEL</t>
+          <t>ITC</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="M9" t="n">
-        <v>370</v>
+        <v>254.7</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>360 - 380</t>
+          <t>249 - 261</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-4% to +3%</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>56%</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-11.1%)</t>
+          <t>Below 200-DMA (-12.8%)</t>
         </is>
       </c>
       <c r="S9" t="n">
@@ -2417,21 +2417,21 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>2026-11-26</t>
+          <t>2026-11-27</t>
         </is>
       </c>
       <c r="V9" t="n">
-        <v>13320</v>
+        <v>21649</v>
       </c>
       <c r="W9" t="n">
-        <v>36</v>
+        <v>85</v>
       </c>
       <c r="X9" t="n">
-        <v>9.300000000000001</v>
+        <v>15.1</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Industrials name under the sector cap</t>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility FMCG name under the sector cap</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
@@ -2441,12 +2441,12 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>No same-sector peer in the universe.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ITC: 48; DABUR: 41</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>Low-risk Industrials holding (medium vol) • below 200-dma (-11.1%) • outperforming Nifty • sector strength 75/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
+          <t>Low-risk FMCG holding (low vol) • below 200-dma (-12.8%) • sector strength 25/100 • regime cautious (partial deploy) • 9 similar past recs: 56% positive, median +0.3%</t>
         </is>
       </c>
     </row>
@@ -4297,15 +4297,9 @@
       <c r="L18" t="n">
         <v>0.41</v>
       </c>
-      <c r="M18" t="n">
-        <v>14.6</v>
-      </c>
-      <c r="N18" t="n">
-        <v>-3.2</v>
-      </c>
-      <c r="O18" t="n">
-        <v>61</v>
-      </c>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
       <c r="P18" t="n">
         <v>41.1</v>
       </c>
@@ -7851,15 +7845,9 @@
       <c r="L62" t="n">
         <v>0.92</v>
       </c>
-      <c r="M62" t="n">
-        <v>22.1</v>
-      </c>
-      <c r="N62" t="n">
-        <v>0</v>
-      </c>
-      <c r="O62" t="n">
-        <v>93</v>
-      </c>
+      <c r="M62" t="inlineStr"/>
+      <c r="N62" t="inlineStr"/>
+      <c r="O62" t="inlineStr"/>
       <c r="P62" t="n">
         <v>112</v>
       </c>
@@ -9471,15 +9459,9 @@
       <c r="L82" t="n">
         <v>0.4</v>
       </c>
-      <c r="M82" t="n">
-        <v>25.7</v>
-      </c>
-      <c r="N82" t="n">
-        <v>-5.4</v>
-      </c>
-      <c r="O82" t="n">
-        <v>21</v>
-      </c>
+      <c r="M82" t="inlineStr"/>
+      <c r="N82" t="inlineStr"/>
+      <c r="O82" t="inlineStr"/>
       <c r="P82" t="n">
         <v>23.2</v>
       </c>
@@ -11411,9 +11393,15 @@
       <c r="L106" t="n">
         <v>-1.05</v>
       </c>
-      <c r="M106" t="inlineStr"/>
-      <c r="N106" t="inlineStr"/>
-      <c r="O106" t="inlineStr"/>
+      <c r="M106" t="n">
+        <v>1</v>
+      </c>
+      <c r="N106" t="n">
+        <v>-17.4</v>
+      </c>
+      <c r="O106" t="n">
+        <v>-1645</v>
+      </c>
       <c r="P106" t="n">
         <v>-51.4</v>
       </c>
@@ -25382,9 +25370,15 @@
       <c r="L279" t="n">
         <v>0.27</v>
       </c>
-      <c r="M279" t="inlineStr"/>
-      <c r="N279" t="inlineStr"/>
-      <c r="O279" t="inlineStr"/>
+      <c r="M279" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="N279" t="n">
+        <v>0</v>
+      </c>
+      <c r="O279" t="n">
+        <v>10</v>
+      </c>
       <c r="P279" t="n">
         <v>10.2</v>
       </c>
@@ -26445,7 +26439,7 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>-10.7</v>
+        <v>-10.4</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -26571,7 +26565,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>-4.5</v>
+        <v>-4.6</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -26613,7 +26607,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>-9.300000000000001</v>
+        <v>-8.6</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -27159,7 +27153,7 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>-12.6</v>
+        <v>-11.8</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -27239,7 +27233,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>7.6%</t>
+          <t>7.5%</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -27269,7 +27263,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>4.4%</t>
         </is>
       </c>
       <c r="C4" t="n">

--- a/reports/AEGIS_LATEST.xlsx
+++ b/reports/AEGIS_LATEST.xlsx
@@ -444,7 +444,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -489,7 +489,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7">
@@ -512,7 +512,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-11-27</t>
+          <t>2026-11-28</t>
         </is>
       </c>
     </row>
@@ -524,7 +524,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ICICIBANK (70)</t>
+          <t>ICICIBANK (71)</t>
         </is>
       </c>
     </row>
@@ -536,7 +536,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ITC (48)</t>
+          <t>DABUR (48)</t>
         </is>
       </c>
     </row>
@@ -548,7 +548,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>DABUR</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>BEL</t>
         </is>
       </c>
     </row>
@@ -571,7 +571,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -688,7 +688,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-28  /  2026-10-28</t>
+          <t>2026-10-29  /  2026-10-29</t>
         </is>
       </c>
     </row>
@@ -760,7 +760,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-11-27</t>
+          <t>2026-11-28</t>
         </is>
       </c>
     </row>
@@ -908,7 +908,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>14.6%</t>
+          <t>14.7%</t>
         </is>
       </c>
     </row>
@@ -1513,11 +1513,11 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Risk/Vol +24 · Historical +20 · Trend/Tech +17 · Sector +5 · Regime +4 = 70</t>
+          <t>Risk/Vol +24 · Historical +20 · Trend/Tech +18 · Sector +5 · Regime +4 = 71</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -1534,7 +1534,7 @@
         <v>66</v>
       </c>
       <c r="G2" t="n">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="H2" t="n">
         <v>96</v>
@@ -1556,11 +1556,11 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>1370.9</v>
+        <v>1377</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>1344 - 1398</t>
+          <t>1350 - 1404</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -1578,7 +1578,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>Above 200-DMA (+1.2%)</t>
+          <t>Above 200-DMA (+1.7%)</t>
         </is>
       </c>
       <c r="S2" t="n">
@@ -1591,17 +1591,17 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>2026-11-27</t>
+          <t>2026-11-28</t>
         </is>
       </c>
       <c r="V2" t="n">
-        <v>20564</v>
+        <v>22032</v>
       </c>
       <c r="W2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="X2" t="n">
-        <v>15.2</v>
+        <v>15.5</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
@@ -1615,12 +1615,12 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ICICIBANK: 70; SBIN: 59, PNB: 55, HDFCBANK: 49</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ICICIBANK: 71; SBIN: 61, PNB: 55, HDFCBANK: 50</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>Low-risk Financials holding (low vol) • above 200-dma (+1.2%) • outperforming Nifty • sector strength 50/100 • regime cautious (partial deploy) • 8 similar past recs: 75% positive, median +5.3%</t>
+          <t>Low-risk Financials holding (low vol) • above 200-dma (+1.7%) • outperforming Nifty • sector strength 50/100 • regime cautious (partial deploy) • 8 similar past recs: 75% positive, median +5.3%</t>
         </is>
       </c>
     </row>
@@ -1631,11 +1631,11 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Risk/Vol +21 · Historical +20 · Trend/Tech +9 · Sector +5 · Regime +4 = 59</t>
+          <t>Risk/Vol +23 · Historical +20 · Trend/Tech +9 · Sector +5 · Regime +4 = 61</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -1652,10 +1652,10 @@
         <v>65</v>
       </c>
       <c r="G3" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H3" t="n">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="I3" t="n">
         <v>50</v>
@@ -1674,11 +1674,11 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>953</v>
+        <v>960.7</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>929 - 977</t>
+          <t>939 - 982</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -1696,11 +1696,11 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-8.3%)</t>
+          <t>Below 200-DMA (-7.5%)</t>
         </is>
       </c>
       <c r="S3" t="n">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -1709,17 +1709,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>2026-11-27</t>
+          <t>2026-11-28</t>
         </is>
       </c>
       <c r="V3" t="n">
-        <v>15248</v>
+        <v>19213</v>
       </c>
       <c r="W3" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="X3" t="n">
-        <v>11</v>
+        <v>13.5</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
@@ -1733,12 +1733,12 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — SBIN: 59; ICICIBANK: 70, PNB: 55, HDFCBANK: 49. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — SBIN: 61; ICICIBANK: 71, PNB: 55, HDFCBANK: 50. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>Low-risk Financials holding (low vol) • below 200-dma (-8.3%) • outperforming Nifty • sector strength 50/100 • regime cautious (partial deploy) • 2 similar past recs: 100% positive, median +8.9%</t>
+          <t>Low-risk Financials holding (low vol) • below 200-dma (-7.5%) • outperforming Nifty • sector strength 50/100 • regime cautious (partial deploy) • 2 similar past recs: 100% positive, median +8.9%</t>
         </is>
       </c>
     </row>
@@ -1749,11 +1749,11 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Risk/Vol +20 · Historical +16 · Trend/Tech +9 · Sector +6 · Regime +4 = 55</t>
+          <t>Risk/Vol +19 · Historical +15 · Trend/Tech +10 · Sector +9 · Regime +4 = 57</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1767,36 +1767,36 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="G4" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="H4" t="n">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="I4" t="n">
-        <v>62</v>
+        <v>88</v>
       </c>
       <c r="J4" t="n">
         <v>29</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>ONGC</t>
+          <t>COALINDIA</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Metal</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>224.4</v>
+        <v>396.2</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>219 - 230</t>
+          <t>386 - 406</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -1810,15 +1810,15 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-12.2%)</t>
+          <t>Below 200-DMA (-8.6%)</t>
         </is>
       </c>
       <c r="S4" t="n">
-        <v>59</v>
+        <v>42</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1827,21 +1827,21 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>2026-11-27</t>
+          <t>2026-11-28</t>
         </is>
       </c>
       <c r="V4" t="n">
-        <v>18176</v>
+        <v>17433</v>
       </c>
       <c r="W4" t="n">
-        <v>81</v>
+        <v>44</v>
       </c>
       <c r="X4" t="n">
-        <v>12.7</v>
+        <v>12.2</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Energy name under the sector cap</t>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Metal name under the sector cap</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1851,12 +1851,12 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ONGC: 55; IOC: 49</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — COALINDIA: 57; TATASTEEL: 52, HINDZINC: 46, SAIL: 38</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>Low-risk Energy holding (low vol) • below 200-dma (-12.2%) • outperforming Nifty • sector strength 62/100 • regime cautious (partial deploy) • 2 similar past recs: 50% positive, median +9.0%</t>
+          <t>Low-risk Metal holding (low vol) • below 200-dma (-8.6%) • outperforming Nifty • sector strength 88/100 • regime cautious (partial deploy) • 3 similar past recs: 67% positive, median +0.8%</t>
         </is>
       </c>
     </row>
@@ -1871,7 +1871,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Risk/Vol +19 · Historical +15 · Sector +9 · Trend/Tech +8 · Regime +4 = 55</t>
+          <t>Risk/Vol +20 · Historical +16 · Trend/Tech +9 · Sector +6 · Regime +4 = 55</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1885,36 +1885,36 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="G5" t="n">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="H5" t="n">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="I5" t="n">
-        <v>88</v>
+        <v>62</v>
       </c>
       <c r="J5" t="n">
         <v>29</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>COALINDIA</t>
+          <t>ONGC</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Metal</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="M5" t="n">
-        <v>395.5</v>
+        <v>224.5</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>385 - 406</t>
+          <t>219 - 230</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -1932,11 +1932,11 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-8.8%)</t>
+          <t>Below 200-DMA (-12.1%)</t>
         </is>
       </c>
       <c r="S5" t="n">
-        <v>37</v>
+        <v>62</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1945,21 +1945,21 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>2026-11-27</t>
+          <t>2026-11-28</t>
         </is>
       </c>
       <c r="V5" t="n">
-        <v>17798</v>
+        <v>17737</v>
       </c>
       <c r="W5" t="n">
-        <v>45</v>
+        <v>79</v>
       </c>
       <c r="X5" t="n">
         <v>12.4</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Metal name under the sector cap</t>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Energy name under the sector cap</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1969,27 +1969,27 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — COALINDIA: 55; TATASTEEL: 51, HINDZINC: 45, SAIL: 39</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ONGC: 55; IOC: 49</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>Low-risk Metal holding (low vol) • below 200-dma (-8.8%) • outperforming Nifty • sector strength 88/100 • regime cautious (partial deploy) • 3 similar past recs: 67% positive, median +0.8%</t>
+          <t>Low-risk Energy holding (low vol) • below 200-dma (-12.1%) • outperforming Nifty • sector strength 62/100 • regime cautious (partial deploy) • 2 similar past recs: 50% positive, median +9.0%</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>ACCUMULATE</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Risk/Vol +16 · Historical +15 · Trend/Tech +10 · Sector +10 · Regime +4 = 55</t>
+          <t>Risk/Vol +16 · Historical +15 · Sector +9 · Trend/Tech +8 · Regime +4 = 52</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -2006,33 +2006,33 @@
         <v>50</v>
       </c>
       <c r="G6" t="n">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="H6" t="n">
         <v>65</v>
       </c>
       <c r="I6" t="n">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="J6" t="n">
         <v>29</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>BEL</t>
+          <t>TATASTEEL</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Metal</t>
         </is>
       </c>
       <c r="M6" t="n">
-        <v>367.6</v>
+        <v>168.3</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>358 - 377</t>
+          <t>164 - 173</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -2046,15 +2046,15 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-11.6%)</t>
+          <t>Below 200-DMA (-13.2%)</t>
         </is>
       </c>
       <c r="S6" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -2063,21 +2063,21 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>2026-11-27</t>
+          <t>2026-11-28</t>
         </is>
       </c>
       <c r="V6" t="n">
-        <v>13234</v>
+        <v>15648</v>
       </c>
       <c r="W6" t="n">
-        <v>36</v>
+        <v>93</v>
       </c>
       <c r="X6" t="n">
-        <v>9.300000000000001</v>
+        <v>10.9</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Industrials name under the sector cap</t>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Metal name under the sector cap</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -2087,12 +2087,12 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>No same-sector peer in the universe.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — TATASTEEL: 52; COALINDIA: 57, HINDZINC: 46, SAIL: 38. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>Low-risk Industrials holding (medium vol) • below 200-dma (-11.6%) • outperforming Nifty • sector strength 100/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
+          <t>Low-risk Metal holding (medium vol) • below 200-dma (-13.2%) • sector strength 88/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
         </is>
       </c>
     </row>
@@ -2103,11 +2103,11 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Risk/Vol +22 · Historical +15 · Trend/Tech +8 · Regime +4 · Sector +4 = 53</t>
+          <t>Risk/Vol +22 · Historical +15 · Trend/Tech +8 · Regime +4 · Sector +2 = 51</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -2124,13 +2124,13 @@
         <v>50</v>
       </c>
       <c r="G7" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="H7" t="n">
         <v>88</v>
       </c>
       <c r="I7" t="n">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="J7" t="n">
         <v>29</v>
@@ -2146,11 +2146,11 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>330 - 346</t>
+          <t>331 - 347</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -2164,15 +2164,15 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-11.8%)</t>
+          <t>Below 200-DMA (-11.5%)</t>
         </is>
       </c>
       <c r="S7" t="n">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -2181,17 +2181,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>2026-11-27</t>
+          <t>2026-11-28</t>
         </is>
       </c>
       <c r="V7" t="n">
-        <v>21294</v>
+        <v>18303</v>
       </c>
       <c r="W7" t="n">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="X7" t="n">
-        <v>14.9</v>
+        <v>12.7</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -2205,12 +2205,12 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — TATAPOWER: 53; NHPC: 44, ADANIPOWER: 34, NLCINDIA: 28</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — TATAPOWER: 51; NHPC: 43, ADANIPOWER: 34, NLCINDIA: 26</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>Low-risk Power holding (low vol) • below 200-dma (-11.8%) • sector strength 38/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
+          <t>Low-risk Power holding (low vol) • below 200-dma (-11.5%) • sector strength 25/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
         </is>
       </c>
     </row>
@@ -2225,7 +2225,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Risk/Vol +17 · Historical +15 · Sector +9 · Trend/Tech +6 · Regime +4 = 51</t>
+          <t>Risk/Vol +21 · Historical +13 · Trend/Tech +9 · Regime +4 · Sector +4 = 51</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -2235,62 +2235,62 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Regime</t>
+          <t>Sector</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="G8" t="n">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="H8" t="n">
-        <v>69</v>
+        <v>85</v>
       </c>
       <c r="I8" t="n">
-        <v>88</v>
+        <v>38</v>
       </c>
       <c r="J8" t="n">
         <v>29</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>TATASTEEL</t>
+          <t>ITC</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Metal</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="M8" t="n">
-        <v>169.3</v>
+        <v>265</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>165 - 174</t>
+          <t>258 - 272</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-4% to +3%</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>56%</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-12.7%)</t>
+          <t>Below 200-DMA (-9.2%)</t>
         </is>
       </c>
       <c r="S8" t="n">
-        <v>38</v>
+        <v>60</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -2299,21 +2299,21 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>2026-11-27</t>
+          <t>2026-11-28</t>
         </is>
       </c>
       <c r="V8" t="n">
-        <v>13376</v>
+        <v>16960</v>
       </c>
       <c r="W8" t="n">
-        <v>79</v>
+        <v>64</v>
       </c>
       <c r="X8" t="n">
-        <v>9.4</v>
+        <v>11.9</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Metal name under the sector cap</t>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility FMCG name under the sector cap</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
@@ -2323,12 +2323,12 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — TATASTEEL: 51; COALINDIA: 55, HINDZINC: 45, SAIL: 39. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ITC: 51; DABUR: 48</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>Low-risk Metal holding (low vol) • below 200-dma (-12.7%) • sector strength 88/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
+          <t>Low-risk FMCG holding (low vol) • below 200-dma (-9.2%) • sector strength 38/100 • regime cautious (partial deploy) • 9 similar past recs: 56% positive, median +0.3%</t>
         </is>
       </c>
     </row>
@@ -2343,7 +2343,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Risk/Vol +23 · Historical +13 · Trend/Tech +6 · Regime +4 · Sector +2 = 48</t>
+          <t>Risk/Vol +18 · Historical +15 · Trend/Tech +7 · Regime +4 · Sector +4 = 48</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2357,23 +2357,23 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="G9" t="n">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="H9" t="n">
-        <v>92</v>
+        <v>73</v>
       </c>
       <c r="I9" t="n">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="J9" t="n">
         <v>29</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>ITC</t>
+          <t>DABUR</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -2382,33 +2382,33 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>254.7</v>
+        <v>369.4</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>249 - 261</t>
+          <t>360 - 379</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>-4% to +3%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>56%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-12.8%)</t>
+          <t>Below 200-DMA (-15.6%)</t>
         </is>
       </c>
       <c r="S9" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -2417,17 +2417,17 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>2026-11-27</t>
+          <t>2026-11-28</t>
         </is>
       </c>
       <c r="V9" t="n">
-        <v>21649</v>
+        <v>15515</v>
       </c>
       <c r="W9" t="n">
-        <v>85</v>
+        <v>42</v>
       </c>
       <c r="X9" t="n">
-        <v>15.1</v>
+        <v>11</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -2441,12 +2441,12 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ITC: 48; DABUR: 41</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — DABUR: 48; ITC: 51. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>Low-risk FMCG holding (low vol) • below 200-dma (-12.8%) • sector strength 25/100 • regime cautious (partial deploy) • 9 similar past recs: 56% positive, median +0.3%</t>
+          <t>Low-risk FMCG holding (low vol) • below 200-dma (-15.6%) • sector strength 38/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
         </is>
       </c>
     </row>
@@ -4297,9 +4297,15 @@
       <c r="L18" t="n">
         <v>0.41</v>
       </c>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
-      <c r="O18" t="inlineStr"/>
+      <c r="M18" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="N18" t="n">
+        <v>-3.2</v>
+      </c>
+      <c r="O18" t="n">
+        <v>61</v>
+      </c>
       <c r="P18" t="n">
         <v>41.1</v>
       </c>
@@ -7845,9 +7851,15 @@
       <c r="L62" t="n">
         <v>0.92</v>
       </c>
-      <c r="M62" t="inlineStr"/>
-      <c r="N62" t="inlineStr"/>
-      <c r="O62" t="inlineStr"/>
+      <c r="M62" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="N62" t="n">
+        <v>0</v>
+      </c>
+      <c r="O62" t="n">
+        <v>93</v>
+      </c>
       <c r="P62" t="n">
         <v>112</v>
       </c>
@@ -9459,9 +9471,15 @@
       <c r="L82" t="n">
         <v>0.4</v>
       </c>
-      <c r="M82" t="inlineStr"/>
-      <c r="N82" t="inlineStr"/>
-      <c r="O82" t="inlineStr"/>
+      <c r="M82" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="N82" t="n">
+        <v>-5.4</v>
+      </c>
+      <c r="O82" t="n">
+        <v>21</v>
+      </c>
       <c r="P82" t="n">
         <v>23.2</v>
       </c>
@@ -26049,16 +26067,16 @@
         <v>56</v>
       </c>
       <c r="D2" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="E2" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F2" t="n">
         <v>-5.6</v>
       </c>
       <c r="G2" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -26439,7 +26457,7 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>-10.4</v>
+        <v>-10.7</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -26565,7 +26583,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>-4.6</v>
+        <v>-4.5</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -26607,7 +26625,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>-8.6</v>
+        <v>-9.300000000000001</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -27205,7 +27223,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27233,7 +27251,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -27248,7 +27266,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>6.3%</t>
+          <t>6.7%</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -27263,11 +27281,11 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>4.4%</t>
+          <t>6.6%</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -27278,7 +27296,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>3.7%</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -27293,7 +27311,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>3.6%</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -27303,47 +27321,32 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>CASH (intentional)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2.7%</t>
+          <t>71.2%</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CASH (intentional)</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>71.2%</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
           <t>100.0%</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>8 stocks / 6 sectors</t>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>8 stocks / 5 sectors</t>
         </is>
       </c>
     </row>

--- a/reports/AEGIS_LATEST.xlsx
+++ b/reports/AEGIS_LATEST.xlsx
@@ -444,7 +444,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -456,7 +456,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Weak  ·  deploy 29%  ·  cash 71%</t>
+          <t>Weak  ·  deploy 48%  ·  cash 52%</t>
         </is>
       </c>
     </row>
@@ -479,7 +479,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6">
@@ -489,7 +489,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7">
@@ -512,7 +512,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-11-28</t>
+          <t>2026-11-29</t>
         </is>
       </c>
     </row>
@@ -524,7 +524,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ICICIBANK (71)</t>
+          <t>ICICIBANK (72)</t>
         </is>
       </c>
     </row>
@@ -536,7 +536,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>DABUR (48)</t>
+          <t>AMBUJACEM (44)</t>
         </is>
       </c>
     </row>
@@ -548,7 +548,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>DABUR</t>
+          <t>AMBUJACEM</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>BEL</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -571,7 +571,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -582,7 +582,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>84%</t>
+          <t>94%</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Hold a 8-stock risk-managed portfolio</t>
+          <t>Hold a 9-stock risk-managed portfolio</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-29  /  2026-10-29</t>
+          <t>2026-10-30  /  2026-10-30</t>
         </is>
       </c>
     </row>
@@ -736,7 +736,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Rs144,000 (29%)</t>
+          <t>Rs240,000 (48%)</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Rs356,000 (71%)</t>
+          <t>Rs260,000 (52%)</t>
         </is>
       </c>
     </row>
@@ -760,7 +760,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-11-28</t>
+          <t>2026-11-29</t>
         </is>
       </c>
     </row>
@@ -920,7 +920,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.86</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>29% (Weak regime)</t>
+          <t>48% (Weak regime)</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>84% (validated process)</t>
+          <t>94% (validated process)</t>
         </is>
       </c>
     </row>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Portfolio grade B (validated) · stock-alpha experimental</t>
+          <t>Portfolio grade A (validated) · stock-alpha experimental</t>
         </is>
       </c>
     </row>
@@ -1361,7 +1361,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB9"/>
+  <dimension ref="A1:AB10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1513,11 +1513,11 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Risk/Vol +24 · Historical +20 · Trend/Tech +18 · Sector +5 · Regime +4 = 71</t>
+          <t>Risk/Vol +24 · Historical +20 · Trend/Tech +18 · Regime +7 · Sector +3 = 72</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -1527,23 +1527,23 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Regime</t>
+          <t>Sector</t>
         </is>
       </c>
       <c r="F2" t="n">
         <v>66</v>
       </c>
       <c r="G2" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H2" t="n">
         <v>96</v>
       </c>
       <c r="I2" t="n">
-        <v>50</v>
+        <v>29</v>
       </c>
       <c r="J2" t="n">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -1556,11 +1556,11 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>1377</v>
+        <v>1399.3</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>1350 - 1404</t>
+          <t>1371 - 1427</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -1578,11 +1578,11 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>Above 200-DMA (+1.7%)</t>
+          <t>Above 200-DMA (+3.3%)</t>
         </is>
       </c>
       <c r="S2" t="n">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -1591,17 +1591,17 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>2026-11-28</t>
+          <t>2026-11-29</t>
         </is>
       </c>
       <c r="V2" t="n">
-        <v>22032</v>
+        <v>29385</v>
       </c>
       <c r="W2" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="X2" t="n">
-        <v>15.5</v>
+        <v>12.4</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
@@ -1615,12 +1615,12 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ICICIBANK: 71; SBIN: 61, PNB: 55, HDFCBANK: 50</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ICICIBANK: 72; SBIN: 62, PNB: 56, HDFCBANK: 51</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>Low-risk Financials holding (low vol) • above 200-dma (+1.7%) • outperforming Nifty • sector strength 50/100 • regime cautious (partial deploy) • 8 similar past recs: 75% positive, median +5.3%</t>
+          <t>Low-risk Financials holding (low vol) • above 200-dma (+3.3%) • outperforming Nifty • sector strength 29/100 • regime cautious (partial deploy) • 8 similar past recs: 75% positive, median +5.3%</t>
         </is>
       </c>
     </row>
@@ -1631,11 +1631,11 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Risk/Vol +23 · Historical +20 · Trend/Tech +9 · Sector +5 · Regime +4 = 61</t>
+          <t>Risk/Vol +23 · Historical +20 · Trend/Tech +9 · Regime +7 · Sector +3 = 62</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -1645,23 +1645,23 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Regime</t>
+          <t>Sector</t>
         </is>
       </c>
       <c r="F3" t="n">
         <v>65</v>
       </c>
       <c r="G3" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H3" t="n">
         <v>92</v>
       </c>
       <c r="I3" t="n">
-        <v>50</v>
+        <v>29</v>
       </c>
       <c r="J3" t="n">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -1674,11 +1674,11 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>960.7</v>
+        <v>963.5</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>939 - 982</t>
+          <t>944 - 984</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -1692,15 +1692,15 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-7.5%)</t>
+          <t>Below 200-DMA (-7.2%)</t>
         </is>
       </c>
       <c r="S3" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -1709,14 +1709,14 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>2026-11-28</t>
+          <t>2026-11-29</t>
         </is>
       </c>
       <c r="V3" t="n">
-        <v>19213</v>
+        <v>31797</v>
       </c>
       <c r="W3" t="n">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="X3" t="n">
         <v>13.5</v>
@@ -1733,12 +1733,12 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — SBIN: 61; ICICIBANK: 71, PNB: 55, HDFCBANK: 50. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — SBIN: 62; ICICIBANK: 72, PNB: 56, HDFCBANK: 51. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>Low-risk Financials holding (low vol) • below 200-dma (-7.5%) • outperforming Nifty • sector strength 50/100 • regime cautious (partial deploy) • 2 similar past recs: 100% positive, median +8.9%</t>
+          <t>Low-risk Financials holding (low vol) • below 200-dma (-7.2%) • outperforming Nifty • sector strength 29/100 • regime cautious (partial deploy) • 2 similar past recs: 100% positive, median +8.9%</t>
         </is>
       </c>
     </row>
@@ -1749,11 +1749,11 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Risk/Vol +19 · Historical +15 · Trend/Tech +10 · Sector +9 · Regime +4 = 57</t>
+          <t>Risk/Vol +20 · Historical +16 · Trend/Tech +9 · Regime +7 · Sector +7 = 59</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1763,40 +1763,40 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Regime</t>
+          <t>Sector</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="G4" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="H4" t="n">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="I4" t="n">
-        <v>88</v>
+        <v>71</v>
       </c>
       <c r="J4" t="n">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>COALINDIA</t>
+          <t>ONGC</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Metal</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>396.2</v>
+        <v>225.2</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>386 - 406</t>
+          <t>220 - 231</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -1810,15 +1810,15 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-8.6%)</t>
+          <t>Below 200-DMA (-11.8%)</t>
         </is>
       </c>
       <c r="S4" t="n">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1827,21 +1827,21 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>2026-11-28</t>
+          <t>2026-11-29</t>
         </is>
       </c>
       <c r="V4" t="n">
-        <v>17433</v>
+        <v>33780</v>
       </c>
       <c r="W4" t="n">
-        <v>44</v>
+        <v>150</v>
       </c>
       <c r="X4" t="n">
-        <v>12.2</v>
+        <v>14.1</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Metal name under the sector cap</t>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Energy name under the sector cap</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1851,12 +1851,12 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — COALINDIA: 57; TATASTEEL: 52, HINDZINC: 46, SAIL: 38</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ONGC: 59; IOC: 53</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>Low-risk Metal holding (low vol) • below 200-dma (-8.6%) • outperforming Nifty • sector strength 88/100 • regime cautious (partial deploy) • 3 similar past recs: 67% positive, median +0.8%</t>
+          <t>Low-risk Energy holding (low vol) • below 200-dma (-11.8%) • outperforming Nifty • sector strength 71/100 • regime cautious (partial deploy) • 2 similar past recs: 50% positive, median +9.0%</t>
         </is>
       </c>
     </row>
@@ -1867,11 +1867,11 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Risk/Vol +20 · Historical +16 · Trend/Tech +9 · Sector +6 · Regime +4 = 55</t>
+          <t>Risk/Vol +19 · Historical +15 · Sector +9 · Trend/Tech +7 · Regime +7 = 57</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1885,36 +1885,36 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="G5" t="n">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="H5" t="n">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="I5" t="n">
-        <v>62</v>
+        <v>86</v>
       </c>
       <c r="J5" t="n">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>ONGC</t>
+          <t>COALINDIA</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Metal</t>
         </is>
       </c>
       <c r="M5" t="n">
-        <v>224.5</v>
+        <v>387.8</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>219 - 230</t>
+          <t>378 - 398</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -1928,15 +1928,15 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-12.1%)</t>
+          <t>Below 200-DMA (-10.5%)</t>
         </is>
       </c>
       <c r="S5" t="n">
-        <v>62</v>
+        <v>33</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1945,21 +1945,21 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>2026-11-28</t>
+          <t>2026-11-29</t>
         </is>
       </c>
       <c r="V5" t="n">
-        <v>17737</v>
+        <v>28309</v>
       </c>
       <c r="W5" t="n">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="X5" t="n">
-        <v>12.4</v>
+        <v>11.9</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Energy name under the sector cap</t>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Metal name under the sector cap</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1969,93 +1969,93 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ONGC: 55; IOC: 49</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — COALINDIA: 57; TATASTEEL: 55, HINDZINC: 48, SAIL: 40</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>Low-risk Energy holding (low vol) • below 200-dma (-12.1%) • outperforming Nifty • sector strength 62/100 • regime cautious (partial deploy) • 2 similar past recs: 50% positive, median +9.0%</t>
+          <t>Low-risk Metal holding (low vol) • below 200-dma (-10.5%) • outperforming Nifty • sector strength 86/100 • regime cautious (partial deploy) • 3 similar past recs: 67% positive, median +0.8%</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ACCUMULATE</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="B6" t="n">
+        <v>56</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Risk/Vol +21 · Historical +13 · Trend/Tech +9 · Regime +7 · Sector +6 = 56</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Risk/Vol</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Sector</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>44</v>
+      </c>
+      <c r="G6" t="n">
+        <v>45</v>
+      </c>
+      <c r="H6" t="n">
+        <v>84</v>
+      </c>
+      <c r="I6" t="n">
+        <v>57</v>
+      </c>
+      <c r="J6" t="n">
+        <v>48</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>ITC</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>FMCG</t>
+        </is>
+      </c>
+      <c r="M6" t="n">
+        <v>263.7</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>257 - 270</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>-4% to +3%</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>56%</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>73</v>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>Below 200-DMA (-9.5%)</t>
+        </is>
+      </c>
+      <c r="S6" t="n">
         <v>52</v>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Risk/Vol +16 · Historical +15 · Sector +9 · Trend/Tech +8 · Regime +4 = 52</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Risk/Vol</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Regime</t>
-        </is>
-      </c>
-      <c r="F6" t="n">
-        <v>50</v>
-      </c>
-      <c r="G6" t="n">
-        <v>39</v>
-      </c>
-      <c r="H6" t="n">
-        <v>65</v>
-      </c>
-      <c r="I6" t="n">
-        <v>88</v>
-      </c>
-      <c r="J6" t="n">
-        <v>29</v>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>TATASTEEL</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>Metal</t>
-        </is>
-      </c>
-      <c r="M6" t="n">
-        <v>168.3</v>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>164 - 173</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Q6" t="n">
-        <v>63</v>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>Below 200-DMA (-13.2%)</t>
-        </is>
-      </c>
-      <c r="S6" t="n">
-        <v>42</v>
-      </c>
       <c r="T6" t="inlineStr">
         <is>
           <t>2 months (2M)</t>
@@ -2063,21 +2063,21 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>2026-11-28</t>
+          <t>2026-11-29</t>
         </is>
       </c>
       <c r="V6" t="n">
-        <v>15648</v>
+        <v>30062</v>
       </c>
       <c r="W6" t="n">
-        <v>93</v>
+        <v>114</v>
       </c>
       <c r="X6" t="n">
-        <v>10.9</v>
+        <v>12.6</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Metal name under the sector cap</t>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility FMCG name under the sector cap</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -2087,27 +2087,27 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — TATASTEEL: 52; COALINDIA: 57, HINDZINC: 46, SAIL: 38. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ITC: 56; DABUR: 51</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>Low-risk Metal holding (medium vol) • below 200-dma (-13.2%) • sector strength 88/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
+          <t>Low-risk FMCG holding (low vol) • below 200-dma (-9.5%) • outperforming Nifty • sector strength 57/100 • regime cautious (partial deploy) • 9 similar past recs: 56% positive, median +0.3%</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ACCUMULATE</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Risk/Vol +22 · Historical +15 · Trend/Tech +8 · Regime +4 · Sector +2 = 51</t>
+          <t>Risk/Vol +22 · Historical +15 · Trend/Tech +8 · Regime +7 · Sector +4 = 56</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -2124,16 +2124,16 @@
         <v>50</v>
       </c>
       <c r="G7" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="H7" t="n">
         <v>88</v>
       </c>
       <c r="I7" t="n">
-        <v>25</v>
+        <v>43</v>
       </c>
       <c r="J7" t="n">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -2146,11 +2146,11 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>339</v>
+        <v>344.5</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>331 - 347</t>
+          <t>336 - 353</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -2164,15 +2164,15 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-11.5%)</t>
+          <t>Below 200-DMA (-10.0%)</t>
         </is>
       </c>
       <c r="S7" t="n">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -2181,17 +2181,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>2026-11-28</t>
+          <t>2026-11-29</t>
         </is>
       </c>
       <c r="V7" t="n">
-        <v>18303</v>
+        <v>26182</v>
       </c>
       <c r="W7" t="n">
-        <v>54</v>
+        <v>76</v>
       </c>
       <c r="X7" t="n">
-        <v>12.7</v>
+        <v>10.9</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -2205,27 +2205,27 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — TATAPOWER: 51; NHPC: 43, ADANIPOWER: 34, NLCINDIA: 26</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — TATAPOWER: 56; NHPC: 56, ADANIPOWER: 39, NLCINDIA: 33</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>Low-risk Power holding (low vol) • below 200-dma (-11.5%) • sector strength 25/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
+          <t>Low-risk Power holding (low vol) • below 200-dma (-10.0%) • sector strength 43/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ACCUMULATE</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Risk/Vol +21 · Historical +13 · Trend/Tech +9 · Regime +4 · Sector +4 = 51</t>
+          <t>Risk/Vol +16 · Historical +15 · Sector +9 · Trend/Tech +8 · Regime +7 = 55</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -2235,62 +2235,62 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Sector</t>
+          <t>Regime</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="G8" t="n">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="H8" t="n">
-        <v>85</v>
+        <v>64</v>
       </c>
       <c r="I8" t="n">
-        <v>38</v>
+        <v>86</v>
       </c>
       <c r="J8" t="n">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>ITC</t>
+          <t>TATASTEEL</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>Metal</t>
         </is>
       </c>
       <c r="M8" t="n">
-        <v>265</v>
+        <v>167.9</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>258 - 272</t>
+          <t>163 - 172</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>-4% to +3%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>56%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-9.2%)</t>
+          <t>Below 200-DMA (-13.4%)</t>
         </is>
       </c>
       <c r="S8" t="n">
-        <v>60</v>
+        <v>41</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -2299,21 +2299,21 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>2026-11-28</t>
+          <t>2026-11-29</t>
         </is>
       </c>
       <c r="V8" t="n">
-        <v>16960</v>
+        <v>13766</v>
       </c>
       <c r="W8" t="n">
-        <v>64</v>
+        <v>82</v>
       </c>
       <c r="X8" t="n">
-        <v>11.9</v>
+        <v>5.8</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility FMCG name under the sector cap</t>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Metal name under the sector cap</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
@@ -2323,12 +2323,12 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ITC: 51; DABUR: 48</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — TATASTEEL: 55; COALINDIA: 57, HINDZINC: 48, SAIL: 40. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>Low-risk FMCG holding (low vol) • below 200-dma (-9.2%) • sector strength 38/100 • regime cautious (partial deploy) • 9 similar past recs: 56% positive, median +0.3%</t>
+          <t>Low-risk Metal holding (medium vol) • below 200-dma (-13.4%) • sector strength 86/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
         </is>
       </c>
     </row>
@@ -2339,11 +2339,11 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Risk/Vol +18 · Historical +15 · Trend/Tech +7 · Regime +4 · Sector +4 = 48</t>
+          <t>Risk/Vol +18 · Historical +15 · Regime +7 · Sector +6 · Trend/Tech +5 = 51</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2353,23 +2353,23 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Sector</t>
+          <t>Trend/Tech</t>
         </is>
       </c>
       <c r="F9" t="n">
         <v>50</v>
       </c>
       <c r="G9" t="n">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="H9" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="I9" t="n">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="J9" t="n">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -2382,11 +2382,11 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>369.4</v>
+        <v>368</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>360 - 379</t>
+          <t>358 - 377</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -2400,15 +2400,15 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-15.6%)</t>
+          <t>Below 200-DMA (-15.8%)</t>
         </is>
       </c>
       <c r="S9" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -2417,17 +2417,17 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>2026-11-28</t>
+          <t>2026-11-29</t>
         </is>
       </c>
       <c r="V9" t="n">
-        <v>15515</v>
+        <v>32380</v>
       </c>
       <c r="W9" t="n">
-        <v>42</v>
+        <v>88</v>
       </c>
       <c r="X9" t="n">
-        <v>11</v>
+        <v>13.6</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -2441,12 +2441,130 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — DABUR: 48; ITC: 51. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — DABUR: 51; ITC: 56. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>Low-risk FMCG holding (low vol) • below 200-dma (-15.6%) • sector strength 38/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
+          <t>Low-risk FMCG holding (low vol) • below 200-dma (-15.8%) • sector strength 57/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>44</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Historical +15 · Risk/Vol +15 · Regime +7 · Trend/Tech +6 · Sector +1 = 44</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Historical</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Sector</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>50</v>
+      </c>
+      <c r="G10" t="n">
+        <v>28</v>
+      </c>
+      <c r="H10" t="n">
+        <v>60</v>
+      </c>
+      <c r="I10" t="n">
+        <v>14</v>
+      </c>
+      <c r="J10" t="n">
+        <v>48</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>AMBUJACEM</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>Cement</t>
+        </is>
+      </c>
+      <c r="M10" t="n">
+        <v>353.1</v>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>343 - 363</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>60</v>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>Below 200-DMA (-19.2%)</t>
+        </is>
+      </c>
+      <c r="S10" t="n">
+        <v>58</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>2 months (2M)</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>2026-11-29</t>
+        </is>
+      </c>
+      <c r="V10" t="n">
+        <v>12360</v>
+      </c>
+      <c r="W10" t="n">
+        <v>35</v>
+      </c>
+      <c r="X10" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>Historical + Risk/Vol strongest; chosen as a lowest-volatility Cement name under the sector cap</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>Fundamentals · Earnings · News · Flows</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>No same-sector peer in the universe.</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>Low-risk Cement holding (medium vol) • below 200-dma (-19.2%) • sector strength 14/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
         </is>
       </c>
     </row>
@@ -27223,7 +27341,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27246,12 +27364,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>12.6%</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -27261,12 +27379,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Metal</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>6.7%</t>
+          <t>12.4%</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -27276,12 +27394,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>Metal</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>6.6%</t>
+          <t>8.5%</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -27291,12 +27409,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Power</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>6.8%</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -27306,12 +27424,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Power</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>3.6%</t>
+          <t>5.3%</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -27321,32 +27439,47 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CASH (intentional)</t>
+          <t>Cement</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>71.2%</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>CASH (intentional)</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>52.0%</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>8 stocks / 5 sectors</t>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>9 stocks / 6 sectors</t>
         </is>
       </c>
     </row>
@@ -27592,7 +27725,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>The PORTFOLIO process (grade B): beat Nifty 68% of cycles, ~half the drawdown, higher risk-adjusted return. Out-of-sample tested.</t>
+          <t>The PORTFOLIO process (grade A): beat Nifty 68% of cycles, ~half the drawdown, higher risk-adjusted return. Out-of-sample tested.</t>
         </is>
       </c>
     </row>
@@ -27688,7 +27821,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>VALIDATED — grade B · beat Nifty 68% of cycles</t>
+          <t>VALIDATED — grade A · beat Nifty 68% of cycles</t>
         </is>
       </c>
     </row>
